--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -15094,10 +15094,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128399856</v>
+        <v>128398760</v>
       </c>
       <c r="B139" t="n">
-        <v>57673</v>
+        <v>82873</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15105,34 +15105,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>426646</v>
+        <v>426232</v>
       </c>
       <c r="R139" t="n">
-        <v>7051365</v>
+        <v>7051062</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15162,14 +15162,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15184,57 +15189,57 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128399827</v>
+        <v>128398733</v>
       </c>
       <c r="B140" t="n">
-        <v>91358</v>
+        <v>92055</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>426813</v>
+        <v>426361</v>
       </c>
       <c r="R140" t="n">
-        <v>7051371</v>
+        <v>7051151</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15264,9 +15269,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15281,22 +15296,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128399909</v>
+        <v>128398820</v>
       </c>
       <c r="B141" t="n">
-        <v>57673</v>
+        <v>91376</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15304,34 +15319,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>426175</v>
+        <v>426196</v>
       </c>
       <c r="R141" t="n">
-        <v>7051323</v>
+        <v>7051340</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15361,14 +15376,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15383,44 +15403,44 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128399839</v>
+        <v>128399856</v>
       </c>
       <c r="B142" t="n">
-        <v>92055</v>
+        <v>57673</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15430,10 +15450,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>425971</v>
+        <v>426646</v>
       </c>
       <c r="R142" t="n">
-        <v>7051280</v>
+        <v>7051365</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15466,6 +15486,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15492,10 +15517,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128398760</v>
+        <v>128399827</v>
       </c>
       <c r="B143" t="n">
-        <v>82873</v>
+        <v>91358</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15503,34 +15528,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>426232</v>
+        <v>426813</v>
       </c>
       <c r="R143" t="n">
-        <v>7051062</v>
+        <v>7051371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15560,19 +15585,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15587,57 +15602,57 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128398733</v>
+        <v>128399909</v>
       </c>
       <c r="B144" t="n">
-        <v>92055</v>
+        <v>57673</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>426361</v>
+        <v>426175</v>
       </c>
       <c r="R144" t="n">
-        <v>7051151</v>
+        <v>7051323</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15667,19 +15682,14 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>16:02</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>16:02</t>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15694,57 +15704,57 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128398820</v>
+        <v>128399839</v>
       </c>
       <c r="B145" t="n">
-        <v>91376</v>
+        <v>92055</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>426196</v>
+        <v>425971</v>
       </c>
       <c r="R145" t="n">
-        <v>7051340</v>
+        <v>7051280</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15774,19 +15784,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>10:04</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15801,12 +15801,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -2412,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128399849</v>
+        <v>128398762</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>91376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,34 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>426803</v>
+        <v>426225</v>
       </c>
       <c r="R18" t="n">
-        <v>7051353</v>
+        <v>7051098</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,14 +2480,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,22 +2507,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128399949</v>
+        <v>128398790</v>
       </c>
       <c r="B19" t="n">
-        <v>88761</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,34 +2530,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426768</v>
+        <v>425825</v>
       </c>
       <c r="R19" t="n">
-        <v>7051367</v>
+        <v>7051257</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,9 +2592,24 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,22 +2624,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128399940</v>
+        <v>128399849</v>
       </c>
       <c r="B20" t="n">
-        <v>91376</v>
+        <v>57673</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2646,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426338</v>
+        <v>426803</v>
       </c>
       <c r="R20" t="n">
-        <v>7050977</v>
+        <v>7051353</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,6 +2707,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398762</v>
+        <v>128399949</v>
       </c>
       <c r="B21" t="n">
-        <v>91376</v>
+        <v>88761</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,34 +2749,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426225</v>
+        <v>426768</v>
       </c>
       <c r="R21" t="n">
-        <v>7051098</v>
+        <v>7051367</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,19 +2806,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,22 +2823,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398790</v>
+        <v>128399940</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>91376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,39 +2846,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425825</v>
+        <v>426338</v>
       </c>
       <c r="R22" t="n">
-        <v>7051257</v>
+        <v>7050977</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2888,24 +2903,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2920,12 +2920,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -12192,7 +12192,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128398793</v>
+        <v>128399865</v>
       </c>
       <c r="B112" t="n">
         <v>57673</v>
@@ -12221,21 +12221,16 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>425908</v>
+        <v>426360</v>
       </c>
       <c r="R112" t="n">
-        <v>7051281</v>
+        <v>7050960</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12265,24 +12260,14 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:57</t>
-        </is>
-      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12297,19 +12282,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128398719</v>
+        <v>128398793</v>
       </c>
       <c r="B113" t="n">
         <v>57673</v>
@@ -12349,10 +12334,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>426799</v>
+        <v>425908</v>
       </c>
       <c r="R113" t="n">
-        <v>7051328</v>
+        <v>7051281</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12384,7 +12369,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12394,7 +12379,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -12426,48 +12411,50 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128398804</v>
+        <v>128398719</v>
       </c>
       <c r="B114" t="n">
-        <v>75154</v>
+        <v>57673</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426000</v>
+        <v>426799</v>
       </c>
       <c r="R114" t="n">
-        <v>7051290</v>
+        <v>7051328</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12499,7 +12486,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12509,7 +12496,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12517,11 +12509,6 @@
       </c>
       <c r="AE114" t="b">
         <v>0</v>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG114" t="b">
         <v>0</v>
@@ -12541,50 +12528,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128398822</v>
+        <v>128398804</v>
       </c>
       <c r="B115" t="n">
-        <v>57673</v>
+        <v>75154</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426200</v>
+        <v>426000</v>
       </c>
       <c r="R115" t="n">
-        <v>7051338</v>
+        <v>7051290</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12616,7 +12601,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12626,12 +12611,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12639,6 +12619,11 @@
       </c>
       <c r="AE115" t="b">
         <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG115" t="b">
         <v>0</v>
@@ -12658,10 +12643,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128398802</v>
+        <v>128398822</v>
       </c>
       <c r="B116" t="n">
-        <v>91654</v>
+        <v>57673</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12669,34 +12654,39 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>425985</v>
+        <v>426200</v>
       </c>
       <c r="R116" t="n">
-        <v>7051282</v>
+        <v>7051338</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12728,7 +12718,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12738,7 +12728,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12765,10 +12760,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128398743</v>
+        <v>128398802</v>
       </c>
       <c r="B117" t="n">
-        <v>91354</v>
+        <v>91654</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12776,21 +12771,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12800,10 +12795,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426371</v>
+        <v>425985</v>
       </c>
       <c r="R117" t="n">
-        <v>7050917</v>
+        <v>7051282</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12835,7 +12830,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12845,7 +12840,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12872,32 +12867,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128398734</v>
+        <v>128398743</v>
       </c>
       <c r="B118" t="n">
-        <v>92055</v>
+        <v>91354</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12907,10 +12902,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426329</v>
+        <v>426371</v>
       </c>
       <c r="R118" t="n">
-        <v>7051146</v>
+        <v>7050917</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12942,7 +12937,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12952,7 +12947,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12979,50 +12974,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128398814</v>
+        <v>128398734</v>
       </c>
       <c r="B119" t="n">
-        <v>57673</v>
+        <v>92055</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426097</v>
+        <v>426329</v>
       </c>
       <c r="R119" t="n">
-        <v>7051199</v>
+        <v>7051146</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13054,7 +13044,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13064,12 +13054,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13096,10 +13081,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128398727</v>
+        <v>128398814</v>
       </c>
       <c r="B120" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13107,34 +13092,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426516</v>
+        <v>426097</v>
       </c>
       <c r="R120" t="n">
-        <v>7051239</v>
+        <v>7051199</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13166,7 +13156,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13176,7 +13166,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13203,10 +13198,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399865</v>
+        <v>128398727</v>
       </c>
       <c r="B121" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13214,34 +13209,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426360</v>
+        <v>426516</v>
       </c>
       <c r="R121" t="n">
-        <v>7050960</v>
+        <v>7051239</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13271,14 +13266,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13293,12 +13293,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -16522,50 +16522,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128398779</v>
+        <v>128399843</v>
       </c>
       <c r="B153" t="n">
-        <v>57673</v>
+        <v>92055</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>425818</v>
+        <v>426425</v>
       </c>
       <c r="R153" t="n">
-        <v>7051169</v>
+        <v>7051273</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16595,24 +16590,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16627,22 +16607,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128398720</v>
+        <v>128399899</v>
       </c>
       <c r="B154" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16650,34 +16630,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>426773</v>
+        <v>425928</v>
       </c>
       <c r="R154" t="n">
-        <v>7051341</v>
+        <v>7051283</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16707,19 +16687,14 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>16:57</t>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16734,44 +16709,44 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128399843</v>
+        <v>128399934</v>
       </c>
       <c r="B155" t="n">
-        <v>92055</v>
+        <v>91372</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16781,10 +16756,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>426425</v>
+        <v>426135</v>
       </c>
       <c r="R155" t="n">
-        <v>7051273</v>
+        <v>7051163</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16843,7 +16818,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128399899</v>
+        <v>128399869</v>
       </c>
       <c r="B156" t="n">
         <v>57673</v>
@@ -16878,10 +16853,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>425928</v>
+        <v>426163</v>
       </c>
       <c r="R156" t="n">
-        <v>7051283</v>
+        <v>7050993</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16918,7 +16893,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16945,10 +16920,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128399934</v>
+        <v>128398779</v>
       </c>
       <c r="B157" t="n">
-        <v>91372</v>
+        <v>57673</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16956,34 +16931,39 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>426135</v>
+        <v>425818</v>
       </c>
       <c r="R157" t="n">
-        <v>7051163</v>
+        <v>7051169</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17013,9 +16993,24 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17030,22 +17025,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128399869</v>
+        <v>128398720</v>
       </c>
       <c r="B158" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17053,34 +17048,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>426163</v>
+        <v>426773</v>
       </c>
       <c r="R158" t="n">
-        <v>7050993</v>
+        <v>7051341</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17110,14 +17105,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17132,12 +17132,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -9796,10 +9796,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128398787</v>
+        <v>128399890</v>
       </c>
       <c r="B89" t="n">
-        <v>75148</v>
+        <v>57673</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9807,34 +9807,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>425795</v>
+        <v>425829</v>
       </c>
       <c r="R89" t="n">
-        <v>7051251</v>
+        <v>7051228</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9864,19 +9864,14 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:16</t>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9891,22 +9886,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128398800</v>
+        <v>128399877</v>
       </c>
       <c r="B90" t="n">
-        <v>91372</v>
+        <v>57673</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9914,34 +9909,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>425985</v>
+        <v>426231</v>
       </c>
       <c r="R90" t="n">
-        <v>7051282</v>
+        <v>7051067</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9971,19 +9966,14 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:20</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9998,57 +9988,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128398736</v>
+        <v>128399910</v>
       </c>
       <c r="B91" t="n">
-        <v>92055</v>
+        <v>57673</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>426352</v>
+        <v>426170</v>
       </c>
       <c r="R91" t="n">
-        <v>7051151</v>
+        <v>7051345</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10078,19 +10068,14 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:56</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:56</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10105,22 +10090,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128398749</v>
+        <v>128399918</v>
       </c>
       <c r="B92" t="n">
-        <v>86674</v>
+        <v>91308</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10128,34 +10113,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>427</v>
+        <v>112</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>426252</v>
+        <v>426224</v>
       </c>
       <c r="R92" t="n">
-        <v>7050919</v>
+        <v>7050981</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10185,24 +10170,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10217,19 +10187,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399890</v>
+        <v>128399896</v>
       </c>
       <c r="B93" t="n">
         <v>57673</v>
@@ -10264,10 +10234,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>425829</v>
+        <v>425889</v>
       </c>
       <c r="R93" t="n">
-        <v>7051228</v>
+        <v>7051248</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10304,7 +10274,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10331,10 +10301,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399877</v>
+        <v>128399930</v>
       </c>
       <c r="B94" t="n">
-        <v>57673</v>
+        <v>91372</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10342,21 +10312,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10366,10 +10336,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426231</v>
+        <v>426267</v>
       </c>
       <c r="R94" t="n">
-        <v>7051067</v>
+        <v>7050942</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10402,11 +10372,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10433,10 +10398,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399910</v>
+        <v>128399931</v>
       </c>
       <c r="B95" t="n">
-        <v>57673</v>
+        <v>91372</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10444,21 +10409,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10468,10 +10433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426170</v>
+        <v>426252</v>
       </c>
       <c r="R95" t="n">
-        <v>7051345</v>
+        <v>7050958</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10504,11 +10469,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10535,10 +10495,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399918</v>
+        <v>128399929</v>
       </c>
       <c r="B96" t="n">
-        <v>91308</v>
+        <v>91372</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10546,21 +10506,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10570,10 +10530,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426224</v>
+        <v>426276</v>
       </c>
       <c r="R96" t="n">
-        <v>7050981</v>
+        <v>7050944</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10632,7 +10592,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399896</v>
+        <v>128399906</v>
       </c>
       <c r="B97" t="n">
         <v>57673</v>
@@ -10667,10 +10627,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425889</v>
+        <v>426053</v>
       </c>
       <c r="R97" t="n">
-        <v>7051248</v>
+        <v>7051256</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10734,10 +10694,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399930</v>
+        <v>128399867</v>
       </c>
       <c r="B98" t="n">
-        <v>91372</v>
+        <v>57673</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10745,21 +10705,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10769,10 +10729,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426267</v>
+        <v>426331</v>
       </c>
       <c r="R98" t="n">
-        <v>7050942</v>
+        <v>7050912</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10805,6 +10765,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10831,10 +10796,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399931</v>
+        <v>128399879</v>
       </c>
       <c r="B99" t="n">
-        <v>91372</v>
+        <v>57673</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10842,21 +10807,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10866,10 +10831,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>426252</v>
+        <v>426055</v>
       </c>
       <c r="R99" t="n">
-        <v>7050958</v>
+        <v>7051223</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10902,6 +10867,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10928,10 +10898,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399929</v>
+        <v>128398787</v>
       </c>
       <c r="B100" t="n">
-        <v>91372</v>
+        <v>75148</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10939,34 +10909,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426276</v>
+        <v>425795</v>
       </c>
       <c r="R100" t="n">
-        <v>7050944</v>
+        <v>7051251</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10996,9 +10966,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11013,22 +10993,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399906</v>
+        <v>128398800</v>
       </c>
       <c r="B101" t="n">
-        <v>57673</v>
+        <v>91372</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11036,34 +11016,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426053</v>
+        <v>425985</v>
       </c>
       <c r="R101" t="n">
-        <v>7051256</v>
+        <v>7051282</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11093,14 +11073,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11115,57 +11100,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399867</v>
+        <v>128398736</v>
       </c>
       <c r="B102" t="n">
-        <v>57673</v>
+        <v>92055</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426331</v>
+        <v>426352</v>
       </c>
       <c r="R102" t="n">
-        <v>7050912</v>
+        <v>7051151</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11195,14 +11180,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11217,22 +11207,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399879</v>
+        <v>128398749</v>
       </c>
       <c r="B103" t="n">
-        <v>57673</v>
+        <v>86674</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11240,34 +11230,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>427</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426055</v>
+        <v>426252</v>
       </c>
       <c r="R103" t="n">
-        <v>7051223</v>
+        <v>7050919</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11297,14 +11287,24 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11319,12 +11319,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12192,7 +12192,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128399865</v>
+        <v>128398793</v>
       </c>
       <c r="B112" t="n">
         <v>57673</v>
@@ -12221,16 +12221,21 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>426360</v>
+        <v>425908</v>
       </c>
       <c r="R112" t="n">
-        <v>7050960</v>
+        <v>7051281</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12260,14 +12265,24 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12282,19 +12297,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128398793</v>
+        <v>128398719</v>
       </c>
       <c r="B113" t="n">
         <v>57673</v>
@@ -12334,10 +12349,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>425908</v>
+        <v>426799</v>
       </c>
       <c r="R113" t="n">
-        <v>7051281</v>
+        <v>7051328</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12369,7 +12384,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12379,7 +12394,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -12411,50 +12426,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128398719</v>
+        <v>128398804</v>
       </c>
       <c r="B114" t="n">
-        <v>57673</v>
+        <v>75154</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426799</v>
+        <v>426000</v>
       </c>
       <c r="R114" t="n">
-        <v>7051328</v>
+        <v>7051290</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12486,7 +12499,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12496,12 +12509,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12509,6 +12517,11 @@
       </c>
       <c r="AE114" t="b">
         <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG114" t="b">
         <v>0</v>
@@ -12528,48 +12541,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128398804</v>
+        <v>128398822</v>
       </c>
       <c r="B115" t="n">
-        <v>75154</v>
+        <v>57673</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426000</v>
+        <v>426200</v>
       </c>
       <c r="R115" t="n">
-        <v>7051290</v>
+        <v>7051338</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12601,7 +12616,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12611,7 +12626,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12619,11 +12639,6 @@
       </c>
       <c r="AE115" t="b">
         <v>0</v>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG115" t="b">
         <v>0</v>
@@ -12643,10 +12658,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128398822</v>
+        <v>128398802</v>
       </c>
       <c r="B116" t="n">
-        <v>57673</v>
+        <v>91654</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12654,39 +12669,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426200</v>
+        <v>425985</v>
       </c>
       <c r="R116" t="n">
-        <v>7051338</v>
+        <v>7051282</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12718,7 +12728,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12728,12 +12738,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12760,10 +12765,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128398802</v>
+        <v>128398743</v>
       </c>
       <c r="B117" t="n">
-        <v>91654</v>
+        <v>91354</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12771,21 +12776,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12795,10 +12800,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>425985</v>
+        <v>426371</v>
       </c>
       <c r="R117" t="n">
-        <v>7051282</v>
+        <v>7050917</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12830,7 +12835,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12840,7 +12845,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12867,32 +12872,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128398743</v>
+        <v>128398734</v>
       </c>
       <c r="B118" t="n">
-        <v>91354</v>
+        <v>92055</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12902,10 +12907,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426371</v>
+        <v>426329</v>
       </c>
       <c r="R118" t="n">
-        <v>7050917</v>
+        <v>7051146</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12937,7 +12942,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12947,7 +12952,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12974,45 +12979,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128398734</v>
+        <v>128398814</v>
       </c>
       <c r="B119" t="n">
-        <v>92055</v>
+        <v>57673</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426329</v>
+        <v>426097</v>
       </c>
       <c r="R119" t="n">
-        <v>7051146</v>
+        <v>7051199</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13044,7 +13054,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13054,7 +13064,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13081,10 +13096,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128398814</v>
+        <v>128398727</v>
       </c>
       <c r="B120" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13092,39 +13107,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426097</v>
+        <v>426516</v>
       </c>
       <c r="R120" t="n">
-        <v>7051199</v>
+        <v>7051239</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13156,7 +13166,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13166,12 +13176,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13198,10 +13203,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128398727</v>
+        <v>128399865</v>
       </c>
       <c r="B121" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13209,34 +13214,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426516</v>
+        <v>426360</v>
       </c>
       <c r="R121" t="n">
-        <v>7051239</v>
+        <v>7050960</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13266,19 +13271,14 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>16:22</t>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13293,12 +13293,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -16522,45 +16522,50 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128399843</v>
+        <v>128398779</v>
       </c>
       <c r="B153" t="n">
-        <v>92055</v>
+        <v>57673</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>426425</v>
+        <v>425818</v>
       </c>
       <c r="R153" t="n">
-        <v>7051273</v>
+        <v>7051169</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16590,9 +16595,24 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16607,22 +16627,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128399899</v>
+        <v>128398720</v>
       </c>
       <c r="B154" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16630,34 +16650,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>425928</v>
+        <v>426773</v>
       </c>
       <c r="R154" t="n">
-        <v>7051283</v>
+        <v>7051341</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16687,14 +16707,19 @@
           <t>2025-09-12</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16709,44 +16734,44 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128399934</v>
+        <v>128399843</v>
       </c>
       <c r="B155" t="n">
-        <v>91372</v>
+        <v>92055</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16756,10 +16781,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>426135</v>
+        <v>426425</v>
       </c>
       <c r="R155" t="n">
-        <v>7051163</v>
+        <v>7051273</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16818,7 +16843,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128399869</v>
+        <v>128399899</v>
       </c>
       <c r="B156" t="n">
         <v>57673</v>
@@ -16853,10 +16878,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>426163</v>
+        <v>425928</v>
       </c>
       <c r="R156" t="n">
-        <v>7050993</v>
+        <v>7051283</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16893,7 +16918,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16920,10 +16945,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128398779</v>
+        <v>128399934</v>
       </c>
       <c r="B157" t="n">
-        <v>57673</v>
+        <v>91372</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16931,39 +16956,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>425818</v>
+        <v>426135</v>
       </c>
       <c r="R157" t="n">
-        <v>7051169</v>
+        <v>7051163</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16993,24 +17013,9 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17025,22 +17030,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128398720</v>
+        <v>128399869</v>
       </c>
       <c r="B158" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17048,34 +17053,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Stor-Grässjön N, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>426773</v>
+        <v>426163</v>
       </c>
       <c r="R158" t="n">
-        <v>7051341</v>
+        <v>7050993</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17105,19 +17110,14 @@
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-12</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>16:57</t>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17132,12 +17132,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -4218,32 +4218,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398801</v>
+        <v>128398755</v>
       </c>
       <c r="B34" t="n">
-        <v>91814</v>
+        <v>79032</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425985</v>
+        <v>426166</v>
       </c>
       <c r="R34" t="n">
-        <v>7051282</v>
+        <v>7050989</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,50 +4325,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128398741</v>
+        <v>128398801</v>
       </c>
       <c r="B35" t="n">
-        <v>57673</v>
+        <v>91814</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426298</v>
+        <v>425985</v>
       </c>
       <c r="R35" t="n">
-        <v>7051029</v>
+        <v>7051282</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4400,7 +4395,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4410,12 +4405,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,10 +4432,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128398755</v>
+        <v>128398741</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4453,34 +4443,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426166</v>
+        <v>426298</v>
       </c>
       <c r="R36" t="n">
-        <v>7050989</v>
+        <v>7051029</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4512,7 +4507,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4522,7 +4517,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -6286,10 +6286,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128398743</v>
+        <v>128398727</v>
       </c>
       <c r="B53" t="n">
-        <v>91356</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6297,21 +6297,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426371</v>
+        <v>426516</v>
       </c>
       <c r="R53" t="n">
-        <v>7050917</v>
+        <v>7051239</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6393,45 +6393,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398802</v>
+        <v>128398804</v>
       </c>
       <c r="B54" t="n">
-        <v>91656</v>
+        <v>75154</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>425985</v>
+        <v>426000</v>
       </c>
       <c r="R54" t="n">
-        <v>7051282</v>
+        <v>7051290</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6463,7 +6466,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6473,7 +6476,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,6 +6484,11 @@
       </c>
       <c r="AE54" t="b">
         <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -6500,10 +6508,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398727</v>
+        <v>128398743</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>91356</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6511,21 +6519,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6535,10 +6543,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426516</v>
+        <v>426371</v>
       </c>
       <c r="R55" t="n">
-        <v>7051239</v>
+        <v>7050917</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6570,7 +6578,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6580,7 +6588,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6607,48 +6615,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398804</v>
+        <v>128398802</v>
       </c>
       <c r="B56" t="n">
-        <v>75154</v>
+        <v>91656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426000</v>
+        <v>425985</v>
       </c>
       <c r="R56" t="n">
-        <v>7051290</v>
+        <v>7051282</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6680,7 +6685,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6690,7 +6695,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6698,11 +6703,6 @@
       </c>
       <c r="AE56" t="b">
         <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398783</v>
+        <v>128398726</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>75147</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>425733</v>
+        <v>426522</v>
       </c>
       <c r="R61" t="n">
-        <v>7051205</v>
+        <v>7051242</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,6 +7281,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7638,32 +7653,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128398726</v>
+        <v>128398783</v>
       </c>
       <c r="B65" t="n">
-        <v>75147</v>
+        <v>79032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7673,10 +7688,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426522</v>
+        <v>425733</v>
       </c>
       <c r="R65" t="n">
-        <v>7051242</v>
+        <v>7051205</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7708,7 +7723,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7718,7 +7733,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7729,21 +7744,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128398720</v>
+        <v>128398779</v>
       </c>
       <c r="B73" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8520,34 +8520,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426773</v>
+        <v>425818</v>
       </c>
       <c r="R73" t="n">
-        <v>7051341</v>
+        <v>7051169</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8579,7 +8584,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8589,7 +8594,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8616,10 +8626,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128398779</v>
+        <v>128398720</v>
       </c>
       <c r="B74" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8627,39 +8637,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>425818</v>
+        <v>426773</v>
       </c>
       <c r="R74" t="n">
-        <v>7051169</v>
+        <v>7051341</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8691,7 +8696,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8701,12 +8706,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8733,27 +8733,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128398815</v>
+        <v>128398772</v>
       </c>
       <c r="B75" t="n">
-        <v>91767</v>
+        <v>92057</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6040186</v>
+        <v>3298</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8763,10 +8768,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426114</v>
+        <v>426065</v>
       </c>
       <c r="R75" t="n">
-        <v>7051205</v>
+        <v>7051192</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8798,7 +8803,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8808,7 +8813,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8835,32 +8840,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128398772</v>
+        <v>128398754</v>
       </c>
       <c r="B76" t="n">
-        <v>92057</v>
+        <v>80136</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8870,10 +8875,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426065</v>
+        <v>426191</v>
       </c>
       <c r="R76" t="n">
-        <v>7051192</v>
+        <v>7050957</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8905,7 +8910,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8915,7 +8920,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8926,6 +8931,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8942,10 +8962,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128398754</v>
+        <v>128398815</v>
       </c>
       <c r="B77" t="n">
-        <v>80136</v>
+        <v>91767</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8953,21 +8973,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8977,10 +8992,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426191</v>
+        <v>426114</v>
       </c>
       <c r="R77" t="n">
-        <v>7050957</v>
+        <v>7051205</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9012,7 +9027,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9022,7 +9037,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9033,21 +9048,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY195"/>
+  <dimension ref="A1:AY196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128398742</v>
+        <v>128398786</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>75163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426374</v>
+        <v>425776</v>
       </c>
       <c r="R2" t="n">
-        <v>7050919</v>
+        <v>7051259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128398786</v>
+        <v>128398759</v>
       </c>
       <c r="B3" t="n">
-        <v>75148</v>
+        <v>88853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425776</v>
+        <v>426187</v>
       </c>
       <c r="R3" t="n">
-        <v>7051259</v>
+        <v>7051025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,21 +888,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128398798</v>
+        <v>128398758</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>82942</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425947</v>
+        <v>426187</v>
       </c>
       <c r="R4" t="n">
-        <v>7051321</v>
+        <v>7051025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1014,7 @@
         <v>128398722</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128398758</v>
+        <v>128398798</v>
       </c>
       <c r="B6" t="n">
-        <v>82873</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426187</v>
+        <v>425947</v>
       </c>
       <c r="R6" t="n">
-        <v>7051025</v>
+        <v>7051321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128398759</v>
+        <v>128398742</v>
       </c>
       <c r="B7" t="n">
-        <v>88761</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,34 +1236,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426187</v>
+        <v>426374</v>
       </c>
       <c r="R7" t="n">
-        <v>7051025</v>
+        <v>7050919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1310,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1345,7 @@
         <v>128398746</v>
       </c>
       <c r="B8" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>128398768</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128398774</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>128398775</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>128398762</v>
       </c>
       <c r="B12" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>128398790</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>128398740</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>128398811</v>
       </c>
       <c r="B15" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128398824</v>
+        <v>128398776</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426331</v>
+        <v>425869</v>
       </c>
       <c r="R16" t="n">
-        <v>7051374</v>
+        <v>7051201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128398776</v>
+        <v>128398824</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425869</v>
+        <v>426331</v>
       </c>
       <c r="R17" t="n">
-        <v>7051201</v>
+        <v>7051374</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,7 +2455,7 @@
         <v>128398737</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,32 +2569,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128398803</v>
+        <v>128398770</v>
       </c>
       <c r="B19" t="n">
-        <v>92057</v>
+        <v>91906</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425994</v>
+        <v>426115</v>
       </c>
       <c r="R19" t="n">
-        <v>7051287</v>
+        <v>7051178</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,32 +2676,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398773</v>
+        <v>128398803</v>
       </c>
       <c r="B20" t="n">
-        <v>75154</v>
+        <v>92149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6486</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425978</v>
+        <v>425994</v>
       </c>
       <c r="R20" t="n">
-        <v>7051231</v>
+        <v>7051287</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,32 +2783,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398821</v>
+        <v>128398718</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>92754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426200</v>
+        <v>426807</v>
       </c>
       <c r="R21" t="n">
-        <v>7051338</v>
+        <v>7051311</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398753</v>
+        <v>128398771</v>
       </c>
       <c r="B22" t="n">
-        <v>80135</v>
+        <v>91470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,21 +2901,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426191</v>
+        <v>426068</v>
       </c>
       <c r="R22" t="n">
-        <v>7050957</v>
+        <v>7051189</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2981,21 +2981,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3012,10 +2997,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398752</v>
+        <v>128398821</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3047,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426206</v>
+        <v>426200</v>
       </c>
       <c r="R23" t="n">
-        <v>7050935</v>
+        <v>7051338</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,7 +3067,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3077,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,32 +3104,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398770</v>
+        <v>128398730</v>
       </c>
       <c r="B24" t="n">
-        <v>91814</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3154,10 +3139,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426115</v>
+        <v>426382</v>
       </c>
       <c r="R24" t="n">
-        <v>7051178</v>
+        <v>7051149</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,7 +3174,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3199,7 +3184,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,57 +3211,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398805</v>
+        <v>128398773</v>
       </c>
       <c r="B25" t="n">
-        <v>57833</v>
+        <v>75169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6486</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425999</v>
+        <v>425978</v>
       </c>
       <c r="R25" t="n">
-        <v>7051258</v>
+        <v>7051231</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3305,7 +3281,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3315,7 +3291,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3342,10 +3318,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398730</v>
+        <v>128398753</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>80188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,21 +3329,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3377,10 +3353,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426382</v>
+        <v>426191</v>
       </c>
       <c r="R26" t="n">
-        <v>7051149</v>
+        <v>7050957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3412,7 +3388,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3422,7 +3398,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3433,6 +3409,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3449,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398771</v>
+        <v>128398729</v>
       </c>
       <c r="B27" t="n">
-        <v>91378</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3460,21 +3451,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3484,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426068</v>
+        <v>426468</v>
       </c>
       <c r="R27" t="n">
-        <v>7051189</v>
+        <v>7051179</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3519,7 +3510,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3529,7 +3520,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3556,10 +3547,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398729</v>
+        <v>128398752</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3591,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426468</v>
+        <v>426206</v>
       </c>
       <c r="R28" t="n">
-        <v>7051179</v>
+        <v>7050935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3626,7 +3617,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3636,7 +3627,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3663,48 +3654,57 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128398718</v>
+        <v>128398805</v>
       </c>
       <c r="B29" t="n">
-        <v>92662</v>
+        <v>57845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426807</v>
+        <v>425999</v>
       </c>
       <c r="R29" t="n">
-        <v>7051311</v>
+        <v>7051258</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,7 +3773,7 @@
         <v>128398819</v>
       </c>
       <c r="B30" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,32 +3877,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398788</v>
+        <v>128398724</v>
       </c>
       <c r="B31" t="n">
-        <v>75147</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425804</v>
+        <v>426447</v>
       </c>
       <c r="R31" t="n">
-        <v>7051255</v>
+        <v>7051254</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,11 +3968,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Glasbjörk</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3989,32 +3984,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398791</v>
+        <v>128398788</v>
       </c>
       <c r="B32" t="n">
-        <v>75148</v>
+        <v>75162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4024,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425847</v>
+        <v>425804</v>
       </c>
       <c r="R32" t="n">
-        <v>7051261</v>
+        <v>7051255</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4059,7 +4054,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4064,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4081,19 +4076,9 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Glasbjörk</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4111,10 +4096,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398724</v>
+        <v>128398791</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>75163</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4122,21 +4107,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4146,10 +4131,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426447</v>
+        <v>425847</v>
       </c>
       <c r="R33" t="n">
-        <v>7051254</v>
+        <v>7051261</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4181,7 +4166,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4191,7 +4176,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4202,6 +4187,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4218,10 +4218,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398755</v>
+        <v>128398741</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4229,34 +4229,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426166</v>
+        <v>426298</v>
       </c>
       <c r="R34" t="n">
-        <v>7050989</v>
+        <v>7051029</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4288,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4303,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,7 +4338,7 @@
         <v>128398801</v>
       </c>
       <c r="B35" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4432,10 +4442,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128398741</v>
+        <v>128398738</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4443,39 +4453,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426298</v>
+        <v>426341</v>
       </c>
       <c r="R36" t="n">
-        <v>7051029</v>
+        <v>7051103</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4507,7 +4512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4517,12 +4522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4549,10 +4549,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398738</v>
+        <v>128398755</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426341</v>
+        <v>426166</v>
       </c>
       <c r="R37" t="n">
-        <v>7051103</v>
+        <v>7050989</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4659,7 +4659,7 @@
         <v>128398794</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>128398785</v>
       </c>
       <c r="B39" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128398808</v>
+        <v>128398795</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>91470</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426012</v>
+        <v>425894</v>
       </c>
       <c r="R40" t="n">
-        <v>7051229</v>
+        <v>7051343</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4977,10 +4977,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128398795</v>
+        <v>128398808</v>
       </c>
       <c r="B41" t="n">
-        <v>91378</v>
+        <v>79083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4988,21 +4988,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425894</v>
+        <v>426012</v>
       </c>
       <c r="R41" t="n">
-        <v>7051343</v>
+        <v>7051229</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,32 +5084,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128398749</v>
+        <v>128398736</v>
       </c>
       <c r="B42" t="n">
-        <v>86674</v>
+        <v>92149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>427</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426252</v>
+        <v>426352</v>
       </c>
       <c r="R42" t="n">
-        <v>7050919</v>
+        <v>7051151</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,12 +5164,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5199,7 +5194,7 @@
         <v>128398787</v>
       </c>
       <c r="B43" t="n">
-        <v>75148</v>
+        <v>75163</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5303,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128398736</v>
+        <v>128398749</v>
       </c>
       <c r="B44" t="n">
-        <v>92057</v>
+        <v>86766</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>427</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5338,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426352</v>
+        <v>426252</v>
       </c>
       <c r="R44" t="n">
-        <v>7051151</v>
+        <v>7050919</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5368,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5383,7 +5378,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5413,7 +5413,7 @@
         <v>128398800</v>
       </c>
       <c r="B45" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>128398731</v>
       </c>
       <c r="B46" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5624,10 +5624,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398807</v>
+        <v>128398797</v>
       </c>
       <c r="B47" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,39 +5635,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426011</v>
+        <v>425919</v>
       </c>
       <c r="R47" t="n">
-        <v>7051282</v>
+        <v>7051350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5699,7 +5694,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5709,12 +5704,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5741,10 +5731,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128398721</v>
+        <v>128398812</v>
       </c>
       <c r="B48" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5752,39 +5742,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426773</v>
+        <v>426097</v>
       </c>
       <c r="R48" t="n">
-        <v>7051349</v>
+        <v>7051199</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5816,7 +5801,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5826,12 +5811,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5861,7 +5841,7 @@
         <v>128398725</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5965,10 +5945,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128398797</v>
+        <v>128398807</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,34 +5956,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>425919</v>
+        <v>426011</v>
       </c>
       <c r="R50" t="n">
-        <v>7051350</v>
+        <v>7051282</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6035,7 +6020,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6045,7 +6030,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,10 +6062,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128398812</v>
+        <v>128398721</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6083,34 +6073,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426097</v>
+        <v>426773</v>
       </c>
       <c r="R51" t="n">
-        <v>7051199</v>
+        <v>7051349</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6142,7 +6137,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6152,7 +6147,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,32 +6179,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398734</v>
+        <v>128398743</v>
       </c>
       <c r="B52" t="n">
-        <v>92057</v>
+        <v>91448</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6214,10 +6214,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426329</v>
+        <v>426371</v>
       </c>
       <c r="R52" t="n">
-        <v>7051146</v>
+        <v>7050917</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6289,7 +6289,7 @@
         <v>128398727</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>128398804</v>
       </c>
       <c r="B54" t="n">
-        <v>75154</v>
+        <v>75169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6508,10 +6508,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398743</v>
+        <v>128398793</v>
       </c>
       <c r="B55" t="n">
-        <v>91356</v>
+        <v>57685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6519,34 +6519,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426371</v>
+        <v>425908</v>
       </c>
       <c r="R55" t="n">
-        <v>7050917</v>
+        <v>7051281</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6578,7 +6583,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6588,7 +6593,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6615,10 +6625,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398802</v>
+        <v>128398822</v>
       </c>
       <c r="B56" t="n">
-        <v>91656</v>
+        <v>57685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6626,34 +6636,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>425985</v>
+        <v>426200</v>
       </c>
       <c r="R56" t="n">
-        <v>7051282</v>
+        <v>7051338</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6685,7 +6700,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6695,7 +6710,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6722,10 +6742,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398793</v>
+        <v>128398719</v>
       </c>
       <c r="B57" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6762,10 +6782,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425908</v>
+        <v>426799</v>
       </c>
       <c r="R57" t="n">
-        <v>7051281</v>
+        <v>7051328</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6797,7 +6817,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6807,7 +6827,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6839,50 +6859,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398814</v>
+        <v>128398734</v>
       </c>
       <c r="B58" t="n">
-        <v>57673</v>
+        <v>92149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426097</v>
+        <v>426329</v>
       </c>
       <c r="R58" t="n">
-        <v>7051199</v>
+        <v>7051146</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6914,7 +6929,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6924,12 +6939,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6956,10 +6966,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398822</v>
+        <v>128398802</v>
       </c>
       <c r="B59" t="n">
-        <v>57673</v>
+        <v>91748</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6967,39 +6977,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426200</v>
+        <v>425985</v>
       </c>
       <c r="R59" t="n">
-        <v>7051338</v>
+        <v>7051282</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7031,7 +7036,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7041,12 +7046,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7073,10 +7073,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398719</v>
+        <v>128398814</v>
       </c>
       <c r="B60" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426799</v>
+        <v>426097</v>
       </c>
       <c r="R60" t="n">
-        <v>7051328</v>
+        <v>7051199</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398726</v>
+        <v>128398769</v>
       </c>
       <c r="B61" t="n">
-        <v>75147</v>
+        <v>91452</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426522</v>
+        <v>426135</v>
       </c>
       <c r="R61" t="n">
-        <v>7051242</v>
+        <v>7051154</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,21 +7281,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7312,10 +7297,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398769</v>
+        <v>128398783</v>
       </c>
       <c r="B62" t="n">
-        <v>91360</v>
+        <v>79083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7323,21 +7308,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7347,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426135</v>
+        <v>425733</v>
       </c>
       <c r="R62" t="n">
-        <v>7051154</v>
+        <v>7051205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7382,7 +7367,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7392,7 +7377,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7422,7 +7407,7 @@
         <v>128398745</v>
       </c>
       <c r="B63" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7539,7 +7524,7 @@
         <v>128398781</v>
       </c>
       <c r="B64" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7653,32 +7638,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128398783</v>
+        <v>128398726</v>
       </c>
       <c r="B65" t="n">
-        <v>79032</v>
+        <v>75162</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7688,10 +7673,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>425733</v>
+        <v>426522</v>
       </c>
       <c r="R65" t="n">
-        <v>7051205</v>
+        <v>7051242</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7723,7 +7708,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7733,7 +7718,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7744,6 +7729,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7760,10 +7760,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128398763</v>
+        <v>128398796</v>
       </c>
       <c r="B66" t="n">
-        <v>79032</v>
+        <v>78060</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7771,21 +7771,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>426227</v>
+        <v>425919</v>
       </c>
       <c r="R66" t="n">
-        <v>7051105</v>
+        <v>7051350</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7867,10 +7867,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128398796</v>
+        <v>128398763</v>
       </c>
       <c r="B67" t="n">
-        <v>78015</v>
+        <v>79083</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7878,21 +7878,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>425919</v>
+        <v>426227</v>
       </c>
       <c r="R67" t="n">
-        <v>7051350</v>
+        <v>7051105</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7977,7 +7977,7 @@
         <v>128398733</v>
       </c>
       <c r="B68" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8081,10 +8081,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128398820</v>
+        <v>128398760</v>
       </c>
       <c r="B69" t="n">
-        <v>91378</v>
+        <v>82942</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8092,21 +8092,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426196</v>
+        <v>426232</v>
       </c>
       <c r="R69" t="n">
-        <v>7051340</v>
+        <v>7051062</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8188,10 +8188,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128398760</v>
+        <v>128398820</v>
       </c>
       <c r="B70" t="n">
-        <v>82873</v>
+        <v>91470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8199,21 +8199,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426232</v>
+        <v>426196</v>
       </c>
       <c r="R70" t="n">
-        <v>7051062</v>
+        <v>7051340</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8295,10 +8295,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128398818</v>
+        <v>128398777</v>
       </c>
       <c r="B71" t="n">
-        <v>79032</v>
+        <v>82942</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8306,21 +8306,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426191</v>
+        <v>425861</v>
       </c>
       <c r="R71" t="n">
-        <v>7051296</v>
+        <v>7051195</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8402,10 +8402,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128398777</v>
+        <v>128398818</v>
       </c>
       <c r="B72" t="n">
-        <v>82873</v>
+        <v>79083</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8413,21 +8413,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>425861</v>
+        <v>426191</v>
       </c>
       <c r="R72" t="n">
-        <v>7051195</v>
+        <v>7051296</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128398779</v>
+        <v>128398720</v>
       </c>
       <c r="B73" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8520,39 +8520,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>425818</v>
+        <v>426773</v>
       </c>
       <c r="R73" t="n">
-        <v>7051169</v>
+        <v>7051341</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8584,7 +8579,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8594,12 +8589,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8626,10 +8616,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128398720</v>
+        <v>128398779</v>
       </c>
       <c r="B74" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8637,34 +8627,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426773</v>
+        <v>425818</v>
       </c>
       <c r="R74" t="n">
-        <v>7051341</v>
+        <v>7051169</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8696,7 +8691,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8706,7 +8701,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8733,45 +8733,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128398772</v>
+        <v>128398789</v>
       </c>
       <c r="B75" t="n">
-        <v>92057</v>
+        <v>57685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426065</v>
+        <v>425804</v>
       </c>
       <c r="R75" t="n">
-        <v>7051192</v>
+        <v>7051258</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8803,7 +8808,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8813,7 +8818,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8840,10 +8850,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128398754</v>
+        <v>128398815</v>
       </c>
       <c r="B76" t="n">
-        <v>80136</v>
+        <v>91859</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8851,21 +8861,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8875,10 +8880,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426191</v>
+        <v>426114</v>
       </c>
       <c r="R76" t="n">
-        <v>7050957</v>
+        <v>7051205</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8910,7 +8915,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8920,7 +8925,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8931,21 +8936,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8962,27 +8952,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128398815</v>
+        <v>128398772</v>
       </c>
       <c r="B77" t="n">
-        <v>91767</v>
+        <v>92149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6040186</v>
+        <v>3298</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8992,10 +8987,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426114</v>
+        <v>426065</v>
       </c>
       <c r="R77" t="n">
-        <v>7051205</v>
+        <v>7051192</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9027,7 +9022,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9037,7 +9032,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9064,10 +9059,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128398789</v>
+        <v>128398754</v>
       </c>
       <c r="B78" t="n">
-        <v>57673</v>
+        <v>80189</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9075,39 +9070,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>425804</v>
+        <v>426191</v>
       </c>
       <c r="R78" t="n">
-        <v>7051258</v>
+        <v>7050957</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9139,7 +9129,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9149,12 +9139,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9165,6 +9150,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9181,10 +9181,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128398813</v>
+        <v>128398723</v>
       </c>
       <c r="B79" t="n">
-        <v>82873</v>
+        <v>79083</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9192,21 +9192,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426097</v>
+        <v>426515</v>
       </c>
       <c r="R79" t="n">
-        <v>7051199</v>
+        <v>7051308</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9288,10 +9288,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128398765</v>
+        <v>128398751</v>
       </c>
       <c r="B80" t="n">
-        <v>82873</v>
+        <v>79083</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426186</v>
+        <v>426239</v>
       </c>
       <c r="R80" t="n">
-        <v>7051125</v>
+        <v>7050935</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9398,7 +9398,7 @@
         <v>128398780</v>
       </c>
       <c r="B81" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>128398784</v>
       </c>
       <c r="B82" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9629,10 +9629,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128398723</v>
+        <v>128398813</v>
       </c>
       <c r="B83" t="n">
-        <v>79032</v>
+        <v>82942</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9640,21 +9640,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9664,10 +9664,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>426515</v>
+        <v>426097</v>
       </c>
       <c r="R83" t="n">
-        <v>7051308</v>
+        <v>7051199</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9699,7 +9699,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9736,10 +9736,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128398751</v>
+        <v>128398765</v>
       </c>
       <c r="B84" t="n">
-        <v>79032</v>
+        <v>82942</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9747,21 +9747,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>426239</v>
+        <v>426186</v>
       </c>
       <c r="R84" t="n">
-        <v>7050935</v>
+        <v>7051125</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9843,10 +9843,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128398728</v>
+        <v>128398761</v>
       </c>
       <c r="B85" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9854,39 +9854,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>426475</v>
+        <v>426231</v>
       </c>
       <c r="R85" t="n">
-        <v>7051191</v>
+        <v>7051061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9918,7 +9913,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9928,12 +9923,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9960,10 +9950,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128398761</v>
+        <v>128398728</v>
       </c>
       <c r="B86" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9971,34 +9961,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>426231</v>
+        <v>426475</v>
       </c>
       <c r="R86" t="n">
-        <v>7051061</v>
+        <v>7051191</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10030,7 +10025,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10040,7 +10035,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10070,7 +10070,7 @@
         <v>128399908</v>
       </c>
       <c r="B87" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>128399850</v>
       </c>
       <c r="B88" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>128399888</v>
       </c>
       <c r="B89" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>128399916</v>
       </c>
       <c r="B90" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>128399875</v>
       </c>
       <c r="B91" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>128399895</v>
       </c>
       <c r="B92" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399940</v>
+        <v>128399949</v>
       </c>
       <c r="B93" t="n">
-        <v>91378</v>
+        <v>88853</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426338</v>
+        <v>426768</v>
       </c>
       <c r="R93" t="n">
-        <v>7050977</v>
+        <v>7051367</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10776,10 +10776,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399949</v>
+        <v>128399940</v>
       </c>
       <c r="B94" t="n">
-        <v>88761</v>
+        <v>91470</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10787,21 +10787,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426768</v>
+        <v>426338</v>
       </c>
       <c r="R94" t="n">
-        <v>7051367</v>
+        <v>7050977</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10876,7 +10876,7 @@
         <v>128399849</v>
       </c>
       <c r="B95" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>128399898</v>
       </c>
       <c r="B96" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11077,32 +11077,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399832</v>
+        <v>128399886</v>
       </c>
       <c r="B97" t="n">
-        <v>92057</v>
+        <v>57685</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11112,10 +11112,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426401</v>
+        <v>425743</v>
       </c>
       <c r="R97" t="n">
-        <v>7051237</v>
+        <v>7051241</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11148,6 +11148,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11174,10 +11179,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399836</v>
+        <v>128399832</v>
       </c>
       <c r="B98" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11209,10 +11214,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426093</v>
+        <v>426401</v>
       </c>
       <c r="R98" t="n">
-        <v>7051184</v>
+        <v>7051237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11271,32 +11276,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399886</v>
+        <v>128399836</v>
       </c>
       <c r="B99" t="n">
-        <v>57673</v>
+        <v>92149</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11306,10 +11311,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425743</v>
+        <v>426093</v>
       </c>
       <c r="R99" t="n">
-        <v>7051241</v>
+        <v>7051184</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11342,11 +11347,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399907</v>
+        <v>128399922</v>
       </c>
       <c r="B100" t="n">
-        <v>57673</v>
+        <v>91448</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426064</v>
+        <v>426343</v>
       </c>
       <c r="R100" t="n">
-        <v>7051249</v>
+        <v>7050915</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11444,11 +11444,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11475,10 +11470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399889</v>
+        <v>128399936</v>
       </c>
       <c r="B101" t="n">
-        <v>57673</v>
+        <v>91466</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11486,21 +11481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11510,10 +11505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425774</v>
+        <v>425967</v>
       </c>
       <c r="R101" t="n">
-        <v>7051222</v>
+        <v>7051278</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11546,11 +11541,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11577,10 +11567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399941</v>
+        <v>128399829</v>
       </c>
       <c r="B102" t="n">
-        <v>91378</v>
+        <v>91452</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11588,21 +11578,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11612,10 +11602,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425987</v>
+        <v>426191</v>
       </c>
       <c r="R102" t="n">
-        <v>7051259</v>
+        <v>7050972</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11674,10 +11664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399922</v>
+        <v>128399941</v>
       </c>
       <c r="B103" t="n">
-        <v>91356</v>
+        <v>91470</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11685,21 +11675,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11709,10 +11699,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426343</v>
+        <v>425987</v>
       </c>
       <c r="R103" t="n">
-        <v>7050915</v>
+        <v>7051259</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11771,10 +11761,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128399936</v>
+        <v>128399907</v>
       </c>
       <c r="B104" t="n">
-        <v>91374</v>
+        <v>57685</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11782,21 +11772,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11806,10 +11796,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>425967</v>
+        <v>426064</v>
       </c>
       <c r="R104" t="n">
-        <v>7051278</v>
+        <v>7051249</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11842,6 +11832,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11868,10 +11863,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128399829</v>
+        <v>128399889</v>
       </c>
       <c r="B105" t="n">
-        <v>91360</v>
+        <v>57685</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11879,21 +11874,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11903,10 +11898,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>426191</v>
+        <v>425774</v>
       </c>
       <c r="R105" t="n">
-        <v>7050972</v>
+        <v>7051222</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11939,6 +11934,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11965,32 +11965,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399834</v>
+        <v>128399903</v>
       </c>
       <c r="B106" t="n">
-        <v>92057</v>
+        <v>57685</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426228</v>
+        <v>425972</v>
       </c>
       <c r="R106" t="n">
-        <v>7050978</v>
+        <v>7051285</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12036,6 +12036,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12062,10 +12067,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399945</v>
+        <v>128399863</v>
       </c>
       <c r="B107" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12073,21 +12078,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12097,10 +12102,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426062</v>
+        <v>426347</v>
       </c>
       <c r="R107" t="n">
-        <v>7051271</v>
+        <v>7050960</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12133,6 +12138,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12159,10 +12169,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399903</v>
+        <v>128399868</v>
       </c>
       <c r="B108" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12194,10 +12204,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>425972</v>
+        <v>426274</v>
       </c>
       <c r="R108" t="n">
-        <v>7051285</v>
+        <v>7050964</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12234,7 +12244,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12261,10 +12271,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399863</v>
+        <v>128399881</v>
       </c>
       <c r="B109" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12296,10 +12306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426347</v>
+        <v>425942</v>
       </c>
       <c r="R109" t="n">
-        <v>7050960</v>
+        <v>7051274</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12336,7 +12346,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12363,32 +12373,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399868</v>
+        <v>128399834</v>
       </c>
       <c r="B110" t="n">
-        <v>57673</v>
+        <v>92149</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12398,10 +12408,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>426274</v>
+        <v>426228</v>
       </c>
       <c r="R110" t="n">
-        <v>7050964</v>
+        <v>7050978</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12434,11 +12444,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12465,10 +12470,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128399881</v>
+        <v>128399945</v>
       </c>
       <c r="B111" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12476,21 +12481,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12500,10 +12505,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>425942</v>
+        <v>426062</v>
       </c>
       <c r="R111" t="n">
-        <v>7051274</v>
+        <v>7051271</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12536,11 +12541,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12567,32 +12567,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128399833</v>
+        <v>128399935</v>
       </c>
       <c r="B112" t="n">
-        <v>92057</v>
+        <v>91466</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12602,10 +12602,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>426263</v>
+        <v>425974</v>
       </c>
       <c r="R112" t="n">
-        <v>7051287</v>
+        <v>7051249</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12664,32 +12664,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128399904</v>
+        <v>128399833</v>
       </c>
       <c r="B113" t="n">
-        <v>57673</v>
+        <v>92149</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>426012</v>
+        <v>426263</v>
       </c>
       <c r="R113" t="n">
-        <v>7051306</v>
+        <v>7051287</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12735,11 +12735,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12766,32 +12761,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128399935</v>
+        <v>128399831</v>
       </c>
       <c r="B114" t="n">
-        <v>91374</v>
+        <v>92149</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12801,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>425974</v>
+        <v>426425</v>
       </c>
       <c r="R114" t="n">
-        <v>7051249</v>
+        <v>7051289</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12863,32 +12858,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399831</v>
+        <v>128399904</v>
       </c>
       <c r="B115" t="n">
-        <v>92057</v>
+        <v>57685</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12898,10 +12893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426425</v>
+        <v>426012</v>
       </c>
       <c r="R115" t="n">
-        <v>7051289</v>
+        <v>7051306</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12934,6 +12929,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12960,10 +12960,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399943</v>
+        <v>128399870</v>
       </c>
       <c r="B116" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12971,21 +12971,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12995,10 +12995,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>425756</v>
+        <v>426156</v>
       </c>
       <c r="R116" t="n">
-        <v>7051245</v>
+        <v>7050998</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13031,6 +13031,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,10 +13062,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128399870</v>
+        <v>128399943</v>
       </c>
       <c r="B117" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13068,21 +13073,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13092,10 +13097,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426156</v>
+        <v>425756</v>
       </c>
       <c r="R117" t="n">
-        <v>7050998</v>
+        <v>7051245</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13128,11 +13133,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13159,32 +13159,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399838</v>
+        <v>128399928</v>
       </c>
       <c r="B118" t="n">
-        <v>92057</v>
+        <v>91466</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>425752</v>
+        <v>426319</v>
       </c>
       <c r="R118" t="n">
-        <v>7051219</v>
+        <v>7051238</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13259,7 +13259,7 @@
         <v>128399872</v>
       </c>
       <c r="B119" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>128399853</v>
       </c>
       <c r="B120" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>128399914</v>
       </c>
       <c r="B121" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13570,10 +13570,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399928</v>
+        <v>128399852</v>
       </c>
       <c r="B122" t="n">
-        <v>91374</v>
+        <v>57685</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13581,21 +13581,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13605,10 +13605,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>426319</v>
+        <v>426765</v>
       </c>
       <c r="R122" t="n">
-        <v>7051238</v>
+        <v>7051373</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13641,6 +13641,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13667,10 +13672,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399852</v>
+        <v>128399897</v>
       </c>
       <c r="B123" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13702,10 +13707,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>426765</v>
+        <v>425892</v>
       </c>
       <c r="R123" t="n">
-        <v>7051373</v>
+        <v>7051251</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13742,7 +13747,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13769,10 +13774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128399897</v>
+        <v>128399902</v>
       </c>
       <c r="B124" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13804,10 +13809,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>425892</v>
+        <v>425902</v>
       </c>
       <c r="R124" t="n">
-        <v>7051251</v>
+        <v>7051312</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13871,10 +13876,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128399902</v>
+        <v>128399871</v>
       </c>
       <c r="B125" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13906,10 +13911,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425902</v>
+        <v>426154</v>
       </c>
       <c r="R125" t="n">
-        <v>7051312</v>
+        <v>7050994</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13973,32 +13978,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399871</v>
+        <v>128399838</v>
       </c>
       <c r="B126" t="n">
-        <v>57673</v>
+        <v>92149</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14008,10 +14013,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426154</v>
+        <v>425752</v>
       </c>
       <c r="R126" t="n">
-        <v>7050994</v>
+        <v>7051219</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14044,11 +14049,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14078,7 +14078,7 @@
         <v>128399901</v>
       </c>
       <c r="B127" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>128399878</v>
       </c>
       <c r="B128" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14279,10 +14279,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399948</v>
+        <v>128399876</v>
       </c>
       <c r="B129" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14290,21 +14290,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426395</v>
+        <v>426244</v>
       </c>
       <c r="R129" t="n">
-        <v>7051398</v>
+        <v>7051052</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14381,10 +14381,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128399876</v>
+        <v>128399905</v>
       </c>
       <c r="B130" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14416,10 +14416,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426244</v>
+        <v>426029</v>
       </c>
       <c r="R130" t="n">
-        <v>7051052</v>
+        <v>7051287</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14483,10 +14483,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399942</v>
+        <v>128399920</v>
       </c>
       <c r="B131" t="n">
-        <v>91378</v>
+        <v>91448</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14494,21 +14494,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14518,10 +14518,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>425904</v>
+        <v>426277</v>
       </c>
       <c r="R131" t="n">
-        <v>7051248</v>
+        <v>7051183</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14580,10 +14580,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399905</v>
+        <v>128399942</v>
       </c>
       <c r="B132" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14591,21 +14591,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14615,10 +14615,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>426029</v>
+        <v>425904</v>
       </c>
       <c r="R132" t="n">
-        <v>7051287</v>
+        <v>7051248</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14651,11 +14651,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14682,10 +14677,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399920</v>
+        <v>128399948</v>
       </c>
       <c r="B133" t="n">
-        <v>91356</v>
+        <v>79083</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14693,21 +14688,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14717,10 +14712,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426277</v>
+        <v>426395</v>
       </c>
       <c r="R133" t="n">
-        <v>7051183</v>
+        <v>7051398</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14753,6 +14748,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14779,10 +14779,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128399930</v>
+        <v>128399918</v>
       </c>
       <c r="B134" t="n">
-        <v>91374</v>
+        <v>91402</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14790,21 +14790,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14814,10 +14814,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>426267</v>
+        <v>426224</v>
       </c>
       <c r="R134" t="n">
-        <v>7050942</v>
+        <v>7050981</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14876,10 +14876,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128399877</v>
+        <v>128399930</v>
       </c>
       <c r="B135" t="n">
-        <v>57673</v>
+        <v>91466</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14887,21 +14887,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>426231</v>
+        <v>426267</v>
       </c>
       <c r="R135" t="n">
-        <v>7051067</v>
+        <v>7050942</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14947,11 +14947,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14981,7 +14976,7 @@
         <v>128399931</v>
       </c>
       <c r="B136" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15075,10 +15070,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128399867</v>
+        <v>128399929</v>
       </c>
       <c r="B137" t="n">
-        <v>57673</v>
+        <v>91466</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15086,21 +15081,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15110,10 +15105,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>426331</v>
+        <v>426276</v>
       </c>
       <c r="R137" t="n">
-        <v>7050912</v>
+        <v>7050944</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15146,11 +15141,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15177,10 +15167,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128399918</v>
+        <v>128399877</v>
       </c>
       <c r="B138" t="n">
-        <v>91310</v>
+        <v>57685</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15188,21 +15178,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15212,10 +15202,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>426224</v>
+        <v>426231</v>
       </c>
       <c r="R138" t="n">
-        <v>7050981</v>
+        <v>7051067</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15248,6 +15238,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15274,10 +15269,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128399929</v>
+        <v>128399867</v>
       </c>
       <c r="B139" t="n">
-        <v>91374</v>
+        <v>57685</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15285,21 +15280,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15309,10 +15304,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>426276</v>
+        <v>426331</v>
       </c>
       <c r="R139" t="n">
-        <v>7050944</v>
+        <v>7050912</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15345,6 +15340,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15374,7 +15374,7 @@
         <v>128399906</v>
       </c>
       <c r="B140" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>128399879</v>
       </c>
       <c r="B141" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>128399896</v>
       </c>
       <c r="B142" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>128399890</v>
       </c>
       <c r="B143" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>128399910</v>
       </c>
       <c r="B144" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15881,10 +15881,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128399880</v>
+        <v>128399933</v>
       </c>
       <c r="B145" t="n">
-        <v>57673</v>
+        <v>91466</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15892,21 +15892,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15916,10 +15916,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425981</v>
+        <v>426218</v>
       </c>
       <c r="R145" t="n">
-        <v>7051240</v>
+        <v>7051146</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15952,11 +15952,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15983,10 +15978,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128399933</v>
+        <v>128399880</v>
       </c>
       <c r="B146" t="n">
-        <v>91374</v>
+        <v>57685</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15994,21 +15989,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16018,10 +16013,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>426218</v>
+        <v>425981</v>
       </c>
       <c r="R146" t="n">
-        <v>7051146</v>
+        <v>7051240</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16054,6 +16049,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16083,7 +16083,7 @@
         <v>128399865</v>
       </c>
       <c r="B147" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>128399828</v>
       </c>
       <c r="B148" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16279,10 +16279,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128399892</v>
+        <v>128399946</v>
       </c>
       <c r="B149" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16290,21 +16290,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16314,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>425853</v>
+        <v>426083</v>
       </c>
       <c r="R149" t="n">
-        <v>7051216</v>
+        <v>7051231</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16350,11 +16350,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16381,10 +16376,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128399883</v>
+        <v>128399937</v>
       </c>
       <c r="B150" t="n">
-        <v>57673</v>
+        <v>91470</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16392,21 +16387,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16416,10 +16411,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425851</v>
+        <v>426734</v>
       </c>
       <c r="R150" t="n">
-        <v>7051202</v>
+        <v>7051350</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16452,11 +16447,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16483,10 +16473,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128399946</v>
+        <v>128399892</v>
       </c>
       <c r="B151" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16494,21 +16484,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16518,10 +16508,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>426083</v>
+        <v>425853</v>
       </c>
       <c r="R151" t="n">
-        <v>7051231</v>
+        <v>7051216</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16554,6 +16544,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16580,10 +16575,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128399937</v>
+        <v>128399883</v>
       </c>
       <c r="B152" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16591,21 +16586,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16615,10 +16610,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>426734</v>
+        <v>425851</v>
       </c>
       <c r="R152" t="n">
-        <v>7051350</v>
+        <v>7051202</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16651,6 +16646,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16680,7 +16680,7 @@
         <v>128399861</v>
       </c>
       <c r="B153" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>128399855</v>
       </c>
       <c r="B154" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>128399885</v>
       </c>
       <c r="B155" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>128399911</v>
       </c>
       <c r="B156" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>128399913</v>
       </c>
       <c r="B157" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17187,45 +17187,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128399839</v>
+        <v>128399827</v>
       </c>
       <c r="B158" t="n">
-        <v>92057</v>
+        <v>91452</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>425971</v>
+        <v>426813</v>
       </c>
       <c r="R158" t="n">
-        <v>7051280</v>
+        <v>7051371</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17284,45 +17284,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128399827</v>
+        <v>128399839</v>
       </c>
       <c r="B159" t="n">
-        <v>91360</v>
+        <v>92149</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Stor-grässjön, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>426813</v>
+        <v>425971</v>
       </c>
       <c r="R159" t="n">
-        <v>7051371</v>
+        <v>7051280</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17384,7 +17384,7 @@
         <v>128399856</v>
       </c>
       <c r="B160" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>128399909</v>
       </c>
       <c r="B161" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17585,32 +17585,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128399837</v>
+        <v>128399926</v>
       </c>
       <c r="B162" t="n">
-        <v>92057</v>
+        <v>91448</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>425757</v>
+        <v>426189</v>
       </c>
       <c r="R162" t="n">
-        <v>7051207</v>
+        <v>7051364</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17682,32 +17682,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128399874</v>
+        <v>128399837</v>
       </c>
       <c r="B163" t="n">
-        <v>57673</v>
+        <v>92149</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17717,10 +17717,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>426194</v>
+        <v>425757</v>
       </c>
       <c r="R163" t="n">
-        <v>7050979</v>
+        <v>7051207</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17753,11 +17753,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17784,32 +17779,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128399926</v>
+        <v>128399840</v>
       </c>
       <c r="B164" t="n">
-        <v>91356</v>
+        <v>92149</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17819,10 +17814,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>426189</v>
+        <v>426131</v>
       </c>
       <c r="R164" t="n">
-        <v>7051364</v>
+        <v>7051242</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17881,10 +17876,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128399864</v>
+        <v>128399874</v>
       </c>
       <c r="B165" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17916,10 +17911,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>426357</v>
+        <v>426194</v>
       </c>
       <c r="R165" t="n">
-        <v>7050965</v>
+        <v>7050979</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17956,7 +17951,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17983,32 +17978,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128399840</v>
+        <v>128399864</v>
       </c>
       <c r="B166" t="n">
-        <v>92057</v>
+        <v>57685</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18018,10 +18013,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>426131</v>
+        <v>426357</v>
       </c>
       <c r="R166" t="n">
-        <v>7051242</v>
+        <v>7050965</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18054,6 +18049,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18080,32 +18080,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128399843</v>
+        <v>128399934</v>
       </c>
       <c r="B167" t="n">
-        <v>92057</v>
+        <v>91466</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18115,10 +18115,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>426425</v>
+        <v>426135</v>
       </c>
       <c r="R167" t="n">
-        <v>7051273</v>
+        <v>7051163</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18177,32 +18177,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128399934</v>
+        <v>128399843</v>
       </c>
       <c r="B168" t="n">
-        <v>91374</v>
+        <v>92149</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18212,10 +18212,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>426135</v>
+        <v>426425</v>
       </c>
       <c r="R168" t="n">
-        <v>7051163</v>
+        <v>7051273</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18277,7 +18277,7 @@
         <v>128399869</v>
       </c>
       <c r="B169" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>128399899</v>
       </c>
       <c r="B170" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18478,10 +18478,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128399884</v>
+        <v>128399921</v>
       </c>
       <c r="B171" t="n">
-        <v>57673</v>
+        <v>91448</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18489,21 +18489,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18513,10 +18513,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>425770</v>
+        <v>426314</v>
       </c>
       <c r="R171" t="n">
-        <v>7051183</v>
+        <v>7050963</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18549,11 +18549,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18583,7 +18578,7 @@
         <v>128399938</v>
       </c>
       <c r="B172" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18677,10 +18672,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128399921</v>
+        <v>128399884</v>
       </c>
       <c r="B173" t="n">
-        <v>91356</v>
+        <v>57685</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18688,21 +18683,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18712,10 +18707,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>426314</v>
+        <v>425770</v>
       </c>
       <c r="R173" t="n">
-        <v>7050963</v>
+        <v>7051183</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18748,6 +18743,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18777,7 +18777,7 @@
         <v>128399893</v>
       </c>
       <c r="B174" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>128399887</v>
       </c>
       <c r="B175" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>128399882</v>
       </c>
       <c r="B176" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>128399854</v>
       </c>
       <c r="B177" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>128399835</v>
       </c>
       <c r="B178" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399950</v>
+        <v>128399944</v>
       </c>
       <c r="B179" t="n">
-        <v>88761</v>
+        <v>91470</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19298,21 +19298,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>426303</v>
+        <v>425889</v>
       </c>
       <c r="R179" t="n">
-        <v>7050905</v>
+        <v>7051300</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19384,10 +19384,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128399951</v>
+        <v>128399950</v>
       </c>
       <c r="B180" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>426062</v>
+        <v>426303</v>
       </c>
       <c r="R180" t="n">
-        <v>7051265</v>
+        <v>7050905</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19481,10 +19481,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399944</v>
+        <v>128399951</v>
       </c>
       <c r="B181" t="n">
-        <v>91378</v>
+        <v>88853</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19492,21 +19492,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19516,10 +19516,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>425889</v>
+        <v>426062</v>
       </c>
       <c r="R181" t="n">
-        <v>7051300</v>
+        <v>7051265</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19578,10 +19578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128399894</v>
+        <v>128399932</v>
       </c>
       <c r="B182" t="n">
-        <v>57673</v>
+        <v>91466</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19589,21 +19589,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>425875</v>
+        <v>426231</v>
       </c>
       <c r="R182" t="n">
-        <v>7051223</v>
+        <v>7051130</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19649,11 +19649,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19680,10 +19675,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128399915</v>
+        <v>128399923</v>
       </c>
       <c r="B183" t="n">
-        <v>57673</v>
+        <v>91448</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19691,21 +19686,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19715,10 +19710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>426224</v>
+        <v>426172</v>
       </c>
       <c r="R183" t="n">
-        <v>7051367</v>
+        <v>7051169</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19751,11 +19746,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19782,10 +19772,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128399912</v>
+        <v>128399894</v>
       </c>
       <c r="B184" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19817,10 +19807,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>426175</v>
+        <v>425875</v>
       </c>
       <c r="R184" t="n">
-        <v>7051336</v>
+        <v>7051223</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19857,7 +19847,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19884,10 +19874,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128399932</v>
+        <v>128399915</v>
       </c>
       <c r="B185" t="n">
-        <v>91374</v>
+        <v>57685</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19895,21 +19885,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19919,10 +19909,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>426231</v>
+        <v>426224</v>
       </c>
       <c r="R185" t="n">
-        <v>7051130</v>
+        <v>7051367</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19955,6 +19945,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19981,10 +19976,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128399923</v>
+        <v>128399912</v>
       </c>
       <c r="B186" t="n">
-        <v>91356</v>
+        <v>57685</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19992,21 +19987,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20016,10 +20011,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>426172</v>
+        <v>426175</v>
       </c>
       <c r="R186" t="n">
-        <v>7051169</v>
+        <v>7051336</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20052,6 +20047,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20081,7 +20081,7 @@
         <v>128399860</v>
       </c>
       <c r="B187" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>128399891</v>
       </c>
       <c r="B188" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>128399873</v>
       </c>
       <c r="B189" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20384,10 +20384,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399939</v>
+        <v>128399862</v>
       </c>
       <c r="B190" t="n">
-        <v>91378</v>
+        <v>57685</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20395,21 +20395,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20419,10 +20419,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426300</v>
+        <v>426292</v>
       </c>
       <c r="R190" t="n">
-        <v>7051058</v>
+        <v>7050995</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20455,6 +20455,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20481,10 +20486,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399862</v>
+        <v>128399925</v>
       </c>
       <c r="B191" t="n">
-        <v>57673</v>
+        <v>91448</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20492,21 +20497,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20516,10 +20521,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426292</v>
+        <v>426047</v>
       </c>
       <c r="R191" t="n">
-        <v>7050995</v>
+        <v>7051252</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20552,11 +20557,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20583,10 +20583,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399925</v>
+        <v>128399939</v>
       </c>
       <c r="B192" t="n">
-        <v>91356</v>
+        <v>91470</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20594,21 +20594,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20618,10 +20618,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426047</v>
+        <v>426300</v>
       </c>
       <c r="R192" t="n">
-        <v>7051252</v>
+        <v>7051058</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20680,10 +20680,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128399846</v>
+        <v>128509948</v>
       </c>
       <c r="B193" t="n">
-        <v>57673</v>
+        <v>56867</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20691,16 +20691,16 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -20708,20 +20708,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>426847</v>
+        <v>426309</v>
       </c>
       <c r="R193" t="n">
-        <v>7051382</v>
+        <v>7051192</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -20755,7 +20771,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Höstsjungande, hörd på lite avstånd, därav osäkerhet i positionen.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20770,22 +20786,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128399847</v>
+        <v>128399846</v>
       </c>
       <c r="B194" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20820,7 +20836,7 @@
         <v>426847</v>
       </c>
       <c r="R194" t="n">
-        <v>7051384</v>
+        <v>7051382</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20857,7 +20873,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20884,10 +20900,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128399845</v>
+        <v>128399847</v>
       </c>
       <c r="B195" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20919,10 +20935,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>426856</v>
+        <v>426847</v>
       </c>
       <c r="R195" t="n">
-        <v>7051368</v>
+        <v>7051384</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20959,7 +20975,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -20983,6 +20999,108 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>128399845</v>
+      </c>
+      <c r="B196" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Stor-grässlåttsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>426856</v>
+      </c>
+      <c r="R196" t="n">
+        <v>7051368</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128398786</v>
+        <v>128398758</v>
       </c>
       <c r="B2" t="n">
-        <v>75163</v>
+        <v>82942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425776</v>
+        <v>426187</v>
       </c>
       <c r="R2" t="n">
-        <v>7051259</v>
+        <v>7051025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128398759</v>
+        <v>128398722</v>
       </c>
       <c r="B3" t="n">
-        <v>88853</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426187</v>
+        <v>426695</v>
       </c>
       <c r="R3" t="n">
-        <v>7051025</v>
+        <v>7051338</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128398758</v>
+        <v>128398798</v>
       </c>
       <c r="B4" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426187</v>
+        <v>425947</v>
       </c>
       <c r="R4" t="n">
-        <v>7051025</v>
+        <v>7051321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128398722</v>
+        <v>128398786</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>75163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426695</v>
+        <v>425776</v>
       </c>
       <c r="R5" t="n">
-        <v>7051338</v>
+        <v>7051259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,6 +1087,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128398798</v>
+        <v>128398759</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>88853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425947</v>
+        <v>426187</v>
       </c>
       <c r="R6" t="n">
-        <v>7051321</v>
+        <v>7051025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128398762</v>
+        <v>128398790</v>
       </c>
       <c r="B12" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426225</v>
+        <v>425825</v>
       </c>
       <c r="R12" t="n">
-        <v>7051098</v>
+        <v>7051257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398790</v>
+        <v>128398762</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425825</v>
+        <v>426225</v>
       </c>
       <c r="R13" t="n">
-        <v>7051257</v>
+        <v>7051098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,12 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128398740</v>
+        <v>128398811</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>91448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426327</v>
+        <v>426091</v>
       </c>
       <c r="R14" t="n">
-        <v>7051074</v>
+        <v>7051202</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128398811</v>
+        <v>128398740</v>
       </c>
       <c r="B15" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426091</v>
+        <v>426327</v>
       </c>
       <c r="R15" t="n">
-        <v>7051202</v>
+        <v>7051074</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2890,32 +2890,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398771</v>
+        <v>128398773</v>
       </c>
       <c r="B22" t="n">
-        <v>91470</v>
+        <v>75169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426068</v>
+        <v>425978</v>
       </c>
       <c r="R22" t="n">
-        <v>7051189</v>
+        <v>7051231</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3104,10 +3104,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398730</v>
+        <v>128398753</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426382</v>
+        <v>426191</v>
       </c>
       <c r="R24" t="n">
-        <v>7051149</v>
+        <v>7050957</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3195,6 +3195,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3211,32 +3226,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398773</v>
+        <v>128398730</v>
       </c>
       <c r="B25" t="n">
-        <v>75169</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3246,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425978</v>
+        <v>426382</v>
       </c>
       <c r="R25" t="n">
-        <v>7051231</v>
+        <v>7051149</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,7 +3296,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3291,7 +3306,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398753</v>
+        <v>128398771</v>
       </c>
       <c r="B26" t="n">
-        <v>80188</v>
+        <v>91470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3329,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3353,10 +3368,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426191</v>
+        <v>426068</v>
       </c>
       <c r="R26" t="n">
-        <v>7050957</v>
+        <v>7051189</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,7 +3403,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3398,7 +3413,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3409,21 +3424,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3770,32 +3770,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128398819</v>
+        <v>128398788</v>
       </c>
       <c r="B30" t="n">
-        <v>91452</v>
+        <v>75162</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426181</v>
+        <v>425804</v>
       </c>
       <c r="R30" t="n">
-        <v>7051325</v>
+        <v>7051255</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3861,6 +3861,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Glasbjörk</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3877,10 +3882,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398724</v>
+        <v>128398791</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>75163</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,21 +3893,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3917,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426447</v>
+        <v>425847</v>
       </c>
       <c r="R31" t="n">
-        <v>7051254</v>
+        <v>7051261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,7 +3952,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3962,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,6 +3973,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3984,32 +4004,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398788</v>
+        <v>128398819</v>
       </c>
       <c r="B32" t="n">
-        <v>75162</v>
+        <v>91452</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4019,10 +4039,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425804</v>
+        <v>426181</v>
       </c>
       <c r="R32" t="n">
-        <v>7051255</v>
+        <v>7051325</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4054,7 +4074,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4064,7 +4084,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4075,11 +4095,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Glasbjörk</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4096,10 +4111,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398791</v>
+        <v>128398724</v>
       </c>
       <c r="B33" t="n">
-        <v>75163</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,21 +4122,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4131,10 +4146,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425847</v>
+        <v>426447</v>
       </c>
       <c r="R33" t="n">
-        <v>7051261</v>
+        <v>7051254</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4166,7 +4181,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4176,7 +4191,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,21 +4202,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4218,50 +4218,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398741</v>
+        <v>128398801</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>91906</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426298</v>
+        <v>425985</v>
       </c>
       <c r="R34" t="n">
-        <v>7051029</v>
+        <v>7051282</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,12 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4335,32 +4325,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128398801</v>
+        <v>128398755</v>
       </c>
       <c r="B35" t="n">
-        <v>91906</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4370,10 +4360,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>425985</v>
+        <v>426166</v>
       </c>
       <c r="R35" t="n">
-        <v>7051282</v>
+        <v>7050989</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4405,7 +4395,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4415,7 +4405,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4549,7 +4539,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398755</v>
+        <v>128398794</v>
       </c>
       <c r="B37" t="n">
         <v>79083</v>
@@ -4584,10 +4574,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426166</v>
+        <v>425876</v>
       </c>
       <c r="R37" t="n">
-        <v>7050989</v>
+        <v>7051324</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4619,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4629,7 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4656,10 +4646,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128398794</v>
+        <v>128398741</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,34 +4657,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>425876</v>
+        <v>426298</v>
       </c>
       <c r="R38" t="n">
-        <v>7051324</v>
+        <v>7051029</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,7 +4721,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4736,7 +4731,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6286,10 +6286,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128398727</v>
+        <v>128398802</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>91748</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6297,21 +6297,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426516</v>
+        <v>425985</v>
       </c>
       <c r="R53" t="n">
-        <v>7051239</v>
+        <v>7051282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6393,48 +6393,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398804</v>
+        <v>128398734</v>
       </c>
       <c r="B54" t="n">
-        <v>75169</v>
+        <v>92149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6486</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426000</v>
+        <v>426329</v>
       </c>
       <c r="R54" t="n">
-        <v>7051290</v>
+        <v>7051146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6466,7 +6463,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6476,7 +6473,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6484,11 +6481,6 @@
       </c>
       <c r="AE54" t="b">
         <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -6508,10 +6500,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398793</v>
+        <v>128398727</v>
       </c>
       <c r="B55" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6519,39 +6511,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>425908</v>
+        <v>426516</v>
       </c>
       <c r="R55" t="n">
-        <v>7051281</v>
+        <v>7051239</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6583,7 +6570,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6593,12 +6580,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6625,50 +6607,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398822</v>
+        <v>128398804</v>
       </c>
       <c r="B56" t="n">
-        <v>57685</v>
+        <v>75169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426200</v>
+        <v>426000</v>
       </c>
       <c r="R56" t="n">
-        <v>7051338</v>
+        <v>7051290</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6700,7 +6680,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6710,12 +6690,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6723,6 +6698,11 @@
       </c>
       <c r="AE56" t="b">
         <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -6742,7 +6722,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398719</v>
+        <v>128398793</v>
       </c>
       <c r="B57" t="n">
         <v>57685</v>
@@ -6782,10 +6762,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426799</v>
+        <v>425908</v>
       </c>
       <c r="R57" t="n">
-        <v>7051328</v>
+        <v>7051281</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6817,7 +6797,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6827,7 +6807,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6859,45 +6839,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398734</v>
+        <v>128398814</v>
       </c>
       <c r="B58" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426329</v>
+        <v>426097</v>
       </c>
       <c r="R58" t="n">
-        <v>7051146</v>
+        <v>7051199</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6929,7 +6914,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6939,7 +6924,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6966,10 +6956,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398802</v>
+        <v>128398822</v>
       </c>
       <c r="B59" t="n">
-        <v>91748</v>
+        <v>57685</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6977,34 +6967,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>425985</v>
+        <v>426200</v>
       </c>
       <c r="R59" t="n">
-        <v>7051282</v>
+        <v>7051338</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7036,7 +7031,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7046,7 +7041,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7073,7 +7073,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398814</v>
+        <v>128398719</v>
       </c>
       <c r="B60" t="n">
         <v>57685</v>
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426097</v>
+        <v>426799</v>
       </c>
       <c r="R60" t="n">
-        <v>7051199</v>
+        <v>7051328</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7190,10 +7190,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398769</v>
+        <v>128398783</v>
       </c>
       <c r="B61" t="n">
-        <v>91452</v>
+        <v>79083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426135</v>
+        <v>425733</v>
       </c>
       <c r="R61" t="n">
-        <v>7051154</v>
+        <v>7051205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7297,32 +7297,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398783</v>
+        <v>128398726</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>75162</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>425733</v>
+        <v>426522</v>
       </c>
       <c r="R62" t="n">
-        <v>7051205</v>
+        <v>7051242</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7388,6 +7388,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7404,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128398745</v>
+        <v>128398769</v>
       </c>
       <c r="B63" t="n">
-        <v>57685</v>
+        <v>91452</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7415,39 +7430,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426353</v>
+        <v>426135</v>
       </c>
       <c r="R63" t="n">
-        <v>7050910</v>
+        <v>7051154</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7479,7 +7489,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7489,12 +7499,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7521,7 +7526,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128398781</v>
+        <v>128398745</v>
       </c>
       <c r="B64" t="n">
         <v>57685</v>
@@ -7561,10 +7566,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>425754</v>
+        <v>426353</v>
       </c>
       <c r="R64" t="n">
-        <v>7051180</v>
+        <v>7050910</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7596,7 +7601,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7606,7 +7611,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7638,45 +7643,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128398726</v>
+        <v>128398781</v>
       </c>
       <c r="B65" t="n">
-        <v>75162</v>
+        <v>57685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426522</v>
+        <v>425754</v>
       </c>
       <c r="R65" t="n">
-        <v>7051242</v>
+        <v>7051180</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7708,7 +7718,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7718,7 +7728,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7729,21 +7744,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7760,10 +7760,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128398796</v>
+        <v>128398763</v>
       </c>
       <c r="B66" t="n">
-        <v>78060</v>
+        <v>79083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7771,21 +7771,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>425919</v>
+        <v>426227</v>
       </c>
       <c r="R66" t="n">
-        <v>7051350</v>
+        <v>7051105</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7867,10 +7867,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128398763</v>
+        <v>128398796</v>
       </c>
       <c r="B67" t="n">
-        <v>79083</v>
+        <v>78060</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7878,21 +7878,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>426227</v>
+        <v>425919</v>
       </c>
       <c r="R67" t="n">
-        <v>7051105</v>
+        <v>7051350</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7974,32 +7974,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128398733</v>
+        <v>128398760</v>
       </c>
       <c r="B68" t="n">
-        <v>92149</v>
+        <v>82942</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426361</v>
+        <v>426232</v>
       </c>
       <c r="R68" t="n">
-        <v>7051151</v>
+        <v>7051062</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8081,32 +8081,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128398760</v>
+        <v>128398733</v>
       </c>
       <c r="B69" t="n">
-        <v>82942</v>
+        <v>92149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426232</v>
+        <v>426361</v>
       </c>
       <c r="R69" t="n">
-        <v>7051062</v>
+        <v>7051151</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8733,10 +8733,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128398789</v>
+        <v>128398754</v>
       </c>
       <c r="B75" t="n">
-        <v>57685</v>
+        <v>80189</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8744,39 +8744,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>425804</v>
+        <v>426191</v>
       </c>
       <c r="R75" t="n">
-        <v>7051258</v>
+        <v>7050957</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8808,7 +8803,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8818,12 +8813,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8834,6 +8824,21 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8850,27 +8855,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128398815</v>
+        <v>128398772</v>
       </c>
       <c r="B76" t="n">
-        <v>91859</v>
+        <v>92149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6040186</v>
+        <v>3298</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8880,10 +8890,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426114</v>
+        <v>426065</v>
       </c>
       <c r="R76" t="n">
-        <v>7051205</v>
+        <v>7051192</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8915,7 +8925,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8925,7 +8935,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8952,45 +8962,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128398772</v>
+        <v>128398789</v>
       </c>
       <c r="B77" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426065</v>
+        <v>425804</v>
       </c>
       <c r="R77" t="n">
-        <v>7051192</v>
+        <v>7051258</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9022,7 +9037,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9032,7 +9047,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9059,10 +9079,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128398754</v>
+        <v>128398815</v>
       </c>
       <c r="B78" t="n">
-        <v>80189</v>
+        <v>91859</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9070,21 +9090,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9094,10 +9109,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>426191</v>
+        <v>426114</v>
       </c>
       <c r="R78" t="n">
-        <v>7050957</v>
+        <v>7051205</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9129,7 +9144,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9139,7 +9154,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9150,21 +9165,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9181,10 +9181,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128398723</v>
+        <v>128398813</v>
       </c>
       <c r="B79" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9192,21 +9192,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426515</v>
+        <v>426097</v>
       </c>
       <c r="R79" t="n">
-        <v>7051308</v>
+        <v>7051199</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9288,10 +9288,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128398751</v>
+        <v>128398765</v>
       </c>
       <c r="B80" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426239</v>
+        <v>426186</v>
       </c>
       <c r="R80" t="n">
-        <v>7050935</v>
+        <v>7051125</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9395,10 +9395,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128398780</v>
+        <v>128398723</v>
       </c>
       <c r="B81" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9406,39 +9406,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>425756</v>
+        <v>426515</v>
       </c>
       <c r="R81" t="n">
-        <v>7051171</v>
+        <v>7051308</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9470,7 +9465,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9480,12 +9475,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9512,10 +9502,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128398784</v>
+        <v>128398751</v>
       </c>
       <c r="B82" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9523,39 +9513,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425712</v>
+        <v>426239</v>
       </c>
       <c r="R82" t="n">
-        <v>7051206</v>
+        <v>7050935</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9587,7 +9572,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9597,12 +9582,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9629,10 +9609,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128398813</v>
+        <v>128398780</v>
       </c>
       <c r="B83" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9640,34 +9620,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>426097</v>
+        <v>425756</v>
       </c>
       <c r="R83" t="n">
-        <v>7051199</v>
+        <v>7051171</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9699,7 +9684,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9709,7 +9694,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9736,10 +9726,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128398765</v>
+        <v>128398784</v>
       </c>
       <c r="B84" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9747,34 +9737,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>426186</v>
+        <v>425712</v>
       </c>
       <c r="R84" t="n">
-        <v>7051125</v>
+        <v>7051206</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9806,7 +9801,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9816,7 +9811,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128399888</v>
+        <v>128399916</v>
       </c>
       <c r="B89" t="n">
         <v>57685</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>425774</v>
+        <v>426279</v>
       </c>
       <c r="R89" t="n">
-        <v>7051220</v>
+        <v>7051408</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128399916</v>
+        <v>128399875</v>
       </c>
       <c r="B90" t="n">
         <v>57685</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>426279</v>
+        <v>426207</v>
       </c>
       <c r="R90" t="n">
-        <v>7051408</v>
+        <v>7051009</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10475,7 +10475,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399875</v>
+        <v>128399888</v>
       </c>
       <c r="B91" t="n">
         <v>57685</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>426207</v>
+        <v>425774</v>
       </c>
       <c r="R91" t="n">
-        <v>7051009</v>
+        <v>7051220</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399949</v>
+        <v>128399849</v>
       </c>
       <c r="B93" t="n">
-        <v>88853</v>
+        <v>57685</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426768</v>
+        <v>426803</v>
       </c>
       <c r="R93" t="n">
-        <v>7051367</v>
+        <v>7051353</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10750,6 +10750,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10776,10 +10781,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399940</v>
+        <v>128399949</v>
       </c>
       <c r="B94" t="n">
-        <v>91470</v>
+        <v>88853</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10787,21 +10792,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10811,10 +10816,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426338</v>
+        <v>426768</v>
       </c>
       <c r="R94" t="n">
-        <v>7050977</v>
+        <v>7051367</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10873,10 +10878,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399849</v>
+        <v>128399940</v>
       </c>
       <c r="B95" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10884,21 +10889,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10908,10 +10913,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426803</v>
+        <v>426338</v>
       </c>
       <c r="R95" t="n">
-        <v>7051353</v>
+        <v>7050977</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10944,11 +10949,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10975,32 +10975,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399898</v>
+        <v>128399832</v>
       </c>
       <c r="B96" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425894</v>
+        <v>426401</v>
       </c>
       <c r="R96" t="n">
-        <v>7051256</v>
+        <v>7051237</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11046,11 +11046,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11077,32 +11072,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399886</v>
+        <v>128399836</v>
       </c>
       <c r="B97" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11112,10 +11107,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425743</v>
+        <v>426093</v>
       </c>
       <c r="R97" t="n">
-        <v>7051241</v>
+        <v>7051184</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11148,11 +11143,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11179,32 +11169,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399832</v>
+        <v>128399898</v>
       </c>
       <c r="B98" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11214,10 +11204,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426401</v>
+        <v>425894</v>
       </c>
       <c r="R98" t="n">
-        <v>7051237</v>
+        <v>7051256</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11250,6 +11240,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11276,32 +11271,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399836</v>
+        <v>128399886</v>
       </c>
       <c r="B99" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11311,10 +11306,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>426093</v>
+        <v>425743</v>
       </c>
       <c r="R99" t="n">
-        <v>7051184</v>
+        <v>7051241</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11347,6 +11342,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11664,10 +11664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399941</v>
+        <v>128399907</v>
       </c>
       <c r="B103" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>425987</v>
+        <v>426064</v>
       </c>
       <c r="R103" t="n">
-        <v>7051259</v>
+        <v>7051249</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11735,6 +11735,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11761,7 +11766,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128399907</v>
+        <v>128399889</v>
       </c>
       <c r="B104" t="n">
         <v>57685</v>
@@ -11796,10 +11801,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>426064</v>
+        <v>425774</v>
       </c>
       <c r="R104" t="n">
-        <v>7051249</v>
+        <v>7051222</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11836,7 +11841,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11863,10 +11868,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128399889</v>
+        <v>128399941</v>
       </c>
       <c r="B105" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11874,21 +11879,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11898,10 +11903,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425774</v>
+        <v>425987</v>
       </c>
       <c r="R105" t="n">
-        <v>7051222</v>
+        <v>7051259</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11934,11 +11939,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11965,7 +11965,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399903</v>
+        <v>128399881</v>
       </c>
       <c r="B106" t="n">
         <v>57685</v>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>425972</v>
+        <v>425942</v>
       </c>
       <c r="R106" t="n">
-        <v>7051285</v>
+        <v>7051274</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12067,32 +12067,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399863</v>
+        <v>128399834</v>
       </c>
       <c r="B107" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12102,10 +12102,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426347</v>
+        <v>426228</v>
       </c>
       <c r="R107" t="n">
-        <v>7050960</v>
+        <v>7050978</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12138,11 +12138,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12169,10 +12164,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399868</v>
+        <v>128399945</v>
       </c>
       <c r="B108" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12180,21 +12175,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12204,10 +12199,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>426274</v>
+        <v>426062</v>
       </c>
       <c r="R108" t="n">
-        <v>7050964</v>
+        <v>7051271</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12240,11 +12235,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12271,7 +12261,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399881</v>
+        <v>128399903</v>
       </c>
       <c r="B109" t="n">
         <v>57685</v>
@@ -12306,10 +12296,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>425942</v>
+        <v>425972</v>
       </c>
       <c r="R109" t="n">
-        <v>7051274</v>
+        <v>7051285</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12346,7 +12336,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12373,32 +12363,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399834</v>
+        <v>128399863</v>
       </c>
       <c r="B110" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12408,10 +12398,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>426228</v>
+        <v>426347</v>
       </c>
       <c r="R110" t="n">
-        <v>7050978</v>
+        <v>7050960</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12444,6 +12434,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12470,10 +12465,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128399945</v>
+        <v>128399868</v>
       </c>
       <c r="B111" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12481,21 +12476,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12505,10 +12500,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>426062</v>
+        <v>426274</v>
       </c>
       <c r="R111" t="n">
-        <v>7051271</v>
+        <v>7050964</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12541,6 +12536,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12567,32 +12567,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128399935</v>
+        <v>128399833</v>
       </c>
       <c r="B112" t="n">
-        <v>91466</v>
+        <v>92149</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12602,10 +12602,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>425974</v>
+        <v>426263</v>
       </c>
       <c r="R112" t="n">
-        <v>7051249</v>
+        <v>7051287</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12664,7 +12664,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128399833</v>
+        <v>128399831</v>
       </c>
       <c r="B113" t="n">
         <v>92149</v>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>426263</v>
+        <v>426425</v>
       </c>
       <c r="R113" t="n">
-        <v>7051287</v>
+        <v>7051289</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12761,32 +12761,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128399831</v>
+        <v>128399904</v>
       </c>
       <c r="B114" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426425</v>
+        <v>426012</v>
       </c>
       <c r="R114" t="n">
-        <v>7051289</v>
+        <v>7051306</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12832,6 +12832,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12858,7 +12863,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399904</v>
+        <v>128399870</v>
       </c>
       <c r="B115" t="n">
         <v>57685</v>
@@ -12893,10 +12898,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426012</v>
+        <v>426156</v>
       </c>
       <c r="R115" t="n">
-        <v>7051306</v>
+        <v>7050998</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12933,7 +12938,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12960,10 +12965,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399870</v>
+        <v>128399935</v>
       </c>
       <c r="B116" t="n">
-        <v>57685</v>
+        <v>91466</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12971,21 +12976,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12995,10 +13000,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426156</v>
+        <v>425974</v>
       </c>
       <c r="R116" t="n">
-        <v>7050998</v>
+        <v>7051249</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13031,11 +13036,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13159,32 +13159,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399928</v>
+        <v>128399838</v>
       </c>
       <c r="B118" t="n">
-        <v>91466</v>
+        <v>92149</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426319</v>
+        <v>425752</v>
       </c>
       <c r="R118" t="n">
-        <v>7051238</v>
+        <v>7051219</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13672,7 +13672,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399897</v>
+        <v>128399902</v>
       </c>
       <c r="B123" t="n">
         <v>57685</v>
@@ -13707,10 +13707,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425892</v>
+        <v>425902</v>
       </c>
       <c r="R123" t="n">
-        <v>7051251</v>
+        <v>7051312</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13774,7 +13774,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128399902</v>
+        <v>128399871</v>
       </c>
       <c r="B124" t="n">
         <v>57685</v>
@@ -13809,10 +13809,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>425902</v>
+        <v>426154</v>
       </c>
       <c r="R124" t="n">
-        <v>7051312</v>
+        <v>7050994</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13876,10 +13876,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128399871</v>
+        <v>128399928</v>
       </c>
       <c r="B125" t="n">
-        <v>57685</v>
+        <v>91466</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13887,21 +13887,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13911,10 +13911,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>426154</v>
+        <v>426319</v>
       </c>
       <c r="R125" t="n">
-        <v>7050994</v>
+        <v>7051238</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13947,11 +13947,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13978,32 +13973,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399838</v>
+        <v>128399897</v>
       </c>
       <c r="B126" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14013,10 +14008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425752</v>
+        <v>425892</v>
       </c>
       <c r="R126" t="n">
-        <v>7051219</v>
+        <v>7051251</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14049,6 +14044,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14075,10 +14075,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128399901</v>
+        <v>128399948</v>
       </c>
       <c r="B127" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425880</v>
+        <v>426395</v>
       </c>
       <c r="R127" t="n">
-        <v>7051304</v>
+        <v>7051398</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14177,7 +14177,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128399878</v>
+        <v>128399901</v>
       </c>
       <c r="B128" t="n">
         <v>57685</v>
@@ -14212,10 +14212,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>426047</v>
+        <v>425880</v>
       </c>
       <c r="R128" t="n">
-        <v>7051186</v>
+        <v>7051304</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14279,7 +14279,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399876</v>
+        <v>128399878</v>
       </c>
       <c r="B129" t="n">
         <v>57685</v>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426244</v>
+        <v>426047</v>
       </c>
       <c r="R129" t="n">
-        <v>7051052</v>
+        <v>7051186</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14381,7 +14381,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128399905</v>
+        <v>128399876</v>
       </c>
       <c r="B130" t="n">
         <v>57685</v>
@@ -14416,10 +14416,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426029</v>
+        <v>426244</v>
       </c>
       <c r="R130" t="n">
-        <v>7051287</v>
+        <v>7051052</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14483,10 +14483,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399920</v>
+        <v>128399905</v>
       </c>
       <c r="B131" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14494,21 +14494,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14518,10 +14518,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426277</v>
+        <v>426029</v>
       </c>
       <c r="R131" t="n">
-        <v>7051183</v>
+        <v>7051287</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14554,6 +14554,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14580,10 +14585,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399942</v>
+        <v>128399920</v>
       </c>
       <c r="B132" t="n">
-        <v>91470</v>
+        <v>91448</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14591,21 +14596,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14615,10 +14620,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>425904</v>
+        <v>426277</v>
       </c>
       <c r="R132" t="n">
-        <v>7051248</v>
+        <v>7051183</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14677,10 +14682,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399948</v>
+        <v>128399942</v>
       </c>
       <c r="B133" t="n">
-        <v>79083</v>
+        <v>91470</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14688,21 +14693,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14712,10 +14717,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426395</v>
+        <v>425904</v>
       </c>
       <c r="R133" t="n">
-        <v>7051398</v>
+        <v>7051248</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14748,11 +14753,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -17187,10 +17187,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128399827</v>
+        <v>128399856</v>
       </c>
       <c r="B158" t="n">
-        <v>91452</v>
+        <v>57685</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17198,34 +17198,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Stor-grässjön, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>426813</v>
+        <v>426646</v>
       </c>
       <c r="R158" t="n">
-        <v>7051371</v>
+        <v>7051365</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17258,6 +17258,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17284,32 +17289,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128399839</v>
+        <v>128399909</v>
       </c>
       <c r="B159" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17319,10 +17324,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>425971</v>
+        <v>426175</v>
       </c>
       <c r="R159" t="n">
-        <v>7051280</v>
+        <v>7051323</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17355,6 +17360,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17381,32 +17391,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128399856</v>
+        <v>128399839</v>
       </c>
       <c r="B160" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17416,10 +17426,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>426646</v>
+        <v>425971</v>
       </c>
       <c r="R160" t="n">
-        <v>7051365</v>
+        <v>7051280</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17452,11 +17462,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17483,10 +17488,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128399909</v>
+        <v>128399827</v>
       </c>
       <c r="B161" t="n">
-        <v>57685</v>
+        <v>91452</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17494,34 +17499,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>426175</v>
+        <v>426813</v>
       </c>
       <c r="R161" t="n">
-        <v>7051323</v>
+        <v>7051371</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17554,11 +17559,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18575,32 +18575,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128399938</v>
+        <v>128399835</v>
       </c>
       <c r="B172" t="n">
-        <v>91470</v>
+        <v>92149</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18610,10 +18610,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>426205</v>
+        <v>426132</v>
       </c>
       <c r="R172" t="n">
-        <v>7051276</v>
+        <v>7051150</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18672,10 +18672,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128399884</v>
+        <v>128399938</v>
       </c>
       <c r="B173" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18683,21 +18683,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18707,10 +18707,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>425770</v>
+        <v>426205</v>
       </c>
       <c r="R173" t="n">
-        <v>7051183</v>
+        <v>7051276</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18743,11 +18743,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18774,7 +18769,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128399893</v>
+        <v>128399884</v>
       </c>
       <c r="B174" t="n">
         <v>57685</v>
@@ -18809,10 +18804,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>425861</v>
+        <v>425770</v>
       </c>
       <c r="R174" t="n">
-        <v>7051227</v>
+        <v>7051183</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18849,7 +18844,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18876,7 +18871,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128399887</v>
+        <v>128399893</v>
       </c>
       <c r="B175" t="n">
         <v>57685</v>
@@ -18911,10 +18906,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425756</v>
+        <v>425861</v>
       </c>
       <c r="R175" t="n">
-        <v>7051229</v>
+        <v>7051227</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18951,7 +18946,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18978,7 +18973,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128399882</v>
+        <v>128399887</v>
       </c>
       <c r="B176" t="n">
         <v>57685</v>
@@ -19013,10 +19008,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425864</v>
+        <v>425756</v>
       </c>
       <c r="R176" t="n">
-        <v>7051211</v>
+        <v>7051229</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19053,7 +19048,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19080,7 +19075,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128399854</v>
+        <v>128399882</v>
       </c>
       <c r="B177" t="n">
         <v>57685</v>
@@ -19109,24 +19104,16 @@
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>426733</v>
+        <v>425864</v>
       </c>
       <c r="R177" t="n">
-        <v>7051347</v>
+        <v>7051211</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19163,7 +19150,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19190,45 +19177,53 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128399835</v>
+        <v>128399854</v>
       </c>
       <c r="B178" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>426132</v>
+        <v>426733</v>
       </c>
       <c r="R178" t="n">
-        <v>7051150</v>
+        <v>7051347</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19261,6 +19256,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19287,10 +19287,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399944</v>
+        <v>128399950</v>
       </c>
       <c r="B179" t="n">
-        <v>91470</v>
+        <v>88853</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19298,21 +19298,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>425889</v>
+        <v>426303</v>
       </c>
       <c r="R179" t="n">
-        <v>7051300</v>
+        <v>7050905</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19384,7 +19384,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128399950</v>
+        <v>128399951</v>
       </c>
       <c r="B180" t="n">
         <v>88853</v>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>426303</v>
+        <v>426062</v>
       </c>
       <c r="R180" t="n">
-        <v>7050905</v>
+        <v>7051265</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19481,10 +19481,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399951</v>
+        <v>128399932</v>
       </c>
       <c r="B181" t="n">
-        <v>88853</v>
+        <v>91466</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19492,21 +19492,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19516,10 +19516,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>426062</v>
+        <v>426231</v>
       </c>
       <c r="R181" t="n">
-        <v>7051265</v>
+        <v>7051130</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19578,10 +19578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128399932</v>
+        <v>128399923</v>
       </c>
       <c r="B182" t="n">
-        <v>91466</v>
+        <v>91448</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19589,21 +19589,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>426231</v>
+        <v>426172</v>
       </c>
       <c r="R182" t="n">
-        <v>7051130</v>
+        <v>7051169</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19675,10 +19675,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128399923</v>
+        <v>128399944</v>
       </c>
       <c r="B183" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19686,21 +19686,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19710,10 +19710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>426172</v>
+        <v>425889</v>
       </c>
       <c r="R183" t="n">
-        <v>7051169</v>
+        <v>7051300</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399873</v>
+        <v>128399925</v>
       </c>
       <c r="B189" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426193</v>
+        <v>426047</v>
       </c>
       <c r="R189" t="n">
-        <v>7050977</v>
+        <v>7051252</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20353,11 +20353,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20384,10 +20379,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399862</v>
+        <v>128399939</v>
       </c>
       <c r="B190" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20395,21 +20390,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20419,10 +20414,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426292</v>
+        <v>426300</v>
       </c>
       <c r="R190" t="n">
-        <v>7050995</v>
+        <v>7051058</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20455,11 +20450,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20486,10 +20476,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B191" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20497,21 +20487,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20521,10 +20511,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R191" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20557,6 +20547,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20583,10 +20578,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399939</v>
+        <v>128399862</v>
       </c>
       <c r="B192" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20594,21 +20589,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20618,10 +20613,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426300</v>
+        <v>426292</v>
       </c>
       <c r="R192" t="n">
-        <v>7051058</v>
+        <v>7050995</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20654,6 +20649,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128398746</v>
+        <v>128398774</v>
       </c>
       <c r="B8" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1353,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426300</v>
+        <v>425970</v>
       </c>
       <c r="R8" t="n">
-        <v>7050902</v>
+        <v>7051235</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128398768</v>
+        <v>128398746</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,39 +1470,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426158</v>
+        <v>426300</v>
       </c>
       <c r="R9" t="n">
-        <v>7051146</v>
+        <v>7050902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,12 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128398774</v>
+        <v>128398768</v>
       </c>
       <c r="B10" t="n">
         <v>57685</v>
@@ -1597,7 +1597,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425970</v>
+        <v>426158</v>
       </c>
       <c r="R10" t="n">
-        <v>7051235</v>
+        <v>7051146</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128398790</v>
+        <v>128398762</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425825</v>
+        <v>426225</v>
       </c>
       <c r="R12" t="n">
-        <v>7051257</v>
+        <v>7051098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,12 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398762</v>
+        <v>128398790</v>
       </c>
       <c r="B13" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426225</v>
+        <v>425825</v>
       </c>
       <c r="R13" t="n">
-        <v>7051098</v>
+        <v>7051257</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2569,32 +2569,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128398770</v>
+        <v>128398771</v>
       </c>
       <c r="B19" t="n">
-        <v>91906</v>
+        <v>91470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426115</v>
+        <v>426068</v>
       </c>
       <c r="R19" t="n">
-        <v>7051178</v>
+        <v>7051189</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,32 +2676,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398803</v>
+        <v>128398729</v>
       </c>
       <c r="B20" t="n">
-        <v>92149</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425994</v>
+        <v>426468</v>
       </c>
       <c r="R20" t="n">
-        <v>7051287</v>
+        <v>7051179</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,32 +2783,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398718</v>
+        <v>128398752</v>
       </c>
       <c r="B21" t="n">
-        <v>92754</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426807</v>
+        <v>426206</v>
       </c>
       <c r="R21" t="n">
-        <v>7051311</v>
+        <v>7050935</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,48 +2890,57 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398773</v>
+        <v>128398805</v>
       </c>
       <c r="B22" t="n">
-        <v>75169</v>
+        <v>57845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6486</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425978</v>
+        <v>425999</v>
       </c>
       <c r="R22" t="n">
-        <v>7051231</v>
+        <v>7051258</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2960,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,32 +3006,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398821</v>
+        <v>128398770</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>91906</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3032,10 +3041,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426200</v>
+        <v>426115</v>
       </c>
       <c r="R23" t="n">
-        <v>7051338</v>
+        <v>7051178</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,7 +3076,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3077,7 +3086,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3104,32 +3113,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398753</v>
+        <v>128398803</v>
       </c>
       <c r="B24" t="n">
-        <v>80188</v>
+        <v>92149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3139,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426191</v>
+        <v>425994</v>
       </c>
       <c r="R24" t="n">
-        <v>7050957</v>
+        <v>7051287</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,7 +3183,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3184,7 +3193,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3195,21 +3204,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3226,32 +3220,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398730</v>
+        <v>128398718</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>92754</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3261,10 +3255,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426382</v>
+        <v>426807</v>
       </c>
       <c r="R25" t="n">
-        <v>7051149</v>
+        <v>7051311</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3296,7 +3290,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3306,7 +3300,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,32 +3327,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398771</v>
+        <v>128398773</v>
       </c>
       <c r="B26" t="n">
-        <v>91470</v>
+        <v>75169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426068</v>
+        <v>425978</v>
       </c>
       <c r="R26" t="n">
-        <v>7051189</v>
+        <v>7051231</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3403,7 +3397,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3413,7 +3407,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3440,7 +3434,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398729</v>
+        <v>128398821</v>
       </c>
       <c r="B27" t="n">
         <v>79083</v>
@@ -3475,10 +3469,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426468</v>
+        <v>426200</v>
       </c>
       <c r="R27" t="n">
-        <v>7051179</v>
+        <v>7051338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3510,7 +3504,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3520,7 +3514,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,10 +3541,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398752</v>
+        <v>128398753</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>80188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3558,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3582,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426206</v>
+        <v>426191</v>
       </c>
       <c r="R28" t="n">
-        <v>7050935</v>
+        <v>7050957</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,7 +3611,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3627,7 +3621,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,6 +3632,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3654,10 +3663,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128398805</v>
+        <v>128398730</v>
       </c>
       <c r="B29" t="n">
-        <v>57845</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,46 +3674,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425999</v>
+        <v>426382</v>
       </c>
       <c r="R29" t="n">
-        <v>7051258</v>
+        <v>7051149</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4218,32 +4218,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398801</v>
+        <v>128398755</v>
       </c>
       <c r="B34" t="n">
-        <v>91906</v>
+        <v>79083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425985</v>
+        <v>426166</v>
       </c>
       <c r="R34" t="n">
-        <v>7051282</v>
+        <v>7050989</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,7 +4325,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128398755</v>
+        <v>128398738</v>
       </c>
       <c r="B35" t="n">
         <v>79083</v>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426166</v>
+        <v>426341</v>
       </c>
       <c r="R35" t="n">
-        <v>7050989</v>
+        <v>7051103</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,7 +4432,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128398738</v>
+        <v>128398794</v>
       </c>
       <c r="B36" t="n">
         <v>79083</v>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426341</v>
+        <v>425876</v>
       </c>
       <c r="R36" t="n">
-        <v>7051103</v>
+        <v>7051324</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4539,10 +4539,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398794</v>
+        <v>128398741</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4550,34 +4550,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425876</v>
+        <v>426298</v>
       </c>
       <c r="R37" t="n">
-        <v>7051324</v>
+        <v>7051029</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4609,7 +4614,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4619,7 +4624,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4646,50 +4656,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128398741</v>
+        <v>128398801</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>91906</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426298</v>
+        <v>425985</v>
       </c>
       <c r="R38" t="n">
-        <v>7051029</v>
+        <v>7051282</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4721,7 +4726,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4731,12 +4736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5084,32 +5084,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128398736</v>
+        <v>128398787</v>
       </c>
       <c r="B42" t="n">
-        <v>92149</v>
+        <v>75163</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426352</v>
+        <v>425795</v>
       </c>
       <c r="R42" t="n">
-        <v>7051151</v>
+        <v>7051251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398787</v>
+        <v>128398749</v>
       </c>
       <c r="B43" t="n">
-        <v>75163</v>
+        <v>86766</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>427</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425795</v>
+        <v>426252</v>
       </c>
       <c r="R43" t="n">
-        <v>7051251</v>
+        <v>7050919</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5271,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5298,10 +5303,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128398749</v>
+        <v>128398800</v>
       </c>
       <c r="B44" t="n">
-        <v>86766</v>
+        <v>91466</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,21 +5314,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>427</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5338,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426252</v>
+        <v>425985</v>
       </c>
       <c r="R44" t="n">
-        <v>7050919</v>
+        <v>7051282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5368,7 +5373,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5378,12 +5383,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5410,32 +5410,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128398800</v>
+        <v>128398736</v>
       </c>
       <c r="B45" t="n">
-        <v>91466</v>
+        <v>92149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425985</v>
+        <v>426352</v>
       </c>
       <c r="R45" t="n">
-        <v>7051282</v>
+        <v>7051151</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5624,10 +5624,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398797</v>
+        <v>128398807</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,34 +5635,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425919</v>
+        <v>426011</v>
       </c>
       <c r="R47" t="n">
-        <v>7051350</v>
+        <v>7051282</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5694,7 +5699,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5704,7 +5709,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5731,10 +5741,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128398812</v>
+        <v>128398721</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5742,34 +5752,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426097</v>
+        <v>426773</v>
       </c>
       <c r="R48" t="n">
-        <v>7051199</v>
+        <v>7051349</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5801,7 +5816,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5811,7 +5826,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5838,7 +5858,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128398725</v>
+        <v>128398797</v>
       </c>
       <c r="B49" t="n">
         <v>79083</v>
@@ -5873,10 +5893,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426492</v>
+        <v>425919</v>
       </c>
       <c r="R49" t="n">
-        <v>7051269</v>
+        <v>7051350</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5908,7 +5928,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5918,7 +5938,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5945,10 +5965,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128398807</v>
+        <v>128398812</v>
       </c>
       <c r="B50" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5956,39 +5976,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426011</v>
+        <v>426097</v>
       </c>
       <c r="R50" t="n">
-        <v>7051282</v>
+        <v>7051199</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6020,7 +6035,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6030,12 +6045,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6062,10 +6072,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128398721</v>
+        <v>128398725</v>
       </c>
       <c r="B51" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6073,39 +6083,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426773</v>
+        <v>426492</v>
       </c>
       <c r="R51" t="n">
-        <v>7051349</v>
+        <v>7051269</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6137,7 +6142,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6147,12 +6152,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7190,10 +7190,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398783</v>
+        <v>128398769</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>425733</v>
+        <v>426135</v>
       </c>
       <c r="R61" t="n">
-        <v>7051205</v>
+        <v>7051154</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7297,32 +7297,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398726</v>
+        <v>128398783</v>
       </c>
       <c r="B62" t="n">
-        <v>75162</v>
+        <v>79083</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426522</v>
+        <v>425733</v>
       </c>
       <c r="R62" t="n">
-        <v>7051242</v>
+        <v>7051205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7388,21 +7388,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7419,10 +7404,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128398769</v>
+        <v>128398745</v>
       </c>
       <c r="B63" t="n">
-        <v>91452</v>
+        <v>57685</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,34 +7415,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426135</v>
+        <v>426353</v>
       </c>
       <c r="R63" t="n">
-        <v>7051154</v>
+        <v>7050910</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7489,7 +7479,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7499,7 +7489,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7526,7 +7521,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128398745</v>
+        <v>128398781</v>
       </c>
       <c r="B64" t="n">
         <v>57685</v>
@@ -7566,10 +7561,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>426353</v>
+        <v>425754</v>
       </c>
       <c r="R64" t="n">
-        <v>7050910</v>
+        <v>7051180</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7601,7 +7596,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7611,7 +7606,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7643,50 +7638,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128398781</v>
+        <v>128398726</v>
       </c>
       <c r="B65" t="n">
-        <v>57685</v>
+        <v>75162</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>425754</v>
+        <v>426522</v>
       </c>
       <c r="R65" t="n">
-        <v>7051180</v>
+        <v>7051242</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7718,7 +7708,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7728,12 +7718,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7744,6 +7729,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128398720</v>
+        <v>128398779</v>
       </c>
       <c r="B73" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8520,34 +8520,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426773</v>
+        <v>425818</v>
       </c>
       <c r="R73" t="n">
-        <v>7051341</v>
+        <v>7051169</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8579,7 +8584,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8589,7 +8594,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8616,10 +8626,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128398779</v>
+        <v>128398720</v>
       </c>
       <c r="B74" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8627,39 +8637,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>425818</v>
+        <v>426773</v>
       </c>
       <c r="R74" t="n">
-        <v>7051169</v>
+        <v>7051341</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8691,7 +8696,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8701,12 +8706,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9395,10 +9395,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128398723</v>
+        <v>128398780</v>
       </c>
       <c r="B81" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9406,34 +9406,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>426515</v>
+        <v>425756</v>
       </c>
       <c r="R81" t="n">
-        <v>7051308</v>
+        <v>7051171</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9465,7 +9470,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9475,7 +9480,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9502,10 +9512,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128398751</v>
+        <v>128398784</v>
       </c>
       <c r="B82" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9513,34 +9523,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426239</v>
+        <v>425712</v>
       </c>
       <c r="R82" t="n">
-        <v>7050935</v>
+        <v>7051206</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9572,7 +9587,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9582,7 +9597,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9609,10 +9629,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128398780</v>
+        <v>128398723</v>
       </c>
       <c r="B83" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9620,39 +9640,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425756</v>
+        <v>426515</v>
       </c>
       <c r="R83" t="n">
-        <v>7051171</v>
+        <v>7051308</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9684,7 +9699,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9694,12 +9709,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9726,10 +9736,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128398784</v>
+        <v>128398751</v>
       </c>
       <c r="B84" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9737,39 +9747,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>425712</v>
+        <v>426239</v>
       </c>
       <c r="R84" t="n">
-        <v>7051206</v>
+        <v>7050935</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9801,7 +9806,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9811,12 +9816,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128399916</v>
+        <v>128399875</v>
       </c>
       <c r="B89" t="n">
         <v>57685</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>426279</v>
+        <v>426207</v>
       </c>
       <c r="R89" t="n">
-        <v>7051408</v>
+        <v>7051009</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128399875</v>
+        <v>128399888</v>
       </c>
       <c r="B90" t="n">
         <v>57685</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>426207</v>
+        <v>425774</v>
       </c>
       <c r="R90" t="n">
-        <v>7051009</v>
+        <v>7051220</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10475,7 +10475,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399888</v>
+        <v>128399916</v>
       </c>
       <c r="B91" t="n">
         <v>57685</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>425774</v>
+        <v>426279</v>
       </c>
       <c r="R91" t="n">
-        <v>7051220</v>
+        <v>7051408</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399849</v>
+        <v>128399949</v>
       </c>
       <c r="B93" t="n">
-        <v>57685</v>
+        <v>88853</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426803</v>
+        <v>426768</v>
       </c>
       <c r="R93" t="n">
-        <v>7051353</v>
+        <v>7051367</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10750,11 +10750,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10781,10 +10776,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399949</v>
+        <v>128399940</v>
       </c>
       <c r="B94" t="n">
-        <v>88853</v>
+        <v>91470</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10792,21 +10787,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10816,10 +10811,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426768</v>
+        <v>426338</v>
       </c>
       <c r="R94" t="n">
-        <v>7051367</v>
+        <v>7050977</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10878,10 +10873,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399940</v>
+        <v>128399849</v>
       </c>
       <c r="B95" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10889,21 +10884,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10913,10 +10908,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426338</v>
+        <v>426803</v>
       </c>
       <c r="R95" t="n">
-        <v>7050977</v>
+        <v>7051353</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10949,6 +10944,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10975,32 +10975,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399832</v>
+        <v>128399898</v>
       </c>
       <c r="B96" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426401</v>
+        <v>425894</v>
       </c>
       <c r="R96" t="n">
-        <v>7051237</v>
+        <v>7051256</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11046,6 +11046,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11072,7 +11077,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399836</v>
+        <v>128399832</v>
       </c>
       <c r="B97" t="n">
         <v>92149</v>
@@ -11107,10 +11112,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426093</v>
+        <v>426401</v>
       </c>
       <c r="R97" t="n">
-        <v>7051184</v>
+        <v>7051237</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11169,32 +11174,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399898</v>
+        <v>128399836</v>
       </c>
       <c r="B98" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11204,10 +11209,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425894</v>
+        <v>426093</v>
       </c>
       <c r="R98" t="n">
-        <v>7051256</v>
+        <v>7051184</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11240,11 +11245,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399922</v>
+        <v>128399941</v>
       </c>
       <c r="B100" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426343</v>
+        <v>425987</v>
       </c>
       <c r="R100" t="n">
-        <v>7050915</v>
+        <v>7051259</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11470,10 +11470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399936</v>
+        <v>128399922</v>
       </c>
       <c r="B101" t="n">
-        <v>91466</v>
+        <v>91448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11481,21 +11481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11505,10 +11505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425967</v>
+        <v>426343</v>
       </c>
       <c r="R101" t="n">
-        <v>7051278</v>
+        <v>7050915</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11567,10 +11567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399829</v>
+        <v>128399936</v>
       </c>
       <c r="B102" t="n">
-        <v>91452</v>
+        <v>91466</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426191</v>
+        <v>425967</v>
       </c>
       <c r="R102" t="n">
-        <v>7050972</v>
+        <v>7051278</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11664,10 +11664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399907</v>
+        <v>128399829</v>
       </c>
       <c r="B103" t="n">
-        <v>57685</v>
+        <v>91452</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426064</v>
+        <v>426191</v>
       </c>
       <c r="R103" t="n">
-        <v>7051249</v>
+        <v>7050972</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11735,11 +11735,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11766,7 +11761,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128399889</v>
+        <v>128399907</v>
       </c>
       <c r="B104" t="n">
         <v>57685</v>
@@ -11801,10 +11796,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>425774</v>
+        <v>426064</v>
       </c>
       <c r="R104" t="n">
-        <v>7051222</v>
+        <v>7051249</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11841,7 +11836,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11868,10 +11863,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128399941</v>
+        <v>128399889</v>
       </c>
       <c r="B105" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11879,21 +11874,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11903,10 +11898,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425987</v>
+        <v>425774</v>
       </c>
       <c r="R105" t="n">
-        <v>7051259</v>
+        <v>7051222</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11939,6 +11934,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11965,32 +11965,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399881</v>
+        <v>128399834</v>
       </c>
       <c r="B106" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>425942</v>
+        <v>426228</v>
       </c>
       <c r="R106" t="n">
-        <v>7051274</v>
+        <v>7050978</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12036,11 +12036,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12067,32 +12062,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399834</v>
+        <v>128399945</v>
       </c>
       <c r="B107" t="n">
-        <v>92149</v>
+        <v>91470</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12102,10 +12097,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426228</v>
+        <v>426062</v>
       </c>
       <c r="R107" t="n">
-        <v>7050978</v>
+        <v>7051271</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12164,10 +12159,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399945</v>
+        <v>128399903</v>
       </c>
       <c r="B108" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12175,21 +12170,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12199,10 +12194,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>426062</v>
+        <v>425972</v>
       </c>
       <c r="R108" t="n">
-        <v>7051271</v>
+        <v>7051285</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12235,6 +12230,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12261,7 +12261,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399903</v>
+        <v>128399863</v>
       </c>
       <c r="B109" t="n">
         <v>57685</v>
@@ -12296,10 +12296,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>425972</v>
+        <v>426347</v>
       </c>
       <c r="R109" t="n">
-        <v>7051285</v>
+        <v>7050960</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12363,7 +12363,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399863</v>
+        <v>128399868</v>
       </c>
       <c r="B110" t="n">
         <v>57685</v>
@@ -12398,10 +12398,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>426347</v>
+        <v>426274</v>
       </c>
       <c r="R110" t="n">
-        <v>7050960</v>
+        <v>7050964</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12465,7 +12465,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128399868</v>
+        <v>128399881</v>
       </c>
       <c r="B111" t="n">
         <v>57685</v>
@@ -12500,10 +12500,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>426274</v>
+        <v>425942</v>
       </c>
       <c r="R111" t="n">
-        <v>7050964</v>
+        <v>7051274</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13159,32 +13159,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399838</v>
+        <v>128399872</v>
       </c>
       <c r="B118" t="n">
-        <v>92149</v>
+        <v>57685</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>425752</v>
+        <v>426187</v>
       </c>
       <c r="R118" t="n">
-        <v>7051219</v>
+        <v>7050975</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13230,6 +13230,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13256,7 +13261,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399872</v>
+        <v>128399853</v>
       </c>
       <c r="B119" t="n">
         <v>57685</v>
@@ -13285,16 +13290,24 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426187</v>
+        <v>426736</v>
       </c>
       <c r="R119" t="n">
-        <v>7050975</v>
+        <v>7051344</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13331,7 +13344,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13358,7 +13371,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399853</v>
+        <v>128399914</v>
       </c>
       <c r="B120" t="n">
         <v>57685</v>
@@ -13387,24 +13400,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426736</v>
+        <v>426219</v>
       </c>
       <c r="R120" t="n">
-        <v>7051344</v>
+        <v>7051364</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13441,7 +13446,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13468,7 +13473,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399914</v>
+        <v>128399852</v>
       </c>
       <c r="B121" t="n">
         <v>57685</v>
@@ -13503,10 +13508,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426219</v>
+        <v>426765</v>
       </c>
       <c r="R121" t="n">
-        <v>7051364</v>
+        <v>7051373</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13570,7 +13575,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399852</v>
+        <v>128399897</v>
       </c>
       <c r="B122" t="n">
         <v>57685</v>
@@ -13605,10 +13610,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>426765</v>
+        <v>425892</v>
       </c>
       <c r="R122" t="n">
-        <v>7051373</v>
+        <v>7051251</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13645,7 +13650,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13973,32 +13978,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399897</v>
+        <v>128399838</v>
       </c>
       <c r="B126" t="n">
-        <v>57685</v>
+        <v>92149</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14008,10 +14013,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425892</v>
+        <v>425752</v>
       </c>
       <c r="R126" t="n">
-        <v>7051251</v>
+        <v>7051219</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14044,11 +14049,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14075,10 +14075,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128399948</v>
+        <v>128399901</v>
       </c>
       <c r="B127" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>426395</v>
+        <v>425880</v>
       </c>
       <c r="R127" t="n">
-        <v>7051398</v>
+        <v>7051304</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14177,7 +14177,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128399901</v>
+        <v>128399878</v>
       </c>
       <c r="B128" t="n">
         <v>57685</v>
@@ -14212,10 +14212,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425880</v>
+        <v>426047</v>
       </c>
       <c r="R128" t="n">
-        <v>7051304</v>
+        <v>7051186</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14279,7 +14279,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399878</v>
+        <v>128399876</v>
       </c>
       <c r="B129" t="n">
         <v>57685</v>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426047</v>
+        <v>426244</v>
       </c>
       <c r="R129" t="n">
-        <v>7051186</v>
+        <v>7051052</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14381,7 +14381,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128399876</v>
+        <v>128399905</v>
       </c>
       <c r="B130" t="n">
         <v>57685</v>
@@ -14416,10 +14416,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426244</v>
+        <v>426029</v>
       </c>
       <c r="R130" t="n">
-        <v>7051052</v>
+        <v>7051287</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14483,10 +14483,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399905</v>
+        <v>128399920</v>
       </c>
       <c r="B131" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14494,21 +14494,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14518,10 +14518,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426029</v>
+        <v>426277</v>
       </c>
       <c r="R131" t="n">
-        <v>7051287</v>
+        <v>7051183</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14554,11 +14554,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14585,10 +14580,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399920</v>
+        <v>128399942</v>
       </c>
       <c r="B132" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14596,21 +14591,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14620,10 +14615,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>426277</v>
+        <v>425904</v>
       </c>
       <c r="R132" t="n">
-        <v>7051183</v>
+        <v>7051248</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14682,10 +14677,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399942</v>
+        <v>128399948</v>
       </c>
       <c r="B133" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14693,21 +14688,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14717,10 +14712,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>425904</v>
+        <v>426395</v>
       </c>
       <c r="R133" t="n">
-        <v>7051248</v>
+        <v>7051398</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14753,6 +14748,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16182,10 +16182,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128399828</v>
+        <v>128399946</v>
       </c>
       <c r="B148" t="n">
-        <v>91452</v>
+        <v>91470</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16193,21 +16193,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16217,10 +16217,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>426225</v>
+        <v>426083</v>
       </c>
       <c r="R148" t="n">
-        <v>7050963</v>
+        <v>7051231</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16279,7 +16279,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128399946</v>
+        <v>128399937</v>
       </c>
       <c r="B149" t="n">
         <v>91470</v>
@@ -16314,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>426083</v>
+        <v>426734</v>
       </c>
       <c r="R149" t="n">
-        <v>7051231</v>
+        <v>7051350</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16376,10 +16376,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128399937</v>
+        <v>128399892</v>
       </c>
       <c r="B150" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16387,21 +16387,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16411,10 +16411,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>426734</v>
+        <v>425853</v>
       </c>
       <c r="R150" t="n">
-        <v>7051350</v>
+        <v>7051216</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16447,6 +16447,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16473,7 +16478,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128399892</v>
+        <v>128399883</v>
       </c>
       <c r="B151" t="n">
         <v>57685</v>
@@ -16508,10 +16513,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>425853</v>
+        <v>425851</v>
       </c>
       <c r="R151" t="n">
-        <v>7051216</v>
+        <v>7051202</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16548,7 +16553,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16575,7 +16580,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128399883</v>
+        <v>128399861</v>
       </c>
       <c r="B152" t="n">
         <v>57685</v>
@@ -16610,10 +16615,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>425851</v>
+        <v>426285</v>
       </c>
       <c r="R152" t="n">
-        <v>7051202</v>
+        <v>7051199</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16650,7 +16655,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16677,7 +16682,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128399861</v>
+        <v>128399855</v>
       </c>
       <c r="B153" t="n">
         <v>57685</v>
@@ -16712,10 +16717,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>426285</v>
+        <v>426639</v>
       </c>
       <c r="R153" t="n">
-        <v>7051199</v>
+        <v>7051351</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16752,7 +16757,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16779,10 +16784,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128399855</v>
+        <v>128399828</v>
       </c>
       <c r="B154" t="n">
-        <v>57685</v>
+        <v>91452</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16790,21 +16795,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16814,10 +16819,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>426639</v>
+        <v>426225</v>
       </c>
       <c r="R154" t="n">
-        <v>7051351</v>
+        <v>7050963</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16850,11 +16855,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B189" t="n">
-        <v>91448</v>
+        <v>57685</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R189" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20353,6 +20353,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20379,10 +20384,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399939</v>
+        <v>128399862</v>
       </c>
       <c r="B190" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20390,21 +20395,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20414,10 +20419,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426300</v>
+        <v>426292</v>
       </c>
       <c r="R190" t="n">
-        <v>7051058</v>
+        <v>7050995</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20450,6 +20455,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20476,10 +20486,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399873</v>
+        <v>128399925</v>
       </c>
       <c r="B191" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20487,21 +20497,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20511,10 +20521,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426193</v>
+        <v>426047</v>
       </c>
       <c r="R191" t="n">
-        <v>7050977</v>
+        <v>7051252</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20547,11 +20557,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20578,10 +20583,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399862</v>
+        <v>128399939</v>
       </c>
       <c r="B192" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20589,21 +20594,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20613,10 +20618,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426292</v>
+        <v>426300</v>
       </c>
       <c r="R192" t="n">
-        <v>7050995</v>
+        <v>7051058</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20649,11 +20654,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128398811</v>
+        <v>128398740</v>
       </c>
       <c r="B14" t="n">
-        <v>91448</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426091</v>
+        <v>426327</v>
       </c>
       <c r="R14" t="n">
-        <v>7051202</v>
+        <v>7051074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128398740</v>
+        <v>128398811</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>91448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426327</v>
+        <v>426091</v>
       </c>
       <c r="R15" t="n">
-        <v>7051074</v>
+        <v>7051202</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3770,32 +3770,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128398788</v>
+        <v>128398724</v>
       </c>
       <c r="B30" t="n">
-        <v>75162</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425804</v>
+        <v>426447</v>
       </c>
       <c r="R30" t="n">
-        <v>7051255</v>
+        <v>7051254</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3861,11 +3861,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Glasbjörk</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3882,32 +3877,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398791</v>
+        <v>128398788</v>
       </c>
       <c r="B31" t="n">
-        <v>75163</v>
+        <v>75162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>492</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3917,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425847</v>
+        <v>425804</v>
       </c>
       <c r="R31" t="n">
-        <v>7051261</v>
+        <v>7051255</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3952,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3962,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3974,19 +3969,9 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Betula pubescens</t>
+          <t>Glasbjörk</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4004,10 +3989,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398819</v>
+        <v>128398791</v>
       </c>
       <c r="B32" t="n">
-        <v>91452</v>
+        <v>75163</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4015,21 +4000,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4039,10 +4024,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426181</v>
+        <v>425847</v>
       </c>
       <c r="R32" t="n">
-        <v>7051325</v>
+        <v>7051261</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4074,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4084,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4095,6 +4080,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4111,10 +4111,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398724</v>
+        <v>128398819</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>91452</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426447</v>
+        <v>426181</v>
       </c>
       <c r="R33" t="n">
-        <v>7051254</v>
+        <v>7051325</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5084,32 +5084,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128398787</v>
+        <v>128398736</v>
       </c>
       <c r="B42" t="n">
-        <v>75163</v>
+        <v>92149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>425795</v>
+        <v>426352</v>
       </c>
       <c r="R42" t="n">
-        <v>7051251</v>
+        <v>7051151</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398749</v>
+        <v>128398787</v>
       </c>
       <c r="B43" t="n">
-        <v>86766</v>
+        <v>75163</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>427</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426252</v>
+        <v>425795</v>
       </c>
       <c r="R43" t="n">
-        <v>7050919</v>
+        <v>7051251</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,12 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5303,10 +5298,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128398800</v>
+        <v>128398749</v>
       </c>
       <c r="B44" t="n">
-        <v>91466</v>
+        <v>86766</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5314,21 +5309,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>427</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5338,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425985</v>
+        <v>426252</v>
       </c>
       <c r="R44" t="n">
-        <v>7051282</v>
+        <v>7050919</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5368,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5383,7 +5378,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5410,32 +5410,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128398736</v>
+        <v>128398800</v>
       </c>
       <c r="B45" t="n">
-        <v>92149</v>
+        <v>91466</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426352</v>
+        <v>425985</v>
       </c>
       <c r="R45" t="n">
-        <v>7051151</v>
+        <v>7051282</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5624,10 +5624,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398807</v>
+        <v>128398797</v>
       </c>
       <c r="B47" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,39 +5635,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426011</v>
+        <v>425919</v>
       </c>
       <c r="R47" t="n">
-        <v>7051282</v>
+        <v>7051350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5699,7 +5694,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5709,12 +5704,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5741,10 +5731,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128398721</v>
+        <v>128398812</v>
       </c>
       <c r="B48" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5752,39 +5742,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426773</v>
+        <v>426097</v>
       </c>
       <c r="R48" t="n">
-        <v>7051349</v>
+        <v>7051199</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5816,7 +5801,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5826,12 +5811,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5858,7 +5838,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128398797</v>
+        <v>128398725</v>
       </c>
       <c r="B49" t="n">
         <v>79083</v>
@@ -5893,10 +5873,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>425919</v>
+        <v>426492</v>
       </c>
       <c r="R49" t="n">
-        <v>7051350</v>
+        <v>7051269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,7 +5908,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5938,7 +5918,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5965,10 +5945,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128398812</v>
+        <v>128398807</v>
       </c>
       <c r="B50" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,34 +5956,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426097</v>
+        <v>426011</v>
       </c>
       <c r="R50" t="n">
-        <v>7051199</v>
+        <v>7051282</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6035,7 +6020,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6045,7 +6030,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,10 +6062,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128398725</v>
+        <v>128398721</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6083,34 +6073,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426492</v>
+        <v>426773</v>
       </c>
       <c r="R51" t="n">
-        <v>7051269</v>
+        <v>7051349</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6142,7 +6137,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6152,7 +6147,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,32 +6179,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398743</v>
+        <v>128398734</v>
       </c>
       <c r="B52" t="n">
-        <v>91448</v>
+        <v>92149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6214,10 +6214,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426371</v>
+        <v>426329</v>
       </c>
       <c r="R52" t="n">
-        <v>7050917</v>
+        <v>7051146</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6286,10 +6286,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128398802</v>
+        <v>128398727</v>
       </c>
       <c r="B53" t="n">
-        <v>91748</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6297,21 +6297,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>425985</v>
+        <v>426516</v>
       </c>
       <c r="R53" t="n">
-        <v>7051282</v>
+        <v>7051239</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6393,45 +6393,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398734</v>
+        <v>128398804</v>
       </c>
       <c r="B54" t="n">
-        <v>92149</v>
+        <v>75169</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>6486</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426329</v>
+        <v>426000</v>
       </c>
       <c r="R54" t="n">
-        <v>7051146</v>
+        <v>7051290</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6463,7 +6466,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6473,7 +6476,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6481,6 +6484,11 @@
       </c>
       <c r="AE54" t="b">
         <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -6500,10 +6508,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398727</v>
+        <v>128398793</v>
       </c>
       <c r="B55" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6511,34 +6519,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426516</v>
+        <v>425908</v>
       </c>
       <c r="R55" t="n">
-        <v>7051239</v>
+        <v>7051281</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6570,7 +6583,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6580,7 +6593,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6607,48 +6625,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398804</v>
+        <v>128398814</v>
       </c>
       <c r="B56" t="n">
-        <v>75169</v>
+        <v>57685</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426000</v>
+        <v>426097</v>
       </c>
       <c r="R56" t="n">
-        <v>7051290</v>
+        <v>7051199</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6680,7 +6700,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6690,7 +6710,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6698,11 +6723,6 @@
       </c>
       <c r="AE56" t="b">
         <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -6722,7 +6742,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398793</v>
+        <v>128398822</v>
       </c>
       <c r="B57" t="n">
         <v>57685</v>
@@ -6762,10 +6782,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425908</v>
+        <v>426200</v>
       </c>
       <c r="R57" t="n">
-        <v>7051281</v>
+        <v>7051338</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6797,7 +6817,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6807,7 +6827,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6839,7 +6859,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398814</v>
+        <v>128398719</v>
       </c>
       <c r="B58" t="n">
         <v>57685</v>
@@ -6879,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426097</v>
+        <v>426799</v>
       </c>
       <c r="R58" t="n">
-        <v>7051199</v>
+        <v>7051328</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6914,7 +6934,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6924,7 +6944,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6956,10 +6976,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398822</v>
+        <v>128398743</v>
       </c>
       <c r="B59" t="n">
-        <v>57685</v>
+        <v>91448</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6967,39 +6987,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426200</v>
+        <v>426371</v>
       </c>
       <c r="R59" t="n">
-        <v>7051338</v>
+        <v>7050917</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7031,7 +7046,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7041,12 +7056,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7073,10 +7083,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398719</v>
+        <v>128398802</v>
       </c>
       <c r="B60" t="n">
-        <v>57685</v>
+        <v>91748</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7084,39 +7094,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426799</v>
+        <v>425985</v>
       </c>
       <c r="R60" t="n">
-        <v>7051328</v>
+        <v>7051282</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7148,7 +7153,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7158,12 +7163,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128398779</v>
+        <v>128398720</v>
       </c>
       <c r="B73" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8520,39 +8520,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>425818</v>
+        <v>426773</v>
       </c>
       <c r="R73" t="n">
-        <v>7051169</v>
+        <v>7051341</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8584,7 +8579,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8594,12 +8589,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8626,10 +8616,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128398720</v>
+        <v>128398779</v>
       </c>
       <c r="B74" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8637,34 +8627,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426773</v>
+        <v>425818</v>
       </c>
       <c r="R74" t="n">
-        <v>7051341</v>
+        <v>7051169</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8696,7 +8691,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8706,7 +8701,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9843,10 +9843,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128398761</v>
+        <v>128398728</v>
       </c>
       <c r="B85" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9854,34 +9854,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>426231</v>
+        <v>426475</v>
       </c>
       <c r="R85" t="n">
-        <v>7051061</v>
+        <v>7051191</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9913,7 +9918,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9923,7 +9928,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9950,10 +9960,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128398728</v>
+        <v>128398761</v>
       </c>
       <c r="B86" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9961,39 +9971,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>426475</v>
+        <v>426231</v>
       </c>
       <c r="R86" t="n">
-        <v>7051191</v>
+        <v>7051061</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10025,7 +10030,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10035,12 +10040,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10070,7 +10070,7 @@
         <v>128399908</v>
       </c>
       <c r="B87" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>128399850</v>
       </c>
       <c r="B88" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10271,10 +10271,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128399875</v>
+        <v>128399888</v>
       </c>
       <c r="B89" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>426207</v>
+        <v>425774</v>
       </c>
       <c r="R89" t="n">
-        <v>7051009</v>
+        <v>7051220</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10373,10 +10373,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128399888</v>
+        <v>128399916</v>
       </c>
       <c r="B90" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>425774</v>
+        <v>426279</v>
       </c>
       <c r="R90" t="n">
-        <v>7051220</v>
+        <v>7051408</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10475,10 +10475,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399916</v>
+        <v>128399875</v>
       </c>
       <c r="B91" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>426279</v>
+        <v>426207</v>
       </c>
       <c r="R91" t="n">
-        <v>7051408</v>
+        <v>7051009</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10580,7 +10580,7 @@
         <v>128399895</v>
       </c>
       <c r="B92" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399949</v>
+        <v>128399940</v>
       </c>
       <c r="B93" t="n">
-        <v>88853</v>
+        <v>91476</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426768</v>
+        <v>426338</v>
       </c>
       <c r="R93" t="n">
-        <v>7051367</v>
+        <v>7050977</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10776,10 +10776,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399940</v>
+        <v>128399949</v>
       </c>
       <c r="B94" t="n">
-        <v>91470</v>
+        <v>88859</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10787,21 +10787,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426338</v>
+        <v>426768</v>
       </c>
       <c r="R94" t="n">
-        <v>7050977</v>
+        <v>7051367</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10876,7 +10876,7 @@
         <v>128399849</v>
       </c>
       <c r="B95" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>128399898</v>
       </c>
       <c r="B96" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11077,32 +11077,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399832</v>
+        <v>128399886</v>
       </c>
       <c r="B97" t="n">
-        <v>92149</v>
+        <v>57689</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11112,10 +11112,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426401</v>
+        <v>425743</v>
       </c>
       <c r="R97" t="n">
-        <v>7051237</v>
+        <v>7051241</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11148,6 +11148,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11174,10 +11179,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399836</v>
+        <v>128399832</v>
       </c>
       <c r="B98" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11209,10 +11214,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426093</v>
+        <v>426401</v>
       </c>
       <c r="R98" t="n">
-        <v>7051184</v>
+        <v>7051237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11271,32 +11276,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399886</v>
+        <v>128399836</v>
       </c>
       <c r="B99" t="n">
-        <v>57685</v>
+        <v>92155</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11306,10 +11311,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425743</v>
+        <v>426093</v>
       </c>
       <c r="R99" t="n">
-        <v>7051241</v>
+        <v>7051184</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11342,11 +11347,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399941</v>
+        <v>128399922</v>
       </c>
       <c r="B100" t="n">
-        <v>91470</v>
+        <v>91454</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425987</v>
+        <v>426343</v>
       </c>
       <c r="R100" t="n">
-        <v>7051259</v>
+        <v>7050915</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11470,10 +11470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399922</v>
+        <v>128399936</v>
       </c>
       <c r="B101" t="n">
-        <v>91448</v>
+        <v>91472</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11481,21 +11481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11505,10 +11505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426343</v>
+        <v>425967</v>
       </c>
       <c r="R101" t="n">
-        <v>7050915</v>
+        <v>7051278</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11567,10 +11567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399936</v>
+        <v>128399829</v>
       </c>
       <c r="B102" t="n">
-        <v>91466</v>
+        <v>91458</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425967</v>
+        <v>426191</v>
       </c>
       <c r="R102" t="n">
-        <v>7051278</v>
+        <v>7050972</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11664,10 +11664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399829</v>
+        <v>128399941</v>
       </c>
       <c r="B103" t="n">
-        <v>91452</v>
+        <v>91476</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426191</v>
+        <v>425987</v>
       </c>
       <c r="R103" t="n">
-        <v>7050972</v>
+        <v>7051259</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11764,7 +11764,7 @@
         <v>128399907</v>
       </c>
       <c r="B104" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>128399889</v>
       </c>
       <c r="B105" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11965,32 +11965,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399834</v>
+        <v>128399945</v>
       </c>
       <c r="B106" t="n">
-        <v>92149</v>
+        <v>91476</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426228</v>
+        <v>426062</v>
       </c>
       <c r="R106" t="n">
-        <v>7050978</v>
+        <v>7051271</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12062,32 +12062,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399945</v>
+        <v>128399834</v>
       </c>
       <c r="B107" t="n">
-        <v>91470</v>
+        <v>92155</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12097,10 +12097,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426062</v>
+        <v>426228</v>
       </c>
       <c r="R107" t="n">
-        <v>7051271</v>
+        <v>7050978</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12162,7 +12162,7 @@
         <v>128399903</v>
       </c>
       <c r="B108" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>128399863</v>
       </c>
       <c r="B109" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>128399868</v>
       </c>
       <c r="B110" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>128399881</v>
       </c>
       <c r="B111" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12567,32 +12567,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128399833</v>
+        <v>128399935</v>
       </c>
       <c r="B112" t="n">
-        <v>92149</v>
+        <v>91472</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12602,10 +12602,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>426263</v>
+        <v>425974</v>
       </c>
       <c r="R112" t="n">
-        <v>7051287</v>
+        <v>7051249</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12664,32 +12664,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128399831</v>
+        <v>128399943</v>
       </c>
       <c r="B113" t="n">
-        <v>92149</v>
+        <v>91476</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>426425</v>
+        <v>425756</v>
       </c>
       <c r="R113" t="n">
-        <v>7051289</v>
+        <v>7051245</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12761,32 +12761,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128399904</v>
+        <v>128399833</v>
       </c>
       <c r="B114" t="n">
-        <v>57685</v>
+        <v>92155</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426012</v>
+        <v>426263</v>
       </c>
       <c r="R114" t="n">
-        <v>7051306</v>
+        <v>7051287</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12832,11 +12832,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12863,32 +12858,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399870</v>
+        <v>128399831</v>
       </c>
       <c r="B115" t="n">
-        <v>57685</v>
+        <v>92155</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12898,10 +12893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426156</v>
+        <v>426425</v>
       </c>
       <c r="R115" t="n">
-        <v>7050998</v>
+        <v>7051289</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12934,11 +12929,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12965,10 +12955,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399935</v>
+        <v>128399904</v>
       </c>
       <c r="B116" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12976,21 +12966,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13000,10 +12990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>425974</v>
+        <v>426012</v>
       </c>
       <c r="R116" t="n">
-        <v>7051249</v>
+        <v>7051306</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13036,6 +13026,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13062,10 +13057,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128399943</v>
+        <v>128399870</v>
       </c>
       <c r="B117" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13073,21 +13068,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13097,10 +13092,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>425756</v>
+        <v>426156</v>
       </c>
       <c r="R117" t="n">
-        <v>7051245</v>
+        <v>7050998</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13133,6 +13128,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13159,32 +13159,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399872</v>
+        <v>128399838</v>
       </c>
       <c r="B118" t="n">
-        <v>57685</v>
+        <v>92155</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426187</v>
+        <v>425752</v>
       </c>
       <c r="R118" t="n">
-        <v>7050975</v>
+        <v>7051219</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13230,11 +13230,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13261,10 +13256,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399853</v>
+        <v>128399928</v>
       </c>
       <c r="B119" t="n">
-        <v>57685</v>
+        <v>91472</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13272,42 +13267,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426736</v>
+        <v>426319</v>
       </c>
       <c r="R119" t="n">
-        <v>7051344</v>
+        <v>7051238</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13340,11 +13327,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13371,10 +13353,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399914</v>
+        <v>128399872</v>
       </c>
       <c r="B120" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13406,10 +13388,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426219</v>
+        <v>426187</v>
       </c>
       <c r="R120" t="n">
-        <v>7051364</v>
+        <v>7050975</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13473,10 +13455,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399852</v>
+        <v>128399853</v>
       </c>
       <c r="B121" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13502,16 +13484,24 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426765</v>
+        <v>426736</v>
       </c>
       <c r="R121" t="n">
-        <v>7051373</v>
+        <v>7051344</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13548,7 +13538,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13575,10 +13565,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399897</v>
+        <v>128399914</v>
       </c>
       <c r="B122" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13610,10 +13600,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>425892</v>
+        <v>426219</v>
       </c>
       <c r="R122" t="n">
-        <v>7051251</v>
+        <v>7051364</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13650,7 +13640,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13677,10 +13667,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399902</v>
+        <v>128399852</v>
       </c>
       <c r="B123" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13712,10 +13702,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425902</v>
+        <v>426765</v>
       </c>
       <c r="R123" t="n">
-        <v>7051312</v>
+        <v>7051373</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13752,7 +13742,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13779,10 +13769,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128399871</v>
+        <v>128399897</v>
       </c>
       <c r="B124" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13814,10 +13804,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>426154</v>
+        <v>425892</v>
       </c>
       <c r="R124" t="n">
-        <v>7050994</v>
+        <v>7051251</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13881,10 +13871,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128399928</v>
+        <v>128399902</v>
       </c>
       <c r="B125" t="n">
-        <v>91466</v>
+        <v>57689</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13892,21 +13882,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13916,10 +13906,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>426319</v>
+        <v>425902</v>
       </c>
       <c r="R125" t="n">
-        <v>7051238</v>
+        <v>7051312</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13952,6 +13942,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13978,32 +13973,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399838</v>
+        <v>128399871</v>
       </c>
       <c r="B126" t="n">
-        <v>92149</v>
+        <v>57689</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14013,10 +14008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425752</v>
+        <v>426154</v>
       </c>
       <c r="R126" t="n">
-        <v>7051219</v>
+        <v>7050994</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14049,6 +14044,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14075,10 +14075,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128399901</v>
+        <v>128399920</v>
       </c>
       <c r="B127" t="n">
-        <v>57685</v>
+        <v>91454</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425880</v>
+        <v>426277</v>
       </c>
       <c r="R127" t="n">
-        <v>7051304</v>
+        <v>7051183</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14146,11 +14146,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14177,10 +14172,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128399878</v>
+        <v>128399942</v>
       </c>
       <c r="B128" t="n">
-        <v>57685</v>
+        <v>91476</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14188,21 +14183,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14212,10 +14207,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>426047</v>
+        <v>425904</v>
       </c>
       <c r="R128" t="n">
-        <v>7051186</v>
+        <v>7051248</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14248,11 +14243,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14279,10 +14269,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399876</v>
+        <v>128399948</v>
       </c>
       <c r="B129" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14290,21 +14280,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14314,10 +14304,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426244</v>
+        <v>426395</v>
       </c>
       <c r="R129" t="n">
-        <v>7051052</v>
+        <v>7051398</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14354,7 +14344,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14381,10 +14371,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128399905</v>
+        <v>128399901</v>
       </c>
       <c r="B130" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14416,10 +14406,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426029</v>
+        <v>425880</v>
       </c>
       <c r="R130" t="n">
-        <v>7051287</v>
+        <v>7051304</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14456,7 +14446,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14483,10 +14473,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399920</v>
+        <v>128399878</v>
       </c>
       <c r="B131" t="n">
-        <v>91448</v>
+        <v>57689</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14494,21 +14484,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14518,10 +14508,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426277</v>
+        <v>426047</v>
       </c>
       <c r="R131" t="n">
-        <v>7051183</v>
+        <v>7051186</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14554,6 +14544,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14580,10 +14575,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399942</v>
+        <v>128399876</v>
       </c>
       <c r="B132" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14591,21 +14586,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14615,10 +14610,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>425904</v>
+        <v>426244</v>
       </c>
       <c r="R132" t="n">
-        <v>7051248</v>
+        <v>7051052</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14651,6 +14646,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14677,10 +14677,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399948</v>
+        <v>128399905</v>
       </c>
       <c r="B133" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14688,21 +14688,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14712,10 +14712,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426395</v>
+        <v>426029</v>
       </c>
       <c r="R133" t="n">
-        <v>7051398</v>
+        <v>7051287</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14782,7 +14782,7 @@
         <v>128399918</v>
       </c>
       <c r="B134" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>128399930</v>
       </c>
       <c r="B135" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>128399931</v>
       </c>
       <c r="B136" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>128399929</v>
       </c>
       <c r="B137" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>128399877</v>
       </c>
       <c r="B138" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>128399867</v>
       </c>
       <c r="B139" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>128399906</v>
       </c>
       <c r="B140" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>128399879</v>
       </c>
       <c r="B141" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>128399896</v>
       </c>
       <c r="B142" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>128399890</v>
       </c>
       <c r="B143" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>128399910</v>
       </c>
       <c r="B144" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>128399933</v>
       </c>
       <c r="B145" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>128399880</v>
       </c>
       <c r="B146" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>128399865</v>
       </c>
       <c r="B147" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16182,10 +16182,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128399946</v>
+        <v>128399828</v>
       </c>
       <c r="B148" t="n">
-        <v>91470</v>
+        <v>91458</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16193,21 +16193,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16217,10 +16217,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>426083</v>
+        <v>426225</v>
       </c>
       <c r="R148" t="n">
-        <v>7051231</v>
+        <v>7050963</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16279,10 +16279,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128399937</v>
+        <v>128399946</v>
       </c>
       <c r="B149" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16314,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>426734</v>
+        <v>426083</v>
       </c>
       <c r="R149" t="n">
-        <v>7051350</v>
+        <v>7051231</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16376,10 +16376,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128399892</v>
+        <v>128399937</v>
       </c>
       <c r="B150" t="n">
-        <v>57685</v>
+        <v>91476</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16387,21 +16387,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16411,10 +16411,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425853</v>
+        <v>426734</v>
       </c>
       <c r="R150" t="n">
-        <v>7051216</v>
+        <v>7051350</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16447,11 +16447,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16478,10 +16473,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128399883</v>
+        <v>128399892</v>
       </c>
       <c r="B151" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16513,10 +16508,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>425851</v>
+        <v>425853</v>
       </c>
       <c r="R151" t="n">
-        <v>7051202</v>
+        <v>7051216</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16553,7 +16548,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16580,10 +16575,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128399861</v>
+        <v>128399883</v>
       </c>
       <c r="B152" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16615,10 +16610,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>426285</v>
+        <v>425851</v>
       </c>
       <c r="R152" t="n">
-        <v>7051199</v>
+        <v>7051202</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16655,7 +16650,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16682,10 +16677,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128399855</v>
+        <v>128399861</v>
       </c>
       <c r="B153" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16717,10 +16712,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>426639</v>
+        <v>426285</v>
       </c>
       <c r="R153" t="n">
-        <v>7051351</v>
+        <v>7051199</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16757,7 +16752,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16784,10 +16779,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128399828</v>
+        <v>128399855</v>
       </c>
       <c r="B154" t="n">
-        <v>91452</v>
+        <v>57689</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16795,21 +16790,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16819,10 +16814,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>426225</v>
+        <v>426639</v>
       </c>
       <c r="R154" t="n">
-        <v>7050963</v>
+        <v>7051351</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16855,6 +16850,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16884,7 +16884,7 @@
         <v>128399885</v>
       </c>
       <c r="B155" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>128399911</v>
       </c>
       <c r="B156" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>128399913</v>
       </c>
       <c r="B157" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17187,32 +17187,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128399856</v>
+        <v>128399839</v>
       </c>
       <c r="B158" t="n">
-        <v>57685</v>
+        <v>92155</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17222,10 +17222,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>426646</v>
+        <v>425971</v>
       </c>
       <c r="R158" t="n">
-        <v>7051365</v>
+        <v>7051280</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17258,11 +17258,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17289,10 +17284,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128399909</v>
+        <v>128399827</v>
       </c>
       <c r="B159" t="n">
-        <v>57685</v>
+        <v>91458</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17300,34 +17295,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>426175</v>
+        <v>426813</v>
       </c>
       <c r="R159" t="n">
-        <v>7051323</v>
+        <v>7051371</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17360,11 +17355,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17391,32 +17381,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128399839</v>
+        <v>128399856</v>
       </c>
       <c r="B160" t="n">
-        <v>92149</v>
+        <v>57689</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17426,10 +17416,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>425971</v>
+        <v>426646</v>
       </c>
       <c r="R160" t="n">
-        <v>7051280</v>
+        <v>7051365</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17462,6 +17452,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17488,10 +17483,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128399827</v>
+        <v>128399909</v>
       </c>
       <c r="B161" t="n">
-        <v>91452</v>
+        <v>57689</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17499,34 +17494,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Stor-grässjön, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>426813</v>
+        <v>426175</v>
       </c>
       <c r="R161" t="n">
-        <v>7051371</v>
+        <v>7051323</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17559,6 +17554,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17585,32 +17585,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128399926</v>
+        <v>128399837</v>
       </c>
       <c r="B162" t="n">
-        <v>91448</v>
+        <v>92155</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>426189</v>
+        <v>425757</v>
       </c>
       <c r="R162" t="n">
-        <v>7051364</v>
+        <v>7051207</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17682,32 +17682,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128399837</v>
+        <v>128399926</v>
       </c>
       <c r="B163" t="n">
-        <v>92149</v>
+        <v>91454</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17717,10 +17717,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>425757</v>
+        <v>426189</v>
       </c>
       <c r="R163" t="n">
-        <v>7051207</v>
+        <v>7051364</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17779,32 +17779,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128399840</v>
+        <v>128399874</v>
       </c>
       <c r="B164" t="n">
-        <v>92149</v>
+        <v>57689</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17814,10 +17814,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>426131</v>
+        <v>426194</v>
       </c>
       <c r="R164" t="n">
-        <v>7051242</v>
+        <v>7050979</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17850,6 +17850,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17876,10 +17881,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128399874</v>
+        <v>128399864</v>
       </c>
       <c r="B165" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17911,10 +17916,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>426194</v>
+        <v>426357</v>
       </c>
       <c r="R165" t="n">
-        <v>7050979</v>
+        <v>7050965</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17951,7 +17956,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17978,32 +17983,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128399864</v>
+        <v>128399840</v>
       </c>
       <c r="B166" t="n">
-        <v>57685</v>
+        <v>92155</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18013,10 +18018,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>426357</v>
+        <v>426131</v>
       </c>
       <c r="R166" t="n">
-        <v>7050965</v>
+        <v>7051242</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18049,11 +18054,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18083,7 +18083,7 @@
         <v>128399934</v>
       </c>
       <c r="B167" t="n">
-        <v>91466</v>
+        <v>91472</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>128399843</v>
       </c>
       <c r="B168" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>128399869</v>
       </c>
       <c r="B169" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>128399899</v>
       </c>
       <c r="B170" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18478,10 +18478,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128399921</v>
+        <v>128399938</v>
       </c>
       <c r="B171" t="n">
-        <v>91448</v>
+        <v>91476</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18489,21 +18489,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18513,10 +18513,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>426314</v>
+        <v>426205</v>
       </c>
       <c r="R171" t="n">
-        <v>7050963</v>
+        <v>7051276</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18578,7 +18578,7 @@
         <v>128399835</v>
       </c>
       <c r="B172" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128399938</v>
+        <v>128399921</v>
       </c>
       <c r="B173" t="n">
-        <v>91470</v>
+        <v>91454</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18683,21 +18683,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18707,10 +18707,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>426205</v>
+        <v>426314</v>
       </c>
       <c r="R173" t="n">
-        <v>7051276</v>
+        <v>7050963</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18772,7 +18772,7 @@
         <v>128399884</v>
       </c>
       <c r="B174" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>128399893</v>
       </c>
       <c r="B175" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>128399887</v>
       </c>
       <c r="B176" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>128399882</v>
       </c>
       <c r="B177" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>128399854</v>
       </c>
       <c r="B178" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399950</v>
+        <v>128399894</v>
       </c>
       <c r="B179" t="n">
-        <v>88853</v>
+        <v>57689</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19298,21 +19298,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>426303</v>
+        <v>425875</v>
       </c>
       <c r="R179" t="n">
-        <v>7050905</v>
+        <v>7051223</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19358,6 +19358,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19384,10 +19389,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128399951</v>
+        <v>128399915</v>
       </c>
       <c r="B180" t="n">
-        <v>88853</v>
+        <v>57689</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19395,21 +19400,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19419,10 +19424,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>426062</v>
+        <v>426224</v>
       </c>
       <c r="R180" t="n">
-        <v>7051265</v>
+        <v>7051367</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19455,6 +19460,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19481,10 +19491,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399932</v>
+        <v>128399923</v>
       </c>
       <c r="B181" t="n">
-        <v>91466</v>
+        <v>91454</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19492,21 +19502,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19516,10 +19526,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>426231</v>
+        <v>426172</v>
       </c>
       <c r="R181" t="n">
-        <v>7051130</v>
+        <v>7051169</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19578,10 +19588,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128399923</v>
+        <v>128399932</v>
       </c>
       <c r="B182" t="n">
-        <v>91448</v>
+        <v>91472</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19589,21 +19599,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19613,10 +19623,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>426172</v>
+        <v>426231</v>
       </c>
       <c r="R182" t="n">
-        <v>7051169</v>
+        <v>7051130</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19678,7 +19688,7 @@
         <v>128399944</v>
       </c>
       <c r="B183" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19772,10 +19782,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128399894</v>
+        <v>128399950</v>
       </c>
       <c r="B184" t="n">
-        <v>57685</v>
+        <v>88859</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19783,21 +19793,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19807,10 +19817,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>425875</v>
+        <v>426303</v>
       </c>
       <c r="R184" t="n">
-        <v>7051223</v>
+        <v>7050905</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19843,11 +19853,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19874,10 +19879,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128399915</v>
+        <v>128399951</v>
       </c>
       <c r="B185" t="n">
-        <v>57685</v>
+        <v>88859</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19885,21 +19890,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19909,10 +19914,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>426224</v>
+        <v>426062</v>
       </c>
       <c r="R185" t="n">
-        <v>7051367</v>
+        <v>7051265</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19945,11 +19950,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19979,7 +19979,7 @@
         <v>128399912</v>
       </c>
       <c r="B186" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>128399860</v>
       </c>
       <c r="B187" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>128399891</v>
       </c>
       <c r="B188" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>128399873</v>
       </c>
       <c r="B189" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>128399862</v>
       </c>
       <c r="B190" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>128399925</v>
       </c>
       <c r="B191" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>128399939</v>
       </c>
       <c r="B192" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>128509948</v>
       </c>
       <c r="B193" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>128399846</v>
       </c>
       <c r="B194" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>128399847</v>
       </c>
       <c r="B195" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128399845</v>
       </c>
       <c r="B196" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128398758</v>
+        <v>128398722</v>
       </c>
       <c r="B2" t="n">
-        <v>82942</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426187</v>
+        <v>426695</v>
       </c>
       <c r="R2" t="n">
-        <v>7051025</v>
+        <v>7051338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128398722</v>
+        <v>128398798</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426695</v>
+        <v>425947</v>
       </c>
       <c r="R3" t="n">
-        <v>7051338</v>
+        <v>7051321</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128398798</v>
+        <v>128398786</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>75167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425947</v>
+        <v>425776</v>
       </c>
       <c r="R4" t="n">
-        <v>7051321</v>
+        <v>7051259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,6 +980,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128398786</v>
+        <v>128398758</v>
       </c>
       <c r="B5" t="n">
-        <v>75163</v>
+        <v>82946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425776</v>
+        <v>426187</v>
       </c>
       <c r="R5" t="n">
-        <v>7051259</v>
+        <v>7051025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,21 +1102,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1121,7 +1121,7 @@
         <v>128398759</v>
       </c>
       <c r="B6" t="n">
-        <v>88853</v>
+        <v>88865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128398742</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128398774</v>
+        <v>128398746</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>91482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,39 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425970</v>
+        <v>426300</v>
       </c>
       <c r="R8" t="n">
-        <v>7051235</v>
+        <v>7050902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128398746</v>
+        <v>128398775</v>
       </c>
       <c r="B9" t="n">
-        <v>91470</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,34 +1460,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426300</v>
+        <v>425892</v>
       </c>
       <c r="R9" t="n">
-        <v>7050902</v>
+        <v>7051220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1534,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128398768</v>
+        <v>128398774</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426158</v>
+        <v>425970</v>
       </c>
       <c r="R10" t="n">
-        <v>7051146</v>
+        <v>7051235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128398775</v>
+        <v>128398768</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425892</v>
+        <v>426158</v>
       </c>
       <c r="R11" t="n">
-        <v>7051220</v>
+        <v>7051146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1803,7 +1803,7 @@
         <v>128398762</v>
       </c>
       <c r="B12" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>128398790</v>
       </c>
       <c r="B13" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128398740</v>
+        <v>128398811</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>91460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426327</v>
+        <v>426091</v>
       </c>
       <c r="R14" t="n">
-        <v>7051074</v>
+        <v>7051202</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128398811</v>
+        <v>128398740</v>
       </c>
       <c r="B15" t="n">
-        <v>91448</v>
+        <v>91482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426091</v>
+        <v>426327</v>
       </c>
       <c r="R15" t="n">
-        <v>7051202</v>
+        <v>7051074</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128398776</v>
+        <v>128398737</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,34 +2249,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425869</v>
+        <v>426345</v>
       </c>
       <c r="R16" t="n">
-        <v>7051201</v>
+        <v>7051102</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2323,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128398824</v>
+        <v>128398776</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426331</v>
+        <v>425869</v>
       </c>
       <c r="R17" t="n">
-        <v>7051374</v>
+        <v>7051201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2425,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2435,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128398737</v>
+        <v>128398824</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,39 +2473,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>426345</v>
+        <v>426331</v>
       </c>
       <c r="R18" t="n">
-        <v>7051102</v>
+        <v>7051374</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,7 +2532,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,12 +2542,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128398771</v>
+        <v>128398821</v>
       </c>
       <c r="B19" t="n">
-        <v>91470</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,21 +2580,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426068</v>
+        <v>426200</v>
       </c>
       <c r="R19" t="n">
-        <v>7051189</v>
+        <v>7051338</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398729</v>
+        <v>128398753</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>80192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426468</v>
+        <v>426191</v>
       </c>
       <c r="R20" t="n">
-        <v>7051179</v>
+        <v>7050957</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,6 +2767,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2783,10 +2798,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398752</v>
+        <v>128398730</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426206</v>
+        <v>426382</v>
       </c>
       <c r="R21" t="n">
-        <v>7050935</v>
+        <v>7051149</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,7 +2868,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2878,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,57 +2905,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398805</v>
+        <v>128398773</v>
       </c>
       <c r="B22" t="n">
-        <v>57845</v>
+        <v>75173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6486</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425999</v>
+        <v>425978</v>
       </c>
       <c r="R22" t="n">
-        <v>7051258</v>
+        <v>7051231</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2969,7 +2975,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2985,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,32 +3012,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398770</v>
+        <v>128398803</v>
       </c>
       <c r="B23" t="n">
-        <v>91906</v>
+        <v>92161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3041,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426115</v>
+        <v>425994</v>
       </c>
       <c r="R23" t="n">
-        <v>7051178</v>
+        <v>7051287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3076,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3086,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,32 +3119,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398803</v>
+        <v>128398729</v>
       </c>
       <c r="B24" t="n">
-        <v>92149</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3148,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425994</v>
+        <v>426468</v>
       </c>
       <c r="R24" t="n">
-        <v>7051287</v>
+        <v>7051179</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3183,7 +3189,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3193,7 +3199,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,32 +3226,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398718</v>
+        <v>128398752</v>
       </c>
       <c r="B25" t="n">
-        <v>92754</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3255,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426807</v>
+        <v>426206</v>
       </c>
       <c r="R25" t="n">
-        <v>7051311</v>
+        <v>7050935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3290,7 +3296,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3300,7 +3306,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3327,32 +3333,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398773</v>
+        <v>128398718</v>
       </c>
       <c r="B26" t="n">
-        <v>75169</v>
+        <v>92766</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6486</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3362,10 +3368,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425978</v>
+        <v>426807</v>
       </c>
       <c r="R26" t="n">
-        <v>7051231</v>
+        <v>7051311</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3397,7 +3403,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3407,7 +3413,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398821</v>
+        <v>128398771</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>91482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3445,21 +3451,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3469,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426200</v>
+        <v>426068</v>
       </c>
       <c r="R27" t="n">
-        <v>7051338</v>
+        <v>7051189</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,7 +3510,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3514,7 +3520,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3541,32 +3547,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398753</v>
+        <v>128398770</v>
       </c>
       <c r="B28" t="n">
-        <v>80188</v>
+        <v>91918</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426191</v>
+        <v>426115</v>
       </c>
       <c r="R28" t="n">
-        <v>7050957</v>
+        <v>7051178</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3611,7 +3617,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3621,7 +3627,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3632,21 +3638,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3663,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128398730</v>
+        <v>128398805</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,37 +3665,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426382</v>
+        <v>425999</v>
       </c>
       <c r="R29" t="n">
-        <v>7051149</v>
+        <v>7051258</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3773,7 +3773,7 @@
         <v>128398724</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3877,32 +3877,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398788</v>
+        <v>128398791</v>
       </c>
       <c r="B31" t="n">
-        <v>75162</v>
+        <v>75167</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425804</v>
+        <v>425847</v>
       </c>
       <c r="R31" t="n">
-        <v>7051255</v>
+        <v>7051261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3969,9 +3969,19 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Glasbjörk</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3989,10 +3999,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398791</v>
+        <v>128398819</v>
       </c>
       <c r="B32" t="n">
-        <v>75163</v>
+        <v>91464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,21 +4010,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4024,10 +4034,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425847</v>
+        <v>426181</v>
       </c>
       <c r="R32" t="n">
-        <v>7051261</v>
+        <v>7051325</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4059,7 +4069,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4079,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,21 +4090,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4111,32 +4106,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398819</v>
+        <v>128398788</v>
       </c>
       <c r="B33" t="n">
-        <v>91452</v>
+        <v>75166</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4146,10 +4141,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426181</v>
+        <v>425804</v>
       </c>
       <c r="R33" t="n">
-        <v>7051325</v>
+        <v>7051255</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4181,7 +4176,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4191,7 +4186,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4202,6 +4197,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Glasbjörk</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4221,7 +4221,7 @@
         <v>128398755</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>128398738</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>128398794</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4539,50 +4539,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398741</v>
+        <v>128398801</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>91918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426298</v>
+        <v>425985</v>
       </c>
       <c r="R37" t="n">
-        <v>7051029</v>
+        <v>7051282</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4614,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4624,12 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4656,45 +4646,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128398801</v>
+        <v>128398741</v>
       </c>
       <c r="B38" t="n">
-        <v>91906</v>
+        <v>57689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>425985</v>
+        <v>426298</v>
       </c>
       <c r="R38" t="n">
-        <v>7051282</v>
+        <v>7051029</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,7 +4721,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4736,7 +4731,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4763,32 +4763,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128398785</v>
+        <v>128398795</v>
       </c>
       <c r="B39" t="n">
-        <v>92149</v>
+        <v>91482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425708</v>
+        <v>425894</v>
       </c>
       <c r="R39" t="n">
-        <v>7051228</v>
+        <v>7051343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4870,10 +4870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128398795</v>
+        <v>128398808</v>
       </c>
       <c r="B40" t="n">
-        <v>91470</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>425894</v>
+        <v>426012</v>
       </c>
       <c r="R40" t="n">
-        <v>7051343</v>
+        <v>7051229</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4977,32 +4977,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128398808</v>
+        <v>128398785</v>
       </c>
       <c r="B41" t="n">
-        <v>79083</v>
+        <v>92161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426012</v>
+        <v>425708</v>
       </c>
       <c r="R41" t="n">
-        <v>7051229</v>
+        <v>7051228</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5087,7 +5087,7 @@
         <v>128398736</v>
       </c>
       <c r="B42" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398787</v>
+        <v>128398800</v>
       </c>
       <c r="B43" t="n">
-        <v>75163</v>
+        <v>91478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425795</v>
+        <v>425985</v>
       </c>
       <c r="R43" t="n">
-        <v>7051251</v>
+        <v>7051282</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5301,7 +5301,7 @@
         <v>128398749</v>
       </c>
       <c r="B44" t="n">
-        <v>86766</v>
+        <v>86776</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5410,10 +5410,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128398800</v>
+        <v>128398787</v>
       </c>
       <c r="B45" t="n">
-        <v>91466</v>
+        <v>75167</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,21 +5421,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425985</v>
+        <v>425795</v>
       </c>
       <c r="R45" t="n">
-        <v>7051282</v>
+        <v>7051251</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5520,7 +5520,7 @@
         <v>128398731</v>
       </c>
       <c r="B46" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>128398797</v>
       </c>
       <c r="B47" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>128398812</v>
       </c>
       <c r="B48" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>128398725</v>
       </c>
       <c r="B49" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>128398807</v>
       </c>
       <c r="B50" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>128398721</v>
       </c>
       <c r="B51" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,32 +6179,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398734</v>
+        <v>128398743</v>
       </c>
       <c r="B52" t="n">
-        <v>92149</v>
+        <v>91460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6214,10 +6214,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426329</v>
+        <v>426371</v>
       </c>
       <c r="R52" t="n">
-        <v>7051146</v>
+        <v>7050917</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6286,10 +6286,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128398727</v>
+        <v>128398802</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>91760</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6297,21 +6297,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426516</v>
+        <v>425985</v>
       </c>
       <c r="R53" t="n">
-        <v>7051239</v>
+        <v>7051282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6393,48 +6393,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398804</v>
+        <v>128398793</v>
       </c>
       <c r="B54" t="n">
-        <v>75169</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426000</v>
+        <v>425908</v>
       </c>
       <c r="R54" t="n">
-        <v>7051290</v>
+        <v>7051281</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6466,7 +6468,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6476,7 +6478,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6484,11 +6491,6 @@
       </c>
       <c r="AE54" t="b">
         <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -6508,10 +6510,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398793</v>
+        <v>128398814</v>
       </c>
       <c r="B55" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6548,10 +6550,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>425908</v>
+        <v>426097</v>
       </c>
       <c r="R55" t="n">
-        <v>7051281</v>
+        <v>7051199</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6583,7 +6585,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6593,7 +6595,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6625,10 +6627,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398814</v>
+        <v>128398719</v>
       </c>
       <c r="B56" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6665,10 +6667,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426097</v>
+        <v>426799</v>
       </c>
       <c r="R56" t="n">
-        <v>7051199</v>
+        <v>7051328</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6700,7 +6702,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6710,7 +6712,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6745,7 +6747,7 @@
         <v>128398822</v>
       </c>
       <c r="B57" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6859,10 +6861,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398719</v>
+        <v>128398727</v>
       </c>
       <c r="B58" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6870,39 +6872,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426799</v>
+        <v>426516</v>
       </c>
       <c r="R58" t="n">
-        <v>7051328</v>
+        <v>7051239</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6934,7 +6931,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6944,12 +6941,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6976,32 +6968,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398743</v>
+        <v>128398734</v>
       </c>
       <c r="B59" t="n">
-        <v>91448</v>
+        <v>92161</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7011,10 +7003,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426371</v>
+        <v>426329</v>
       </c>
       <c r="R59" t="n">
-        <v>7050917</v>
+        <v>7051146</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7046,7 +7038,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7056,7 +7048,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7083,45 +7075,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398802</v>
+        <v>128398804</v>
       </c>
       <c r="B60" t="n">
-        <v>91748</v>
+        <v>75173</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>425985</v>
+        <v>426000</v>
       </c>
       <c r="R60" t="n">
-        <v>7051282</v>
+        <v>7051290</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7153,7 +7148,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7163,7 +7158,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7171,6 +7166,11 @@
       </c>
       <c r="AE60" t="b">
         <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398769</v>
+        <v>128398726</v>
       </c>
       <c r="B61" t="n">
-        <v>91452</v>
+        <v>75166</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426135</v>
+        <v>426522</v>
       </c>
       <c r="R61" t="n">
-        <v>7051154</v>
+        <v>7051242</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,6 +7281,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7297,10 +7312,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398783</v>
+        <v>128398769</v>
       </c>
       <c r="B62" t="n">
-        <v>79083</v>
+        <v>91464</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7308,21 +7323,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7347,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>425733</v>
+        <v>426135</v>
       </c>
       <c r="R62" t="n">
-        <v>7051205</v>
+        <v>7051154</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,7 +7382,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7377,7 +7392,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7404,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128398745</v>
+        <v>128398783</v>
       </c>
       <c r="B63" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7415,39 +7430,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426353</v>
+        <v>425733</v>
       </c>
       <c r="R63" t="n">
-        <v>7050910</v>
+        <v>7051205</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7479,7 +7489,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7489,12 +7499,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7521,10 +7526,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128398781</v>
+        <v>128398745</v>
       </c>
       <c r="B64" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7561,10 +7566,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>425754</v>
+        <v>426353</v>
       </c>
       <c r="R64" t="n">
-        <v>7051180</v>
+        <v>7050910</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7596,7 +7601,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7606,7 +7611,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7638,45 +7643,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128398726</v>
+        <v>128398781</v>
       </c>
       <c r="B65" t="n">
-        <v>75162</v>
+        <v>57689</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426522</v>
+        <v>425754</v>
       </c>
       <c r="R65" t="n">
-        <v>7051242</v>
+        <v>7051180</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7708,7 +7718,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7718,7 +7728,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7729,21 +7744,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7763,7 +7763,7 @@
         <v>128398763</v>
       </c>
       <c r="B66" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>128398796</v>
       </c>
       <c r="B67" t="n">
-        <v>78060</v>
+        <v>78064</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7974,32 +7974,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128398760</v>
+        <v>128398733</v>
       </c>
       <c r="B68" t="n">
-        <v>82942</v>
+        <v>92161</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426232</v>
+        <v>426361</v>
       </c>
       <c r="R68" t="n">
-        <v>7051062</v>
+        <v>7051151</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8081,32 +8081,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128398733</v>
+        <v>128398820</v>
       </c>
       <c r="B69" t="n">
-        <v>92149</v>
+        <v>91482</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426361</v>
+        <v>426196</v>
       </c>
       <c r="R69" t="n">
-        <v>7051151</v>
+        <v>7051340</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8188,10 +8188,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128398820</v>
+        <v>128398760</v>
       </c>
       <c r="B70" t="n">
-        <v>91470</v>
+        <v>82946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8199,21 +8199,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426196</v>
+        <v>426232</v>
       </c>
       <c r="R70" t="n">
-        <v>7051340</v>
+        <v>7051062</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8295,10 +8295,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128398777</v>
+        <v>128398818</v>
       </c>
       <c r="B71" t="n">
-        <v>82942</v>
+        <v>79087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8306,21 +8306,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>425861</v>
+        <v>426191</v>
       </c>
       <c r="R71" t="n">
-        <v>7051195</v>
+        <v>7051296</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8402,10 +8402,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128398818</v>
+        <v>128398777</v>
       </c>
       <c r="B72" t="n">
-        <v>79083</v>
+        <v>82946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8413,21 +8413,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426191</v>
+        <v>425861</v>
       </c>
       <c r="R72" t="n">
-        <v>7051296</v>
+        <v>7051195</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8512,7 +8512,7 @@
         <v>128398720</v>
       </c>
       <c r="B73" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>128398779</v>
       </c>
       <c r="B74" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8733,10 +8733,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128398754</v>
+        <v>128398815</v>
       </c>
       <c r="B75" t="n">
-        <v>80189</v>
+        <v>91871</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8744,21 +8744,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8768,10 +8763,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426191</v>
+        <v>426114</v>
       </c>
       <c r="R75" t="n">
-        <v>7050957</v>
+        <v>7051205</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8803,7 +8798,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8813,7 +8808,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8824,21 +8819,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8855,32 +8835,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128398772</v>
+        <v>128398754</v>
       </c>
       <c r="B76" t="n">
-        <v>92149</v>
+        <v>80193</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8890,10 +8870,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426065</v>
+        <v>426191</v>
       </c>
       <c r="R76" t="n">
-        <v>7051192</v>
+        <v>7050957</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8925,7 +8905,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8935,7 +8915,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8946,6 +8926,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8962,50 +8957,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128398789</v>
+        <v>128398772</v>
       </c>
       <c r="B77" t="n">
-        <v>57685</v>
+        <v>92161</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>425804</v>
+        <v>426065</v>
       </c>
       <c r="R77" t="n">
-        <v>7051258</v>
+        <v>7051192</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9037,7 +9027,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9047,12 +9037,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9079,10 +9064,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128398815</v>
+        <v>128398789</v>
       </c>
       <c r="B78" t="n">
-        <v>91859</v>
+        <v>57689</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9090,29 +9075,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>426114</v>
+        <v>425804</v>
       </c>
       <c r="R78" t="n">
-        <v>7051205</v>
+        <v>7051258</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9144,7 +9139,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9154,7 +9149,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9184,7 +9184,7 @@
         <v>128398813</v>
       </c>
       <c r="B79" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>128398765</v>
       </c>
       <c r="B80" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9395,10 +9395,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128398780</v>
+        <v>128398784</v>
       </c>
       <c r="B81" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9435,10 +9435,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>425756</v>
+        <v>425712</v>
       </c>
       <c r="R81" t="n">
-        <v>7051171</v>
+        <v>7051206</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9512,10 +9512,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128398784</v>
+        <v>128398780</v>
       </c>
       <c r="B82" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
       <c r="I82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9552,10 +9552,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425712</v>
+        <v>425756</v>
       </c>
       <c r="R82" t="n">
-        <v>7051206</v>
+        <v>7051171</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9632,7 +9632,7 @@
         <v>128398723</v>
       </c>
       <c r="B83" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>128398751</v>
       </c>
       <c r="B84" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9843,10 +9843,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128398728</v>
+        <v>128398761</v>
       </c>
       <c r="B85" t="n">
-        <v>57685</v>
+        <v>79087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9854,39 +9854,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>426475</v>
+        <v>426231</v>
       </c>
       <c r="R85" t="n">
-        <v>7051191</v>
+        <v>7051061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9918,7 +9913,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9928,12 +9923,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9960,10 +9950,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128398761</v>
+        <v>128398728</v>
       </c>
       <c r="B86" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9971,34 +9961,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>426231</v>
+        <v>426475</v>
       </c>
       <c r="R86" t="n">
-        <v>7051061</v>
+        <v>7051191</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10030,7 +10025,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10040,7 +10035,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128399888</v>
+        <v>128399895</v>
       </c>
       <c r="B89" t="n">
         <v>57689</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>425774</v>
+        <v>425879</v>
       </c>
       <c r="R89" t="n">
-        <v>7051220</v>
+        <v>7051238</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10475,7 +10475,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399875</v>
+        <v>128399888</v>
       </c>
       <c r="B91" t="n">
         <v>57689</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>426207</v>
+        <v>425774</v>
       </c>
       <c r="R91" t="n">
-        <v>7051009</v>
+        <v>7051220</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128399895</v>
+        <v>128399875</v>
       </c>
       <c r="B92" t="n">
         <v>57689</v>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>425879</v>
+        <v>426207</v>
       </c>
       <c r="R92" t="n">
-        <v>7051238</v>
+        <v>7051009</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10682,7 +10682,7 @@
         <v>128399940</v>
       </c>
       <c r="B93" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10779,7 +10779,7 @@
         <v>128399949</v>
       </c>
       <c r="B94" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399898</v>
+        <v>128399832</v>
       </c>
       <c r="B96" t="n">
-        <v>57689</v>
+        <v>92161</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425894</v>
+        <v>426401</v>
       </c>
       <c r="R96" t="n">
-        <v>7051256</v>
+        <v>7051237</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11046,11 +11046,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11077,32 +11072,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399886</v>
+        <v>128399836</v>
       </c>
       <c r="B97" t="n">
-        <v>57689</v>
+        <v>92161</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11112,10 +11107,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425743</v>
+        <v>426093</v>
       </c>
       <c r="R97" t="n">
-        <v>7051241</v>
+        <v>7051184</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11148,11 +11143,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11179,32 +11169,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399832</v>
+        <v>128399898</v>
       </c>
       <c r="B98" t="n">
-        <v>92155</v>
+        <v>57689</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11214,10 +11204,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426401</v>
+        <v>425894</v>
       </c>
       <c r="R98" t="n">
-        <v>7051237</v>
+        <v>7051256</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11250,6 +11240,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11276,32 +11271,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399836</v>
+        <v>128399886</v>
       </c>
       <c r="B99" t="n">
-        <v>92155</v>
+        <v>57689</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11311,10 +11306,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>426093</v>
+        <v>425743</v>
       </c>
       <c r="R99" t="n">
-        <v>7051184</v>
+        <v>7051241</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11347,6 +11342,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399922</v>
+        <v>128399907</v>
       </c>
       <c r="B100" t="n">
-        <v>91454</v>
+        <v>57689</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426343</v>
+        <v>426064</v>
       </c>
       <c r="R100" t="n">
-        <v>7050915</v>
+        <v>7051249</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11444,6 +11444,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11470,10 +11475,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399936</v>
+        <v>128399889</v>
       </c>
       <c r="B101" t="n">
-        <v>91472</v>
+        <v>57689</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11481,21 +11486,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11505,10 +11510,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425967</v>
+        <v>425774</v>
       </c>
       <c r="R101" t="n">
-        <v>7051278</v>
+        <v>7051222</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11541,6 +11546,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11567,10 +11577,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399829</v>
+        <v>128399941</v>
       </c>
       <c r="B102" t="n">
-        <v>91458</v>
+        <v>91482</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11578,21 +11588,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11602,10 +11612,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426191</v>
+        <v>425987</v>
       </c>
       <c r="R102" t="n">
-        <v>7050972</v>
+        <v>7051259</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11664,10 +11674,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399941</v>
+        <v>128399922</v>
       </c>
       <c r="B103" t="n">
-        <v>91476</v>
+        <v>91460</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11675,21 +11685,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11699,10 +11709,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>425987</v>
+        <v>426343</v>
       </c>
       <c r="R103" t="n">
-        <v>7051259</v>
+        <v>7050915</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11761,10 +11771,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128399907</v>
+        <v>128399936</v>
       </c>
       <c r="B104" t="n">
-        <v>57689</v>
+        <v>91478</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11772,21 +11782,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11796,10 +11806,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>426064</v>
+        <v>425967</v>
       </c>
       <c r="R104" t="n">
-        <v>7051249</v>
+        <v>7051278</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11832,11 +11842,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11863,10 +11868,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128399889</v>
+        <v>128399829</v>
       </c>
       <c r="B105" t="n">
-        <v>57689</v>
+        <v>91464</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11874,21 +11879,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11898,10 +11903,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425774</v>
+        <v>426191</v>
       </c>
       <c r="R105" t="n">
-        <v>7051222</v>
+        <v>7050972</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11934,11 +11939,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11965,32 +11965,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399945</v>
+        <v>128399834</v>
       </c>
       <c r="B106" t="n">
-        <v>91476</v>
+        <v>92161</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426062</v>
+        <v>426228</v>
       </c>
       <c r="R106" t="n">
-        <v>7051271</v>
+        <v>7050978</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12062,32 +12062,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399834</v>
+        <v>128399945</v>
       </c>
       <c r="B107" t="n">
-        <v>92155</v>
+        <v>91482</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12097,10 +12097,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426228</v>
+        <v>426062</v>
       </c>
       <c r="R107" t="n">
-        <v>7050978</v>
+        <v>7051271</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12159,7 +12159,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399903</v>
+        <v>128399863</v>
       </c>
       <c r="B108" t="n">
         <v>57689</v>
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>425972</v>
+        <v>426347</v>
       </c>
       <c r="R108" t="n">
-        <v>7051285</v>
+        <v>7050960</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12261,7 +12261,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399863</v>
+        <v>128399868</v>
       </c>
       <c r="B109" t="n">
         <v>57689</v>
@@ -12296,10 +12296,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426347</v>
+        <v>426274</v>
       </c>
       <c r="R109" t="n">
-        <v>7050960</v>
+        <v>7050964</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12363,7 +12363,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399868</v>
+        <v>128399903</v>
       </c>
       <c r="B110" t="n">
         <v>57689</v>
@@ -12398,10 +12398,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>426274</v>
+        <v>425972</v>
       </c>
       <c r="R110" t="n">
-        <v>7050964</v>
+        <v>7051285</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12570,7 +12570,7 @@
         <v>128399935</v>
       </c>
       <c r="B112" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12664,32 +12664,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128399943</v>
+        <v>128399833</v>
       </c>
       <c r="B113" t="n">
-        <v>91476</v>
+        <v>92161</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>425756</v>
+        <v>426263</v>
       </c>
       <c r="R113" t="n">
-        <v>7051245</v>
+        <v>7051287</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12761,10 +12761,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128399833</v>
+        <v>128399831</v>
       </c>
       <c r="B114" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426263</v>
+        <v>426425</v>
       </c>
       <c r="R114" t="n">
-        <v>7051287</v>
+        <v>7051289</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12858,32 +12858,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399831</v>
+        <v>128399943</v>
       </c>
       <c r="B115" t="n">
-        <v>92155</v>
+        <v>91482</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426425</v>
+        <v>425756</v>
       </c>
       <c r="R115" t="n">
-        <v>7051289</v>
+        <v>7051245</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13162,7 +13162,7 @@
         <v>128399838</v>
       </c>
       <c r="B118" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>128399928</v>
       </c>
       <c r="B119" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399872</v>
+        <v>128399852</v>
       </c>
       <c r="B120" t="n">
         <v>57689</v>
@@ -13388,10 +13388,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426187</v>
+        <v>426765</v>
       </c>
       <c r="R120" t="n">
-        <v>7050975</v>
+        <v>7051373</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13455,7 +13455,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399853</v>
+        <v>128399914</v>
       </c>
       <c r="B121" t="n">
         <v>57689</v>
@@ -13484,24 +13484,16 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426736</v>
+        <v>426219</v>
       </c>
       <c r="R121" t="n">
-        <v>7051344</v>
+        <v>7051364</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13538,7 +13530,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13565,7 +13557,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399914</v>
+        <v>128399897</v>
       </c>
       <c r="B122" t="n">
         <v>57689</v>
@@ -13600,10 +13592,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>426219</v>
+        <v>425892</v>
       </c>
       <c r="R122" t="n">
-        <v>7051364</v>
+        <v>7051251</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13640,7 +13632,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13667,7 +13659,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399852</v>
+        <v>128399853</v>
       </c>
       <c r="B123" t="n">
         <v>57689</v>
@@ -13696,16 +13688,24 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>426765</v>
+        <v>426736</v>
       </c>
       <c r="R123" t="n">
-        <v>7051373</v>
+        <v>7051344</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13769,7 +13769,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128399897</v>
+        <v>128399871</v>
       </c>
       <c r="B124" t="n">
         <v>57689</v>
@@ -13804,10 +13804,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>425892</v>
+        <v>426154</v>
       </c>
       <c r="R124" t="n">
-        <v>7051251</v>
+        <v>7050994</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13973,7 +13973,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399871</v>
+        <v>128399872</v>
       </c>
       <c r="B126" t="n">
         <v>57689</v>
@@ -14008,10 +14008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426154</v>
+        <v>426187</v>
       </c>
       <c r="R126" t="n">
-        <v>7050994</v>
+        <v>7050975</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14075,10 +14075,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128399920</v>
+        <v>128399942</v>
       </c>
       <c r="B127" t="n">
-        <v>91454</v>
+        <v>91482</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>426277</v>
+        <v>425904</v>
       </c>
       <c r="R127" t="n">
-        <v>7051183</v>
+        <v>7051248</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14172,10 +14172,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128399942</v>
+        <v>128399901</v>
       </c>
       <c r="B128" t="n">
-        <v>91476</v>
+        <v>57689</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14183,21 +14183,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14207,10 +14207,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425904</v>
+        <v>425880</v>
       </c>
       <c r="R128" t="n">
-        <v>7051248</v>
+        <v>7051304</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14243,6 +14243,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14269,10 +14274,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399948</v>
+        <v>128399878</v>
       </c>
       <c r="B129" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14280,21 +14285,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14304,10 +14309,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426395</v>
+        <v>426047</v>
       </c>
       <c r="R129" t="n">
-        <v>7051398</v>
+        <v>7051186</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14344,7 +14349,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14371,7 +14376,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128399901</v>
+        <v>128399905</v>
       </c>
       <c r="B130" t="n">
         <v>57689</v>
@@ -14406,10 +14411,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>425880</v>
+        <v>426029</v>
       </c>
       <c r="R130" t="n">
-        <v>7051304</v>
+        <v>7051287</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14446,7 +14451,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14473,7 +14478,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399878</v>
+        <v>128399876</v>
       </c>
       <c r="B131" t="n">
         <v>57689</v>
@@ -14508,10 +14513,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426047</v>
+        <v>426244</v>
       </c>
       <c r="R131" t="n">
-        <v>7051186</v>
+        <v>7051052</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14548,7 +14553,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14575,10 +14580,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399876</v>
+        <v>128399948</v>
       </c>
       <c r="B132" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14586,21 +14591,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14610,10 +14615,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>426244</v>
+        <v>426395</v>
       </c>
       <c r="R132" t="n">
-        <v>7051052</v>
+        <v>7051398</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14650,7 +14655,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14677,10 +14682,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399905</v>
+        <v>128399920</v>
       </c>
       <c r="B133" t="n">
-        <v>57689</v>
+        <v>91460</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14688,21 +14693,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14712,10 +14717,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426029</v>
+        <v>426277</v>
       </c>
       <c r="R133" t="n">
-        <v>7051287</v>
+        <v>7051183</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14748,11 +14753,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14779,10 +14779,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128399918</v>
+        <v>128399930</v>
       </c>
       <c r="B134" t="n">
-        <v>91408</v>
+        <v>91478</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14790,21 +14790,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14814,10 +14814,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>426224</v>
+        <v>426267</v>
       </c>
       <c r="R134" t="n">
-        <v>7050981</v>
+        <v>7050942</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14876,10 +14876,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128399930</v>
+        <v>128399918</v>
       </c>
       <c r="B135" t="n">
-        <v>91472</v>
+        <v>91414</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14887,21 +14887,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>426267</v>
+        <v>426224</v>
       </c>
       <c r="R135" t="n">
-        <v>7050942</v>
+        <v>7050981</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14976,7 +14976,7 @@
         <v>128399931</v>
       </c>
       <c r="B136" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>128399929</v>
       </c>
       <c r="B137" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128399867</v>
+        <v>128399910</v>
       </c>
       <c r="B139" t="n">
         <v>57689</v>
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>426331</v>
+        <v>426170</v>
       </c>
       <c r="R139" t="n">
-        <v>7050912</v>
+        <v>7051345</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15371,7 +15371,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128399906</v>
+        <v>128399879</v>
       </c>
       <c r="B140" t="n">
         <v>57689</v>
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>426053</v>
+        <v>426055</v>
       </c>
       <c r="R140" t="n">
-        <v>7051256</v>
+        <v>7051223</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15473,7 +15473,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128399879</v>
+        <v>128399890</v>
       </c>
       <c r="B141" t="n">
         <v>57689</v>
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>426055</v>
+        <v>425829</v>
       </c>
       <c r="R141" t="n">
-        <v>7051223</v>
+        <v>7051228</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15575,7 +15575,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128399896</v>
+        <v>128399906</v>
       </c>
       <c r="B142" t="n">
         <v>57689</v>
@@ -15610,10 +15610,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>425889</v>
+        <v>426053</v>
       </c>
       <c r="R142" t="n">
-        <v>7051248</v>
+        <v>7051256</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15677,7 +15677,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128399890</v>
+        <v>128399867</v>
       </c>
       <c r="B143" t="n">
         <v>57689</v>
@@ -15712,10 +15712,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>425829</v>
+        <v>426331</v>
       </c>
       <c r="R143" t="n">
-        <v>7051228</v>
+        <v>7050912</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15779,7 +15779,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128399910</v>
+        <v>128399896</v>
       </c>
       <c r="B144" t="n">
         <v>57689</v>
@@ -15814,10 +15814,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>426170</v>
+        <v>425889</v>
       </c>
       <c r="R144" t="n">
-        <v>7051345</v>
+        <v>7051248</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15881,10 +15881,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128399933</v>
+        <v>128399880</v>
       </c>
       <c r="B145" t="n">
-        <v>91472</v>
+        <v>57689</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15892,21 +15892,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15916,10 +15916,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>426218</v>
+        <v>425981</v>
       </c>
       <c r="R145" t="n">
-        <v>7051146</v>
+        <v>7051240</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15952,6 +15952,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15978,10 +15983,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128399880</v>
+        <v>128399933</v>
       </c>
       <c r="B146" t="n">
-        <v>57689</v>
+        <v>91478</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15989,21 +15994,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16013,10 +16018,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>425981</v>
+        <v>426218</v>
       </c>
       <c r="R146" t="n">
-        <v>7051240</v>
+        <v>7051146</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16049,11 +16054,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16185,7 +16185,7 @@
         <v>128399828</v>
       </c>
       <c r="B148" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>128399946</v>
       </c>
       <c r="B149" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>128399937</v>
       </c>
       <c r="B150" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128399892</v>
+        <v>128399883</v>
       </c>
       <c r="B151" t="n">
         <v>57689</v>
@@ -16508,10 +16508,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>425853</v>
+        <v>425851</v>
       </c>
       <c r="R151" t="n">
-        <v>7051216</v>
+        <v>7051202</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16548,7 +16548,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16575,7 +16575,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128399883</v>
+        <v>128399892</v>
       </c>
       <c r="B152" t="n">
         <v>57689</v>
@@ -16610,10 +16610,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>425851</v>
+        <v>425853</v>
       </c>
       <c r="R152" t="n">
-        <v>7051202</v>
+        <v>7051216</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16881,7 +16881,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128399885</v>
+        <v>128399911</v>
       </c>
       <c r="B155" t="n">
         <v>57689</v>
@@ -16916,10 +16916,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>425748</v>
+        <v>426174</v>
       </c>
       <c r="R155" t="n">
-        <v>7051212</v>
+        <v>7051335</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16983,7 +16983,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128399911</v>
+        <v>128399885</v>
       </c>
       <c r="B156" t="n">
         <v>57689</v>
@@ -17018,10 +17018,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>426174</v>
+        <v>425748</v>
       </c>
       <c r="R156" t="n">
-        <v>7051335</v>
+        <v>7051212</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17190,7 +17190,7 @@
         <v>128399839</v>
       </c>
       <c r="B158" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>128399827</v>
       </c>
       <c r="B159" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>128399837</v>
       </c>
       <c r="B162" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17682,32 +17682,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128399926</v>
+        <v>128399840</v>
       </c>
       <c r="B163" t="n">
-        <v>91454</v>
+        <v>92161</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17717,10 +17717,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>426189</v>
+        <v>426131</v>
       </c>
       <c r="R163" t="n">
-        <v>7051364</v>
+        <v>7051242</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17779,10 +17779,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128399874</v>
+        <v>128399926</v>
       </c>
       <c r="B164" t="n">
-        <v>57689</v>
+        <v>91460</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17790,21 +17790,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17814,10 +17814,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>426194</v>
+        <v>426189</v>
       </c>
       <c r="R164" t="n">
-        <v>7050979</v>
+        <v>7051364</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17850,11 +17850,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17983,32 +17978,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128399840</v>
+        <v>128399874</v>
       </c>
       <c r="B166" t="n">
-        <v>92155</v>
+        <v>57689</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18018,10 +18013,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>426131</v>
+        <v>426194</v>
       </c>
       <c r="R166" t="n">
-        <v>7051242</v>
+        <v>7050979</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18054,6 +18049,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18080,32 +18080,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128399934</v>
+        <v>128399843</v>
       </c>
       <c r="B167" t="n">
-        <v>91472</v>
+        <v>92161</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18115,10 +18115,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>426135</v>
+        <v>426425</v>
       </c>
       <c r="R167" t="n">
-        <v>7051163</v>
+        <v>7051273</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18177,32 +18177,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128399843</v>
+        <v>128399934</v>
       </c>
       <c r="B168" t="n">
-        <v>92155</v>
+        <v>91478</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18212,10 +18212,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>426425</v>
+        <v>426135</v>
       </c>
       <c r="R168" t="n">
-        <v>7051273</v>
+        <v>7051163</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18481,7 +18481,7 @@
         <v>128399938</v>
       </c>
       <c r="B171" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18575,32 +18575,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128399835</v>
+        <v>128399882</v>
       </c>
       <c r="B172" t="n">
-        <v>92155</v>
+        <v>57689</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18610,10 +18610,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>426132</v>
+        <v>425864</v>
       </c>
       <c r="R172" t="n">
-        <v>7051150</v>
+        <v>7051211</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18646,6 +18646,11 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18672,32 +18677,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128399921</v>
+        <v>128399835</v>
       </c>
       <c r="B173" t="n">
-        <v>91454</v>
+        <v>92161</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18707,10 +18712,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>426314</v>
+        <v>426132</v>
       </c>
       <c r="R173" t="n">
-        <v>7050963</v>
+        <v>7051150</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18769,10 +18774,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128399884</v>
+        <v>128399921</v>
       </c>
       <c r="B174" t="n">
-        <v>57689</v>
+        <v>91460</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18780,21 +18785,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18804,10 +18809,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>425770</v>
+        <v>426314</v>
       </c>
       <c r="R174" t="n">
-        <v>7051183</v>
+        <v>7050963</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18840,11 +18845,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18871,7 +18871,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128399893</v>
+        <v>128399887</v>
       </c>
       <c r="B175" t="n">
         <v>57689</v>
@@ -18906,10 +18906,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425861</v>
+        <v>425756</v>
       </c>
       <c r="R175" t="n">
-        <v>7051227</v>
+        <v>7051229</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18973,7 +18973,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128399887</v>
+        <v>128399893</v>
       </c>
       <c r="B176" t="n">
         <v>57689</v>
@@ -19008,10 +19008,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425756</v>
+        <v>425861</v>
       </c>
       <c r="R176" t="n">
-        <v>7051229</v>
+        <v>7051227</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19075,7 +19075,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128399882</v>
+        <v>128399884</v>
       </c>
       <c r="B177" t="n">
         <v>57689</v>
@@ -19110,10 +19110,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>425864</v>
+        <v>425770</v>
       </c>
       <c r="R177" t="n">
-        <v>7051211</v>
+        <v>7051183</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19287,7 +19287,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399894</v>
+        <v>128399915</v>
       </c>
       <c r="B179" t="n">
         <v>57689</v>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>425875</v>
+        <v>426224</v>
       </c>
       <c r="R179" t="n">
-        <v>7051223</v>
+        <v>7051367</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19389,7 +19389,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128399915</v>
+        <v>128399860</v>
       </c>
       <c r="B180" t="n">
         <v>57689</v>
@@ -19424,10 +19424,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>426224</v>
+        <v>426309</v>
       </c>
       <c r="R180" t="n">
-        <v>7051367</v>
+        <v>7051245</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19464,7 +19464,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19491,10 +19491,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399923</v>
+        <v>128399894</v>
       </c>
       <c r="B181" t="n">
-        <v>91454</v>
+        <v>57689</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19502,21 +19502,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19526,10 +19526,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>426172</v>
+        <v>425875</v>
       </c>
       <c r="R181" t="n">
-        <v>7051169</v>
+        <v>7051223</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19562,6 +19562,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19588,10 +19593,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128399932</v>
+        <v>128399891</v>
       </c>
       <c r="B182" t="n">
-        <v>91472</v>
+        <v>57689</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19599,21 +19604,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19623,10 +19628,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>426231</v>
+        <v>425844</v>
       </c>
       <c r="R182" t="n">
-        <v>7051130</v>
+        <v>7051240</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19659,6 +19664,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19685,10 +19695,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128399944</v>
+        <v>128399912</v>
       </c>
       <c r="B183" t="n">
-        <v>91476</v>
+        <v>57689</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19696,21 +19706,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19720,10 +19730,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>425889</v>
+        <v>426175</v>
       </c>
       <c r="R183" t="n">
-        <v>7051300</v>
+        <v>7051336</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19756,6 +19766,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19782,10 +19797,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128399950</v>
+        <v>128399944</v>
       </c>
       <c r="B184" t="n">
-        <v>88859</v>
+        <v>91482</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19793,21 +19808,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19817,10 +19832,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>426303</v>
+        <v>425889</v>
       </c>
       <c r="R184" t="n">
-        <v>7050905</v>
+        <v>7051300</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19879,10 +19894,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128399951</v>
+        <v>128399950</v>
       </c>
       <c r="B185" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19914,10 +19929,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>426062</v>
+        <v>426303</v>
       </c>
       <c r="R185" t="n">
-        <v>7051265</v>
+        <v>7050905</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19976,10 +19991,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128399912</v>
+        <v>128399951</v>
       </c>
       <c r="B186" t="n">
-        <v>57689</v>
+        <v>88865</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19987,21 +20002,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20011,10 +20026,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>426175</v>
+        <v>426062</v>
       </c>
       <c r="R186" t="n">
-        <v>7051336</v>
+        <v>7051265</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20047,11 +20062,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20078,10 +20088,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128399860</v>
+        <v>128399932</v>
       </c>
       <c r="B187" t="n">
-        <v>57689</v>
+        <v>91478</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20089,21 +20099,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20113,10 +20123,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>426309</v>
+        <v>426231</v>
       </c>
       <c r="R187" t="n">
-        <v>7051245</v>
+        <v>7051130</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20149,11 +20159,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20180,10 +20185,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128399891</v>
+        <v>128399923</v>
       </c>
       <c r="B188" t="n">
-        <v>57689</v>
+        <v>91460</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20191,21 +20196,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20215,10 +20220,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>425844</v>
+        <v>426172</v>
       </c>
       <c r="R188" t="n">
-        <v>7051240</v>
+        <v>7051169</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20251,11 +20256,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399873</v>
+        <v>128399939</v>
       </c>
       <c r="B189" t="n">
-        <v>57689</v>
+        <v>91482</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426193</v>
+        <v>426300</v>
       </c>
       <c r="R189" t="n">
-        <v>7050977</v>
+        <v>7051058</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20353,11 +20353,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20384,10 +20379,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399862</v>
+        <v>128399925</v>
       </c>
       <c r="B190" t="n">
-        <v>57689</v>
+        <v>91460</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20395,21 +20390,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20419,10 +20414,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426292</v>
+        <v>426047</v>
       </c>
       <c r="R190" t="n">
-        <v>7050995</v>
+        <v>7051252</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20455,11 +20450,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20486,10 +20476,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B191" t="n">
-        <v>91454</v>
+        <v>57689</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20497,21 +20487,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20521,10 +20511,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R191" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20557,6 +20547,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20583,10 +20578,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399939</v>
+        <v>128399862</v>
       </c>
       <c r="B192" t="n">
-        <v>91476</v>
+        <v>57689</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20594,21 +20589,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20618,10 +20613,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426300</v>
+        <v>426292</v>
       </c>
       <c r="R192" t="n">
-        <v>7051058</v>
+        <v>7050995</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20654,6 +20649,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -2569,32 +2569,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128398821</v>
+        <v>128398773</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>75173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426200</v>
+        <v>425978</v>
       </c>
       <c r="R19" t="n">
-        <v>7051338</v>
+        <v>7051231</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398753</v>
+        <v>128398821</v>
       </c>
       <c r="B20" t="n">
-        <v>80192</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426191</v>
+        <v>426200</v>
       </c>
       <c r="R20" t="n">
-        <v>7050957</v>
+        <v>7051338</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,21 +2767,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2798,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398730</v>
+        <v>128398753</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2809,21 +2794,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2833,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426382</v>
+        <v>426191</v>
       </c>
       <c r="R21" t="n">
-        <v>7051149</v>
+        <v>7050957</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2868,7 +2853,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2878,7 +2863,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2889,6 +2874,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2905,32 +2905,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398773</v>
+        <v>128398730</v>
       </c>
       <c r="B22" t="n">
-        <v>75173</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425978</v>
+        <v>426382</v>
       </c>
       <c r="R22" t="n">
-        <v>7051231</v>
+        <v>7051149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3012,32 +3012,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398803</v>
+        <v>128398729</v>
       </c>
       <c r="B23" t="n">
-        <v>92161</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425994</v>
+        <v>426468</v>
       </c>
       <c r="R23" t="n">
-        <v>7051287</v>
+        <v>7051179</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398729</v>
+        <v>128398752</v>
       </c>
       <c r="B24" t="n">
         <v>79087</v>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426468</v>
+        <v>426206</v>
       </c>
       <c r="R24" t="n">
-        <v>7051179</v>
+        <v>7050935</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,32 +3226,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398752</v>
+        <v>128398803</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>92161</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426206</v>
+        <v>425994</v>
       </c>
       <c r="R25" t="n">
-        <v>7050935</v>
+        <v>7051287</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,32 +3333,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398718</v>
+        <v>128398771</v>
       </c>
       <c r="B26" t="n">
-        <v>92766</v>
+        <v>91482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426807</v>
+        <v>426068</v>
       </c>
       <c r="R26" t="n">
-        <v>7051311</v>
+        <v>7051189</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3440,32 +3440,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398771</v>
+        <v>128398770</v>
       </c>
       <c r="B27" t="n">
-        <v>91482</v>
+        <v>91918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426068</v>
+        <v>426115</v>
       </c>
       <c r="R27" t="n">
-        <v>7051189</v>
+        <v>7051178</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,32 +3547,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398770</v>
+        <v>128398718</v>
       </c>
       <c r="B28" t="n">
-        <v>91918</v>
+        <v>92766</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426115</v>
+        <v>426807</v>
       </c>
       <c r="R28" t="n">
-        <v>7051178</v>
+        <v>7051311</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398791</v>
+        <v>128398819</v>
       </c>
       <c r="B31" t="n">
-        <v>75167</v>
+        <v>91464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425847</v>
+        <v>426181</v>
       </c>
       <c r="R31" t="n">
-        <v>7051261</v>
+        <v>7051325</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,21 +3968,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3999,32 +3984,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398819</v>
+        <v>128398788</v>
       </c>
       <c r="B32" t="n">
-        <v>91464</v>
+        <v>75166</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4034,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426181</v>
+        <v>425804</v>
       </c>
       <c r="R32" t="n">
-        <v>7051325</v>
+        <v>7051255</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4069,7 +4054,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4079,7 +4064,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4090,6 +4075,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Glasbjörk</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4106,32 +4096,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398788</v>
+        <v>128398791</v>
       </c>
       <c r="B33" t="n">
-        <v>75166</v>
+        <v>75167</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4141,10 +4131,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425804</v>
+        <v>425847</v>
       </c>
       <c r="R33" t="n">
-        <v>7051255</v>
+        <v>7051261</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4176,7 +4166,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4186,7 +4176,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4198,9 +4188,19 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Glasbjörk</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398800</v>
+        <v>128398787</v>
       </c>
       <c r="B43" t="n">
-        <v>91478</v>
+        <v>75167</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425985</v>
+        <v>425795</v>
       </c>
       <c r="R43" t="n">
-        <v>7051282</v>
+        <v>7051251</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128398749</v>
+        <v>128398800</v>
       </c>
       <c r="B44" t="n">
-        <v>86776</v>
+        <v>91478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>427</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426252</v>
+        <v>425985</v>
       </c>
       <c r="R44" t="n">
-        <v>7050919</v>
+        <v>7051282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5378,12 +5378,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5410,10 +5405,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128398787</v>
+        <v>128398749</v>
       </c>
       <c r="B45" t="n">
-        <v>75167</v>
+        <v>86776</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,21 +5416,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>308</v>
+        <v>427</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5445,10 +5440,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425795</v>
+        <v>426252</v>
       </c>
       <c r="R45" t="n">
-        <v>7051251</v>
+        <v>7050919</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5480,7 +5475,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5490,7 +5485,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398726</v>
+        <v>128398783</v>
       </c>
       <c r="B61" t="n">
-        <v>75166</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426522</v>
+        <v>425733</v>
       </c>
       <c r="R61" t="n">
-        <v>7051242</v>
+        <v>7051205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,21 +7281,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7312,32 +7297,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398769</v>
+        <v>128398726</v>
       </c>
       <c r="B62" t="n">
-        <v>91464</v>
+        <v>75166</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7347,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426135</v>
+        <v>426522</v>
       </c>
       <c r="R62" t="n">
-        <v>7051154</v>
+        <v>7051242</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7382,7 +7367,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7392,7 +7377,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7403,6 +7388,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7419,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128398783</v>
+        <v>128398769</v>
       </c>
       <c r="B63" t="n">
-        <v>79087</v>
+        <v>91464</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,21 +7430,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>425733</v>
+        <v>426135</v>
       </c>
       <c r="R63" t="n">
-        <v>7051205</v>
+        <v>7051154</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128399895</v>
+        <v>128399888</v>
       </c>
       <c r="B89" t="n">
         <v>57689</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>425879</v>
+        <v>425774</v>
       </c>
       <c r="R89" t="n">
-        <v>7051238</v>
+        <v>7051220</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128399916</v>
+        <v>128399875</v>
       </c>
       <c r="B90" t="n">
         <v>57689</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>426279</v>
+        <v>426207</v>
       </c>
       <c r="R90" t="n">
-        <v>7051408</v>
+        <v>7051009</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10475,7 +10475,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399888</v>
+        <v>128399895</v>
       </c>
       <c r="B91" t="n">
         <v>57689</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>425774</v>
+        <v>425879</v>
       </c>
       <c r="R91" t="n">
-        <v>7051220</v>
+        <v>7051238</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128399875</v>
+        <v>128399916</v>
       </c>
       <c r="B92" t="n">
         <v>57689</v>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>426207</v>
+        <v>426279</v>
       </c>
       <c r="R92" t="n">
-        <v>7051009</v>
+        <v>7051408</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11475,10 +11475,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399889</v>
+        <v>128399941</v>
       </c>
       <c r="B101" t="n">
-        <v>57689</v>
+        <v>91482</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11486,21 +11486,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425774</v>
+        <v>425987</v>
       </c>
       <c r="R101" t="n">
-        <v>7051222</v>
+        <v>7051259</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11546,11 +11546,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11577,10 +11572,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399941</v>
+        <v>128399922</v>
       </c>
       <c r="B102" t="n">
-        <v>91482</v>
+        <v>91460</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11588,21 +11583,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11612,10 +11607,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425987</v>
+        <v>426343</v>
       </c>
       <c r="R102" t="n">
-        <v>7051259</v>
+        <v>7050915</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11674,10 +11669,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399922</v>
+        <v>128399936</v>
       </c>
       <c r="B103" t="n">
-        <v>91460</v>
+        <v>91478</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11685,21 +11680,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11709,10 +11704,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426343</v>
+        <v>425967</v>
       </c>
       <c r="R103" t="n">
-        <v>7050915</v>
+        <v>7051278</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11771,10 +11766,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128399936</v>
+        <v>128399829</v>
       </c>
       <c r="B104" t="n">
-        <v>91478</v>
+        <v>91464</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11782,21 +11777,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11806,10 +11801,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>425967</v>
+        <v>426191</v>
       </c>
       <c r="R104" t="n">
-        <v>7051278</v>
+        <v>7050972</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11868,10 +11863,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128399829</v>
+        <v>128399889</v>
       </c>
       <c r="B105" t="n">
-        <v>91464</v>
+        <v>57689</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11879,21 +11874,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11903,10 +11898,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>426191</v>
+        <v>425774</v>
       </c>
       <c r="R105" t="n">
-        <v>7050972</v>
+        <v>7051222</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11939,6 +11934,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11965,32 +11965,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399834</v>
+        <v>128399863</v>
       </c>
       <c r="B106" t="n">
-        <v>92161</v>
+        <v>57689</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426228</v>
+        <v>426347</v>
       </c>
       <c r="R106" t="n">
-        <v>7050978</v>
+        <v>7050960</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12036,6 +12036,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12062,10 +12067,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399945</v>
+        <v>128399868</v>
       </c>
       <c r="B107" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12073,21 +12078,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12097,10 +12102,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426062</v>
+        <v>426274</v>
       </c>
       <c r="R107" t="n">
-        <v>7051271</v>
+        <v>7050964</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12133,6 +12138,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12159,7 +12169,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399863</v>
+        <v>128399903</v>
       </c>
       <c r="B108" t="n">
         <v>57689</v>
@@ -12194,10 +12204,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>426347</v>
+        <v>425972</v>
       </c>
       <c r="R108" t="n">
-        <v>7050960</v>
+        <v>7051285</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12261,7 +12271,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399868</v>
+        <v>128399881</v>
       </c>
       <c r="B109" t="n">
         <v>57689</v>
@@ -12296,10 +12306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426274</v>
+        <v>425942</v>
       </c>
       <c r="R109" t="n">
-        <v>7050964</v>
+        <v>7051274</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12336,7 +12346,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12363,32 +12373,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399903</v>
+        <v>128399834</v>
       </c>
       <c r="B110" t="n">
-        <v>57689</v>
+        <v>92161</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12398,10 +12408,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>425972</v>
+        <v>426228</v>
       </c>
       <c r="R110" t="n">
-        <v>7051285</v>
+        <v>7050978</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12434,11 +12444,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12465,10 +12470,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128399881</v>
+        <v>128399945</v>
       </c>
       <c r="B111" t="n">
-        <v>57689</v>
+        <v>91482</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12476,21 +12481,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12500,10 +12505,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>425942</v>
+        <v>426062</v>
       </c>
       <c r="R111" t="n">
-        <v>7051274</v>
+        <v>7051271</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12536,11 +12541,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13256,10 +13256,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399928</v>
+        <v>128399852</v>
       </c>
       <c r="B119" t="n">
-        <v>91478</v>
+        <v>57689</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13267,21 +13267,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426319</v>
+        <v>426765</v>
       </c>
       <c r="R119" t="n">
-        <v>7051238</v>
+        <v>7051373</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13327,6 +13327,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13353,7 +13358,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399852</v>
+        <v>128399914</v>
       </c>
       <c r="B120" t="n">
         <v>57689</v>
@@ -13388,10 +13393,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426765</v>
+        <v>426219</v>
       </c>
       <c r="R120" t="n">
-        <v>7051373</v>
+        <v>7051364</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13455,7 +13460,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399914</v>
+        <v>128399897</v>
       </c>
       <c r="B121" t="n">
         <v>57689</v>
@@ -13490,10 +13495,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426219</v>
+        <v>425892</v>
       </c>
       <c r="R121" t="n">
-        <v>7051364</v>
+        <v>7051251</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13530,7 +13535,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13557,7 +13562,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399897</v>
+        <v>128399853</v>
       </c>
       <c r="B122" t="n">
         <v>57689</v>
@@ -13586,16 +13591,24 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>425892</v>
+        <v>426736</v>
       </c>
       <c r="R122" t="n">
-        <v>7051251</v>
+        <v>7051344</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13632,7 +13645,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13659,10 +13672,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399853</v>
+        <v>128399928</v>
       </c>
       <c r="B123" t="n">
-        <v>57689</v>
+        <v>91478</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13670,42 +13683,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>426736</v>
+        <v>426319</v>
       </c>
       <c r="R123" t="n">
-        <v>7051344</v>
+        <v>7051238</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13738,11 +13743,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14876,10 +14876,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128399918</v>
+        <v>128399931</v>
       </c>
       <c r="B135" t="n">
-        <v>91414</v>
+        <v>91478</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14887,21 +14887,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>426224</v>
+        <v>426252</v>
       </c>
       <c r="R135" t="n">
-        <v>7050981</v>
+        <v>7050958</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14973,7 +14973,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128399931</v>
+        <v>128399929</v>
       </c>
       <c r="B136" t="n">
         <v>91478</v>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>426252</v>
+        <v>426276</v>
       </c>
       <c r="R136" t="n">
-        <v>7050958</v>
+        <v>7050944</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15070,10 +15070,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128399929</v>
+        <v>128399918</v>
       </c>
       <c r="B137" t="n">
-        <v>91478</v>
+        <v>91414</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15081,21 +15081,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15105,10 +15105,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>426276</v>
+        <v>426224</v>
       </c>
       <c r="R137" t="n">
-        <v>7050944</v>
+        <v>7050981</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15881,10 +15881,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128399880</v>
+        <v>128399933</v>
       </c>
       <c r="B145" t="n">
-        <v>57689</v>
+        <v>91478</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15892,21 +15892,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15916,10 +15916,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425981</v>
+        <v>426218</v>
       </c>
       <c r="R145" t="n">
-        <v>7051240</v>
+        <v>7051146</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15952,11 +15952,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15983,10 +15978,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128399933</v>
+        <v>128399880</v>
       </c>
       <c r="B146" t="n">
-        <v>91478</v>
+        <v>57689</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15994,21 +15989,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16018,10 +16013,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>426218</v>
+        <v>425981</v>
       </c>
       <c r="R146" t="n">
-        <v>7051146</v>
+        <v>7051240</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16054,6 +16049,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399939</v>
+        <v>128399925</v>
       </c>
       <c r="B189" t="n">
-        <v>91482</v>
+        <v>91460</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426300</v>
+        <v>426047</v>
       </c>
       <c r="R189" t="n">
-        <v>7051058</v>
+        <v>7051252</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20379,10 +20379,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B190" t="n">
-        <v>91460</v>
+        <v>57689</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20390,21 +20390,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20414,10 +20414,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R190" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20450,6 +20450,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20476,7 +20481,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399873</v>
+        <v>128399862</v>
       </c>
       <c r="B191" t="n">
         <v>57689</v>
@@ -20511,10 +20516,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426193</v>
+        <v>426292</v>
       </c>
       <c r="R191" t="n">
-        <v>7050977</v>
+        <v>7050995</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20551,7 +20556,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20578,10 +20583,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399862</v>
+        <v>128399939</v>
       </c>
       <c r="B192" t="n">
-        <v>57689</v>
+        <v>91482</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20589,21 +20594,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20613,10 +20618,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426292</v>
+        <v>426300</v>
       </c>
       <c r="R192" t="n">
-        <v>7050995</v>
+        <v>7051058</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20649,11 +20654,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128398722</v>
+        <v>128398786</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>75169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426695</v>
+        <v>425776</v>
       </c>
       <c r="R2" t="n">
-        <v>7051338</v>
+        <v>7051259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +766,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128398798</v>
+        <v>128398758</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425947</v>
+        <v>426187</v>
       </c>
       <c r="R3" t="n">
-        <v>7051321</v>
+        <v>7051025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128398786</v>
+        <v>128398759</v>
       </c>
       <c r="B4" t="n">
-        <v>75167</v>
+        <v>88867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425776</v>
+        <v>426187</v>
       </c>
       <c r="R4" t="n">
-        <v>7051259</v>
+        <v>7051025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,21 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128398758</v>
+        <v>128398722</v>
       </c>
       <c r="B5" t="n">
-        <v>82946</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426187</v>
+        <v>426695</v>
       </c>
       <c r="R5" t="n">
-        <v>7051025</v>
+        <v>7051338</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128398759</v>
+        <v>128398798</v>
       </c>
       <c r="B6" t="n">
-        <v>88865</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426187</v>
+        <v>425947</v>
       </c>
       <c r="R6" t="n">
-        <v>7051025</v>
+        <v>7051321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,7 +1345,7 @@
         <v>128398746</v>
       </c>
       <c r="B8" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128398775</v>
+        <v>128398768</v>
       </c>
       <c r="B9" t="n">
         <v>57689</v>
@@ -1480,7 +1480,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425892</v>
+        <v>426158</v>
       </c>
       <c r="R9" t="n">
-        <v>7051220</v>
+        <v>7051146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128398774</v>
+        <v>128398775</v>
       </c>
       <c r="B10" t="n">
         <v>57689</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425970</v>
+        <v>425892</v>
       </c>
       <c r="R10" t="n">
-        <v>7051235</v>
+        <v>7051220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128398768</v>
+        <v>128398774</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1714,7 +1714,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426158</v>
+        <v>425970</v>
       </c>
       <c r="R11" t="n">
-        <v>7051146</v>
+        <v>7051235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128398762</v>
+        <v>128398790</v>
       </c>
       <c r="B12" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426225</v>
+        <v>425825</v>
       </c>
       <c r="R12" t="n">
-        <v>7051098</v>
+        <v>7051257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398790</v>
+        <v>128398762</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425825</v>
+        <v>426225</v>
       </c>
       <c r="R13" t="n">
-        <v>7051257</v>
+        <v>7051098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,12 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,7 +2027,7 @@
         <v>128398811</v>
       </c>
       <c r="B14" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>128398740</v>
       </c>
       <c r="B15" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128398737</v>
+        <v>128398776</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,39 +2249,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426345</v>
+        <v>425869</v>
       </c>
       <c r="R16" t="n">
-        <v>7051102</v>
+        <v>7051201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,12 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:52</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128398776</v>
+        <v>128398824</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425869</v>
+        <v>426331</v>
       </c>
       <c r="R17" t="n">
-        <v>7051201</v>
+        <v>7051374</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2425,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2435,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128398824</v>
+        <v>128398737</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2473,34 +2463,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>426331</v>
+        <v>426345</v>
       </c>
       <c r="R18" t="n">
-        <v>7051374</v>
+        <v>7051102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2532,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2542,7 +2537,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,32 +2569,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128398773</v>
+        <v>128398803</v>
       </c>
       <c r="B19" t="n">
-        <v>75173</v>
+        <v>92163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6486</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425978</v>
+        <v>425994</v>
       </c>
       <c r="R19" t="n">
-        <v>7051231</v>
+        <v>7051287</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398821</v>
+        <v>128398805</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,37 +2687,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426200</v>
+        <v>425999</v>
       </c>
       <c r="R20" t="n">
-        <v>7051338</v>
+        <v>7051258</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,32 +2792,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398753</v>
+        <v>128398718</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>92768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2818,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426191</v>
+        <v>426807</v>
       </c>
       <c r="R21" t="n">
-        <v>7050957</v>
+        <v>7051311</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,21 +2883,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2905,32 +2899,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398730</v>
+        <v>128398770</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2940,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426382</v>
+        <v>426115</v>
       </c>
       <c r="R22" t="n">
-        <v>7051149</v>
+        <v>7051178</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2985,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3012,10 +3006,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398729</v>
+        <v>128398771</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3023,21 +3017,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3047,10 +3041,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426468</v>
+        <v>426068</v>
       </c>
       <c r="R23" t="n">
-        <v>7051179</v>
+        <v>7051189</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,7 +3076,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3086,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,32 +3113,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398752</v>
+        <v>128398773</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>75175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3154,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426206</v>
+        <v>425978</v>
       </c>
       <c r="R24" t="n">
-        <v>7050935</v>
+        <v>7051231</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,7 +3183,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3199,7 +3193,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,32 +3220,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398803</v>
+        <v>128398821</v>
       </c>
       <c r="B25" t="n">
-        <v>92161</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3261,10 +3255,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425994</v>
+        <v>426200</v>
       </c>
       <c r="R25" t="n">
-        <v>7051287</v>
+        <v>7051338</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3296,7 +3290,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3306,7 +3300,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3333,10 +3327,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398771</v>
+        <v>128398753</v>
       </c>
       <c r="B26" t="n">
-        <v>91482</v>
+        <v>80194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3338,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,10 +3362,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426068</v>
+        <v>426191</v>
       </c>
       <c r="R26" t="n">
-        <v>7051189</v>
+        <v>7050957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3403,7 +3397,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3413,7 +3407,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3424,6 +3418,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3440,32 +3449,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398770</v>
+        <v>128398730</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3475,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426115</v>
+        <v>426382</v>
       </c>
       <c r="R27" t="n">
-        <v>7051178</v>
+        <v>7051149</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3510,7 +3519,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3520,7 +3529,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,32 +3556,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398718</v>
+        <v>128398729</v>
       </c>
       <c r="B28" t="n">
-        <v>92766</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3582,10 +3591,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426807</v>
+        <v>426468</v>
       </c>
       <c r="R28" t="n">
-        <v>7051311</v>
+        <v>7051179</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,7 +3626,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3627,7 +3636,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3654,10 +3663,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128398805</v>
+        <v>128398752</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,46 +3674,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>425999</v>
+        <v>426206</v>
       </c>
       <c r="R29" t="n">
-        <v>7051258</v>
+        <v>7050935</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128398724</v>
+        <v>128398819</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>91466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426447</v>
+        <v>426181</v>
       </c>
       <c r="R30" t="n">
-        <v>7051254</v>
+        <v>7051325</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3877,32 +3877,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398819</v>
+        <v>128398788</v>
       </c>
       <c r="B31" t="n">
-        <v>91464</v>
+        <v>75168</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426181</v>
+        <v>425804</v>
       </c>
       <c r="R31" t="n">
-        <v>7051325</v>
+        <v>7051255</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,6 +3968,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Glasbjörk</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3984,32 +3989,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398788</v>
+        <v>128398791</v>
       </c>
       <c r="B32" t="n">
-        <v>75166</v>
+        <v>75169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4019,10 +4024,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425804</v>
+        <v>425847</v>
       </c>
       <c r="R32" t="n">
-        <v>7051255</v>
+        <v>7051261</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4054,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4064,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4076,9 +4081,19 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Glasbjörk</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4096,10 +4111,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398791</v>
+        <v>128398724</v>
       </c>
       <c r="B33" t="n">
-        <v>75167</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,21 +4122,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4131,10 +4146,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425847</v>
+        <v>426447</v>
       </c>
       <c r="R33" t="n">
-        <v>7051261</v>
+        <v>7051254</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4166,7 +4181,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4176,7 +4191,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,21 +4202,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4218,32 +4218,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398755</v>
+        <v>128398801</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>91920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426166</v>
+        <v>425985</v>
       </c>
       <c r="R34" t="n">
-        <v>7050989</v>
+        <v>7051282</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,10 +4325,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128398738</v>
+        <v>128398755</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426341</v>
+        <v>426166</v>
       </c>
       <c r="R35" t="n">
-        <v>7051103</v>
+        <v>7050989</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,10 +4432,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128398794</v>
+        <v>128398738</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425876</v>
+        <v>426341</v>
       </c>
       <c r="R36" t="n">
-        <v>7051324</v>
+        <v>7051103</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4539,32 +4539,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398801</v>
+        <v>128398794</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425985</v>
+        <v>425876</v>
       </c>
       <c r="R37" t="n">
-        <v>7051282</v>
+        <v>7051324</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4766,7 +4766,7 @@
         <v>128398795</v>
       </c>
       <c r="B39" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4870,32 +4870,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128398808</v>
+        <v>128398785</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>92163</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426012</v>
+        <v>425708</v>
       </c>
       <c r="R40" t="n">
-        <v>7051229</v>
+        <v>7051228</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4977,32 +4977,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128398785</v>
+        <v>128398808</v>
       </c>
       <c r="B41" t="n">
-        <v>92161</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425708</v>
+        <v>426012</v>
       </c>
       <c r="R41" t="n">
-        <v>7051228</v>
+        <v>7051229</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,32 +5084,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128398736</v>
+        <v>128398800</v>
       </c>
       <c r="B42" t="n">
-        <v>92161</v>
+        <v>91480</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426352</v>
+        <v>425985</v>
       </c>
       <c r="R42" t="n">
-        <v>7051151</v>
+        <v>7051282</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,32 +5191,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398787</v>
+        <v>128398736</v>
       </c>
       <c r="B43" t="n">
-        <v>75167</v>
+        <v>92163</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425795</v>
+        <v>426352</v>
       </c>
       <c r="R43" t="n">
-        <v>7051251</v>
+        <v>7051151</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128398800</v>
+        <v>128398787</v>
       </c>
       <c r="B44" t="n">
-        <v>91478</v>
+        <v>75169</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425985</v>
+        <v>425795</v>
       </c>
       <c r="R44" t="n">
-        <v>7051282</v>
+        <v>7051251</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5408,7 +5408,7 @@
         <v>128398749</v>
       </c>
       <c r="B45" t="n">
-        <v>86776</v>
+        <v>86778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5517,45 +5517,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128398731</v>
+        <v>128398807</v>
       </c>
       <c r="B46" t="n">
-        <v>92161</v>
+        <v>57689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426369</v>
+        <v>426011</v>
       </c>
       <c r="R46" t="n">
-        <v>7051152</v>
+        <v>7051282</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5587,7 +5592,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5597,7 +5602,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,10 +5634,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398797</v>
+        <v>128398721</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,34 +5645,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425919</v>
+        <v>426773</v>
       </c>
       <c r="R47" t="n">
-        <v>7051350</v>
+        <v>7051349</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5694,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5704,7 +5719,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5731,32 +5751,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128398812</v>
+        <v>128398731</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>92163</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5766,10 +5786,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426097</v>
+        <v>426369</v>
       </c>
       <c r="R48" t="n">
-        <v>7051199</v>
+        <v>7051152</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5801,7 +5821,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5811,7 +5831,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5838,10 +5858,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128398725</v>
+        <v>128398797</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5873,10 +5893,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426492</v>
+        <v>425919</v>
       </c>
       <c r="R49" t="n">
-        <v>7051269</v>
+        <v>7051350</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5908,7 +5928,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5918,7 +5938,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5945,10 +5965,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128398807</v>
+        <v>128398812</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5956,39 +5976,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426011</v>
+        <v>426097</v>
       </c>
       <c r="R50" t="n">
-        <v>7051282</v>
+        <v>7051199</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6020,7 +6035,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6030,12 +6045,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6062,10 +6072,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128398721</v>
+        <v>128398725</v>
       </c>
       <c r="B51" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6073,39 +6083,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426773</v>
+        <v>426492</v>
       </c>
       <c r="R51" t="n">
-        <v>7051349</v>
+        <v>7051269</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6137,7 +6142,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6147,12 +6152,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6182,7 +6182,7 @@
         <v>128398743</v>
       </c>
       <c r="B52" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>128398802</v>
       </c>
       <c r="B53" t="n">
-        <v>91760</v>
+        <v>91762</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6393,50 +6393,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398793</v>
+        <v>128398734</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>425908</v>
+        <v>426329</v>
       </c>
       <c r="R54" t="n">
-        <v>7051281</v>
+        <v>7051146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6468,7 +6463,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6478,12 +6473,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6510,10 +6500,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398814</v>
+        <v>128398727</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6521,39 +6511,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426097</v>
+        <v>426516</v>
       </c>
       <c r="R55" t="n">
-        <v>7051199</v>
+        <v>7051239</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6585,7 +6570,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6595,12 +6580,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6627,50 +6607,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398719</v>
+        <v>128398804</v>
       </c>
       <c r="B56" t="n">
-        <v>57689</v>
+        <v>75175</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426799</v>
+        <v>426000</v>
       </c>
       <c r="R56" t="n">
-        <v>7051328</v>
+        <v>7051290</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6702,7 +6680,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6712,12 +6690,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6725,6 +6698,11 @@
       </c>
       <c r="AE56" t="b">
         <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -6744,7 +6722,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398822</v>
+        <v>128398793</v>
       </c>
       <c r="B57" t="n">
         <v>57689</v>
@@ -6784,10 +6762,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426200</v>
+        <v>425908</v>
       </c>
       <c r="R57" t="n">
-        <v>7051338</v>
+        <v>7051281</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6819,7 +6797,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6829,7 +6807,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6861,10 +6839,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398727</v>
+        <v>128398814</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6872,34 +6850,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426516</v>
+        <v>426097</v>
       </c>
       <c r="R58" t="n">
-        <v>7051239</v>
+        <v>7051199</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6931,7 +6914,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6941,7 +6924,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6968,45 +6956,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398734</v>
+        <v>128398822</v>
       </c>
       <c r="B59" t="n">
-        <v>92161</v>
+        <v>57689</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426329</v>
+        <v>426200</v>
       </c>
       <c r="R59" t="n">
-        <v>7051146</v>
+        <v>7051338</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7038,7 +7031,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7048,7 +7041,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7075,48 +7073,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398804</v>
+        <v>128398719</v>
       </c>
       <c r="B60" t="n">
-        <v>75173</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426000</v>
+        <v>426799</v>
       </c>
       <c r="R60" t="n">
-        <v>7051290</v>
+        <v>7051328</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7158,7 +7158,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7166,11 +7171,6 @@
       </c>
       <c r="AE60" t="b">
         <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398783</v>
+        <v>128398726</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>75168</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>425733</v>
+        <v>426522</v>
       </c>
       <c r="R61" t="n">
-        <v>7051205</v>
+        <v>7051242</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,6 +7281,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7297,32 +7312,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398726</v>
+        <v>128398769</v>
       </c>
       <c r="B62" t="n">
-        <v>75166</v>
+        <v>91466</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7347,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426522</v>
+        <v>426135</v>
       </c>
       <c r="R62" t="n">
-        <v>7051242</v>
+        <v>7051154</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,7 +7382,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7377,7 +7392,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7388,21 +7403,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7419,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128398769</v>
+        <v>128398783</v>
       </c>
       <c r="B63" t="n">
-        <v>91464</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,21 +7430,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426135</v>
+        <v>425733</v>
       </c>
       <c r="R63" t="n">
-        <v>7051154</v>
+        <v>7051205</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7763,7 +7763,7 @@
         <v>128398763</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>128398796</v>
       </c>
       <c r="B67" t="n">
-        <v>78064</v>
+        <v>78066</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7974,32 +7974,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128398733</v>
+        <v>128398820</v>
       </c>
       <c r="B68" t="n">
-        <v>92161</v>
+        <v>91484</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426361</v>
+        <v>426196</v>
       </c>
       <c r="R68" t="n">
-        <v>7051151</v>
+        <v>7051340</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8081,32 +8081,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128398820</v>
+        <v>128398733</v>
       </c>
       <c r="B69" t="n">
-        <v>91482</v>
+        <v>92163</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426196</v>
+        <v>426361</v>
       </c>
       <c r="R69" t="n">
-        <v>7051340</v>
+        <v>7051151</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8191,7 +8191,7 @@
         <v>128398760</v>
       </c>
       <c r="B70" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128398818</v>
+        <v>128398777</v>
       </c>
       <c r="B71" t="n">
-        <v>79087</v>
+        <v>82948</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8306,21 +8306,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426191</v>
+        <v>425861</v>
       </c>
       <c r="R71" t="n">
-        <v>7051296</v>
+        <v>7051195</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8402,10 +8402,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128398777</v>
+        <v>128398818</v>
       </c>
       <c r="B72" t="n">
-        <v>82946</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8413,21 +8413,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>425861</v>
+        <v>426191</v>
       </c>
       <c r="R72" t="n">
-        <v>7051195</v>
+        <v>7051296</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8512,7 +8512,7 @@
         <v>128398720</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>128398815</v>
       </c>
       <c r="B75" t="n">
-        <v>91871</v>
+        <v>91873</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>128398754</v>
       </c>
       <c r="B76" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>128398772</v>
       </c>
       <c r="B77" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>128398813</v>
       </c>
       <c r="B79" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>128398765</v>
       </c>
       <c r="B80" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9395,10 +9395,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128398784</v>
+        <v>128398723</v>
       </c>
       <c r="B81" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9406,39 +9406,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>425712</v>
+        <v>426515</v>
       </c>
       <c r="R81" t="n">
-        <v>7051206</v>
+        <v>7051308</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9470,7 +9465,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9480,12 +9475,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9512,10 +9502,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128398780</v>
+        <v>128398751</v>
       </c>
       <c r="B82" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9523,39 +9513,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>425756</v>
+        <v>426239</v>
       </c>
       <c r="R82" t="n">
-        <v>7051171</v>
+        <v>7050935</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9587,7 +9572,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9597,12 +9582,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9629,10 +9609,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128398723</v>
+        <v>128398780</v>
       </c>
       <c r="B83" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9640,34 +9620,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>426515</v>
+        <v>425756</v>
       </c>
       <c r="R83" t="n">
-        <v>7051308</v>
+        <v>7051171</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9699,7 +9684,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9709,7 +9694,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9736,10 +9726,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128398751</v>
+        <v>128398784</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9747,34 +9737,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>426239</v>
+        <v>425712</v>
       </c>
       <c r="R84" t="n">
-        <v>7050935</v>
+        <v>7051206</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9806,7 +9801,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9816,7 +9811,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9846,7 +9846,7 @@
         <v>128398761</v>
       </c>
       <c r="B85" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128399875</v>
+        <v>128399916</v>
       </c>
       <c r="B90" t="n">
         <v>57689</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>426207</v>
+        <v>426279</v>
       </c>
       <c r="R90" t="n">
-        <v>7051009</v>
+        <v>7051408</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10475,7 +10475,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399895</v>
+        <v>128399875</v>
       </c>
       <c r="B91" t="n">
         <v>57689</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>425879</v>
+        <v>426207</v>
       </c>
       <c r="R91" t="n">
-        <v>7051238</v>
+        <v>7051009</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128399916</v>
+        <v>128399895</v>
       </c>
       <c r="B92" t="n">
         <v>57689</v>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>426279</v>
+        <v>425879</v>
       </c>
       <c r="R92" t="n">
-        <v>7051408</v>
+        <v>7051238</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399940</v>
+        <v>128399949</v>
       </c>
       <c r="B93" t="n">
-        <v>91482</v>
+        <v>88867</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426338</v>
+        <v>426768</v>
       </c>
       <c r="R93" t="n">
-        <v>7050977</v>
+        <v>7051367</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10776,10 +10776,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399949</v>
+        <v>128399849</v>
       </c>
       <c r="B94" t="n">
-        <v>88865</v>
+        <v>57689</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10787,21 +10787,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426768</v>
+        <v>426803</v>
       </c>
       <c r="R94" t="n">
-        <v>7051367</v>
+        <v>7051353</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10847,6 +10847,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10873,10 +10878,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399849</v>
+        <v>128399940</v>
       </c>
       <c r="B95" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10884,21 +10889,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10908,10 +10913,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426803</v>
+        <v>426338</v>
       </c>
       <c r="R95" t="n">
-        <v>7051353</v>
+        <v>7050977</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10944,11 +10949,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10978,7 +10978,7 @@
         <v>128399832</v>
       </c>
       <c r="B96" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>128399836</v>
       </c>
       <c r="B97" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399907</v>
+        <v>128399941</v>
       </c>
       <c r="B100" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426064</v>
+        <v>425987</v>
       </c>
       <c r="R100" t="n">
-        <v>7051249</v>
+        <v>7051259</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11444,11 +11444,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11475,10 +11470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399941</v>
+        <v>128399922</v>
       </c>
       <c r="B101" t="n">
-        <v>91482</v>
+        <v>91462</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11486,21 +11481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11510,10 +11505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425987</v>
+        <v>426343</v>
       </c>
       <c r="R101" t="n">
-        <v>7051259</v>
+        <v>7050915</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11572,10 +11567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399922</v>
+        <v>128399936</v>
       </c>
       <c r="B102" t="n">
-        <v>91460</v>
+        <v>91480</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11583,21 +11578,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11607,10 +11602,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426343</v>
+        <v>425967</v>
       </c>
       <c r="R102" t="n">
-        <v>7050915</v>
+        <v>7051278</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11669,10 +11664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399936</v>
+        <v>128399829</v>
       </c>
       <c r="B103" t="n">
-        <v>91478</v>
+        <v>91466</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11680,21 +11675,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11704,10 +11699,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>425967</v>
+        <v>426191</v>
       </c>
       <c r="R103" t="n">
-        <v>7051278</v>
+        <v>7050972</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11766,10 +11761,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128399829</v>
+        <v>128399907</v>
       </c>
       <c r="B104" t="n">
-        <v>91464</v>
+        <v>57689</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11777,21 +11772,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11801,10 +11796,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>426191</v>
+        <v>426064</v>
       </c>
       <c r="R104" t="n">
-        <v>7050972</v>
+        <v>7051249</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11837,6 +11832,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11965,10 +11965,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399863</v>
+        <v>128399945</v>
       </c>
       <c r="B106" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11976,21 +11976,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426347</v>
+        <v>426062</v>
       </c>
       <c r="R106" t="n">
-        <v>7050960</v>
+        <v>7051271</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12036,11 +12036,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12067,32 +12062,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399868</v>
+        <v>128399834</v>
       </c>
       <c r="B107" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12102,10 +12097,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426274</v>
+        <v>426228</v>
       </c>
       <c r="R107" t="n">
-        <v>7050964</v>
+        <v>7050978</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12138,11 +12133,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12271,7 +12261,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399881</v>
+        <v>128399863</v>
       </c>
       <c r="B109" t="n">
         <v>57689</v>
@@ -12306,10 +12296,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>425942</v>
+        <v>426347</v>
       </c>
       <c r="R109" t="n">
-        <v>7051274</v>
+        <v>7050960</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12346,7 +12336,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12373,32 +12363,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399834</v>
+        <v>128399868</v>
       </c>
       <c r="B110" t="n">
-        <v>92161</v>
+        <v>57689</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12408,10 +12398,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>426228</v>
+        <v>426274</v>
       </c>
       <c r="R110" t="n">
-        <v>7050978</v>
+        <v>7050964</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12444,6 +12434,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12470,10 +12465,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128399945</v>
+        <v>128399881</v>
       </c>
       <c r="B111" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12481,21 +12476,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12505,10 +12500,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>426062</v>
+        <v>425942</v>
       </c>
       <c r="R111" t="n">
-        <v>7051271</v>
+        <v>7051274</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12541,6 +12536,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12567,10 +12567,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128399935</v>
+        <v>128399943</v>
       </c>
       <c r="B112" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12578,21 +12578,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12602,10 +12602,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>425974</v>
+        <v>425756</v>
       </c>
       <c r="R112" t="n">
-        <v>7051249</v>
+        <v>7051245</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12667,7 +12667,7 @@
         <v>128399833</v>
       </c>
       <c r="B113" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>128399831</v>
       </c>
       <c r="B114" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12858,10 +12858,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399943</v>
+        <v>128399904</v>
       </c>
       <c r="B115" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12869,21 +12869,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>425756</v>
+        <v>426012</v>
       </c>
       <c r="R115" t="n">
-        <v>7051245</v>
+        <v>7051306</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12929,6 +12929,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12955,7 +12960,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399904</v>
+        <v>128399870</v>
       </c>
       <c r="B116" t="n">
         <v>57689</v>
@@ -12990,10 +12995,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426012</v>
+        <v>426156</v>
       </c>
       <c r="R116" t="n">
-        <v>7051306</v>
+        <v>7050998</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13030,7 +13035,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,10 +13062,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128399870</v>
+        <v>128399935</v>
       </c>
       <c r="B117" t="n">
-        <v>57689</v>
+        <v>91480</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13068,21 +13073,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13092,10 +13097,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426156</v>
+        <v>425974</v>
       </c>
       <c r="R117" t="n">
-        <v>7050998</v>
+        <v>7051249</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13128,11 +13133,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13159,32 +13159,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399838</v>
+        <v>128399928</v>
       </c>
       <c r="B118" t="n">
-        <v>92161</v>
+        <v>91480</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>425752</v>
+        <v>426319</v>
       </c>
       <c r="R118" t="n">
-        <v>7051219</v>
+        <v>7051238</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13256,32 +13256,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399852</v>
+        <v>128399838</v>
       </c>
       <c r="B119" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426765</v>
+        <v>425752</v>
       </c>
       <c r="R119" t="n">
-        <v>7051373</v>
+        <v>7051219</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13327,11 +13327,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13358,7 +13353,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399914</v>
+        <v>128399872</v>
       </c>
       <c r="B120" t="n">
         <v>57689</v>
@@ -13393,10 +13388,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426219</v>
+        <v>426187</v>
       </c>
       <c r="R120" t="n">
-        <v>7051364</v>
+        <v>7050975</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13460,7 +13455,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399897</v>
+        <v>128399853</v>
       </c>
       <c r="B121" t="n">
         <v>57689</v>
@@ -13489,16 +13484,24 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>425892</v>
+        <v>426736</v>
       </c>
       <c r="R121" t="n">
-        <v>7051251</v>
+        <v>7051344</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13535,7 +13538,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13562,7 +13565,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399853</v>
+        <v>128399914</v>
       </c>
       <c r="B122" t="n">
         <v>57689</v>
@@ -13591,24 +13594,16 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>426736</v>
+        <v>426219</v>
       </c>
       <c r="R122" t="n">
-        <v>7051344</v>
+        <v>7051364</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13645,7 +13640,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13672,10 +13667,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399928</v>
+        <v>128399852</v>
       </c>
       <c r="B123" t="n">
-        <v>91478</v>
+        <v>57689</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13683,21 +13678,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13707,10 +13702,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>426319</v>
+        <v>426765</v>
       </c>
       <c r="R123" t="n">
-        <v>7051238</v>
+        <v>7051373</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13743,6 +13738,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13769,7 +13769,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128399871</v>
+        <v>128399897</v>
       </c>
       <c r="B124" t="n">
         <v>57689</v>
@@ -13804,10 +13804,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>426154</v>
+        <v>425892</v>
       </c>
       <c r="R124" t="n">
-        <v>7050994</v>
+        <v>7051251</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13973,7 +13973,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399872</v>
+        <v>128399871</v>
       </c>
       <c r="B126" t="n">
         <v>57689</v>
@@ -14008,10 +14008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426187</v>
+        <v>426154</v>
       </c>
       <c r="R126" t="n">
-        <v>7050975</v>
+        <v>7050994</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14075,10 +14075,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128399942</v>
+        <v>128399920</v>
       </c>
       <c r="B127" t="n">
-        <v>91482</v>
+        <v>91462</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425904</v>
+        <v>426277</v>
       </c>
       <c r="R127" t="n">
-        <v>7051248</v>
+        <v>7051183</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14172,10 +14172,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128399901</v>
+        <v>128399942</v>
       </c>
       <c r="B128" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14183,21 +14183,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14207,10 +14207,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425880</v>
+        <v>425904</v>
       </c>
       <c r="R128" t="n">
-        <v>7051304</v>
+        <v>7051248</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14243,11 +14243,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14274,10 +14269,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399878</v>
+        <v>128399948</v>
       </c>
       <c r="B129" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14285,21 +14280,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14309,10 +14304,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426047</v>
+        <v>426395</v>
       </c>
       <c r="R129" t="n">
-        <v>7051186</v>
+        <v>7051398</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14349,7 +14344,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14376,7 +14371,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128399905</v>
+        <v>128399901</v>
       </c>
       <c r="B130" t="n">
         <v>57689</v>
@@ -14411,10 +14406,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426029</v>
+        <v>425880</v>
       </c>
       <c r="R130" t="n">
-        <v>7051287</v>
+        <v>7051304</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14451,7 +14446,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14478,7 +14473,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399876</v>
+        <v>128399878</v>
       </c>
       <c r="B131" t="n">
         <v>57689</v>
@@ -14513,10 +14508,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426244</v>
+        <v>426047</v>
       </c>
       <c r="R131" t="n">
-        <v>7051052</v>
+        <v>7051186</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14553,7 +14548,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14580,10 +14575,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399948</v>
+        <v>128399876</v>
       </c>
       <c r="B132" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14591,21 +14586,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14615,10 +14610,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>426395</v>
+        <v>426244</v>
       </c>
       <c r="R132" t="n">
-        <v>7051398</v>
+        <v>7051052</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14655,7 +14650,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14682,10 +14677,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399920</v>
+        <v>128399905</v>
       </c>
       <c r="B133" t="n">
-        <v>91460</v>
+        <v>57689</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14693,21 +14688,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14717,10 +14712,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426277</v>
+        <v>426029</v>
       </c>
       <c r="R133" t="n">
-        <v>7051183</v>
+        <v>7051287</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14753,6 +14748,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14779,10 +14779,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128399930</v>
+        <v>128399918</v>
       </c>
       <c r="B134" t="n">
-        <v>91478</v>
+        <v>91416</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14790,21 +14790,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14814,10 +14814,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>426267</v>
+        <v>426224</v>
       </c>
       <c r="R134" t="n">
-        <v>7050942</v>
+        <v>7050981</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14876,10 +14876,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128399931</v>
+        <v>128399929</v>
       </c>
       <c r="B135" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>426252</v>
+        <v>426276</v>
       </c>
       <c r="R135" t="n">
-        <v>7050958</v>
+        <v>7050944</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14973,10 +14973,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128399929</v>
+        <v>128399930</v>
       </c>
       <c r="B136" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>426276</v>
+        <v>426267</v>
       </c>
       <c r="R136" t="n">
-        <v>7050944</v>
+        <v>7050942</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15070,10 +15070,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128399918</v>
+        <v>128399931</v>
       </c>
       <c r="B137" t="n">
-        <v>91414</v>
+        <v>91480</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15081,21 +15081,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15105,10 +15105,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>426224</v>
+        <v>426252</v>
       </c>
       <c r="R137" t="n">
-        <v>7050981</v>
+        <v>7050958</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15269,7 +15269,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128399910</v>
+        <v>128399867</v>
       </c>
       <c r="B139" t="n">
         <v>57689</v>
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>426170</v>
+        <v>426331</v>
       </c>
       <c r="R139" t="n">
-        <v>7051345</v>
+        <v>7050912</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15371,7 +15371,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128399879</v>
+        <v>128399906</v>
       </c>
       <c r="B140" t="n">
         <v>57689</v>
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>426055</v>
+        <v>426053</v>
       </c>
       <c r="R140" t="n">
-        <v>7051223</v>
+        <v>7051256</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15473,7 +15473,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128399890</v>
+        <v>128399879</v>
       </c>
       <c r="B141" t="n">
         <v>57689</v>
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>425829</v>
+        <v>426055</v>
       </c>
       <c r="R141" t="n">
-        <v>7051228</v>
+        <v>7051223</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15548,7 +15548,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15575,7 +15575,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128399906</v>
+        <v>128399896</v>
       </c>
       <c r="B142" t="n">
         <v>57689</v>
@@ -15610,10 +15610,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>426053</v>
+        <v>425889</v>
       </c>
       <c r="R142" t="n">
-        <v>7051256</v>
+        <v>7051248</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15677,7 +15677,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128399867</v>
+        <v>128399890</v>
       </c>
       <c r="B143" t="n">
         <v>57689</v>
@@ -15712,10 +15712,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>426331</v>
+        <v>425829</v>
       </c>
       <c r="R143" t="n">
-        <v>7050912</v>
+        <v>7051228</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15779,7 +15779,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128399896</v>
+        <v>128399910</v>
       </c>
       <c r="B144" t="n">
         <v>57689</v>
@@ -15814,10 +15814,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>425889</v>
+        <v>426170</v>
       </c>
       <c r="R144" t="n">
-        <v>7051248</v>
+        <v>7051345</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15881,10 +15881,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128399933</v>
+        <v>128399880</v>
       </c>
       <c r="B145" t="n">
-        <v>91478</v>
+        <v>57689</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15892,21 +15892,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15916,10 +15916,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>426218</v>
+        <v>425981</v>
       </c>
       <c r="R145" t="n">
-        <v>7051146</v>
+        <v>7051240</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15952,6 +15952,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15978,10 +15983,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128399880</v>
+        <v>128399933</v>
       </c>
       <c r="B146" t="n">
-        <v>57689</v>
+        <v>91480</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15989,21 +15994,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16013,10 +16018,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>425981</v>
+        <v>426218</v>
       </c>
       <c r="R146" t="n">
-        <v>7051240</v>
+        <v>7051146</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16049,11 +16054,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16185,7 +16185,7 @@
         <v>128399828</v>
       </c>
       <c r="B148" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16279,10 +16279,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128399946</v>
+        <v>128399937</v>
       </c>
       <c r="B149" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16314,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>426083</v>
+        <v>426734</v>
       </c>
       <c r="R149" t="n">
-        <v>7051231</v>
+        <v>7051350</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16376,10 +16376,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128399937</v>
+        <v>128399946</v>
       </c>
       <c r="B150" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16411,10 +16411,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>426734</v>
+        <v>426083</v>
       </c>
       <c r="R150" t="n">
-        <v>7051350</v>
+        <v>7051231</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16473,7 +16473,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128399883</v>
+        <v>128399892</v>
       </c>
       <c r="B151" t="n">
         <v>57689</v>
@@ -16508,10 +16508,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>425851</v>
+        <v>425853</v>
       </c>
       <c r="R151" t="n">
-        <v>7051202</v>
+        <v>7051216</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16548,7 +16548,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16575,7 +16575,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128399892</v>
+        <v>128399883</v>
       </c>
       <c r="B152" t="n">
         <v>57689</v>
@@ -16610,10 +16610,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>425853</v>
+        <v>425851</v>
       </c>
       <c r="R152" t="n">
-        <v>7051216</v>
+        <v>7051202</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16881,7 +16881,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128399911</v>
+        <v>128399885</v>
       </c>
       <c r="B155" t="n">
         <v>57689</v>
@@ -16916,10 +16916,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>426174</v>
+        <v>425748</v>
       </c>
       <c r="R155" t="n">
-        <v>7051335</v>
+        <v>7051212</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16983,7 +16983,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128399885</v>
+        <v>128399911</v>
       </c>
       <c r="B156" t="n">
         <v>57689</v>
@@ -17018,10 +17018,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>425748</v>
+        <v>426174</v>
       </c>
       <c r="R156" t="n">
-        <v>7051212</v>
+        <v>7051335</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17187,45 +17187,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128399839</v>
+        <v>128399827</v>
       </c>
       <c r="B158" t="n">
-        <v>92161</v>
+        <v>91466</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>425971</v>
+        <v>426813</v>
       </c>
       <c r="R158" t="n">
-        <v>7051280</v>
+        <v>7051371</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17284,45 +17284,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128399827</v>
+        <v>128399839</v>
       </c>
       <c r="B159" t="n">
-        <v>91464</v>
+        <v>92163</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Stor-grässjön, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>426813</v>
+        <v>425971</v>
       </c>
       <c r="R159" t="n">
-        <v>7051371</v>
+        <v>7051280</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17585,10 +17585,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128399837</v>
+        <v>128399840</v>
       </c>
       <c r="B162" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>425757</v>
+        <v>426131</v>
       </c>
       <c r="R162" t="n">
-        <v>7051207</v>
+        <v>7051242</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17682,32 +17682,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128399840</v>
+        <v>128399926</v>
       </c>
       <c r="B163" t="n">
-        <v>92161</v>
+        <v>91462</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17717,10 +17717,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>426131</v>
+        <v>426189</v>
       </c>
       <c r="R163" t="n">
-        <v>7051242</v>
+        <v>7051364</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17779,32 +17779,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128399926</v>
+        <v>128399837</v>
       </c>
       <c r="B164" t="n">
-        <v>91460</v>
+        <v>92163</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17814,10 +17814,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>426189</v>
+        <v>425757</v>
       </c>
       <c r="R164" t="n">
-        <v>7051364</v>
+        <v>7051207</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17876,7 +17876,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128399864</v>
+        <v>128399874</v>
       </c>
       <c r="B165" t="n">
         <v>57689</v>
@@ -17911,10 +17911,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>426357</v>
+        <v>426194</v>
       </c>
       <c r="R165" t="n">
-        <v>7050965</v>
+        <v>7050979</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17978,7 +17978,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128399874</v>
+        <v>128399864</v>
       </c>
       <c r="B166" t="n">
         <v>57689</v>
@@ -18013,10 +18013,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>426194</v>
+        <v>426357</v>
       </c>
       <c r="R166" t="n">
-        <v>7050979</v>
+        <v>7050965</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18080,32 +18080,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128399843</v>
+        <v>128399934</v>
       </c>
       <c r="B167" t="n">
-        <v>92161</v>
+        <v>91480</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18115,10 +18115,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>426425</v>
+        <v>426135</v>
       </c>
       <c r="R167" t="n">
-        <v>7051273</v>
+        <v>7051163</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18177,32 +18177,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128399934</v>
+        <v>128399843</v>
       </c>
       <c r="B168" t="n">
-        <v>91478</v>
+        <v>92163</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18212,10 +18212,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>426135</v>
+        <v>426425</v>
       </c>
       <c r="R168" t="n">
-        <v>7051163</v>
+        <v>7051273</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18481,7 +18481,7 @@
         <v>128399938</v>
       </c>
       <c r="B171" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18575,10 +18575,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128399882</v>
+        <v>128399921</v>
       </c>
       <c r="B172" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18586,21 +18586,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18610,10 +18610,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>425864</v>
+        <v>426314</v>
       </c>
       <c r="R172" t="n">
-        <v>7051211</v>
+        <v>7050963</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18646,11 +18646,6 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18680,7 +18675,7 @@
         <v>128399835</v>
       </c>
       <c r="B173" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18774,10 +18769,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128399921</v>
+        <v>128399884</v>
       </c>
       <c r="B174" t="n">
-        <v>91460</v>
+        <v>57689</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18785,21 +18780,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18809,10 +18804,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>426314</v>
+        <v>425770</v>
       </c>
       <c r="R174" t="n">
-        <v>7050963</v>
+        <v>7051183</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18845,6 +18840,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18871,7 +18871,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128399887</v>
+        <v>128399893</v>
       </c>
       <c r="B175" t="n">
         <v>57689</v>
@@ -18906,10 +18906,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425756</v>
+        <v>425861</v>
       </c>
       <c r="R175" t="n">
-        <v>7051229</v>
+        <v>7051227</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18973,7 +18973,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128399893</v>
+        <v>128399887</v>
       </c>
       <c r="B176" t="n">
         <v>57689</v>
@@ -19008,10 +19008,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425861</v>
+        <v>425756</v>
       </c>
       <c r="R176" t="n">
-        <v>7051227</v>
+        <v>7051229</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19075,7 +19075,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128399884</v>
+        <v>128399882</v>
       </c>
       <c r="B177" t="n">
         <v>57689</v>
@@ -19110,10 +19110,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>425770</v>
+        <v>425864</v>
       </c>
       <c r="R177" t="n">
-        <v>7051183</v>
+        <v>7051211</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19150,7 +19150,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19287,10 +19287,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399915</v>
+        <v>128399932</v>
       </c>
       <c r="B179" t="n">
-        <v>57689</v>
+        <v>91480</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19298,21 +19298,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>426224</v>
+        <v>426231</v>
       </c>
       <c r="R179" t="n">
-        <v>7051367</v>
+        <v>7051130</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19358,11 +19358,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19389,10 +19384,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128399860</v>
+        <v>128399923</v>
       </c>
       <c r="B180" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19400,21 +19395,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19424,10 +19419,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>426309</v>
+        <v>426172</v>
       </c>
       <c r="R180" t="n">
-        <v>7051245</v>
+        <v>7051169</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19460,11 +19455,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19491,10 +19481,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399894</v>
+        <v>128399944</v>
       </c>
       <c r="B181" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19502,21 +19492,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19526,10 +19516,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>425875</v>
+        <v>425889</v>
       </c>
       <c r="R181" t="n">
-        <v>7051223</v>
+        <v>7051300</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19562,11 +19552,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19593,10 +19578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128399891</v>
+        <v>128399950</v>
       </c>
       <c r="B182" t="n">
-        <v>57689</v>
+        <v>88867</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19604,21 +19589,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19628,10 +19613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>425844</v>
+        <v>426303</v>
       </c>
       <c r="R182" t="n">
-        <v>7051240</v>
+        <v>7050905</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19664,11 +19649,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19695,10 +19675,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128399912</v>
+        <v>128399951</v>
       </c>
       <c r="B183" t="n">
-        <v>57689</v>
+        <v>88867</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19706,21 +19686,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19730,10 +19710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>426175</v>
+        <v>426062</v>
       </c>
       <c r="R183" t="n">
-        <v>7051336</v>
+        <v>7051265</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19766,11 +19746,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19797,10 +19772,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128399944</v>
+        <v>128399894</v>
       </c>
       <c r="B184" t="n">
-        <v>91482</v>
+        <v>57689</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19808,21 +19783,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19832,10 +19807,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>425889</v>
+        <v>425875</v>
       </c>
       <c r="R184" t="n">
-        <v>7051300</v>
+        <v>7051223</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19868,6 +19843,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19894,10 +19874,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128399950</v>
+        <v>128399915</v>
       </c>
       <c r="B185" t="n">
-        <v>88865</v>
+        <v>57689</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19905,21 +19885,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19929,10 +19909,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>426303</v>
+        <v>426224</v>
       </c>
       <c r="R185" t="n">
-        <v>7050905</v>
+        <v>7051367</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19965,6 +19945,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19991,10 +19976,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128399951</v>
+        <v>128399912</v>
       </c>
       <c r="B186" t="n">
-        <v>88865</v>
+        <v>57689</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20002,21 +19987,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20026,10 +20011,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>426062</v>
+        <v>426175</v>
       </c>
       <c r="R186" t="n">
-        <v>7051265</v>
+        <v>7051336</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20062,6 +20047,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20088,10 +20078,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128399932</v>
+        <v>128399860</v>
       </c>
       <c r="B187" t="n">
-        <v>91478</v>
+        <v>57689</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20099,21 +20089,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20123,10 +20113,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>426231</v>
+        <v>426309</v>
       </c>
       <c r="R187" t="n">
-        <v>7051130</v>
+        <v>7051245</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20159,6 +20149,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20185,10 +20180,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128399923</v>
+        <v>128399891</v>
       </c>
       <c r="B188" t="n">
-        <v>91460</v>
+        <v>57689</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20196,21 +20191,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20220,10 +20215,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>426172</v>
+        <v>425844</v>
       </c>
       <c r="R188" t="n">
-        <v>7051169</v>
+        <v>7051240</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20256,6 +20251,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B189" t="n">
-        <v>91460</v>
+        <v>57689</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R189" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20353,6 +20353,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20379,7 +20384,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399873</v>
+        <v>128399862</v>
       </c>
       <c r="B190" t="n">
         <v>57689</v>
@@ -20414,10 +20419,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426193</v>
+        <v>426292</v>
       </c>
       <c r="R190" t="n">
-        <v>7050977</v>
+        <v>7050995</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20454,7 +20459,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20481,10 +20486,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399862</v>
+        <v>128399925</v>
       </c>
       <c r="B191" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20492,21 +20497,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20516,10 +20521,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426292</v>
+        <v>426047</v>
       </c>
       <c r="R191" t="n">
-        <v>7050995</v>
+        <v>7051252</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20552,11 +20557,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20586,7 +20586,7 @@
         <v>128399939</v>
       </c>
       <c r="B192" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128398775</v>
+        <v>128398774</v>
       </c>
       <c r="B10" t="n">
         <v>57689</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425892</v>
+        <v>425970</v>
       </c>
       <c r="R10" t="n">
-        <v>7051220</v>
+        <v>7051235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128398774</v>
+        <v>128398775</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425970</v>
+        <v>425892</v>
       </c>
       <c r="R11" t="n">
-        <v>7051235</v>
+        <v>7051220</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128398790</v>
+        <v>128398762</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425825</v>
+        <v>426225</v>
       </c>
       <c r="R12" t="n">
-        <v>7051257</v>
+        <v>7051098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,12 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398762</v>
+        <v>128398790</v>
       </c>
       <c r="B13" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426225</v>
+        <v>425825</v>
       </c>
       <c r="R13" t="n">
-        <v>7051098</v>
+        <v>7051257</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2569,32 +2569,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128398803</v>
+        <v>128398770</v>
       </c>
       <c r="B19" t="n">
-        <v>92163</v>
+        <v>91920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425994</v>
+        <v>426115</v>
       </c>
       <c r="R19" t="n">
-        <v>7051287</v>
+        <v>7051178</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,57 +2676,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398805</v>
+        <v>128398718</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>92768</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425999</v>
+        <v>426807</v>
       </c>
       <c r="R20" t="n">
-        <v>7051258</v>
+        <v>7051311</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2755,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,32 +2783,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398718</v>
+        <v>128398773</v>
       </c>
       <c r="B21" t="n">
-        <v>92768</v>
+        <v>75175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>6486</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426807</v>
+        <v>425978</v>
       </c>
       <c r="R21" t="n">
-        <v>7051311</v>
+        <v>7051231</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,7 +2853,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2872,7 +2863,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,32 +2890,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398770</v>
+        <v>128398753</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2934,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426115</v>
+        <v>426191</v>
       </c>
       <c r="R22" t="n">
-        <v>7051178</v>
+        <v>7050957</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2969,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2970,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,6 +2981,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3006,10 +3012,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398771</v>
+        <v>128398730</v>
       </c>
       <c r="B23" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,21 +3023,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3041,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426068</v>
+        <v>426382</v>
       </c>
       <c r="R23" t="n">
-        <v>7051189</v>
+        <v>7051149</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3076,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3086,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,48 +3119,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398773</v>
+        <v>128398805</v>
       </c>
       <c r="B24" t="n">
-        <v>75175</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6486</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425978</v>
+        <v>425999</v>
       </c>
       <c r="R24" t="n">
-        <v>7051231</v>
+        <v>7051258</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3183,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3193,7 +3208,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,32 +3235,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398821</v>
+        <v>128398803</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>92163</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3255,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426200</v>
+        <v>425994</v>
       </c>
       <c r="R25" t="n">
-        <v>7051338</v>
+        <v>7051287</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3290,7 +3305,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3300,7 +3315,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3327,10 +3342,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398753</v>
+        <v>128398771</v>
       </c>
       <c r="B26" t="n">
-        <v>80194</v>
+        <v>91484</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,21 +3353,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3362,10 +3377,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426191</v>
+        <v>426068</v>
       </c>
       <c r="R26" t="n">
-        <v>7050957</v>
+        <v>7051189</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3397,7 +3412,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3407,7 +3422,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3418,21 +3433,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3449,7 +3449,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398730</v>
+        <v>128398821</v>
       </c>
       <c r="B27" t="n">
         <v>79089</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426382</v>
+        <v>426200</v>
       </c>
       <c r="R27" t="n">
-        <v>7051149</v>
+        <v>7051338</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4218,32 +4218,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398801</v>
+        <v>128398755</v>
       </c>
       <c r="B34" t="n">
-        <v>91920</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425985</v>
+        <v>426166</v>
       </c>
       <c r="R34" t="n">
-        <v>7051282</v>
+        <v>7050989</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,7 +4325,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128398755</v>
+        <v>128398738</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426166</v>
+        <v>426341</v>
       </c>
       <c r="R35" t="n">
-        <v>7050989</v>
+        <v>7051103</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,7 +4432,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128398738</v>
+        <v>128398794</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426341</v>
+        <v>425876</v>
       </c>
       <c r="R36" t="n">
-        <v>7051103</v>
+        <v>7051324</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4539,32 +4539,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398794</v>
+        <v>128398801</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>91920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425876</v>
+        <v>425985</v>
       </c>
       <c r="R37" t="n">
-        <v>7051324</v>
+        <v>7051282</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5084,10 +5084,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128398800</v>
+        <v>128398787</v>
       </c>
       <c r="B42" t="n">
-        <v>91480</v>
+        <v>75169</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5095,21 +5095,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>425985</v>
+        <v>425795</v>
       </c>
       <c r="R42" t="n">
-        <v>7051282</v>
+        <v>7051251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,32 +5191,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398736</v>
+        <v>128398800</v>
       </c>
       <c r="B43" t="n">
-        <v>92163</v>
+        <v>91480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426352</v>
+        <v>425985</v>
       </c>
       <c r="R43" t="n">
-        <v>7051151</v>
+        <v>7051282</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128398787</v>
+        <v>128398749</v>
       </c>
       <c r="B44" t="n">
-        <v>75169</v>
+        <v>86778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,21 +5309,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>308</v>
+        <v>427</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>425795</v>
+        <v>426252</v>
       </c>
       <c r="R44" t="n">
-        <v>7051251</v>
+        <v>7050919</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5378,7 +5378,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5405,32 +5410,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128398749</v>
+        <v>128398736</v>
       </c>
       <c r="B45" t="n">
-        <v>86778</v>
+        <v>92163</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>427</v>
+        <v>3298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5440,10 +5445,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426252</v>
+        <v>426352</v>
       </c>
       <c r="R45" t="n">
-        <v>7050919</v>
+        <v>7051151</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5475,7 +5480,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5485,12 +5490,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5517,50 +5517,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128398807</v>
+        <v>128398731</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426011</v>
+        <v>426369</v>
       </c>
       <c r="R46" t="n">
-        <v>7051282</v>
+        <v>7051152</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5592,7 +5587,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5602,12 +5597,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5634,10 +5624,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398721</v>
+        <v>128398797</v>
       </c>
       <c r="B47" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5645,39 +5635,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426773</v>
+        <v>425919</v>
       </c>
       <c r="R47" t="n">
-        <v>7051349</v>
+        <v>7051350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5694,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5719,12 +5704,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,32 +5731,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128398731</v>
+        <v>128398812</v>
       </c>
       <c r="B48" t="n">
-        <v>92163</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5786,10 +5766,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426369</v>
+        <v>426097</v>
       </c>
       <c r="R48" t="n">
-        <v>7051152</v>
+        <v>7051199</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5821,7 +5801,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5831,7 +5811,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5858,7 +5838,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128398797</v>
+        <v>128398725</v>
       </c>
       <c r="B49" t="n">
         <v>79089</v>
@@ -5893,10 +5873,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>425919</v>
+        <v>426492</v>
       </c>
       <c r="R49" t="n">
-        <v>7051350</v>
+        <v>7051269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,7 +5908,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5938,7 +5918,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5965,10 +5945,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128398812</v>
+        <v>128398807</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,34 +5956,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426097</v>
+        <v>426011</v>
       </c>
       <c r="R50" t="n">
-        <v>7051199</v>
+        <v>7051282</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6035,7 +6020,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6045,7 +6030,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,10 +6062,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128398725</v>
+        <v>128398721</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6083,34 +6073,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426492</v>
+        <v>426773</v>
       </c>
       <c r="R51" t="n">
-        <v>7051269</v>
+        <v>7051349</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6142,7 +6137,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6152,7 +6147,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398743</v>
+        <v>128398793</v>
       </c>
       <c r="B52" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6190,34 +6190,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426371</v>
+        <v>425908</v>
       </c>
       <c r="R52" t="n">
-        <v>7050917</v>
+        <v>7051281</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6249,7 +6254,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6259,7 +6264,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6286,10 +6296,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128398802</v>
+        <v>128398814</v>
       </c>
       <c r="B53" t="n">
-        <v>91762</v>
+        <v>57689</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6297,34 +6307,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>425985</v>
+        <v>426097</v>
       </c>
       <c r="R53" t="n">
-        <v>7051282</v>
+        <v>7051199</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6356,7 +6371,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6366,7 +6381,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6393,45 +6413,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398734</v>
+        <v>128398822</v>
       </c>
       <c r="B54" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426329</v>
+        <v>426200</v>
       </c>
       <c r="R54" t="n">
-        <v>7051146</v>
+        <v>7051338</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6463,7 +6488,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6473,7 +6498,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6500,10 +6530,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398727</v>
+        <v>128398719</v>
       </c>
       <c r="B55" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6511,34 +6541,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426516</v>
+        <v>426799</v>
       </c>
       <c r="R55" t="n">
-        <v>7051239</v>
+        <v>7051328</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6570,7 +6605,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6580,7 +6615,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6607,48 +6647,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398804</v>
+        <v>128398727</v>
       </c>
       <c r="B56" t="n">
-        <v>75175</v>
+        <v>79089</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426000</v>
+        <v>426516</v>
       </c>
       <c r="R56" t="n">
-        <v>7051290</v>
+        <v>7051239</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6680,7 +6717,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6690,7 +6727,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6698,11 +6735,6 @@
       </c>
       <c r="AE56" t="b">
         <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -6722,50 +6754,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398793</v>
+        <v>128398804</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>75175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425908</v>
+        <v>426000</v>
       </c>
       <c r="R57" t="n">
-        <v>7051281</v>
+        <v>7051290</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6797,7 +6827,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6807,12 +6837,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6820,6 +6845,11 @@
       </c>
       <c r="AE57" t="b">
         <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG57" t="b">
         <v>0</v>
@@ -6839,10 +6869,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398814</v>
+        <v>128398743</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6850,39 +6880,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426097</v>
+        <v>426371</v>
       </c>
       <c r="R58" t="n">
-        <v>7051199</v>
+        <v>7050917</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6914,7 +6939,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6924,12 +6949,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6956,10 +6976,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398822</v>
+        <v>128398802</v>
       </c>
       <c r="B59" t="n">
-        <v>57689</v>
+        <v>91762</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6967,39 +6987,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426200</v>
+        <v>425985</v>
       </c>
       <c r="R59" t="n">
-        <v>7051338</v>
+        <v>7051282</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7031,7 +7046,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7041,12 +7056,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7073,50 +7083,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398719</v>
+        <v>128398734</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426799</v>
+        <v>426329</v>
       </c>
       <c r="R60" t="n">
-        <v>7051328</v>
+        <v>7051146</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7148,7 +7153,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7158,12 +7163,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7974,10 +7974,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128398820</v>
+        <v>128398760</v>
       </c>
       <c r="B68" t="n">
-        <v>91484</v>
+        <v>82948</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7985,21 +7985,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426196</v>
+        <v>426232</v>
       </c>
       <c r="R68" t="n">
-        <v>7051340</v>
+        <v>7051062</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8081,32 +8081,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128398733</v>
+        <v>128398820</v>
       </c>
       <c r="B69" t="n">
-        <v>92163</v>
+        <v>91484</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426361</v>
+        <v>426196</v>
       </c>
       <c r="R69" t="n">
-        <v>7051151</v>
+        <v>7051340</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8188,32 +8188,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128398760</v>
+        <v>128398733</v>
       </c>
       <c r="B70" t="n">
-        <v>82948</v>
+        <v>92163</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426232</v>
+        <v>426361</v>
       </c>
       <c r="R70" t="n">
-        <v>7051062</v>
+        <v>7051151</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128398720</v>
+        <v>128398779</v>
       </c>
       <c r="B73" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8520,34 +8520,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426773</v>
+        <v>425818</v>
       </c>
       <c r="R73" t="n">
-        <v>7051341</v>
+        <v>7051169</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8579,7 +8584,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8589,7 +8594,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8616,10 +8626,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128398779</v>
+        <v>128398720</v>
       </c>
       <c r="B74" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8627,39 +8637,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>425818</v>
+        <v>426773</v>
       </c>
       <c r="R74" t="n">
-        <v>7051169</v>
+        <v>7051341</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8691,7 +8696,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8701,12 +8706,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8835,10 +8835,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128398754</v>
+        <v>128398789</v>
       </c>
       <c r="B76" t="n">
-        <v>80195</v>
+        <v>57689</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8846,34 +8846,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426191</v>
+        <v>425804</v>
       </c>
       <c r="R76" t="n">
-        <v>7050957</v>
+        <v>7051258</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8905,7 +8910,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8915,7 +8920,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8926,21 +8936,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8957,32 +8952,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128398772</v>
+        <v>128398754</v>
       </c>
       <c r="B77" t="n">
-        <v>92163</v>
+        <v>80195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8992,10 +8987,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426065</v>
+        <v>426191</v>
       </c>
       <c r="R77" t="n">
-        <v>7051192</v>
+        <v>7050957</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9027,7 +9022,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9037,7 +9032,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9048,6 +9043,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9064,50 +9074,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128398789</v>
+        <v>128398772</v>
       </c>
       <c r="B78" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>425804</v>
+        <v>426065</v>
       </c>
       <c r="R78" t="n">
-        <v>7051258</v>
+        <v>7051192</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9139,7 +9144,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9149,12 +9154,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9181,10 +9181,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128398813</v>
+        <v>128398723</v>
       </c>
       <c r="B79" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9192,21 +9192,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426097</v>
+        <v>426515</v>
       </c>
       <c r="R79" t="n">
-        <v>7051199</v>
+        <v>7051308</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9288,10 +9288,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128398765</v>
+        <v>128398751</v>
       </c>
       <c r="B80" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426186</v>
+        <v>426239</v>
       </c>
       <c r="R80" t="n">
-        <v>7051125</v>
+        <v>7050935</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9395,10 +9395,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128398723</v>
+        <v>128398784</v>
       </c>
       <c r="B81" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9406,34 +9406,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>426515</v>
+        <v>425712</v>
       </c>
       <c r="R81" t="n">
-        <v>7051308</v>
+        <v>7051206</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9465,7 +9470,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9475,7 +9480,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9502,10 +9512,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128398751</v>
+        <v>128398813</v>
       </c>
       <c r="B82" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9513,21 +9523,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9537,10 +9547,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426239</v>
+        <v>426097</v>
       </c>
       <c r="R82" t="n">
-        <v>7050935</v>
+        <v>7051199</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9572,7 +9582,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9582,7 +9592,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9609,10 +9619,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128398780</v>
+        <v>128398765</v>
       </c>
       <c r="B83" t="n">
-        <v>57689</v>
+        <v>82948</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9620,39 +9630,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425756</v>
+        <v>426186</v>
       </c>
       <c r="R83" t="n">
-        <v>7051171</v>
+        <v>7051125</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9684,7 +9689,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9694,12 +9699,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9726,7 +9726,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128398784</v>
+        <v>128398780</v>
       </c>
       <c r="B84" t="n">
         <v>57689</v>
@@ -9757,7 +9757,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>425712</v>
+        <v>425756</v>
       </c>
       <c r="R84" t="n">
-        <v>7051206</v>
+        <v>7051171</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10776,10 +10776,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399849</v>
+        <v>128399940</v>
       </c>
       <c r="B94" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10787,21 +10787,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426803</v>
+        <v>426338</v>
       </c>
       <c r="R94" t="n">
-        <v>7051353</v>
+        <v>7050977</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10847,11 +10847,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10878,10 +10873,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399940</v>
+        <v>128399849</v>
       </c>
       <c r="B95" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10889,21 +10884,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10913,10 +10908,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426338</v>
+        <v>426803</v>
       </c>
       <c r="R95" t="n">
-        <v>7050977</v>
+        <v>7051353</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10949,6 +10944,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12567,10 +12567,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128399943</v>
+        <v>128399935</v>
       </c>
       <c r="B112" t="n">
-        <v>91484</v>
+        <v>91480</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12578,21 +12578,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12602,10 +12602,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>425756</v>
+        <v>425974</v>
       </c>
       <c r="R112" t="n">
-        <v>7051245</v>
+        <v>7051249</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12858,10 +12858,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399904</v>
+        <v>128399943</v>
       </c>
       <c r="B115" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12869,21 +12869,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12893,10 +12893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426012</v>
+        <v>425756</v>
       </c>
       <c r="R115" t="n">
-        <v>7051306</v>
+        <v>7051245</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12929,11 +12929,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12960,7 +12955,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399870</v>
+        <v>128399904</v>
       </c>
       <c r="B116" t="n">
         <v>57689</v>
@@ -12995,10 +12990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426156</v>
+        <v>426012</v>
       </c>
       <c r="R116" t="n">
-        <v>7050998</v>
+        <v>7051306</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13035,7 +13030,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13062,10 +13057,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128399935</v>
+        <v>128399870</v>
       </c>
       <c r="B117" t="n">
-        <v>91480</v>
+        <v>57689</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13073,21 +13068,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13097,10 +13092,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>425974</v>
+        <v>426156</v>
       </c>
       <c r="R117" t="n">
-        <v>7051249</v>
+        <v>7050998</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13133,6 +13128,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14779,10 +14779,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128399918</v>
+        <v>128399930</v>
       </c>
       <c r="B134" t="n">
-        <v>91416</v>
+        <v>91480</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14790,21 +14790,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14814,10 +14814,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>426224</v>
+        <v>426267</v>
       </c>
       <c r="R134" t="n">
-        <v>7050981</v>
+        <v>7050942</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14876,7 +14876,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128399929</v>
+        <v>128399931</v>
       </c>
       <c r="B135" t="n">
         <v>91480</v>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>426276</v>
+        <v>426252</v>
       </c>
       <c r="R135" t="n">
-        <v>7050944</v>
+        <v>7050958</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14973,10 +14973,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128399930</v>
+        <v>128399918</v>
       </c>
       <c r="B136" t="n">
-        <v>91480</v>
+        <v>91416</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14984,21 +14984,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>426267</v>
+        <v>426224</v>
       </c>
       <c r="R136" t="n">
-        <v>7050942</v>
+        <v>7050981</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15070,7 +15070,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128399931</v>
+        <v>128399929</v>
       </c>
       <c r="B137" t="n">
         <v>91480</v>
@@ -15105,10 +15105,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>426252</v>
+        <v>426276</v>
       </c>
       <c r="R137" t="n">
-        <v>7050958</v>
+        <v>7050944</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15881,10 +15881,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128399880</v>
+        <v>128399933</v>
       </c>
       <c r="B145" t="n">
-        <v>57689</v>
+        <v>91480</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15892,21 +15892,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15916,10 +15916,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425981</v>
+        <v>426218</v>
       </c>
       <c r="R145" t="n">
-        <v>7051240</v>
+        <v>7051146</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15952,11 +15952,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15983,10 +15978,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128399933</v>
+        <v>128399880</v>
       </c>
       <c r="B146" t="n">
-        <v>91480</v>
+        <v>57689</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15994,21 +15989,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16018,10 +16013,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>426218</v>
+        <v>425981</v>
       </c>
       <c r="R146" t="n">
-        <v>7051146</v>
+        <v>7051240</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16054,6 +16049,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17585,7 +17585,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128399840</v>
+        <v>128399837</v>
       </c>
       <c r="B162" t="n">
         <v>92163</v>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>426131</v>
+        <v>425757</v>
       </c>
       <c r="R162" t="n">
-        <v>7051242</v>
+        <v>7051207</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17682,32 +17682,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128399926</v>
+        <v>128399840</v>
       </c>
       <c r="B163" t="n">
-        <v>91462</v>
+        <v>92163</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17717,10 +17717,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>426189</v>
+        <v>426131</v>
       </c>
       <c r="R163" t="n">
-        <v>7051364</v>
+        <v>7051242</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17779,32 +17779,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128399837</v>
+        <v>128399926</v>
       </c>
       <c r="B164" t="n">
-        <v>92163</v>
+        <v>91462</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17814,10 +17814,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>425757</v>
+        <v>426189</v>
       </c>
       <c r="R164" t="n">
-        <v>7051207</v>
+        <v>7051364</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18177,32 +18177,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128399843</v>
+        <v>128399899</v>
       </c>
       <c r="B168" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18212,10 +18212,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>426425</v>
+        <v>425928</v>
       </c>
       <c r="R168" t="n">
-        <v>7051273</v>
+        <v>7051283</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18248,6 +18248,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18274,32 +18279,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128399869</v>
+        <v>128399843</v>
       </c>
       <c r="B169" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18309,10 +18314,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>426163</v>
+        <v>426425</v>
       </c>
       <c r="R169" t="n">
-        <v>7050993</v>
+        <v>7051273</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18345,11 +18350,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18376,7 +18376,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128399899</v>
+        <v>128399869</v>
       </c>
       <c r="B170" t="n">
         <v>57689</v>
@@ -18411,10 +18411,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>425928</v>
+        <v>426163</v>
       </c>
       <c r="R170" t="n">
-        <v>7051283</v>
+        <v>7050993</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18478,10 +18478,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128399938</v>
+        <v>128399854</v>
       </c>
       <c r="B171" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18489,34 +18489,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>426205</v>
+        <v>426733</v>
       </c>
       <c r="R171" t="n">
-        <v>7051276</v>
+        <v>7051347</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18549,6 +18557,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18672,32 +18685,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128399835</v>
+        <v>128399884</v>
       </c>
       <c r="B173" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18707,10 +18720,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>426132</v>
+        <v>425770</v>
       </c>
       <c r="R173" t="n">
-        <v>7051150</v>
+        <v>7051183</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18743,6 +18756,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18769,7 +18787,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128399884</v>
+        <v>128399893</v>
       </c>
       <c r="B174" t="n">
         <v>57689</v>
@@ -18804,10 +18822,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>425770</v>
+        <v>425861</v>
       </c>
       <c r="R174" t="n">
-        <v>7051183</v>
+        <v>7051227</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18844,7 +18862,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18871,7 +18889,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128399893</v>
+        <v>128399887</v>
       </c>
       <c r="B175" t="n">
         <v>57689</v>
@@ -18906,10 +18924,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425861</v>
+        <v>425756</v>
       </c>
       <c r="R175" t="n">
-        <v>7051227</v>
+        <v>7051229</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18946,7 +18964,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18973,7 +18991,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128399887</v>
+        <v>128399882</v>
       </c>
       <c r="B176" t="n">
         <v>57689</v>
@@ -19008,10 +19026,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425756</v>
+        <v>425864</v>
       </c>
       <c r="R176" t="n">
-        <v>7051229</v>
+        <v>7051211</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19048,7 +19066,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19075,32 +19093,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128399882</v>
+        <v>128399835</v>
       </c>
       <c r="B177" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19110,10 +19128,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>425864</v>
+        <v>426132</v>
       </c>
       <c r="R177" t="n">
-        <v>7051211</v>
+        <v>7051150</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19146,11 +19164,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19177,10 +19190,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128399854</v>
+        <v>128399938</v>
       </c>
       <c r="B178" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19188,42 +19201,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>426733</v>
+        <v>426205</v>
       </c>
       <c r="R178" t="n">
-        <v>7051347</v>
+        <v>7051276</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19256,11 +19261,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19287,10 +19287,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399932</v>
+        <v>128399950</v>
       </c>
       <c r="B179" t="n">
-        <v>91480</v>
+        <v>88867</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19298,21 +19298,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>426231</v>
+        <v>426303</v>
       </c>
       <c r="R179" t="n">
-        <v>7051130</v>
+        <v>7050905</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19384,10 +19384,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128399923</v>
+        <v>128399951</v>
       </c>
       <c r="B180" t="n">
-        <v>91462</v>
+        <v>88867</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19395,21 +19395,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>426172</v>
+        <v>426062</v>
       </c>
       <c r="R180" t="n">
-        <v>7051169</v>
+        <v>7051265</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19481,10 +19481,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399944</v>
+        <v>128399932</v>
       </c>
       <c r="B181" t="n">
-        <v>91484</v>
+        <v>91480</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19492,21 +19492,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19516,10 +19516,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>425889</v>
+        <v>426231</v>
       </c>
       <c r="R181" t="n">
-        <v>7051300</v>
+        <v>7051130</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19578,10 +19578,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128399950</v>
+        <v>128399923</v>
       </c>
       <c r="B182" t="n">
-        <v>88867</v>
+        <v>91462</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19589,21 +19589,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>426303</v>
+        <v>426172</v>
       </c>
       <c r="R182" t="n">
-        <v>7050905</v>
+        <v>7051169</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19675,10 +19675,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128399951</v>
+        <v>128399944</v>
       </c>
       <c r="B183" t="n">
-        <v>88867</v>
+        <v>91484</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19686,21 +19686,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19710,10 +19710,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>426062</v>
+        <v>425889</v>
       </c>
       <c r="R183" t="n">
-        <v>7051265</v>
+        <v>7051300</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399873</v>
+        <v>128399925</v>
       </c>
       <c r="B189" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426193</v>
+        <v>426047</v>
       </c>
       <c r="R189" t="n">
-        <v>7050977</v>
+        <v>7051252</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20353,11 +20353,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20384,10 +20379,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399862</v>
+        <v>128399939</v>
       </c>
       <c r="B190" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20395,21 +20390,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20419,10 +20414,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426292</v>
+        <v>426300</v>
       </c>
       <c r="R190" t="n">
-        <v>7050995</v>
+        <v>7051058</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20455,11 +20450,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20486,10 +20476,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B191" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20497,21 +20487,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20521,10 +20511,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R191" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20557,6 +20547,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20583,10 +20578,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399939</v>
+        <v>128399862</v>
       </c>
       <c r="B192" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20594,21 +20589,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20618,10 +20613,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426300</v>
+        <v>426292</v>
       </c>
       <c r="R192" t="n">
-        <v>7051058</v>
+        <v>7050995</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20654,6 +20649,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128398722</v>
+        <v>128398742</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1022,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426695</v>
+        <v>426374</v>
       </c>
       <c r="R5" t="n">
-        <v>7051338</v>
+        <v>7050919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128398798</v>
+        <v>128398722</v>
       </c>
       <c r="B6" t="n">
         <v>79089</v>
@@ -1153,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425947</v>
+        <v>426695</v>
       </c>
       <c r="R6" t="n">
-        <v>7051321</v>
+        <v>7051338</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128398742</v>
+        <v>128398798</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,39 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426374</v>
+        <v>425947</v>
       </c>
       <c r="R7" t="n">
-        <v>7050919</v>
+        <v>7051321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,12 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -4218,32 +4218,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398755</v>
+        <v>128398801</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>91920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426166</v>
+        <v>425985</v>
       </c>
       <c r="R34" t="n">
-        <v>7050989</v>
+        <v>7051282</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,10 +4325,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128398738</v>
+        <v>128398741</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,34 +4336,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426341</v>
+        <v>426298</v>
       </c>
       <c r="R35" t="n">
-        <v>7051103</v>
+        <v>7051029</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4395,7 +4400,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4405,7 +4410,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,7 +4442,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128398794</v>
+        <v>128398755</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4467,10 +4477,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425876</v>
+        <v>426166</v>
       </c>
       <c r="R36" t="n">
-        <v>7051324</v>
+        <v>7050989</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4502,7 +4512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4512,7 +4522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4539,32 +4549,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398801</v>
+        <v>128398738</v>
       </c>
       <c r="B37" t="n">
-        <v>91920</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4574,10 +4584,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425985</v>
+        <v>426341</v>
       </c>
       <c r="R37" t="n">
-        <v>7051282</v>
+        <v>7051103</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4609,7 +4619,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4619,7 +4629,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4646,10 +4656,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128398741</v>
+        <v>128398794</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4657,39 +4667,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426298</v>
+        <v>425876</v>
       </c>
       <c r="R38" t="n">
-        <v>7051029</v>
+        <v>7051324</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4721,7 +4726,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4731,12 +4736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398726</v>
+        <v>128398783</v>
       </c>
       <c r="B61" t="n">
-        <v>75168</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426522</v>
+        <v>425733</v>
       </c>
       <c r="R61" t="n">
-        <v>7051242</v>
+        <v>7051205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,21 +7281,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7312,32 +7297,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398769</v>
+        <v>128398726</v>
       </c>
       <c r="B62" t="n">
-        <v>91466</v>
+        <v>75168</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7347,10 +7332,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426135</v>
+        <v>426522</v>
       </c>
       <c r="R62" t="n">
-        <v>7051154</v>
+        <v>7051242</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7382,7 +7367,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7392,7 +7377,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7403,6 +7388,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7419,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128398783</v>
+        <v>128398769</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>91466</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,21 +7430,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>425733</v>
+        <v>426135</v>
       </c>
       <c r="R63" t="n">
-        <v>7051205</v>
+        <v>7051154</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -10975,32 +10975,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399832</v>
+        <v>128399898</v>
       </c>
       <c r="B96" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426401</v>
+        <v>425894</v>
       </c>
       <c r="R96" t="n">
-        <v>7051237</v>
+        <v>7051256</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11046,6 +11046,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11072,32 +11077,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399836</v>
+        <v>128399886</v>
       </c>
       <c r="B97" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11107,10 +11112,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426093</v>
+        <v>425743</v>
       </c>
       <c r="R97" t="n">
-        <v>7051184</v>
+        <v>7051241</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11143,6 +11148,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11169,32 +11179,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399898</v>
+        <v>128399832</v>
       </c>
       <c r="B98" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11204,10 +11214,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425894</v>
+        <v>426401</v>
       </c>
       <c r="R98" t="n">
-        <v>7051256</v>
+        <v>7051237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11240,11 +11250,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11271,32 +11276,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399886</v>
+        <v>128399836</v>
       </c>
       <c r="B99" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11306,10 +11311,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425743</v>
+        <v>426093</v>
       </c>
       <c r="R99" t="n">
-        <v>7051241</v>
+        <v>7051184</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11342,11 +11347,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399941</v>
+        <v>128399922</v>
       </c>
       <c r="B100" t="n">
-        <v>91484</v>
+        <v>91462</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>425987</v>
+        <v>426343</v>
       </c>
       <c r="R100" t="n">
-        <v>7051259</v>
+        <v>7050915</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11470,10 +11470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399922</v>
+        <v>128399936</v>
       </c>
       <c r="B101" t="n">
-        <v>91462</v>
+        <v>91480</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11481,21 +11481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11505,10 +11505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426343</v>
+        <v>425967</v>
       </c>
       <c r="R101" t="n">
-        <v>7050915</v>
+        <v>7051278</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11567,10 +11567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399936</v>
+        <v>128399829</v>
       </c>
       <c r="B102" t="n">
-        <v>91480</v>
+        <v>91466</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425967</v>
+        <v>426191</v>
       </c>
       <c r="R102" t="n">
-        <v>7051278</v>
+        <v>7050972</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11664,10 +11664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399829</v>
+        <v>128399941</v>
       </c>
       <c r="B103" t="n">
-        <v>91466</v>
+        <v>91484</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11675,21 +11675,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426191</v>
+        <v>425987</v>
       </c>
       <c r="R103" t="n">
-        <v>7050972</v>
+        <v>7051259</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12664,32 +12664,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128399833</v>
+        <v>128399943</v>
       </c>
       <c r="B113" t="n">
-        <v>92163</v>
+        <v>91484</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>426263</v>
+        <v>425756</v>
       </c>
       <c r="R113" t="n">
-        <v>7051287</v>
+        <v>7051245</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12761,32 +12761,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128399831</v>
+        <v>128399904</v>
       </c>
       <c r="B114" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426425</v>
+        <v>426012</v>
       </c>
       <c r="R114" t="n">
-        <v>7051289</v>
+        <v>7051306</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12832,6 +12832,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12858,10 +12863,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399943</v>
+        <v>128399870</v>
       </c>
       <c r="B115" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12869,21 +12874,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12893,10 +12898,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>425756</v>
+        <v>426156</v>
       </c>
       <c r="R115" t="n">
-        <v>7051245</v>
+        <v>7050998</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12929,6 +12934,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12955,32 +12965,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399904</v>
+        <v>128399833</v>
       </c>
       <c r="B116" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12990,10 +13000,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426012</v>
+        <v>426263</v>
       </c>
       <c r="R116" t="n">
-        <v>7051306</v>
+        <v>7051287</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13026,11 +13036,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,32 +13062,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128399870</v>
+        <v>128399831</v>
       </c>
       <c r="B117" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13092,10 +13097,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426156</v>
+        <v>426425</v>
       </c>
       <c r="R117" t="n">
-        <v>7050998</v>
+        <v>7051289</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13128,11 +13133,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13159,10 +13159,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399928</v>
+        <v>128399872</v>
       </c>
       <c r="B118" t="n">
-        <v>91480</v>
+        <v>57689</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13170,21 +13170,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426319</v>
+        <v>426187</v>
       </c>
       <c r="R118" t="n">
-        <v>7051238</v>
+        <v>7050975</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13230,6 +13230,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13256,45 +13261,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399838</v>
+        <v>128399853</v>
       </c>
       <c r="B119" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>425752</v>
+        <v>426736</v>
       </c>
       <c r="R119" t="n">
-        <v>7051219</v>
+        <v>7051344</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13327,6 +13340,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13353,7 +13371,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399872</v>
+        <v>128399914</v>
       </c>
       <c r="B120" t="n">
         <v>57689</v>
@@ -13388,10 +13406,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426187</v>
+        <v>426219</v>
       </c>
       <c r="R120" t="n">
-        <v>7050975</v>
+        <v>7051364</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13455,7 +13473,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399853</v>
+        <v>128399852</v>
       </c>
       <c r="B121" t="n">
         <v>57689</v>
@@ -13484,24 +13502,16 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426736</v>
+        <v>426765</v>
       </c>
       <c r="R121" t="n">
-        <v>7051344</v>
+        <v>7051373</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13538,7 +13548,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13565,7 +13575,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399914</v>
+        <v>128399897</v>
       </c>
       <c r="B122" t="n">
         <v>57689</v>
@@ -13600,10 +13610,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>426219</v>
+        <v>425892</v>
       </c>
       <c r="R122" t="n">
-        <v>7051364</v>
+        <v>7051251</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13640,7 +13650,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13667,7 +13677,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399852</v>
+        <v>128399902</v>
       </c>
       <c r="B123" t="n">
         <v>57689</v>
@@ -13702,10 +13712,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>426765</v>
+        <v>425902</v>
       </c>
       <c r="R123" t="n">
-        <v>7051373</v>
+        <v>7051312</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13742,7 +13752,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13769,7 +13779,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128399897</v>
+        <v>128399871</v>
       </c>
       <c r="B124" t="n">
         <v>57689</v>
@@ -13804,10 +13814,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>425892</v>
+        <v>426154</v>
       </c>
       <c r="R124" t="n">
-        <v>7051251</v>
+        <v>7050994</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13871,32 +13881,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128399902</v>
+        <v>128399838</v>
       </c>
       <c r="B125" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13906,10 +13916,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425902</v>
+        <v>425752</v>
       </c>
       <c r="R125" t="n">
-        <v>7051312</v>
+        <v>7051219</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13942,11 +13952,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13973,10 +13978,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399871</v>
+        <v>128399928</v>
       </c>
       <c r="B126" t="n">
-        <v>57689</v>
+        <v>91480</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13984,21 +13989,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14008,10 +14013,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426154</v>
+        <v>426319</v>
       </c>
       <c r="R126" t="n">
-        <v>7050994</v>
+        <v>7051238</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14044,11 +14049,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -18177,32 +18177,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128399899</v>
+        <v>128399843</v>
       </c>
       <c r="B168" t="n">
-        <v>57689</v>
+        <v>92163</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18212,10 +18212,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>425928</v>
+        <v>426425</v>
       </c>
       <c r="R168" t="n">
-        <v>7051283</v>
+        <v>7051273</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18248,11 +18248,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18279,32 +18274,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128399843</v>
+        <v>128399869</v>
       </c>
       <c r="B169" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18314,10 +18309,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>426425</v>
+        <v>426163</v>
       </c>
       <c r="R169" t="n">
-        <v>7051273</v>
+        <v>7050993</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18350,6 +18345,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18376,7 +18376,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128399869</v>
+        <v>128399899</v>
       </c>
       <c r="B170" t="n">
         <v>57689</v>
@@ -18411,10 +18411,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>426163</v>
+        <v>425928</v>
       </c>
       <c r="R170" t="n">
-        <v>7050993</v>
+        <v>7051283</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19287,10 +19287,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399950</v>
+        <v>128399894</v>
       </c>
       <c r="B179" t="n">
-        <v>88867</v>
+        <v>57689</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19298,21 +19298,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>426303</v>
+        <v>425875</v>
       </c>
       <c r="R179" t="n">
-        <v>7050905</v>
+        <v>7051223</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19358,6 +19358,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19384,10 +19389,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128399951</v>
+        <v>128399915</v>
       </c>
       <c r="B180" t="n">
-        <v>88867</v>
+        <v>57689</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19395,21 +19400,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19419,10 +19424,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>426062</v>
+        <v>426224</v>
       </c>
       <c r="R180" t="n">
-        <v>7051265</v>
+        <v>7051367</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19455,6 +19460,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19481,10 +19491,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399932</v>
+        <v>128399912</v>
       </c>
       <c r="B181" t="n">
-        <v>91480</v>
+        <v>57689</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19492,21 +19502,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19516,10 +19526,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>426231</v>
+        <v>426175</v>
       </c>
       <c r="R181" t="n">
-        <v>7051130</v>
+        <v>7051336</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19552,6 +19562,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19578,10 +19593,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128399923</v>
+        <v>128399891</v>
       </c>
       <c r="B182" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19589,21 +19604,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19613,10 +19628,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>426172</v>
+        <v>425844</v>
       </c>
       <c r="R182" t="n">
-        <v>7051169</v>
+        <v>7051240</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19649,6 +19664,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19675,10 +19695,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128399944</v>
+        <v>128399950</v>
       </c>
       <c r="B183" t="n">
-        <v>91484</v>
+        <v>88867</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19686,21 +19706,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19710,10 +19730,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>425889</v>
+        <v>426303</v>
       </c>
       <c r="R183" t="n">
-        <v>7051300</v>
+        <v>7050905</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19772,10 +19792,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128399894</v>
+        <v>128399951</v>
       </c>
       <c r="B184" t="n">
-        <v>57689</v>
+        <v>88867</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19783,21 +19803,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19807,10 +19827,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>425875</v>
+        <v>426062</v>
       </c>
       <c r="R184" t="n">
-        <v>7051223</v>
+        <v>7051265</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19843,11 +19863,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19874,10 +19889,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128399915</v>
+        <v>128399932</v>
       </c>
       <c r="B185" t="n">
-        <v>57689</v>
+        <v>91480</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19885,21 +19900,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19909,10 +19924,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>426224</v>
+        <v>426231</v>
       </c>
       <c r="R185" t="n">
-        <v>7051367</v>
+        <v>7051130</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19945,11 +19960,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19976,10 +19986,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128399912</v>
+        <v>128399923</v>
       </c>
       <c r="B186" t="n">
-        <v>57689</v>
+        <v>91462</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19987,21 +19997,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20011,10 +20021,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>426175</v>
+        <v>426172</v>
       </c>
       <c r="R186" t="n">
-        <v>7051336</v>
+        <v>7051169</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20047,11 +20057,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20078,10 +20083,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128399860</v>
+        <v>128399944</v>
       </c>
       <c r="B187" t="n">
-        <v>57689</v>
+        <v>91484</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20089,21 +20094,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20113,10 +20118,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>426309</v>
+        <v>425889</v>
       </c>
       <c r="R187" t="n">
-        <v>7051245</v>
+        <v>7051300</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20149,11 +20154,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20180,7 +20180,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128399891</v>
+        <v>128399860</v>
       </c>
       <c r="B188" t="n">
         <v>57689</v>
@@ -20215,10 +20215,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>425844</v>
+        <v>426309</v>
       </c>
       <c r="R188" t="n">
-        <v>7051240</v>
+        <v>7051245</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128398758</v>
+        <v>128398759</v>
       </c>
       <c r="B3" t="n">
-        <v>82948</v>
+        <v>88867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128398759</v>
+        <v>128398758</v>
       </c>
       <c r="B4" t="n">
-        <v>88867</v>
+        <v>82948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128398742</v>
+        <v>128398722</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,39 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426374</v>
+        <v>426695</v>
       </c>
       <c r="R5" t="n">
-        <v>7050919</v>
+        <v>7051338</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128398722</v>
+        <v>128398798</v>
       </c>
       <c r="B6" t="n">
         <v>79089</v>
@@ -1163,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426695</v>
+        <v>425947</v>
       </c>
       <c r="R6" t="n">
-        <v>7051338</v>
+        <v>7051321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128398798</v>
+        <v>128398742</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,34 +1236,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>425947</v>
+        <v>426374</v>
       </c>
       <c r="R7" t="n">
-        <v>7051321</v>
+        <v>7050919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1310,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128398746</v>
+        <v>128398775</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,34 +1353,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426300</v>
+        <v>425892</v>
       </c>
       <c r="R8" t="n">
-        <v>7050902</v>
+        <v>7051220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,7 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128398768</v>
+        <v>128398774</v>
       </c>
       <c r="B9" t="n">
         <v>57689</v>
@@ -1480,7 +1490,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1489,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426158</v>
+        <v>425970</v>
       </c>
       <c r="R9" t="n">
-        <v>7051146</v>
+        <v>7051235</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1566,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128398774</v>
+        <v>128398746</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,39 +1587,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425970</v>
+        <v>426300</v>
       </c>
       <c r="R10" t="n">
-        <v>7051235</v>
+        <v>7050902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,12 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128398775</v>
+        <v>128398768</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1714,7 +1714,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425892</v>
+        <v>426158</v>
       </c>
       <c r="R11" t="n">
-        <v>7051220</v>
+        <v>7051146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128398762</v>
+        <v>128398790</v>
       </c>
       <c r="B12" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426225</v>
+        <v>425825</v>
       </c>
       <c r="R12" t="n">
-        <v>7051098</v>
+        <v>7051257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398790</v>
+        <v>128398762</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425825</v>
+        <v>426225</v>
       </c>
       <c r="R13" t="n">
-        <v>7051257</v>
+        <v>7051098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,12 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,7 +2027,7 @@
         <v>128398811</v>
       </c>
       <c r="B14" t="n">
-        <v>91462</v>
+        <v>91463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>128398740</v>
       </c>
       <c r="B15" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128398776</v>
+        <v>128398824</v>
       </c>
       <c r="B16" t="n">
         <v>79089</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425869</v>
+        <v>426331</v>
       </c>
       <c r="R16" t="n">
-        <v>7051201</v>
+        <v>7051374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,7 +2345,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128398824</v>
+        <v>128398776</v>
       </c>
       <c r="B17" t="n">
         <v>79089</v>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426331</v>
+        <v>425869</v>
       </c>
       <c r="R17" t="n">
-        <v>7051374</v>
+        <v>7051201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2572,7 +2572,7 @@
         <v>128398770</v>
       </c>
       <c r="B19" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398718</v>
+        <v>128398803</v>
       </c>
       <c r="B20" t="n">
-        <v>92768</v>
+        <v>92164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426807</v>
+        <v>425994</v>
       </c>
       <c r="R20" t="n">
-        <v>7051311</v>
+        <v>7051287</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,48 +2783,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398773</v>
+        <v>128398805</v>
       </c>
       <c r="B21" t="n">
-        <v>75175</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6486</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425978</v>
+        <v>425999</v>
       </c>
       <c r="R21" t="n">
-        <v>7051231</v>
+        <v>7051258</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,7 +2862,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2872,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398753</v>
+        <v>128398730</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,21 +2910,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426191</v>
+        <v>426382</v>
       </c>
       <c r="R22" t="n">
-        <v>7050957</v>
+        <v>7051149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,7 +2969,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2979,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2981,21 +2990,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3012,7 +3006,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398730</v>
+        <v>128398821</v>
       </c>
       <c r="B23" t="n">
         <v>79089</v>
@@ -3047,10 +3041,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426382</v>
+        <v>426200</v>
       </c>
       <c r="R23" t="n">
-        <v>7051149</v>
+        <v>7051338</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,7 +3076,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3086,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3113,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398805</v>
+        <v>128398752</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,46 +3124,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425999</v>
+        <v>426206</v>
       </c>
       <c r="R24" t="n">
-        <v>7051258</v>
+        <v>7050935</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3198,7 +3183,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3208,7 +3193,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,32 +3220,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398803</v>
+        <v>128398729</v>
       </c>
       <c r="B25" t="n">
-        <v>92163</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3255,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425994</v>
+        <v>426468</v>
       </c>
       <c r="R25" t="n">
-        <v>7051287</v>
+        <v>7051179</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,7 +3290,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3315,7 +3300,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3345,7 +3330,7 @@
         <v>128398771</v>
       </c>
       <c r="B26" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,32 +3434,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398821</v>
+        <v>128398718</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>92769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3484,10 +3469,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426200</v>
+        <v>426807</v>
       </c>
       <c r="R27" t="n">
-        <v>7051338</v>
+        <v>7051311</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3519,7 +3504,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3529,7 +3514,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3556,32 +3541,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398729</v>
+        <v>128398773</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>75175</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3591,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426468</v>
+        <v>425978</v>
       </c>
       <c r="R28" t="n">
-        <v>7051179</v>
+        <v>7051231</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3626,7 +3611,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3636,7 +3621,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3663,10 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128398752</v>
+        <v>128398753</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3674,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3698,10 +3683,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426206</v>
+        <v>426191</v>
       </c>
       <c r="R29" t="n">
-        <v>7050935</v>
+        <v>7050957</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3733,7 +3718,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3743,7 +3728,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3754,6 +3739,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3770,32 +3770,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128398819</v>
+        <v>128398788</v>
       </c>
       <c r="B30" t="n">
-        <v>91466</v>
+        <v>75168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426181</v>
+        <v>425804</v>
       </c>
       <c r="R30" t="n">
-        <v>7051325</v>
+        <v>7051255</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3861,6 +3861,11 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Glasbjörk</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3877,32 +3882,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398788</v>
+        <v>128398791</v>
       </c>
       <c r="B31" t="n">
-        <v>75168</v>
+        <v>75169</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3917,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425804</v>
+        <v>425847</v>
       </c>
       <c r="R31" t="n">
-        <v>7051255</v>
+        <v>7051261</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,7 +3952,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3962,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3969,9 +3974,19 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Glasbjörk</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3989,10 +4004,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398791</v>
+        <v>128398819</v>
       </c>
       <c r="B32" t="n">
-        <v>75169</v>
+        <v>91467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4000,21 +4015,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4024,10 +4039,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425847</v>
+        <v>426181</v>
       </c>
       <c r="R32" t="n">
-        <v>7051261</v>
+        <v>7051325</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4059,7 +4074,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4069,7 +4084,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4080,21 +4095,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4221,7 +4221,7 @@
         <v>128398801</v>
       </c>
       <c r="B34" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4763,32 +4763,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128398795</v>
+        <v>128398785</v>
       </c>
       <c r="B39" t="n">
-        <v>91484</v>
+        <v>92164</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425894</v>
+        <v>425708</v>
       </c>
       <c r="R39" t="n">
-        <v>7051343</v>
+        <v>7051228</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4870,32 +4870,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128398785</v>
+        <v>128398808</v>
       </c>
       <c r="B40" t="n">
-        <v>92163</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>425708</v>
+        <v>426012</v>
       </c>
       <c r="R40" t="n">
-        <v>7051228</v>
+        <v>7051229</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4977,10 +4977,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128398808</v>
+        <v>128398795</v>
       </c>
       <c r="B41" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4988,21 +4988,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426012</v>
+        <v>425894</v>
       </c>
       <c r="R41" t="n">
-        <v>7051229</v>
+        <v>7051343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,32 +5084,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128398787</v>
+        <v>128398736</v>
       </c>
       <c r="B42" t="n">
-        <v>75169</v>
+        <v>92164</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>425795</v>
+        <v>426352</v>
       </c>
       <c r="R42" t="n">
-        <v>7051251</v>
+        <v>7051151</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398800</v>
+        <v>128398787</v>
       </c>
       <c r="B43" t="n">
-        <v>91480</v>
+        <v>75169</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425985</v>
+        <v>425795</v>
       </c>
       <c r="R43" t="n">
-        <v>7051282</v>
+        <v>7051251</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5410,32 +5410,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128398736</v>
+        <v>128398800</v>
       </c>
       <c r="B45" t="n">
-        <v>92163</v>
+        <v>91481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>426352</v>
+        <v>425985</v>
       </c>
       <c r="R45" t="n">
-        <v>7051151</v>
+        <v>7051282</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5517,32 +5517,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128398731</v>
+        <v>128398797</v>
       </c>
       <c r="B46" t="n">
-        <v>92163</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426369</v>
+        <v>425919</v>
       </c>
       <c r="R46" t="n">
-        <v>7051152</v>
+        <v>7051350</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,7 +5624,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398797</v>
+        <v>128398725</v>
       </c>
       <c r="B47" t="n">
         <v>79089</v>
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>425919</v>
+        <v>426492</v>
       </c>
       <c r="R47" t="n">
-        <v>7051350</v>
+        <v>7051269</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5838,32 +5838,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128398725</v>
+        <v>128398731</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>92164</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426492</v>
+        <v>426369</v>
       </c>
       <c r="R49" t="n">
-        <v>7051269</v>
+        <v>7051152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398793</v>
+        <v>128398743</v>
       </c>
       <c r="B52" t="n">
-        <v>57689</v>
+        <v>91463</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6190,39 +6190,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>425908</v>
+        <v>426371</v>
       </c>
       <c r="R52" t="n">
-        <v>7051281</v>
+        <v>7050917</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6254,7 +6249,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6264,12 +6259,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6296,10 +6286,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128398814</v>
+        <v>128398727</v>
       </c>
       <c r="B53" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6307,39 +6297,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426097</v>
+        <v>426516</v>
       </c>
       <c r="R53" t="n">
-        <v>7051199</v>
+        <v>7051239</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6371,7 +6356,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6381,12 +6366,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6413,50 +6393,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398822</v>
+        <v>128398804</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>75175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426200</v>
+        <v>426000</v>
       </c>
       <c r="R54" t="n">
-        <v>7051338</v>
+        <v>7051290</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6488,7 +6466,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6498,12 +6476,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6511,6 +6484,11 @@
       </c>
       <c r="AE54" t="b">
         <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -6530,10 +6508,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398719</v>
+        <v>128398802</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>91763</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6541,39 +6519,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426799</v>
+        <v>425985</v>
       </c>
       <c r="R55" t="n">
-        <v>7051328</v>
+        <v>7051282</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6605,7 +6578,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6615,12 +6588,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6647,32 +6615,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398727</v>
+        <v>128398734</v>
       </c>
       <c r="B56" t="n">
-        <v>79089</v>
+        <v>92164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6682,10 +6650,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426516</v>
+        <v>426329</v>
       </c>
       <c r="R56" t="n">
-        <v>7051239</v>
+        <v>7051146</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6717,7 +6685,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6727,7 +6695,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6754,48 +6722,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398804</v>
+        <v>128398793</v>
       </c>
       <c r="B57" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426000</v>
+        <v>425908</v>
       </c>
       <c r="R57" t="n">
-        <v>7051290</v>
+        <v>7051281</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6827,7 +6797,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6837,7 +6807,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6845,11 +6820,6 @@
       </c>
       <c r="AE57" t="b">
         <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG57" t="b">
         <v>0</v>
@@ -6869,10 +6839,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398743</v>
+        <v>128398814</v>
       </c>
       <c r="B58" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6880,34 +6850,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426371</v>
+        <v>426097</v>
       </c>
       <c r="R58" t="n">
-        <v>7050917</v>
+        <v>7051199</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6939,7 +6914,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6949,7 +6924,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6976,10 +6956,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398802</v>
+        <v>128398719</v>
       </c>
       <c r="B59" t="n">
-        <v>91762</v>
+        <v>57689</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6987,34 +6967,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>425985</v>
+        <v>426799</v>
       </c>
       <c r="R59" t="n">
-        <v>7051282</v>
+        <v>7051328</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7046,7 +7031,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7056,7 +7041,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7083,45 +7073,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398734</v>
+        <v>128398822</v>
       </c>
       <c r="B60" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426329</v>
+        <v>426200</v>
       </c>
       <c r="R60" t="n">
-        <v>7051146</v>
+        <v>7051338</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7153,7 +7148,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7163,7 +7158,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398783</v>
+        <v>128398726</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>75168</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>425733</v>
+        <v>426522</v>
       </c>
       <c r="R61" t="n">
-        <v>7051205</v>
+        <v>7051242</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,6 +7281,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7297,32 +7312,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398726</v>
+        <v>128398769</v>
       </c>
       <c r="B62" t="n">
-        <v>75168</v>
+        <v>91467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7332,10 +7347,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426522</v>
+        <v>426135</v>
       </c>
       <c r="R62" t="n">
-        <v>7051242</v>
+        <v>7051154</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7367,7 +7382,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7377,7 +7392,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7388,21 +7403,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7419,10 +7419,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128398769</v>
+        <v>128398783</v>
       </c>
       <c r="B63" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,21 +7430,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>426135</v>
+        <v>425733</v>
       </c>
       <c r="R63" t="n">
-        <v>7051154</v>
+        <v>7051205</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8081,32 +8081,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128398820</v>
+        <v>128398733</v>
       </c>
       <c r="B69" t="n">
-        <v>91484</v>
+        <v>92164</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426196</v>
+        <v>426361</v>
       </c>
       <c r="R69" t="n">
-        <v>7051340</v>
+        <v>7051151</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8188,32 +8188,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128398733</v>
+        <v>128398820</v>
       </c>
       <c r="B70" t="n">
-        <v>92163</v>
+        <v>91485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426361</v>
+        <v>426196</v>
       </c>
       <c r="R70" t="n">
-        <v>7051151</v>
+        <v>7051340</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128398779</v>
+        <v>128398720</v>
       </c>
       <c r="B73" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8520,39 +8520,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>425818</v>
+        <v>426773</v>
       </c>
       <c r="R73" t="n">
-        <v>7051169</v>
+        <v>7051341</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8584,7 +8579,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8594,12 +8589,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8626,10 +8616,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128398720</v>
+        <v>128398779</v>
       </c>
       <c r="B74" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8637,34 +8627,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426773</v>
+        <v>425818</v>
       </c>
       <c r="R74" t="n">
-        <v>7051341</v>
+        <v>7051169</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8696,7 +8691,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8706,7 +8701,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8733,10 +8733,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128398815</v>
+        <v>128398789</v>
       </c>
       <c r="B75" t="n">
-        <v>91873</v>
+        <v>57689</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8744,29 +8744,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426114</v>
+        <v>425804</v>
       </c>
       <c r="R75" t="n">
-        <v>7051205</v>
+        <v>7051258</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8798,7 +8808,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8808,7 +8818,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8835,50 +8850,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128398789</v>
+        <v>128398772</v>
       </c>
       <c r="B76" t="n">
-        <v>57689</v>
+        <v>92164</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>425804</v>
+        <v>426065</v>
       </c>
       <c r="R76" t="n">
-        <v>7051258</v>
+        <v>7051192</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8910,7 +8920,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8920,12 +8930,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9074,32 +9079,27 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128398772</v>
+        <v>128398815</v>
       </c>
       <c r="B78" t="n">
-        <v>92163</v>
+        <v>91874</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>426065</v>
+        <v>426114</v>
       </c>
       <c r="R78" t="n">
-        <v>7051192</v>
+        <v>7051205</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9181,10 +9181,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128398723</v>
+        <v>128398813</v>
       </c>
       <c r="B79" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9192,21 +9192,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426515</v>
+        <v>426097</v>
       </c>
       <c r="R79" t="n">
-        <v>7051308</v>
+        <v>7051199</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9288,10 +9288,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128398751</v>
+        <v>128398765</v>
       </c>
       <c r="B80" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426239</v>
+        <v>426186</v>
       </c>
       <c r="R80" t="n">
-        <v>7050935</v>
+        <v>7051125</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9395,10 +9395,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128398784</v>
+        <v>128398723</v>
       </c>
       <c r="B81" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9406,39 +9406,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>425712</v>
+        <v>426515</v>
       </c>
       <c r="R81" t="n">
-        <v>7051206</v>
+        <v>7051308</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9470,7 +9465,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9480,12 +9475,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9512,10 +9502,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128398813</v>
+        <v>128398751</v>
       </c>
       <c r="B82" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9523,21 +9513,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9547,10 +9537,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426097</v>
+        <v>426239</v>
       </c>
       <c r="R82" t="n">
-        <v>7051199</v>
+        <v>7050935</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9582,7 +9572,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9592,7 +9582,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9619,10 +9609,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128398765</v>
+        <v>128398784</v>
       </c>
       <c r="B83" t="n">
-        <v>82948</v>
+        <v>57689</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9630,34 +9620,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>426186</v>
+        <v>425712</v>
       </c>
       <c r="R83" t="n">
-        <v>7051125</v>
+        <v>7051206</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9689,7 +9684,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9699,7 +9694,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10373,7 +10373,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128399916</v>
+        <v>128399875</v>
       </c>
       <c r="B90" t="n">
         <v>57689</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>426279</v>
+        <v>426207</v>
       </c>
       <c r="R90" t="n">
-        <v>7051408</v>
+        <v>7051009</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10475,7 +10475,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399875</v>
+        <v>128399895</v>
       </c>
       <c r="B91" t="n">
         <v>57689</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>426207</v>
+        <v>425879</v>
       </c>
       <c r="R91" t="n">
-        <v>7051009</v>
+        <v>7051238</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128399895</v>
+        <v>128399916</v>
       </c>
       <c r="B92" t="n">
         <v>57689</v>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>425879</v>
+        <v>426279</v>
       </c>
       <c r="R92" t="n">
-        <v>7051238</v>
+        <v>7051408</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399949</v>
+        <v>128399849</v>
       </c>
       <c r="B93" t="n">
-        <v>88867</v>
+        <v>57689</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426768</v>
+        <v>426803</v>
       </c>
       <c r="R93" t="n">
-        <v>7051367</v>
+        <v>7051353</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10750,6 +10750,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10779,7 +10784,7 @@
         <v>128399940</v>
       </c>
       <c r="B94" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10873,10 +10878,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399849</v>
+        <v>128399949</v>
       </c>
       <c r="B95" t="n">
-        <v>57689</v>
+        <v>88867</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10884,21 +10889,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10908,10 +10913,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426803</v>
+        <v>426768</v>
       </c>
       <c r="R95" t="n">
-        <v>7051353</v>
+        <v>7051367</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10944,11 +10949,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10975,32 +10975,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399898</v>
+        <v>128399836</v>
       </c>
       <c r="B96" t="n">
-        <v>57689</v>
+        <v>92164</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425894</v>
+        <v>426093</v>
       </c>
       <c r="R96" t="n">
-        <v>7051256</v>
+        <v>7051184</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11046,11 +11046,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11077,32 +11072,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399886</v>
+        <v>128399832</v>
       </c>
       <c r="B97" t="n">
-        <v>57689</v>
+        <v>92164</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11112,10 +11107,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425743</v>
+        <v>426401</v>
       </c>
       <c r="R97" t="n">
-        <v>7051241</v>
+        <v>7051237</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11148,11 +11143,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11179,32 +11169,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399832</v>
+        <v>128399898</v>
       </c>
       <c r="B98" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11214,10 +11204,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426401</v>
+        <v>425894</v>
       </c>
       <c r="R98" t="n">
-        <v>7051237</v>
+        <v>7051256</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11250,6 +11240,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11276,32 +11271,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399836</v>
+        <v>128399886</v>
       </c>
       <c r="B99" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11311,10 +11306,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>426093</v>
+        <v>425743</v>
       </c>
       <c r="R99" t="n">
-        <v>7051184</v>
+        <v>7051241</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11347,6 +11342,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399922</v>
+        <v>128399829</v>
       </c>
       <c r="B100" t="n">
-        <v>91462</v>
+        <v>91467</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426343</v>
+        <v>426191</v>
       </c>
       <c r="R100" t="n">
-        <v>7050915</v>
+        <v>7050972</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11470,10 +11470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399936</v>
+        <v>128399922</v>
       </c>
       <c r="B101" t="n">
-        <v>91480</v>
+        <v>91463</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11481,21 +11481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11505,10 +11505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425967</v>
+        <v>426343</v>
       </c>
       <c r="R101" t="n">
-        <v>7051278</v>
+        <v>7050915</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11567,10 +11567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399829</v>
+        <v>128399936</v>
       </c>
       <c r="B102" t="n">
-        <v>91466</v>
+        <v>91481</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11578,21 +11578,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11602,10 +11602,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426191</v>
+        <v>425967</v>
       </c>
       <c r="R102" t="n">
-        <v>7050972</v>
+        <v>7051278</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11667,7 +11667,7 @@
         <v>128399941</v>
       </c>
       <c r="B103" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11965,32 +11965,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399945</v>
+        <v>128399834</v>
       </c>
       <c r="B106" t="n">
-        <v>91484</v>
+        <v>92164</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426062</v>
+        <v>426228</v>
       </c>
       <c r="R106" t="n">
-        <v>7051271</v>
+        <v>7050978</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12062,32 +12062,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399834</v>
+        <v>128399945</v>
       </c>
       <c r="B107" t="n">
-        <v>92163</v>
+        <v>91485</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12097,10 +12097,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426228</v>
+        <v>426062</v>
       </c>
       <c r="R107" t="n">
-        <v>7050978</v>
+        <v>7051271</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12159,7 +12159,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399903</v>
+        <v>128399863</v>
       </c>
       <c r="B108" t="n">
         <v>57689</v>
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>425972</v>
+        <v>426347</v>
       </c>
       <c r="R108" t="n">
-        <v>7051285</v>
+        <v>7050960</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12261,7 +12261,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399863</v>
+        <v>128399868</v>
       </c>
       <c r="B109" t="n">
         <v>57689</v>
@@ -12296,10 +12296,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426347</v>
+        <v>426274</v>
       </c>
       <c r="R109" t="n">
-        <v>7050960</v>
+        <v>7050964</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12363,7 +12363,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399868</v>
+        <v>128399903</v>
       </c>
       <c r="B110" t="n">
         <v>57689</v>
@@ -12398,10 +12398,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>426274</v>
+        <v>425972</v>
       </c>
       <c r="R110" t="n">
-        <v>7050964</v>
+        <v>7051285</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12570,7 +12570,7 @@
         <v>128399935</v>
       </c>
       <c r="B112" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12664,32 +12664,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128399943</v>
+        <v>128399831</v>
       </c>
       <c r="B113" t="n">
-        <v>91484</v>
+        <v>92164</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>425756</v>
+        <v>426425</v>
       </c>
       <c r="R113" t="n">
-        <v>7051245</v>
+        <v>7051289</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12761,32 +12761,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128399904</v>
+        <v>128399833</v>
       </c>
       <c r="B114" t="n">
-        <v>57689</v>
+        <v>92164</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426012</v>
+        <v>426263</v>
       </c>
       <c r="R114" t="n">
-        <v>7051306</v>
+        <v>7051287</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12832,11 +12832,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12863,10 +12858,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399870</v>
+        <v>128399943</v>
       </c>
       <c r="B115" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12874,21 +12869,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12898,10 +12893,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426156</v>
+        <v>425756</v>
       </c>
       <c r="R115" t="n">
-        <v>7050998</v>
+        <v>7051245</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12934,11 +12929,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12965,32 +12955,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399833</v>
+        <v>128399904</v>
       </c>
       <c r="B116" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13000,10 +12990,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426263</v>
+        <v>426012</v>
       </c>
       <c r="R116" t="n">
-        <v>7051287</v>
+        <v>7051306</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13036,6 +13026,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13062,32 +13057,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128399831</v>
+        <v>128399870</v>
       </c>
       <c r="B117" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13097,10 +13092,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426425</v>
+        <v>426156</v>
       </c>
       <c r="R117" t="n">
-        <v>7051289</v>
+        <v>7050998</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13133,6 +13128,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13159,10 +13159,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399872</v>
+        <v>128399928</v>
       </c>
       <c r="B118" t="n">
-        <v>57689</v>
+        <v>91481</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13170,21 +13170,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426187</v>
+        <v>426319</v>
       </c>
       <c r="R118" t="n">
-        <v>7050975</v>
+        <v>7051238</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13230,11 +13230,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13261,53 +13256,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399853</v>
+        <v>128399838</v>
       </c>
       <c r="B119" t="n">
-        <v>57689</v>
+        <v>92164</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426736</v>
+        <v>425752</v>
       </c>
       <c r="R119" t="n">
-        <v>7051344</v>
+        <v>7051219</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13340,11 +13327,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13371,7 +13353,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399914</v>
+        <v>128399852</v>
       </c>
       <c r="B120" t="n">
         <v>57689</v>
@@ -13406,10 +13388,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426219</v>
+        <v>426765</v>
       </c>
       <c r="R120" t="n">
-        <v>7051364</v>
+        <v>7051373</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13473,7 +13455,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399852</v>
+        <v>128399914</v>
       </c>
       <c r="B121" t="n">
         <v>57689</v>
@@ -13508,10 +13490,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426765</v>
+        <v>426219</v>
       </c>
       <c r="R121" t="n">
-        <v>7051373</v>
+        <v>7051364</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13677,7 +13659,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399902</v>
+        <v>128399853</v>
       </c>
       <c r="B123" t="n">
         <v>57689</v>
@@ -13706,16 +13688,24 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425902</v>
+        <v>426736</v>
       </c>
       <c r="R123" t="n">
-        <v>7051312</v>
+        <v>7051344</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13752,7 +13742,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13881,32 +13871,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128399838</v>
+        <v>128399902</v>
       </c>
       <c r="B125" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13916,10 +13906,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425752</v>
+        <v>425902</v>
       </c>
       <c r="R125" t="n">
-        <v>7051219</v>
+        <v>7051312</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13952,6 +13942,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13978,10 +13973,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399928</v>
+        <v>128399872</v>
       </c>
       <c r="B126" t="n">
-        <v>91480</v>
+        <v>57689</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13989,21 +13984,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14013,10 +14008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426319</v>
+        <v>426187</v>
       </c>
       <c r="R126" t="n">
-        <v>7051238</v>
+        <v>7050975</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14049,6 +14044,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14075,10 +14075,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128399920</v>
+        <v>128399948</v>
       </c>
       <c r="B127" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>426277</v>
+        <v>426395</v>
       </c>
       <c r="R127" t="n">
-        <v>7051183</v>
+        <v>7051398</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14146,6 +14146,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14172,10 +14177,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128399942</v>
+        <v>128399901</v>
       </c>
       <c r="B128" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14183,21 +14188,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14207,10 +14212,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425904</v>
+        <v>425880</v>
       </c>
       <c r="R128" t="n">
-        <v>7051248</v>
+        <v>7051304</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14243,6 +14248,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14269,10 +14279,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399948</v>
+        <v>128399878</v>
       </c>
       <c r="B129" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14280,21 +14290,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14304,10 +14314,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426395</v>
+        <v>426047</v>
       </c>
       <c r="R129" t="n">
-        <v>7051398</v>
+        <v>7051186</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14344,7 +14354,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14371,7 +14381,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128399901</v>
+        <v>128399905</v>
       </c>
       <c r="B130" t="n">
         <v>57689</v>
@@ -14406,10 +14416,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>425880</v>
+        <v>426029</v>
       </c>
       <c r="R130" t="n">
-        <v>7051304</v>
+        <v>7051287</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14446,7 +14456,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14473,7 +14483,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399878</v>
+        <v>128399876</v>
       </c>
       <c r="B131" t="n">
         <v>57689</v>
@@ -14508,10 +14518,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426047</v>
+        <v>426244</v>
       </c>
       <c r="R131" t="n">
-        <v>7051186</v>
+        <v>7051052</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14548,7 +14558,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14575,10 +14585,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399876</v>
+        <v>128399920</v>
       </c>
       <c r="B132" t="n">
-        <v>57689</v>
+        <v>91463</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14586,21 +14596,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14610,10 +14620,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>426244</v>
+        <v>426277</v>
       </c>
       <c r="R132" t="n">
-        <v>7051052</v>
+        <v>7051183</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14646,11 +14656,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14677,10 +14682,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399905</v>
+        <v>128399942</v>
       </c>
       <c r="B133" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14688,21 +14693,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14712,10 +14717,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426029</v>
+        <v>425904</v>
       </c>
       <c r="R133" t="n">
-        <v>7051287</v>
+        <v>7051248</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14748,11 +14753,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14779,10 +14779,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128399930</v>
+        <v>128399918</v>
       </c>
       <c r="B134" t="n">
-        <v>91480</v>
+        <v>91417</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14790,21 +14790,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14814,10 +14814,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>426267</v>
+        <v>426224</v>
       </c>
       <c r="R134" t="n">
-        <v>7050942</v>
+        <v>7050981</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14876,10 +14876,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128399931</v>
+        <v>128399929</v>
       </c>
       <c r="B135" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>426252</v>
+        <v>426276</v>
       </c>
       <c r="R135" t="n">
-        <v>7050958</v>
+        <v>7050944</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14973,10 +14973,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128399918</v>
+        <v>128399931</v>
       </c>
       <c r="B136" t="n">
-        <v>91416</v>
+        <v>91481</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14984,21 +14984,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>426224</v>
+        <v>426252</v>
       </c>
       <c r="R136" t="n">
-        <v>7050981</v>
+        <v>7050958</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15070,10 +15070,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128399929</v>
+        <v>128399930</v>
       </c>
       <c r="B137" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15105,10 +15105,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>426276</v>
+        <v>426267</v>
       </c>
       <c r="R137" t="n">
-        <v>7050944</v>
+        <v>7050942</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15269,7 +15269,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128399867</v>
+        <v>128399879</v>
       </c>
       <c r="B139" t="n">
         <v>57689</v>
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>426331</v>
+        <v>426055</v>
       </c>
       <c r="R139" t="n">
-        <v>7050912</v>
+        <v>7051223</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15371,7 +15371,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128399906</v>
+        <v>128399890</v>
       </c>
       <c r="B140" t="n">
         <v>57689</v>
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>426053</v>
+        <v>425829</v>
       </c>
       <c r="R140" t="n">
-        <v>7051256</v>
+        <v>7051228</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15473,7 +15473,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128399879</v>
+        <v>128399906</v>
       </c>
       <c r="B141" t="n">
         <v>57689</v>
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>426055</v>
+        <v>426053</v>
       </c>
       <c r="R141" t="n">
-        <v>7051223</v>
+        <v>7051256</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15677,7 +15677,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128399890</v>
+        <v>128399910</v>
       </c>
       <c r="B143" t="n">
         <v>57689</v>
@@ -15712,10 +15712,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>425829</v>
+        <v>426170</v>
       </c>
       <c r="R143" t="n">
-        <v>7051228</v>
+        <v>7051345</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15779,7 +15779,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128399910</v>
+        <v>128399867</v>
       </c>
       <c r="B144" t="n">
         <v>57689</v>
@@ -15814,10 +15814,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>426170</v>
+        <v>426331</v>
       </c>
       <c r="R144" t="n">
-        <v>7051345</v>
+        <v>7050912</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15884,7 +15884,7 @@
         <v>128399933</v>
       </c>
       <c r="B145" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16185,7 +16185,7 @@
         <v>128399828</v>
       </c>
       <c r="B148" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16279,10 +16279,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128399937</v>
+        <v>128399883</v>
       </c>
       <c r="B149" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16290,21 +16290,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16314,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>426734</v>
+        <v>425851</v>
       </c>
       <c r="R149" t="n">
-        <v>7051350</v>
+        <v>7051202</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16350,6 +16350,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16376,10 +16381,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128399946</v>
+        <v>128399892</v>
       </c>
       <c r="B150" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16387,21 +16392,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16411,10 +16416,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>426083</v>
+        <v>425853</v>
       </c>
       <c r="R150" t="n">
-        <v>7051231</v>
+        <v>7051216</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16447,6 +16452,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16473,7 +16483,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128399892</v>
+        <v>128399861</v>
       </c>
       <c r="B151" t="n">
         <v>57689</v>
@@ -16508,10 +16518,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>425853</v>
+        <v>426285</v>
       </c>
       <c r="R151" t="n">
-        <v>7051216</v>
+        <v>7051199</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16575,7 +16585,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128399883</v>
+        <v>128399855</v>
       </c>
       <c r="B152" t="n">
         <v>57689</v>
@@ -16610,10 +16620,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>425851</v>
+        <v>426639</v>
       </c>
       <c r="R152" t="n">
-        <v>7051202</v>
+        <v>7051351</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16677,10 +16687,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128399861</v>
+        <v>128399946</v>
       </c>
       <c r="B153" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16688,21 +16698,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16712,10 +16722,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>426285</v>
+        <v>426083</v>
       </c>
       <c r="R153" t="n">
-        <v>7051199</v>
+        <v>7051231</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16748,11 +16758,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16779,10 +16784,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128399855</v>
+        <v>128399937</v>
       </c>
       <c r="B154" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16790,21 +16795,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16814,10 +16819,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>426639</v>
+        <v>426734</v>
       </c>
       <c r="R154" t="n">
-        <v>7051351</v>
+        <v>7051350</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16850,11 +16855,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17190,7 +17190,7 @@
         <v>128399827</v>
       </c>
       <c r="B158" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>128399839</v>
       </c>
       <c r="B159" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17585,32 +17585,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128399837</v>
+        <v>128399926</v>
       </c>
       <c r="B162" t="n">
-        <v>92163</v>
+        <v>91463</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>425757</v>
+        <v>426189</v>
       </c>
       <c r="R162" t="n">
-        <v>7051207</v>
+        <v>7051364</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17685,7 +17685,7 @@
         <v>128399840</v>
       </c>
       <c r="B163" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17779,32 +17779,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128399926</v>
+        <v>128399837</v>
       </c>
       <c r="B164" t="n">
-        <v>91462</v>
+        <v>92164</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17814,10 +17814,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>426189</v>
+        <v>425757</v>
       </c>
       <c r="R164" t="n">
-        <v>7051364</v>
+        <v>7051207</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17876,7 +17876,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128399874</v>
+        <v>128399864</v>
       </c>
       <c r="B165" t="n">
         <v>57689</v>
@@ -17911,10 +17911,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>426194</v>
+        <v>426357</v>
       </c>
       <c r="R165" t="n">
-        <v>7050979</v>
+        <v>7050965</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17978,7 +17978,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128399864</v>
+        <v>128399874</v>
       </c>
       <c r="B166" t="n">
         <v>57689</v>
@@ -18013,10 +18013,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>426357</v>
+        <v>426194</v>
       </c>
       <c r="R166" t="n">
-        <v>7050965</v>
+        <v>7050979</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18080,32 +18080,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128399934</v>
+        <v>128399843</v>
       </c>
       <c r="B167" t="n">
-        <v>91480</v>
+        <v>92164</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18115,10 +18115,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>426135</v>
+        <v>426425</v>
       </c>
       <c r="R167" t="n">
-        <v>7051163</v>
+        <v>7051273</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18177,32 +18177,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128399843</v>
+        <v>128399899</v>
       </c>
       <c r="B168" t="n">
-        <v>92163</v>
+        <v>57689</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18212,10 +18212,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>426425</v>
+        <v>425928</v>
       </c>
       <c r="R168" t="n">
-        <v>7051273</v>
+        <v>7051283</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18248,6 +18248,11 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18274,10 +18279,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128399869</v>
+        <v>128399934</v>
       </c>
       <c r="B169" t="n">
-        <v>57689</v>
+        <v>91481</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18285,21 +18290,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18309,10 +18314,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>426163</v>
+        <v>426135</v>
       </c>
       <c r="R169" t="n">
-        <v>7050993</v>
+        <v>7051163</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18345,11 +18350,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18376,7 +18376,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128399899</v>
+        <v>128399869</v>
       </c>
       <c r="B170" t="n">
         <v>57689</v>
@@ -18411,10 +18411,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>425928</v>
+        <v>426163</v>
       </c>
       <c r="R170" t="n">
-        <v>7051283</v>
+        <v>7050993</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18478,10 +18478,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128399854</v>
+        <v>128399921</v>
       </c>
       <c r="B171" t="n">
-        <v>57689</v>
+        <v>91463</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18489,42 +18489,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>426733</v>
+        <v>426314</v>
       </c>
       <c r="R171" t="n">
-        <v>7051347</v>
+        <v>7050963</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18557,11 +18549,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18588,10 +18575,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128399921</v>
+        <v>128399887</v>
       </c>
       <c r="B172" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18599,21 +18586,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18623,10 +18610,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>426314</v>
+        <v>425756</v>
       </c>
       <c r="R172" t="n">
-        <v>7050963</v>
+        <v>7051229</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18659,6 +18646,11 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18685,7 +18677,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128399884</v>
+        <v>128399893</v>
       </c>
       <c r="B173" t="n">
         <v>57689</v>
@@ -18720,10 +18712,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>425770</v>
+        <v>425861</v>
       </c>
       <c r="R173" t="n">
-        <v>7051183</v>
+        <v>7051227</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18760,7 +18752,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18787,7 +18779,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128399893</v>
+        <v>128399884</v>
       </c>
       <c r="B174" t="n">
         <v>57689</v>
@@ -18822,10 +18814,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>425861</v>
+        <v>425770</v>
       </c>
       <c r="R174" t="n">
-        <v>7051227</v>
+        <v>7051183</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18862,7 +18854,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18889,7 +18881,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128399887</v>
+        <v>128399854</v>
       </c>
       <c r="B175" t="n">
         <v>57689</v>
@@ -18918,16 +18910,24 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425756</v>
+        <v>426733</v>
       </c>
       <c r="R175" t="n">
-        <v>7051229</v>
+        <v>7051347</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19096,7 +19096,7 @@
         <v>128399835</v>
       </c>
       <c r="B177" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>128399938</v>
       </c>
       <c r="B178" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399894</v>
+        <v>128399944</v>
       </c>
       <c r="B179" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19298,21 +19298,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>425875</v>
+        <v>425889</v>
       </c>
       <c r="R179" t="n">
-        <v>7051223</v>
+        <v>7051300</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19358,11 +19358,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19491,7 +19486,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399912</v>
+        <v>128399860</v>
       </c>
       <c r="B181" t="n">
         <v>57689</v>
@@ -19526,10 +19521,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>426175</v>
+        <v>426309</v>
       </c>
       <c r="R181" t="n">
-        <v>7051336</v>
+        <v>7051245</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19566,7 +19561,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19593,7 +19588,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128399891</v>
+        <v>128399894</v>
       </c>
       <c r="B182" t="n">
         <v>57689</v>
@@ -19628,10 +19623,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>425844</v>
+        <v>425875</v>
       </c>
       <c r="R182" t="n">
-        <v>7051240</v>
+        <v>7051223</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19668,7 +19663,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19695,10 +19690,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128399950</v>
+        <v>128399891</v>
       </c>
       <c r="B183" t="n">
-        <v>88867</v>
+        <v>57689</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19706,21 +19701,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19730,10 +19725,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>426303</v>
+        <v>425844</v>
       </c>
       <c r="R183" t="n">
-        <v>7050905</v>
+        <v>7051240</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19766,6 +19761,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19792,10 +19792,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128399951</v>
+        <v>128399912</v>
       </c>
       <c r="B184" t="n">
-        <v>88867</v>
+        <v>57689</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19803,21 +19803,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19827,10 +19827,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>426062</v>
+        <v>426175</v>
       </c>
       <c r="R184" t="n">
-        <v>7051265</v>
+        <v>7051336</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19863,6 +19863,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19889,10 +19894,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128399932</v>
+        <v>128399951</v>
       </c>
       <c r="B185" t="n">
-        <v>91480</v>
+        <v>88867</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19900,21 +19905,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19924,10 +19929,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>426231</v>
+        <v>426062</v>
       </c>
       <c r="R185" t="n">
-        <v>7051130</v>
+        <v>7051265</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19986,10 +19991,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128399923</v>
+        <v>128399950</v>
       </c>
       <c r="B186" t="n">
-        <v>91462</v>
+        <v>88867</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19997,21 +20002,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20021,10 +20026,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>426172</v>
+        <v>426303</v>
       </c>
       <c r="R186" t="n">
-        <v>7051169</v>
+        <v>7050905</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20083,10 +20088,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128399944</v>
+        <v>128399923</v>
       </c>
       <c r="B187" t="n">
-        <v>91484</v>
+        <v>91463</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20094,21 +20099,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20118,10 +20123,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>425889</v>
+        <v>426172</v>
       </c>
       <c r="R187" t="n">
-        <v>7051300</v>
+        <v>7051169</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20180,10 +20185,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128399860</v>
+        <v>128399932</v>
       </c>
       <c r="B188" t="n">
-        <v>57689</v>
+        <v>91481</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20191,21 +20196,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20215,10 +20220,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>426309</v>
+        <v>426231</v>
       </c>
       <c r="R188" t="n">
-        <v>7051245</v>
+        <v>7051130</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20251,11 +20256,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B189" t="n">
-        <v>91462</v>
+        <v>57689</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R189" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20353,6 +20353,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20379,10 +20384,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399939</v>
+        <v>128399862</v>
       </c>
       <c r="B190" t="n">
-        <v>91484</v>
+        <v>57689</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20390,21 +20395,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20414,10 +20419,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426300</v>
+        <v>426292</v>
       </c>
       <c r="R190" t="n">
-        <v>7051058</v>
+        <v>7050995</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20450,6 +20455,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20476,10 +20486,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399873</v>
+        <v>128399925</v>
       </c>
       <c r="B191" t="n">
-        <v>57689</v>
+        <v>91463</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20487,21 +20497,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20511,10 +20521,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426193</v>
+        <v>426047</v>
       </c>
       <c r="R191" t="n">
-        <v>7050977</v>
+        <v>7051252</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20547,11 +20557,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20578,10 +20583,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399862</v>
+        <v>128399939</v>
       </c>
       <c r="B192" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20589,21 +20594,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20613,10 +20618,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426292</v>
+        <v>426300</v>
       </c>
       <c r="R192" t="n">
-        <v>7050995</v>
+        <v>7051058</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20649,11 +20654,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -1342,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128398775</v>
+        <v>128398768</v>
       </c>
       <c r="B8" t="n">
         <v>57689</v>
@@ -1373,7 +1373,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>425892</v>
+        <v>426158</v>
       </c>
       <c r="R8" t="n">
-        <v>7051220</v>
+        <v>7051146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128398774</v>
+        <v>128398746</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,39 +1470,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425970</v>
+        <v>426300</v>
       </c>
       <c r="R9" t="n">
-        <v>7051235</v>
+        <v>7050902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,12 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128398746</v>
+        <v>128398775</v>
       </c>
       <c r="B10" t="n">
-        <v>91485</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,34 +1577,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426300</v>
+        <v>425892</v>
       </c>
       <c r="R10" t="n">
-        <v>7050902</v>
+        <v>7051220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1651,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128398768</v>
+        <v>128398774</v>
       </c>
       <c r="B11" t="n">
         <v>57689</v>
@@ -1714,7 +1714,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426158</v>
+        <v>425970</v>
       </c>
       <c r="R11" t="n">
-        <v>7051146</v>
+        <v>7051235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128398790</v>
+        <v>128398762</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>91485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425825</v>
+        <v>426225</v>
       </c>
       <c r="R12" t="n">
-        <v>7051257</v>
+        <v>7051098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,12 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398762</v>
+        <v>128398790</v>
       </c>
       <c r="B13" t="n">
-        <v>91485</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426225</v>
+        <v>425825</v>
       </c>
       <c r="R13" t="n">
-        <v>7051098</v>
+        <v>7051257</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2783,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398805</v>
+        <v>128398730</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,46 +2794,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425999</v>
+        <v>426382</v>
       </c>
       <c r="R21" t="n">
-        <v>7051258</v>
+        <v>7051149</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2862,7 +2853,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2872,7 +2863,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,7 +2890,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398730</v>
+        <v>128398821</v>
       </c>
       <c r="B22" t="n">
         <v>79089</v>
@@ -2934,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426382</v>
+        <v>426200</v>
       </c>
       <c r="R22" t="n">
-        <v>7051149</v>
+        <v>7051338</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2969,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2970,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,7 +2997,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398821</v>
+        <v>128398752</v>
       </c>
       <c r="B23" t="n">
         <v>79089</v>
@@ -3041,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426200</v>
+        <v>426206</v>
       </c>
       <c r="R23" t="n">
-        <v>7051338</v>
+        <v>7050935</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3076,7 +3067,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3086,7 +3077,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,7 +3104,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398752</v>
+        <v>128398729</v>
       </c>
       <c r="B24" t="n">
         <v>79089</v>
@@ -3148,10 +3139,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426206</v>
+        <v>426468</v>
       </c>
       <c r="R24" t="n">
-        <v>7050935</v>
+        <v>7051179</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3183,7 +3174,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3193,7 +3184,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,32 +3211,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398729</v>
+        <v>128398718</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>92769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3255,10 +3246,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426468</v>
+        <v>426807</v>
       </c>
       <c r="R25" t="n">
-        <v>7051179</v>
+        <v>7051311</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3290,7 +3281,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3300,7 +3291,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3327,32 +3318,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398771</v>
+        <v>128398773</v>
       </c>
       <c r="B26" t="n">
-        <v>91485</v>
+        <v>75175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3362,10 +3353,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426068</v>
+        <v>425978</v>
       </c>
       <c r="R26" t="n">
-        <v>7051189</v>
+        <v>7051231</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3397,7 +3388,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3407,7 +3398,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,32 +3425,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398718</v>
+        <v>128398753</v>
       </c>
       <c r="B27" t="n">
-        <v>92769</v>
+        <v>80194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3469,10 +3460,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426807</v>
+        <v>426191</v>
       </c>
       <c r="R27" t="n">
-        <v>7051311</v>
+        <v>7050957</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,7 +3495,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3514,7 +3505,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3525,6 +3516,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3541,32 +3547,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398773</v>
+        <v>128398771</v>
       </c>
       <c r="B28" t="n">
-        <v>75175</v>
+        <v>91485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6486</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>425978</v>
+        <v>426068</v>
       </c>
       <c r="R28" t="n">
-        <v>7051231</v>
+        <v>7051189</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3611,7 +3617,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3621,7 +3627,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,10 +3654,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128398753</v>
+        <v>128398805</v>
       </c>
       <c r="B29" t="n">
-        <v>80194</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,37 +3665,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>426191</v>
+        <v>425999</v>
       </c>
       <c r="R29" t="n">
-        <v>7050957</v>
+        <v>7051258</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3718,7 +3733,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3728,7 +3743,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3739,21 +3754,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4763,32 +4763,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128398785</v>
+        <v>128398808</v>
       </c>
       <c r="B39" t="n">
-        <v>92164</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425708</v>
+        <v>426012</v>
       </c>
       <c r="R39" t="n">
-        <v>7051228</v>
+        <v>7051229</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4870,10 +4870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128398808</v>
+        <v>128398795</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426012</v>
+        <v>425894</v>
       </c>
       <c r="R40" t="n">
-        <v>7051229</v>
+        <v>7051343</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4977,32 +4977,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128398795</v>
+        <v>128398785</v>
       </c>
       <c r="B41" t="n">
-        <v>91485</v>
+        <v>92164</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425894</v>
+        <v>425708</v>
       </c>
       <c r="R41" t="n">
-        <v>7051343</v>
+        <v>7051228</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5517,32 +5517,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128398797</v>
+        <v>128398731</v>
       </c>
       <c r="B46" t="n">
-        <v>79089</v>
+        <v>92164</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>425919</v>
+        <v>426369</v>
       </c>
       <c r="R46" t="n">
-        <v>7051350</v>
+        <v>7051152</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,10 +5624,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398725</v>
+        <v>128398807</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,34 +5635,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426492</v>
+        <v>426011</v>
       </c>
       <c r="R47" t="n">
-        <v>7051269</v>
+        <v>7051282</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5694,7 +5699,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5704,7 +5709,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5731,7 +5741,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128398812</v>
+        <v>128398797</v>
       </c>
       <c r="B48" t="n">
         <v>79089</v>
@@ -5766,10 +5776,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426097</v>
+        <v>425919</v>
       </c>
       <c r="R48" t="n">
-        <v>7051199</v>
+        <v>7051350</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5801,7 +5811,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5811,7 +5821,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5838,32 +5848,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128398731</v>
+        <v>128398725</v>
       </c>
       <c r="B49" t="n">
-        <v>92164</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5873,10 +5883,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426369</v>
+        <v>426492</v>
       </c>
       <c r="R49" t="n">
-        <v>7051152</v>
+        <v>7051269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5908,7 +5918,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5918,7 +5928,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5945,10 +5955,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128398807</v>
+        <v>128398812</v>
       </c>
       <c r="B50" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5956,39 +5966,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426011</v>
+        <v>426097</v>
       </c>
       <c r="R50" t="n">
-        <v>7051282</v>
+        <v>7051199</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6020,7 +6025,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6030,12 +6035,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398743</v>
+        <v>128398802</v>
       </c>
       <c r="B52" t="n">
-        <v>91463</v>
+        <v>91763</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6190,21 +6190,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6214,10 +6214,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426371</v>
+        <v>425985</v>
       </c>
       <c r="R52" t="n">
-        <v>7050917</v>
+        <v>7051282</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6393,48 +6393,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398804</v>
+        <v>128398793</v>
       </c>
       <c r="B54" t="n">
-        <v>75175</v>
+        <v>57689</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6486</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426000</v>
+        <v>425908</v>
       </c>
       <c r="R54" t="n">
-        <v>7051290</v>
+        <v>7051281</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6466,7 +6468,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6476,7 +6478,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6484,11 +6491,6 @@
       </c>
       <c r="AE54" t="b">
         <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -6508,10 +6510,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398802</v>
+        <v>128398814</v>
       </c>
       <c r="B55" t="n">
-        <v>91763</v>
+        <v>57689</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6519,34 +6521,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>425985</v>
+        <v>426097</v>
       </c>
       <c r="R55" t="n">
-        <v>7051282</v>
+        <v>7051199</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6578,7 +6585,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6588,7 +6595,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6615,45 +6627,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398734</v>
+        <v>128398719</v>
       </c>
       <c r="B56" t="n">
-        <v>92164</v>
+        <v>57689</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426329</v>
+        <v>426799</v>
       </c>
       <c r="R56" t="n">
-        <v>7051146</v>
+        <v>7051328</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6685,7 +6702,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6695,7 +6712,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6722,7 +6744,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398793</v>
+        <v>128398822</v>
       </c>
       <c r="B57" t="n">
         <v>57689</v>
@@ -6762,10 +6784,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>425908</v>
+        <v>426200</v>
       </c>
       <c r="R57" t="n">
-        <v>7051281</v>
+        <v>7051338</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6797,7 +6819,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6807,7 +6829,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6839,10 +6861,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398814</v>
+        <v>128398743</v>
       </c>
       <c r="B58" t="n">
-        <v>57689</v>
+        <v>91463</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6850,39 +6872,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426097</v>
+        <v>426371</v>
       </c>
       <c r="R58" t="n">
-        <v>7051199</v>
+        <v>7050917</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6914,7 +6931,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6924,12 +6941,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6956,50 +6968,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398719</v>
+        <v>128398734</v>
       </c>
       <c r="B59" t="n">
-        <v>57689</v>
+        <v>92164</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426799</v>
+        <v>426329</v>
       </c>
       <c r="R59" t="n">
-        <v>7051328</v>
+        <v>7051146</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7031,7 +7038,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7041,12 +7048,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7073,50 +7075,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398822</v>
+        <v>128398804</v>
       </c>
       <c r="B60" t="n">
-        <v>57689</v>
+        <v>75175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426200</v>
+        <v>426000</v>
       </c>
       <c r="R60" t="n">
-        <v>7051338</v>
+        <v>7051290</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7158,12 +7158,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7171,6 +7166,11 @@
       </c>
       <c r="AE60" t="b">
         <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -8733,50 +8733,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128398789</v>
+        <v>128398772</v>
       </c>
       <c r="B75" t="n">
-        <v>57689</v>
+        <v>92164</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>425804</v>
+        <v>426065</v>
       </c>
       <c r="R75" t="n">
-        <v>7051258</v>
+        <v>7051192</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8808,7 +8803,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8818,12 +8813,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8850,32 +8840,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128398772</v>
+        <v>128398754</v>
       </c>
       <c r="B76" t="n">
-        <v>92164</v>
+        <v>80195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8885,10 +8875,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426065</v>
+        <v>426191</v>
       </c>
       <c r="R76" t="n">
-        <v>7051192</v>
+        <v>7050957</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8920,7 +8910,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8930,7 +8920,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8941,6 +8931,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8957,10 +8962,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128398754</v>
+        <v>128398789</v>
       </c>
       <c r="B77" t="n">
-        <v>80195</v>
+        <v>57689</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8968,34 +8973,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426191</v>
+        <v>425804</v>
       </c>
       <c r="R77" t="n">
-        <v>7050957</v>
+        <v>7051258</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9027,7 +9037,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9037,7 +9047,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9048,21 +9063,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10067,10 +10067,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128399908</v>
+        <v>128399850</v>
       </c>
       <c r="B87" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>426080</v>
+        <v>426803</v>
       </c>
       <c r="R87" t="n">
-        <v>7051237</v>
+        <v>7051361</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10169,10 +10169,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128399850</v>
+        <v>128399908</v>
       </c>
       <c r="B88" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10204,10 +10204,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>426803</v>
+        <v>426080</v>
       </c>
       <c r="R88" t="n">
-        <v>7051361</v>
+        <v>7051237</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10274,7 +10274,7 @@
         <v>128399888</v>
       </c>
       <c r="B89" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10373,10 +10373,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128399875</v>
+        <v>128399916</v>
       </c>
       <c r="B90" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>426207</v>
+        <v>426279</v>
       </c>
       <c r="R90" t="n">
-        <v>7051009</v>
+        <v>7051408</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10475,10 +10475,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399895</v>
+        <v>128399875</v>
       </c>
       <c r="B91" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>425879</v>
+        <v>426207</v>
       </c>
       <c r="R91" t="n">
-        <v>7051238</v>
+        <v>7051009</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10577,10 +10577,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128399916</v>
+        <v>128399895</v>
       </c>
       <c r="B92" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>426279</v>
+        <v>425879</v>
       </c>
       <c r="R92" t="n">
-        <v>7051408</v>
+        <v>7051238</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399849</v>
+        <v>128399949</v>
       </c>
       <c r="B93" t="n">
-        <v>57689</v>
+        <v>88894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426803</v>
+        <v>426768</v>
       </c>
       <c r="R93" t="n">
-        <v>7051353</v>
+        <v>7051367</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10750,11 +10750,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10784,7 +10779,7 @@
         <v>128399940</v>
       </c>
       <c r="B94" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10878,10 +10873,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399949</v>
+        <v>128399849</v>
       </c>
       <c r="B95" t="n">
-        <v>88867</v>
+        <v>57716</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10889,21 +10884,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10913,10 +10908,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426768</v>
+        <v>426803</v>
       </c>
       <c r="R95" t="n">
-        <v>7051367</v>
+        <v>7051353</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10949,6 +10944,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10975,32 +10975,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399836</v>
+        <v>128399886</v>
       </c>
       <c r="B96" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>426093</v>
+        <v>425743</v>
       </c>
       <c r="R96" t="n">
-        <v>7051184</v>
+        <v>7051241</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11046,6 +11046,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11075,7 +11080,7 @@
         <v>128399832</v>
       </c>
       <c r="B97" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11169,32 +11174,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399898</v>
+        <v>128399836</v>
       </c>
       <c r="B98" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11204,10 +11209,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>425894</v>
+        <v>426093</v>
       </c>
       <c r="R98" t="n">
-        <v>7051256</v>
+        <v>7051184</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11240,11 +11245,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11271,10 +11271,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399886</v>
+        <v>128399898</v>
       </c>
       <c r="B99" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425743</v>
+        <v>425894</v>
       </c>
       <c r="R99" t="n">
-        <v>7051241</v>
+        <v>7051256</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399829</v>
+        <v>128399907</v>
       </c>
       <c r="B100" t="n">
-        <v>91467</v>
+        <v>57716</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426191</v>
+        <v>426064</v>
       </c>
       <c r="R100" t="n">
-        <v>7050972</v>
+        <v>7051249</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11444,6 +11444,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11470,10 +11475,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399922</v>
+        <v>128399889</v>
       </c>
       <c r="B101" t="n">
-        <v>91463</v>
+        <v>57716</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11481,21 +11486,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11505,10 +11510,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426343</v>
+        <v>425774</v>
       </c>
       <c r="R101" t="n">
-        <v>7050915</v>
+        <v>7051222</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11541,6 +11546,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11567,10 +11577,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399936</v>
+        <v>128399941</v>
       </c>
       <c r="B102" t="n">
-        <v>91481</v>
+        <v>91512</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11578,21 +11588,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11602,10 +11612,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425967</v>
+        <v>425987</v>
       </c>
       <c r="R102" t="n">
-        <v>7051278</v>
+        <v>7051259</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11664,10 +11674,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399941</v>
+        <v>128399922</v>
       </c>
       <c r="B103" t="n">
-        <v>91485</v>
+        <v>91490</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11675,21 +11685,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11699,10 +11709,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>425987</v>
+        <v>426343</v>
       </c>
       <c r="R103" t="n">
-        <v>7051259</v>
+        <v>7050915</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11761,10 +11771,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128399907</v>
+        <v>128399936</v>
       </c>
       <c r="B104" t="n">
-        <v>57689</v>
+        <v>91508</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11772,21 +11782,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11796,10 +11806,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>426064</v>
+        <v>425967</v>
       </c>
       <c r="R104" t="n">
-        <v>7051249</v>
+        <v>7051278</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11832,11 +11842,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11863,10 +11868,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128399889</v>
+        <v>128399829</v>
       </c>
       <c r="B105" t="n">
-        <v>57689</v>
+        <v>91494</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11874,21 +11879,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11898,10 +11903,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>425774</v>
+        <v>426191</v>
       </c>
       <c r="R105" t="n">
-        <v>7051222</v>
+        <v>7050972</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11934,11 +11939,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11965,32 +11965,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399834</v>
+        <v>128399903</v>
       </c>
       <c r="B106" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426228</v>
+        <v>425972</v>
       </c>
       <c r="R106" t="n">
-        <v>7050978</v>
+        <v>7051285</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12036,6 +12036,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12062,10 +12067,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399945</v>
+        <v>128399863</v>
       </c>
       <c r="B107" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12073,21 +12078,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12097,10 +12102,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426062</v>
+        <v>426347</v>
       </c>
       <c r="R107" t="n">
-        <v>7051271</v>
+        <v>7050960</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12133,6 +12138,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12159,10 +12169,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399863</v>
+        <v>128399868</v>
       </c>
       <c r="B108" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12194,10 +12204,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>426347</v>
+        <v>426274</v>
       </c>
       <c r="R108" t="n">
-        <v>7050960</v>
+        <v>7050964</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12234,7 +12244,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12261,10 +12271,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399868</v>
+        <v>128399881</v>
       </c>
       <c r="B109" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12296,10 +12306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426274</v>
+        <v>425942</v>
       </c>
       <c r="R109" t="n">
-        <v>7050964</v>
+        <v>7051274</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12336,7 +12346,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12363,32 +12373,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399903</v>
+        <v>128399834</v>
       </c>
       <c r="B110" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12398,10 +12408,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>425972</v>
+        <v>426228</v>
       </c>
       <c r="R110" t="n">
-        <v>7051285</v>
+        <v>7050978</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12434,11 +12444,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12465,10 +12470,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128399881</v>
+        <v>128399945</v>
       </c>
       <c r="B111" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12476,21 +12481,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12500,10 +12505,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>425942</v>
+        <v>426062</v>
       </c>
       <c r="R111" t="n">
-        <v>7051274</v>
+        <v>7051271</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12536,11 +12541,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12570,7 +12570,7 @@
         <v>128399935</v>
       </c>
       <c r="B112" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12664,32 +12664,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128399831</v>
+        <v>128399943</v>
       </c>
       <c r="B113" t="n">
-        <v>92164</v>
+        <v>91512</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>426425</v>
+        <v>425756</v>
       </c>
       <c r="R113" t="n">
-        <v>7051289</v>
+        <v>7051245</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12761,32 +12761,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128399833</v>
+        <v>128399904</v>
       </c>
       <c r="B114" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12796,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426263</v>
+        <v>426012</v>
       </c>
       <c r="R114" t="n">
-        <v>7051287</v>
+        <v>7051306</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12832,6 +12832,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12858,10 +12863,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399943</v>
+        <v>128399870</v>
       </c>
       <c r="B115" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12869,21 +12874,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12893,10 +12898,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>425756</v>
+        <v>426156</v>
       </c>
       <c r="R115" t="n">
-        <v>7051245</v>
+        <v>7050998</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12929,6 +12934,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12955,32 +12965,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399904</v>
+        <v>128399833</v>
       </c>
       <c r="B116" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12990,10 +13000,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426012</v>
+        <v>426263</v>
       </c>
       <c r="R116" t="n">
-        <v>7051306</v>
+        <v>7051287</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13026,11 +13036,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13057,32 +13062,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128399870</v>
+        <v>128399831</v>
       </c>
       <c r="B117" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13092,10 +13097,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426156</v>
+        <v>426425</v>
       </c>
       <c r="R117" t="n">
-        <v>7050998</v>
+        <v>7051289</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13128,11 +13133,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13159,10 +13159,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399928</v>
+        <v>128399872</v>
       </c>
       <c r="B118" t="n">
-        <v>91481</v>
+        <v>57716</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13170,21 +13170,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426319</v>
+        <v>426187</v>
       </c>
       <c r="R118" t="n">
-        <v>7051238</v>
+        <v>7050975</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13230,6 +13230,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13256,45 +13261,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399838</v>
+        <v>128399853</v>
       </c>
       <c r="B119" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>425752</v>
+        <v>426736</v>
       </c>
       <c r="R119" t="n">
-        <v>7051219</v>
+        <v>7051344</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13327,6 +13340,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13353,10 +13371,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399852</v>
+        <v>128399914</v>
       </c>
       <c r="B120" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13388,10 +13406,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426765</v>
+        <v>426219</v>
       </c>
       <c r="R120" t="n">
-        <v>7051373</v>
+        <v>7051364</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13455,10 +13473,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399914</v>
+        <v>128399852</v>
       </c>
       <c r="B121" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13490,10 +13508,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426219</v>
+        <v>426765</v>
       </c>
       <c r="R121" t="n">
-        <v>7051364</v>
+        <v>7051373</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13560,7 +13578,7 @@
         <v>128399897</v>
       </c>
       <c r="B122" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13659,10 +13677,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399853</v>
+        <v>128399902</v>
       </c>
       <c r="B123" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13688,24 +13706,16 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>426736</v>
+        <v>425902</v>
       </c>
       <c r="R123" t="n">
-        <v>7051344</v>
+        <v>7051312</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13742,7 +13752,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13772,7 +13782,7 @@
         <v>128399871</v>
       </c>
       <c r="B124" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13871,10 +13881,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128399902</v>
+        <v>128399928</v>
       </c>
       <c r="B125" t="n">
-        <v>57689</v>
+        <v>91508</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13882,21 +13892,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13906,10 +13916,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>425902</v>
+        <v>426319</v>
       </c>
       <c r="R125" t="n">
-        <v>7051312</v>
+        <v>7051238</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13942,11 +13952,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13973,32 +13978,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399872</v>
+        <v>128399838</v>
       </c>
       <c r="B126" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14008,10 +14013,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426187</v>
+        <v>425752</v>
       </c>
       <c r="R126" t="n">
-        <v>7050975</v>
+        <v>7051219</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14044,11 +14049,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14075,10 +14075,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128399948</v>
+        <v>128399901</v>
       </c>
       <c r="B127" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>426395</v>
+        <v>425880</v>
       </c>
       <c r="R127" t="n">
-        <v>7051398</v>
+        <v>7051304</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14177,10 +14177,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128399901</v>
+        <v>128399878</v>
       </c>
       <c r="B128" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14212,10 +14212,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>425880</v>
+        <v>426047</v>
       </c>
       <c r="R128" t="n">
-        <v>7051304</v>
+        <v>7051186</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14279,10 +14279,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399878</v>
+        <v>128399876</v>
       </c>
       <c r="B129" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14314,10 +14314,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426047</v>
+        <v>426244</v>
       </c>
       <c r="R129" t="n">
-        <v>7051186</v>
+        <v>7051052</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14384,7 +14384,7 @@
         <v>128399905</v>
       </c>
       <c r="B130" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14483,10 +14483,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399876</v>
+        <v>128399920</v>
       </c>
       <c r="B131" t="n">
-        <v>57689</v>
+        <v>91490</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14494,21 +14494,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14518,10 +14518,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426244</v>
+        <v>426277</v>
       </c>
       <c r="R131" t="n">
-        <v>7051052</v>
+        <v>7051183</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14554,11 +14554,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14585,10 +14580,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399920</v>
+        <v>128399942</v>
       </c>
       <c r="B132" t="n">
-        <v>91463</v>
+        <v>91512</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14596,21 +14591,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14620,10 +14615,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>426277</v>
+        <v>425904</v>
       </c>
       <c r="R132" t="n">
-        <v>7051183</v>
+        <v>7051248</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14682,10 +14677,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399942</v>
+        <v>128399948</v>
       </c>
       <c r="B133" t="n">
-        <v>91485</v>
+        <v>79116</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14693,21 +14688,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14717,10 +14712,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>425904</v>
+        <v>426395</v>
       </c>
       <c r="R133" t="n">
-        <v>7051248</v>
+        <v>7051398</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14753,6 +14748,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14779,10 +14779,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128399918</v>
+        <v>128399930</v>
       </c>
       <c r="B134" t="n">
-        <v>91417</v>
+        <v>91508</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14790,21 +14790,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14814,10 +14814,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>426224</v>
+        <v>426267</v>
       </c>
       <c r="R134" t="n">
-        <v>7050981</v>
+        <v>7050942</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14876,10 +14876,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128399929</v>
+        <v>128399931</v>
       </c>
       <c r="B135" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>426276</v>
+        <v>426252</v>
       </c>
       <c r="R135" t="n">
-        <v>7050944</v>
+        <v>7050958</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14973,10 +14973,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128399931</v>
+        <v>128399929</v>
       </c>
       <c r="B136" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>426252</v>
+        <v>426276</v>
       </c>
       <c r="R136" t="n">
-        <v>7050958</v>
+        <v>7050944</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15070,10 +15070,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128399930</v>
+        <v>128399918</v>
       </c>
       <c r="B137" t="n">
-        <v>91481</v>
+        <v>91444</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15081,21 +15081,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15105,10 +15105,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>426267</v>
+        <v>426224</v>
       </c>
       <c r="R137" t="n">
-        <v>7050942</v>
+        <v>7050981</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15170,7 +15170,7 @@
         <v>128399877</v>
       </c>
       <c r="B138" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15269,10 +15269,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128399879</v>
+        <v>128399867</v>
       </c>
       <c r="B139" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15304,10 +15304,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>426055</v>
+        <v>426331</v>
       </c>
       <c r="R139" t="n">
-        <v>7051223</v>
+        <v>7050912</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15371,10 +15371,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128399890</v>
+        <v>128399906</v>
       </c>
       <c r="B140" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15406,10 +15406,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>425829</v>
+        <v>426053</v>
       </c>
       <c r="R140" t="n">
-        <v>7051228</v>
+        <v>7051256</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15473,10 +15473,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128399906</v>
+        <v>128399879</v>
       </c>
       <c r="B141" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15508,10 +15508,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>426053</v>
+        <v>426055</v>
       </c>
       <c r="R141" t="n">
-        <v>7051256</v>
+        <v>7051223</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15578,7 +15578,7 @@
         <v>128399896</v>
       </c>
       <c r="B142" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15677,10 +15677,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128399910</v>
+        <v>128399890</v>
       </c>
       <c r="B143" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15712,10 +15712,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>426170</v>
+        <v>425829</v>
       </c>
       <c r="R143" t="n">
-        <v>7051345</v>
+        <v>7051228</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15779,10 +15779,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128399867</v>
+        <v>128399910</v>
       </c>
       <c r="B144" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15814,10 +15814,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>426331</v>
+        <v>426170</v>
       </c>
       <c r="R144" t="n">
-        <v>7050912</v>
+        <v>7051345</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15881,10 +15881,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128399933</v>
+        <v>128399880</v>
       </c>
       <c r="B145" t="n">
-        <v>91481</v>
+        <v>57716</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15892,21 +15892,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15916,10 +15916,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>426218</v>
+        <v>425981</v>
       </c>
       <c r="R145" t="n">
-        <v>7051146</v>
+        <v>7051240</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15952,6 +15952,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15978,10 +15983,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128399880</v>
+        <v>128399933</v>
       </c>
       <c r="B146" t="n">
-        <v>57689</v>
+        <v>91508</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15989,21 +15994,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16013,10 +16018,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>425981</v>
+        <v>426218</v>
       </c>
       <c r="R146" t="n">
-        <v>7051240</v>
+        <v>7051146</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16049,11 +16054,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16083,7 +16083,7 @@
         <v>128399865</v>
       </c>
       <c r="B147" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16182,10 +16182,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128399828</v>
+        <v>128399883</v>
       </c>
       <c r="B148" t="n">
-        <v>91467</v>
+        <v>57716</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16193,21 +16193,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16217,10 +16217,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>426225</v>
+        <v>425851</v>
       </c>
       <c r="R148" t="n">
-        <v>7050963</v>
+        <v>7051202</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16253,6 +16253,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16279,10 +16284,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128399883</v>
+        <v>128399828</v>
       </c>
       <c r="B149" t="n">
-        <v>57689</v>
+        <v>91494</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16290,21 +16295,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16314,10 +16319,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>425851</v>
+        <v>426225</v>
       </c>
       <c r="R149" t="n">
-        <v>7051202</v>
+        <v>7050963</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16350,11 +16355,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16384,7 +16384,7 @@
         <v>128399892</v>
       </c>
       <c r="B150" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>128399861</v>
       </c>
       <c r="B151" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>128399855</v>
       </c>
       <c r="B152" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16687,10 +16687,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128399946</v>
+        <v>128399937</v>
       </c>
       <c r="B153" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16722,10 +16722,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>426083</v>
+        <v>426734</v>
       </c>
       <c r="R153" t="n">
-        <v>7051231</v>
+        <v>7051350</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16784,10 +16784,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128399937</v>
+        <v>128399946</v>
       </c>
       <c r="B154" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>426734</v>
+        <v>426083</v>
       </c>
       <c r="R154" t="n">
-        <v>7051350</v>
+        <v>7051231</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16884,7 +16884,7 @@
         <v>128399885</v>
       </c>
       <c r="B155" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>128399911</v>
       </c>
       <c r="B156" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>128399913</v>
       </c>
       <c r="B157" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17187,10 +17187,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128399827</v>
+        <v>128399856</v>
       </c>
       <c r="B158" t="n">
-        <v>91467</v>
+        <v>57716</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17198,34 +17198,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Stor-grässjön, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>426813</v>
+        <v>426646</v>
       </c>
       <c r="R158" t="n">
-        <v>7051371</v>
+        <v>7051365</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17258,6 +17258,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17284,32 +17289,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128399839</v>
+        <v>128399909</v>
       </c>
       <c r="B159" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17319,10 +17324,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>425971</v>
+        <v>426175</v>
       </c>
       <c r="R159" t="n">
-        <v>7051280</v>
+        <v>7051323</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17355,6 +17360,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17381,32 +17391,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128399856</v>
+        <v>128399839</v>
       </c>
       <c r="B160" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17416,10 +17426,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>426646</v>
+        <v>425971</v>
       </c>
       <c r="R160" t="n">
-        <v>7051365</v>
+        <v>7051280</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17452,11 +17462,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17483,10 +17488,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128399909</v>
+        <v>128399827</v>
       </c>
       <c r="B161" t="n">
-        <v>57689</v>
+        <v>91494</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17494,34 +17499,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>426175</v>
+        <v>426813</v>
       </c>
       <c r="R161" t="n">
-        <v>7051323</v>
+        <v>7051371</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17554,11 +17559,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17585,10 +17585,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128399926</v>
+        <v>128399874</v>
       </c>
       <c r="B162" t="n">
-        <v>91463</v>
+        <v>57716</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17596,21 +17596,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>426189</v>
+        <v>426194</v>
       </c>
       <c r="R162" t="n">
-        <v>7051364</v>
+        <v>7050979</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17656,6 +17656,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17682,32 +17687,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128399840</v>
+        <v>128399864</v>
       </c>
       <c r="B163" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17717,10 +17722,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>426131</v>
+        <v>426357</v>
       </c>
       <c r="R163" t="n">
-        <v>7051242</v>
+        <v>7050965</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17753,6 +17758,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17782,7 +17792,7 @@
         <v>128399837</v>
       </c>
       <c r="B164" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17876,32 +17886,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128399864</v>
+        <v>128399840</v>
       </c>
       <c r="B165" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17911,10 +17921,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>426357</v>
+        <v>426131</v>
       </c>
       <c r="R165" t="n">
-        <v>7050965</v>
+        <v>7051242</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17947,11 +17957,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17978,10 +17983,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128399874</v>
+        <v>128399926</v>
       </c>
       <c r="B166" t="n">
-        <v>57689</v>
+        <v>91490</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17989,21 +17994,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18013,10 +18018,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>426194</v>
+        <v>426189</v>
       </c>
       <c r="R166" t="n">
-        <v>7050979</v>
+        <v>7051364</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18049,11 +18054,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18080,32 +18080,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128399843</v>
+        <v>128399869</v>
       </c>
       <c r="B167" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18115,10 +18115,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>426425</v>
+        <v>426163</v>
       </c>
       <c r="R167" t="n">
-        <v>7051273</v>
+        <v>7050993</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18151,6 +18151,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18180,7 +18185,7 @@
         <v>128399899</v>
       </c>
       <c r="B168" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18279,32 +18284,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128399934</v>
+        <v>128399843</v>
       </c>
       <c r="B169" t="n">
-        <v>91481</v>
+        <v>92191</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18314,10 +18319,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>426135</v>
+        <v>426425</v>
       </c>
       <c r="R169" t="n">
-        <v>7051163</v>
+        <v>7051273</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18376,10 +18381,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128399869</v>
+        <v>128399934</v>
       </c>
       <c r="B170" t="n">
-        <v>57689</v>
+        <v>91508</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18387,21 +18392,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18411,10 +18416,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>426163</v>
+        <v>426135</v>
       </c>
       <c r="R170" t="n">
-        <v>7050993</v>
+        <v>7051163</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18447,11 +18452,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18478,10 +18478,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128399921</v>
+        <v>128399854</v>
       </c>
       <c r="B171" t="n">
-        <v>91463</v>
+        <v>57716</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18489,34 +18489,42 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>426314</v>
+        <v>426733</v>
       </c>
       <c r="R171" t="n">
-        <v>7050963</v>
+        <v>7051347</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18549,6 +18557,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18575,10 +18588,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128399887</v>
+        <v>128399884</v>
       </c>
       <c r="B172" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18610,10 +18623,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>425756</v>
+        <v>425770</v>
       </c>
       <c r="R172" t="n">
-        <v>7051229</v>
+        <v>7051183</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18680,7 +18693,7 @@
         <v>128399893</v>
       </c>
       <c r="B173" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18779,10 +18792,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128399884</v>
+        <v>128399887</v>
       </c>
       <c r="B174" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18814,10 +18827,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>425770</v>
+        <v>425756</v>
       </c>
       <c r="R174" t="n">
-        <v>7051183</v>
+        <v>7051229</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18881,10 +18894,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128399854</v>
+        <v>128399882</v>
       </c>
       <c r="B175" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18910,24 +18923,16 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>426733</v>
+        <v>425864</v>
       </c>
       <c r="R175" t="n">
-        <v>7051347</v>
+        <v>7051211</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18964,7 +18969,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18991,32 +18996,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128399882</v>
+        <v>128399835</v>
       </c>
       <c r="B176" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19026,10 +19031,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>425864</v>
+        <v>426132</v>
       </c>
       <c r="R176" t="n">
-        <v>7051211</v>
+        <v>7051150</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19062,11 +19067,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19093,32 +19093,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128399835</v>
+        <v>128399938</v>
       </c>
       <c r="B177" t="n">
-        <v>92164</v>
+        <v>91512</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19128,10 +19128,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>426132</v>
+        <v>426205</v>
       </c>
       <c r="R177" t="n">
-        <v>7051150</v>
+        <v>7051276</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19190,10 +19190,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128399938</v>
+        <v>128399921</v>
       </c>
       <c r="B178" t="n">
-        <v>91485</v>
+        <v>91490</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19201,21 +19201,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19225,10 +19225,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>426205</v>
+        <v>426314</v>
       </c>
       <c r="R178" t="n">
-        <v>7051276</v>
+        <v>7050963</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19287,10 +19287,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128399944</v>
+        <v>128399932</v>
       </c>
       <c r="B179" t="n">
-        <v>91485</v>
+        <v>91508</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19298,21 +19298,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19322,10 +19322,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>425889</v>
+        <v>426231</v>
       </c>
       <c r="R179" t="n">
-        <v>7051300</v>
+        <v>7051130</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19384,10 +19384,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128399915</v>
+        <v>128399950</v>
       </c>
       <c r="B180" t="n">
-        <v>57689</v>
+        <v>88894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19395,21 +19395,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>426224</v>
+        <v>426303</v>
       </c>
       <c r="R180" t="n">
-        <v>7051367</v>
+        <v>7050905</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19455,11 +19455,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19486,10 +19481,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128399860</v>
+        <v>128399951</v>
       </c>
       <c r="B181" t="n">
-        <v>57689</v>
+        <v>88894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19497,21 +19492,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19521,10 +19516,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>426309</v>
+        <v>426062</v>
       </c>
       <c r="R181" t="n">
-        <v>7051245</v>
+        <v>7051265</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19557,11 +19552,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19591,7 +19581,7 @@
         <v>128399894</v>
       </c>
       <c r="B182" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19690,10 +19680,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128399891</v>
+        <v>128399915</v>
       </c>
       <c r="B183" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19725,10 +19715,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>425844</v>
+        <v>426224</v>
       </c>
       <c r="R183" t="n">
-        <v>7051240</v>
+        <v>7051367</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19795,7 +19785,7 @@
         <v>128399912</v>
       </c>
       <c r="B184" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19894,10 +19884,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128399951</v>
+        <v>128399860</v>
       </c>
       <c r="B185" t="n">
-        <v>88867</v>
+        <v>57716</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19905,21 +19895,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19929,10 +19919,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>426062</v>
+        <v>426309</v>
       </c>
       <c r="R185" t="n">
-        <v>7051265</v>
+        <v>7051245</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19965,6 +19955,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19991,10 +19986,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128399950</v>
+        <v>128399891</v>
       </c>
       <c r="B186" t="n">
-        <v>88867</v>
+        <v>57716</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20002,21 +19997,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20026,10 +20021,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>426303</v>
+        <v>425844</v>
       </c>
       <c r="R186" t="n">
-        <v>7050905</v>
+        <v>7051240</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20062,6 +20057,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20091,7 +20091,7 @@
         <v>128399923</v>
       </c>
       <c r="B187" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20185,10 +20185,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128399932</v>
+        <v>128399944</v>
       </c>
       <c r="B188" t="n">
-        <v>91481</v>
+        <v>91512</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20196,21 +20196,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20220,10 +20220,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>426231</v>
+        <v>425889</v>
       </c>
       <c r="R188" t="n">
-        <v>7051130</v>
+        <v>7051300</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399873</v>
+        <v>128399925</v>
       </c>
       <c r="B189" t="n">
-        <v>57689</v>
+        <v>91490</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426193</v>
+        <v>426047</v>
       </c>
       <c r="R189" t="n">
-        <v>7050977</v>
+        <v>7051252</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20353,11 +20353,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20384,10 +20379,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399862</v>
+        <v>128399939</v>
       </c>
       <c r="B190" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20395,21 +20390,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20419,10 +20414,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426292</v>
+        <v>426300</v>
       </c>
       <c r="R190" t="n">
-        <v>7050995</v>
+        <v>7051058</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20455,11 +20450,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20486,10 +20476,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B191" t="n">
-        <v>91463</v>
+        <v>57716</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20497,21 +20487,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20521,10 +20511,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R191" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20557,6 +20547,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20583,10 +20578,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399939</v>
+        <v>128399862</v>
       </c>
       <c r="B192" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20594,21 +20589,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20618,10 +20613,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426300</v>
+        <v>426292</v>
       </c>
       <c r="R192" t="n">
-        <v>7051058</v>
+        <v>7050995</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20654,6 +20649,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20683,7 +20683,7 @@
         <v>128509948</v>
       </c>
       <c r="B193" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>128399846</v>
       </c>
       <c r="B194" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>128399847</v>
       </c>
       <c r="B195" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>128399845</v>
       </c>
       <c r="B196" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128398786</v>
       </c>
       <c r="B2" t="n">
-        <v>75169</v>
+        <v>75196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>128398759</v>
       </c>
       <c r="B3" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128398758</v>
+        <v>128398742</v>
       </c>
       <c r="B4" t="n">
-        <v>82948</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426187</v>
+        <v>426374</v>
       </c>
       <c r="R4" t="n">
-        <v>7051025</v>
+        <v>7050919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1024,7 @@
         <v>128398722</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1131,7 @@
         <v>128398798</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128398742</v>
+        <v>128398758</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>82975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,39 +1246,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426374</v>
+        <v>426187</v>
       </c>
       <c r="R7" t="n">
-        <v>7050919</v>
+        <v>7051025</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,12 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1345,7 @@
         <v>128398768</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128398746</v>
+        <v>128398774</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,34 +1470,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426300</v>
+        <v>425970</v>
       </c>
       <c r="R9" t="n">
-        <v>7050902</v>
+        <v>7051235</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1544,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,7 +1579,7 @@
         <v>128398775</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128398774</v>
+        <v>128398746</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,39 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>425970</v>
+        <v>426300</v>
       </c>
       <c r="R11" t="n">
-        <v>7051235</v>
+        <v>7050902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,12 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128398762</v>
+        <v>128398790</v>
       </c>
       <c r="B12" t="n">
-        <v>91485</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,34 +1811,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426225</v>
+        <v>425825</v>
       </c>
       <c r="R12" t="n">
-        <v>7051098</v>
+        <v>7051257</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398790</v>
+        <v>128398762</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>91512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,39 +1928,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425825</v>
+        <v>426225</v>
       </c>
       <c r="R13" t="n">
-        <v>7051257</v>
+        <v>7051098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,12 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,7 +2027,7 @@
         <v>128398811</v>
       </c>
       <c r="B14" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>128398740</v>
       </c>
       <c r="B15" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>128398824</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>128398776</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>128398737</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2569,32 +2569,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128398770</v>
+        <v>128398803</v>
       </c>
       <c r="B19" t="n">
-        <v>91921</v>
+        <v>92191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426115</v>
+        <v>425994</v>
       </c>
       <c r="R19" t="n">
-        <v>7051178</v>
+        <v>7051287</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2676,32 +2676,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398803</v>
+        <v>128398770</v>
       </c>
       <c r="B20" t="n">
-        <v>92164</v>
+        <v>91948</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425994</v>
+        <v>426115</v>
       </c>
       <c r="R20" t="n">
-        <v>7051287</v>
+        <v>7051178</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398730</v>
+        <v>128398821</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426382</v>
+        <v>426200</v>
       </c>
       <c r="R21" t="n">
-        <v>7051149</v>
+        <v>7051338</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398821</v>
+        <v>128398729</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426200</v>
+        <v>426468</v>
       </c>
       <c r="R22" t="n">
-        <v>7051338</v>
+        <v>7051179</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,7 +3000,7 @@
         <v>128398752</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398729</v>
+        <v>128398771</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>91512</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426468</v>
+        <v>426068</v>
       </c>
       <c r="R24" t="n">
-        <v>7051179</v>
+        <v>7051189</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3214,7 +3214,7 @@
         <v>128398718</v>
       </c>
       <c r="B25" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>128398773</v>
       </c>
       <c r="B26" t="n">
-        <v>75175</v>
+        <v>75202</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>128398753</v>
       </c>
       <c r="B27" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398771</v>
+        <v>128398730</v>
       </c>
       <c r="B28" t="n">
-        <v>91485</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3558,21 +3558,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426068</v>
+        <v>426382</v>
       </c>
       <c r="R28" t="n">
-        <v>7051189</v>
+        <v>7051149</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3657,7 +3657,7 @@
         <v>128398805</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3770,32 +3770,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128398788</v>
+        <v>128398724</v>
       </c>
       <c r="B30" t="n">
-        <v>75168</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>425804</v>
+        <v>426447</v>
       </c>
       <c r="R30" t="n">
-        <v>7051255</v>
+        <v>7051254</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3861,11 +3861,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Glasbjörk</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3882,10 +3877,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398791</v>
+        <v>128398819</v>
       </c>
       <c r="B31" t="n">
-        <v>75169</v>
+        <v>91494</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,21 +3888,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3917,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>425847</v>
+        <v>426181</v>
       </c>
       <c r="R31" t="n">
-        <v>7051261</v>
+        <v>7051325</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3952,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3962,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,21 +3968,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4004,32 +3984,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398819</v>
+        <v>128398788</v>
       </c>
       <c r="B32" t="n">
-        <v>91467</v>
+        <v>75195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4039,10 +4019,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426181</v>
+        <v>425804</v>
       </c>
       <c r="R32" t="n">
-        <v>7051325</v>
+        <v>7051255</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4074,7 +4054,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4084,7 +4064,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4095,6 +4075,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Glasbjörk</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4111,10 +4096,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398724</v>
+        <v>128398791</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>75196</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4122,21 +4107,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4146,10 +4131,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426447</v>
+        <v>425847</v>
       </c>
       <c r="R33" t="n">
-        <v>7051254</v>
+        <v>7051261</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4181,7 +4166,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4191,7 +4176,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4202,6 +4187,21 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4218,32 +4218,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398801</v>
+        <v>128398755</v>
       </c>
       <c r="B34" t="n">
-        <v>91921</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>425985</v>
+        <v>426166</v>
       </c>
       <c r="R34" t="n">
-        <v>7051282</v>
+        <v>7050989</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,10 +4325,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128398741</v>
+        <v>128398738</v>
       </c>
       <c r="B35" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,39 +4336,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426298</v>
+        <v>426341</v>
       </c>
       <c r="R35" t="n">
-        <v>7051029</v>
+        <v>7051103</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4400,7 +4395,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4410,12 +4405,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4442,10 +4432,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128398755</v>
+        <v>128398794</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4477,10 +4467,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426166</v>
+        <v>425876</v>
       </c>
       <c r="R36" t="n">
-        <v>7050989</v>
+        <v>7051324</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4512,7 +4502,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4522,7 +4512,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4549,32 +4539,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398738</v>
+        <v>128398801</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>91948</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4584,10 +4574,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>426341</v>
+        <v>425985</v>
       </c>
       <c r="R37" t="n">
-        <v>7051103</v>
+        <v>7051282</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4619,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4629,7 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4656,10 +4646,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128398794</v>
+        <v>128398741</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,34 +4657,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>425876</v>
+        <v>426298</v>
       </c>
       <c r="R38" t="n">
-        <v>7051324</v>
+        <v>7051029</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4726,7 +4721,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4736,7 +4731,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4763,10 +4763,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128398808</v>
+        <v>128398795</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>91512</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4774,21 +4774,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426012</v>
+        <v>425894</v>
       </c>
       <c r="R39" t="n">
-        <v>7051229</v>
+        <v>7051343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4870,10 +4870,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128398795</v>
+        <v>128398808</v>
       </c>
       <c r="B40" t="n">
-        <v>91485</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,21 +4881,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>425894</v>
+        <v>426012</v>
       </c>
       <c r="R40" t="n">
-        <v>7051343</v>
+        <v>7051229</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4980,7 +4980,7 @@
         <v>128398785</v>
       </c>
       <c r="B41" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,32 +5084,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128398736</v>
+        <v>128398787</v>
       </c>
       <c r="B42" t="n">
-        <v>92164</v>
+        <v>75196</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426352</v>
+        <v>425795</v>
       </c>
       <c r="R42" t="n">
-        <v>7051151</v>
+        <v>7051251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398787</v>
+        <v>128398749</v>
       </c>
       <c r="B43" t="n">
-        <v>75169</v>
+        <v>86805</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>427</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>425795</v>
+        <v>426252</v>
       </c>
       <c r="R43" t="n">
-        <v>7051251</v>
+        <v>7050919</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,7 +5271,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5298,32 +5303,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128398749</v>
+        <v>128398736</v>
       </c>
       <c r="B44" t="n">
-        <v>86778</v>
+        <v>92191</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>427</v>
+        <v>3298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5333,10 +5338,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426252</v>
+        <v>426352</v>
       </c>
       <c r="R44" t="n">
-        <v>7050919</v>
+        <v>7051151</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5368,7 +5373,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5378,12 +5383,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5413,7 +5413,7 @@
         <v>128398800</v>
       </c>
       <c r="B45" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5517,45 +5517,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128398731</v>
+        <v>128398807</v>
       </c>
       <c r="B46" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426369</v>
+        <v>426011</v>
       </c>
       <c r="R46" t="n">
-        <v>7051152</v>
+        <v>7051282</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5587,7 +5592,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5597,7 +5602,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,10 +5634,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398807</v>
+        <v>128398721</v>
       </c>
       <c r="B47" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5664,10 +5674,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426011</v>
+        <v>426773</v>
       </c>
       <c r="R47" t="n">
-        <v>7051282</v>
+        <v>7051349</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5699,7 +5709,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5709,7 +5719,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5744,7 +5754,7 @@
         <v>128398797</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5848,10 +5858,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128398725</v>
+        <v>128398812</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5883,10 +5893,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426492</v>
+        <v>426097</v>
       </c>
       <c r="R49" t="n">
-        <v>7051269</v>
+        <v>7051199</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5918,7 +5928,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5928,7 +5938,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5955,10 +5965,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128398812</v>
+        <v>128398725</v>
       </c>
       <c r="B50" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5990,10 +6000,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426097</v>
+        <v>426492</v>
       </c>
       <c r="R50" t="n">
-        <v>7051199</v>
+        <v>7051269</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6025,7 +6035,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6035,7 +6045,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6062,50 +6072,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128398721</v>
+        <v>128398731</v>
       </c>
       <c r="B51" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426773</v>
+        <v>426369</v>
       </c>
       <c r="R51" t="n">
-        <v>7051349</v>
+        <v>7051152</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6137,7 +6142,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6147,12 +6152,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,45 +6179,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398802</v>
+        <v>128398804</v>
       </c>
       <c r="B52" t="n">
-        <v>91763</v>
+        <v>75202</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>425985</v>
+        <v>426000</v>
       </c>
       <c r="R52" t="n">
-        <v>7051282</v>
+        <v>7051290</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6249,7 +6252,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6259,7 +6262,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6267,6 +6270,11 @@
       </c>
       <c r="AE52" t="b">
         <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -6286,10 +6294,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128398727</v>
+        <v>128398793</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6297,34 +6305,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>426516</v>
+        <v>425908</v>
       </c>
       <c r="R53" t="n">
-        <v>7051239</v>
+        <v>7051281</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6356,7 +6369,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6366,7 +6379,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6393,50 +6411,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398793</v>
+        <v>128398734</v>
       </c>
       <c r="B54" t="n">
-        <v>57689</v>
+        <v>92191</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>425908</v>
+        <v>426329</v>
       </c>
       <c r="R54" t="n">
-        <v>7051281</v>
+        <v>7051146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6468,7 +6481,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6478,12 +6491,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6510,10 +6518,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398814</v>
+        <v>128398743</v>
       </c>
       <c r="B55" t="n">
-        <v>57689</v>
+        <v>91490</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6521,39 +6529,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426097</v>
+        <v>426371</v>
       </c>
       <c r="R55" t="n">
-        <v>7051199</v>
+        <v>7050917</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6585,7 +6588,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6595,12 +6598,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:22</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6627,10 +6625,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398719</v>
+        <v>128398802</v>
       </c>
       <c r="B56" t="n">
-        <v>57689</v>
+        <v>91790</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6638,39 +6636,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426799</v>
+        <v>425985</v>
       </c>
       <c r="R56" t="n">
-        <v>7051328</v>
+        <v>7051282</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6702,7 +6695,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6712,12 +6705,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6744,10 +6732,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398822</v>
+        <v>128398814</v>
       </c>
       <c r="B57" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6784,10 +6772,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426200</v>
+        <v>426097</v>
       </c>
       <c r="R57" t="n">
-        <v>7051338</v>
+        <v>7051199</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6819,7 +6807,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6829,7 +6817,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6861,10 +6849,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398743</v>
+        <v>128398822</v>
       </c>
       <c r="B58" t="n">
-        <v>91463</v>
+        <v>57716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6872,34 +6860,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426371</v>
+        <v>426200</v>
       </c>
       <c r="R58" t="n">
-        <v>7050917</v>
+        <v>7051338</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6931,7 +6924,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6941,7 +6934,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6968,45 +6966,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398734</v>
+        <v>128398719</v>
       </c>
       <c r="B59" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426329</v>
+        <v>426799</v>
       </c>
       <c r="R59" t="n">
-        <v>7051146</v>
+        <v>7051328</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7038,7 +7041,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7048,7 +7051,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7075,48 +7083,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398804</v>
+        <v>128398727</v>
       </c>
       <c r="B60" t="n">
-        <v>75175</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426000</v>
+        <v>426516</v>
       </c>
       <c r="R60" t="n">
-        <v>7051290</v>
+        <v>7051239</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7148,7 +7153,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7158,7 +7163,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7166,11 +7171,6 @@
       </c>
       <c r="AE60" t="b">
         <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398726</v>
+        <v>128398769</v>
       </c>
       <c r="B61" t="n">
-        <v>75168</v>
+        <v>91494</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426522</v>
+        <v>426135</v>
       </c>
       <c r="R61" t="n">
-        <v>7051242</v>
+        <v>7051154</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,21 +7281,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7312,10 +7297,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398769</v>
+        <v>128398781</v>
       </c>
       <c r="B62" t="n">
-        <v>91467</v>
+        <v>57716</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7323,34 +7308,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>426135</v>
+        <v>425754</v>
       </c>
       <c r="R62" t="n">
-        <v>7051154</v>
+        <v>7051180</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7382,7 +7372,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7392,7 +7382,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7422,7 +7417,7 @@
         <v>128398783</v>
       </c>
       <c r="B63" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7529,7 +7524,7 @@
         <v>128398745</v>
       </c>
       <c r="B64" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7643,50 +7638,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128398781</v>
+        <v>128398726</v>
       </c>
       <c r="B65" t="n">
-        <v>57689</v>
+        <v>75195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>425754</v>
+        <v>426522</v>
       </c>
       <c r="R65" t="n">
-        <v>7051180</v>
+        <v>7051242</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7718,7 +7708,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7728,12 +7718,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7744,6 +7729,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7760,10 +7760,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128398763</v>
+        <v>128398796</v>
       </c>
       <c r="B66" t="n">
-        <v>79089</v>
+        <v>78093</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7771,21 +7771,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>426227</v>
+        <v>425919</v>
       </c>
       <c r="R66" t="n">
-        <v>7051105</v>
+        <v>7051350</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7867,10 +7867,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128398796</v>
+        <v>128398763</v>
       </c>
       <c r="B67" t="n">
-        <v>78066</v>
+        <v>79116</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7878,21 +7878,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>425919</v>
+        <v>426227</v>
       </c>
       <c r="R67" t="n">
-        <v>7051350</v>
+        <v>7051105</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7974,32 +7974,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128398760</v>
+        <v>128398733</v>
       </c>
       <c r="B68" t="n">
-        <v>82948</v>
+        <v>92191</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8009,10 +8009,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>426232</v>
+        <v>426361</v>
       </c>
       <c r="R68" t="n">
-        <v>7051062</v>
+        <v>7051151</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8081,32 +8081,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128398733</v>
+        <v>128398760</v>
       </c>
       <c r="B69" t="n">
-        <v>92164</v>
+        <v>82975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426361</v>
+        <v>426232</v>
       </c>
       <c r="R69" t="n">
-        <v>7051151</v>
+        <v>7051062</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8191,7 +8191,7 @@
         <v>128398820</v>
       </c>
       <c r="B70" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>128398777</v>
       </c>
       <c r="B71" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>128398818</v>
       </c>
       <c r="B72" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8509,10 +8509,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128398720</v>
+        <v>128398779</v>
       </c>
       <c r="B73" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8520,34 +8520,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426773</v>
+        <v>425818</v>
       </c>
       <c r="R73" t="n">
-        <v>7051341</v>
+        <v>7051169</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8579,7 +8584,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8589,7 +8594,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8616,10 +8626,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128398779</v>
+        <v>128398720</v>
       </c>
       <c r="B74" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8627,39 +8637,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>425818</v>
+        <v>426773</v>
       </c>
       <c r="R74" t="n">
-        <v>7051169</v>
+        <v>7051341</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8691,7 +8696,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8701,12 +8706,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8733,45 +8733,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128398772</v>
+        <v>128398789</v>
       </c>
       <c r="B75" t="n">
-        <v>92164</v>
+        <v>57716</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426065</v>
+        <v>425804</v>
       </c>
       <c r="R75" t="n">
-        <v>7051192</v>
+        <v>7051258</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8803,7 +8808,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8813,7 +8818,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8840,32 +8850,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128398754</v>
+        <v>128398772</v>
       </c>
       <c r="B76" t="n">
-        <v>80195</v>
+        <v>92191</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8875,10 +8885,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426191</v>
+        <v>426065</v>
       </c>
       <c r="R76" t="n">
-        <v>7050957</v>
+        <v>7051192</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8910,7 +8920,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8920,7 +8930,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8931,21 +8941,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8962,10 +8957,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128398789</v>
+        <v>128398754</v>
       </c>
       <c r="B77" t="n">
-        <v>57689</v>
+        <v>80222</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8973,39 +8968,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>425804</v>
+        <v>426191</v>
       </c>
       <c r="R77" t="n">
-        <v>7051258</v>
+        <v>7050957</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9037,7 +9027,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9047,12 +9037,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9063,6 +9048,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9082,7 +9082,7 @@
         <v>128398815</v>
       </c>
       <c r="B78" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>128398813</v>
       </c>
       <c r="B79" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128398765</v>
+        <v>128398723</v>
       </c>
       <c r="B80" t="n">
-        <v>82948</v>
+        <v>79116</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9299,21 +9299,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9323,10 +9323,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426186</v>
+        <v>426515</v>
       </c>
       <c r="R80" t="n">
-        <v>7051125</v>
+        <v>7051308</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9395,10 +9395,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128398723</v>
+        <v>128398751</v>
       </c>
       <c r="B81" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>426515</v>
+        <v>426239</v>
       </c>
       <c r="R81" t="n">
-        <v>7051308</v>
+        <v>7050935</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9502,10 +9502,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128398751</v>
+        <v>128398765</v>
       </c>
       <c r="B82" t="n">
-        <v>79089</v>
+        <v>82975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9513,21 +9513,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9537,10 +9537,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>426239</v>
+        <v>426186</v>
       </c>
       <c r="R82" t="n">
-        <v>7050935</v>
+        <v>7051125</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9609,10 +9609,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128398784</v>
+        <v>128398780</v>
       </c>
       <c r="B83" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
       <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425712</v>
+        <v>425756</v>
       </c>
       <c r="R83" t="n">
-        <v>7051206</v>
+        <v>7051171</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9726,10 +9726,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128398780</v>
+        <v>128398784</v>
       </c>
       <c r="B84" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>425756</v>
+        <v>425712</v>
       </c>
       <c r="R84" t="n">
-        <v>7051171</v>
+        <v>7051206</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -9843,10 +9843,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128398761</v>
+        <v>128398728</v>
       </c>
       <c r="B85" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9854,34 +9854,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>426231</v>
+        <v>426475</v>
       </c>
       <c r="R85" t="n">
-        <v>7051061</v>
+        <v>7051191</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9913,7 +9918,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9923,7 +9928,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9950,10 +9960,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128398728</v>
+        <v>128398761</v>
       </c>
       <c r="B86" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9961,39 +9971,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>426475</v>
+        <v>426231</v>
       </c>
       <c r="R86" t="n">
-        <v>7051191</v>
+        <v>7051061</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10025,7 +10030,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10035,12 +10040,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399949</v>
+        <v>128399849</v>
       </c>
       <c r="B93" t="n">
-        <v>88894</v>
+        <v>57716</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426768</v>
+        <v>426803</v>
       </c>
       <c r="R93" t="n">
-        <v>7051367</v>
+        <v>7051353</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10750,6 +10750,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10776,10 +10781,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399940</v>
+        <v>128399949</v>
       </c>
       <c r="B94" t="n">
-        <v>91512</v>
+        <v>88894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10787,21 +10792,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10811,10 +10816,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426338</v>
+        <v>426768</v>
       </c>
       <c r="R94" t="n">
-        <v>7050977</v>
+        <v>7051367</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10873,10 +10878,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399849</v>
+        <v>128399940</v>
       </c>
       <c r="B95" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10884,21 +10889,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10908,10 +10913,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426803</v>
+        <v>426338</v>
       </c>
       <c r="R95" t="n">
-        <v>7051353</v>
+        <v>7050977</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10944,11 +10949,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10975,7 +10975,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399886</v>
+        <v>128399898</v>
       </c>
       <c r="B96" t="n">
         <v>57716</v>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425743</v>
+        <v>425894</v>
       </c>
       <c r="R96" t="n">
-        <v>7051241</v>
+        <v>7051256</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11077,32 +11077,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399832</v>
+        <v>128399886</v>
       </c>
       <c r="B97" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11112,10 +11112,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>426401</v>
+        <v>425743</v>
       </c>
       <c r="R97" t="n">
-        <v>7051237</v>
+        <v>7051241</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11148,6 +11148,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11174,7 +11179,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399836</v>
+        <v>128399832</v>
       </c>
       <c r="B98" t="n">
         <v>92191</v>
@@ -11209,10 +11214,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426093</v>
+        <v>426401</v>
       </c>
       <c r="R98" t="n">
-        <v>7051184</v>
+        <v>7051237</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11271,32 +11276,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399898</v>
+        <v>128399836</v>
       </c>
       <c r="B99" t="n">
-        <v>57716</v>
+        <v>92191</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11306,10 +11311,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>425894</v>
+        <v>426093</v>
       </c>
       <c r="R99" t="n">
-        <v>7051256</v>
+        <v>7051184</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11342,11 +11347,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128399907</v>
+        <v>128399922</v>
       </c>
       <c r="B100" t="n">
-        <v>57716</v>
+        <v>91490</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11384,21 +11384,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426064</v>
+        <v>426343</v>
       </c>
       <c r="R100" t="n">
-        <v>7051249</v>
+        <v>7050915</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11444,11 +11444,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11475,10 +11470,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128399889</v>
+        <v>128399936</v>
       </c>
       <c r="B101" t="n">
-        <v>57716</v>
+        <v>91508</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11486,21 +11481,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11510,10 +11505,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>425774</v>
+        <v>425967</v>
       </c>
       <c r="R101" t="n">
-        <v>7051222</v>
+        <v>7051278</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11546,11 +11541,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11577,10 +11567,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128399941</v>
+        <v>128399829</v>
       </c>
       <c r="B102" t="n">
-        <v>91512</v>
+        <v>91494</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11588,21 +11578,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11612,10 +11602,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>425987</v>
+        <v>426191</v>
       </c>
       <c r="R102" t="n">
-        <v>7051259</v>
+        <v>7050972</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11674,10 +11664,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128399922</v>
+        <v>128399941</v>
       </c>
       <c r="B103" t="n">
-        <v>91490</v>
+        <v>91512</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11685,21 +11675,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11709,10 +11699,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426343</v>
+        <v>425987</v>
       </c>
       <c r="R103" t="n">
-        <v>7050915</v>
+        <v>7051259</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11771,10 +11761,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128399936</v>
+        <v>128399907</v>
       </c>
       <c r="B104" t="n">
-        <v>91508</v>
+        <v>57716</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11782,21 +11772,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11806,10 +11796,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>425967</v>
+        <v>426064</v>
       </c>
       <c r="R104" t="n">
-        <v>7051278</v>
+        <v>7051249</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11842,6 +11832,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11868,10 +11863,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128399829</v>
+        <v>128399889</v>
       </c>
       <c r="B105" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11879,21 +11874,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11903,10 +11898,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>426191</v>
+        <v>425774</v>
       </c>
       <c r="R105" t="n">
-        <v>7050972</v>
+        <v>7051222</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11939,6 +11934,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11965,7 +11965,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399903</v>
+        <v>128399863</v>
       </c>
       <c r="B106" t="n">
         <v>57716</v>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>425972</v>
+        <v>426347</v>
       </c>
       <c r="R106" t="n">
-        <v>7051285</v>
+        <v>7050960</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12067,7 +12067,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399863</v>
+        <v>128399868</v>
       </c>
       <c r="B107" t="n">
         <v>57716</v>
@@ -12102,10 +12102,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426347</v>
+        <v>426274</v>
       </c>
       <c r="R107" t="n">
-        <v>7050960</v>
+        <v>7050964</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12142,7 +12142,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12169,7 +12169,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399868</v>
+        <v>128399881</v>
       </c>
       <c r="B108" t="n">
         <v>57716</v>
@@ -12204,10 +12204,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>426274</v>
+        <v>425942</v>
       </c>
       <c r="R108" t="n">
-        <v>7050964</v>
+        <v>7051274</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12271,32 +12271,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399881</v>
+        <v>128399834</v>
       </c>
       <c r="B109" t="n">
-        <v>57716</v>
+        <v>92191</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>425942</v>
+        <v>426228</v>
       </c>
       <c r="R109" t="n">
-        <v>7051274</v>
+        <v>7050978</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12342,11 +12342,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12373,32 +12368,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399834</v>
+        <v>128399903</v>
       </c>
       <c r="B110" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12408,10 +12403,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>426228</v>
+        <v>425972</v>
       </c>
       <c r="R110" t="n">
-        <v>7050978</v>
+        <v>7051285</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12444,6 +12439,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13159,10 +13159,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128399872</v>
+        <v>128399928</v>
       </c>
       <c r="B118" t="n">
-        <v>57716</v>
+        <v>91508</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13170,21 +13170,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13194,10 +13194,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426187</v>
+        <v>426319</v>
       </c>
       <c r="R118" t="n">
-        <v>7050975</v>
+        <v>7051238</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13230,11 +13230,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13261,7 +13256,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399853</v>
+        <v>128399872</v>
       </c>
       <c r="B119" t="n">
         <v>57716</v>
@@ -13290,24 +13285,16 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426736</v>
+        <v>426187</v>
       </c>
       <c r="R119" t="n">
-        <v>7051344</v>
+        <v>7050975</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13344,7 +13331,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13371,7 +13358,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399914</v>
+        <v>128399853</v>
       </c>
       <c r="B120" t="n">
         <v>57716</v>
@@ -13400,16 +13387,24 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426219</v>
+        <v>426736</v>
       </c>
       <c r="R120" t="n">
-        <v>7051364</v>
+        <v>7051344</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13446,7 +13441,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13473,7 +13468,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399852</v>
+        <v>128399914</v>
       </c>
       <c r="B121" t="n">
         <v>57716</v>
@@ -13508,10 +13503,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426765</v>
+        <v>426219</v>
       </c>
       <c r="R121" t="n">
-        <v>7051373</v>
+        <v>7051364</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13575,7 +13570,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399897</v>
+        <v>128399852</v>
       </c>
       <c r="B122" t="n">
         <v>57716</v>
@@ -13610,10 +13605,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>425892</v>
+        <v>426765</v>
       </c>
       <c r="R122" t="n">
-        <v>7051251</v>
+        <v>7051373</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13650,7 +13645,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13677,7 +13672,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399902</v>
+        <v>128399897</v>
       </c>
       <c r="B123" t="n">
         <v>57716</v>
@@ -13712,10 +13707,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425902</v>
+        <v>425892</v>
       </c>
       <c r="R123" t="n">
-        <v>7051312</v>
+        <v>7051251</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13779,7 +13774,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128399871</v>
+        <v>128399902</v>
       </c>
       <c r="B124" t="n">
         <v>57716</v>
@@ -13814,10 +13809,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>426154</v>
+        <v>425902</v>
       </c>
       <c r="R124" t="n">
-        <v>7050994</v>
+        <v>7051312</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13881,10 +13876,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128399928</v>
+        <v>128399871</v>
       </c>
       <c r="B125" t="n">
-        <v>91508</v>
+        <v>57716</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13892,21 +13887,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13916,10 +13911,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>426319</v>
+        <v>426154</v>
       </c>
       <c r="R125" t="n">
-        <v>7051238</v>
+        <v>7050994</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13952,6 +13947,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -16182,10 +16182,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128399883</v>
+        <v>128399828</v>
       </c>
       <c r="B148" t="n">
-        <v>57716</v>
+        <v>91494</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16193,21 +16193,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16217,10 +16217,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>425851</v>
+        <v>426225</v>
       </c>
       <c r="R148" t="n">
-        <v>7051202</v>
+        <v>7050963</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16253,11 +16253,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16284,10 +16279,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128399828</v>
+        <v>128399937</v>
       </c>
       <c r="B149" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16295,21 +16290,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16319,10 +16314,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>426225</v>
+        <v>426734</v>
       </c>
       <c r="R149" t="n">
-        <v>7050963</v>
+        <v>7051350</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16381,10 +16376,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128399892</v>
+        <v>128399946</v>
       </c>
       <c r="B150" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16392,21 +16387,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16416,10 +16411,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>425853</v>
+        <v>426083</v>
       </c>
       <c r="R150" t="n">
-        <v>7051216</v>
+        <v>7051231</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16452,11 +16447,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16483,7 +16473,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128399861</v>
+        <v>128399892</v>
       </c>
       <c r="B151" t="n">
         <v>57716</v>
@@ -16518,10 +16508,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>426285</v>
+        <v>425853</v>
       </c>
       <c r="R151" t="n">
-        <v>7051199</v>
+        <v>7051216</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16585,7 +16575,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128399855</v>
+        <v>128399883</v>
       </c>
       <c r="B152" t="n">
         <v>57716</v>
@@ -16620,10 +16610,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>426639</v>
+        <v>425851</v>
       </c>
       <c r="R152" t="n">
-        <v>7051351</v>
+        <v>7051202</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16687,10 +16677,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128399937</v>
+        <v>128399861</v>
       </c>
       <c r="B153" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16698,21 +16688,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16722,10 +16712,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>426734</v>
+        <v>426285</v>
       </c>
       <c r="R153" t="n">
-        <v>7051350</v>
+        <v>7051199</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16758,6 +16748,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16784,10 +16779,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128399946</v>
+        <v>128399855</v>
       </c>
       <c r="B154" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16795,21 +16790,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16819,10 +16814,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>426083</v>
+        <v>426639</v>
       </c>
       <c r="R154" t="n">
-        <v>7051231</v>
+        <v>7051351</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16855,6 +16850,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17585,32 +17585,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128399874</v>
+        <v>128399837</v>
       </c>
       <c r="B162" t="n">
-        <v>57716</v>
+        <v>92191</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>426194</v>
+        <v>425757</v>
       </c>
       <c r="R162" t="n">
-        <v>7050979</v>
+        <v>7051207</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17656,11 +17656,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17687,32 +17682,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128399864</v>
+        <v>128399840</v>
       </c>
       <c r="B163" t="n">
-        <v>57716</v>
+        <v>92191</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17722,10 +17717,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>426357</v>
+        <v>426131</v>
       </c>
       <c r="R163" t="n">
-        <v>7050965</v>
+        <v>7051242</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17758,11 +17753,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17789,32 +17779,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128399837</v>
+        <v>128399926</v>
       </c>
       <c r="B164" t="n">
-        <v>92191</v>
+        <v>91490</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17824,10 +17814,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>425757</v>
+        <v>426189</v>
       </c>
       <c r="R164" t="n">
-        <v>7051207</v>
+        <v>7051364</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17886,32 +17876,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128399840</v>
+        <v>128399874</v>
       </c>
       <c r="B165" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17921,10 +17911,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>426131</v>
+        <v>426194</v>
       </c>
       <c r="R165" t="n">
-        <v>7051242</v>
+        <v>7050979</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17957,6 +17947,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17983,10 +17978,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128399926</v>
+        <v>128399864</v>
       </c>
       <c r="B166" t="n">
-        <v>91490</v>
+        <v>57716</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17994,21 +17989,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18018,10 +18013,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>426189</v>
+        <v>426357</v>
       </c>
       <c r="R166" t="n">
-        <v>7051364</v>
+        <v>7050965</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18054,6 +18049,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18478,10 +18478,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128399854</v>
+        <v>128399938</v>
       </c>
       <c r="B171" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18489,42 +18489,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>426733</v>
+        <v>426205</v>
       </c>
       <c r="R171" t="n">
-        <v>7051347</v>
+        <v>7051276</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18557,11 +18549,6 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18996,45 +18983,53 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128399835</v>
+        <v>128399854</v>
       </c>
       <c r="B176" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>426132</v>
+        <v>426733</v>
       </c>
       <c r="R176" t="n">
-        <v>7051150</v>
+        <v>7051347</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19067,6 +19062,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19093,32 +19093,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128399938</v>
+        <v>128399835</v>
       </c>
       <c r="B177" t="n">
-        <v>91512</v>
+        <v>92191</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19128,10 +19128,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>426205</v>
+        <v>426132</v>
       </c>
       <c r="R177" t="n">
-        <v>7051276</v>
+        <v>7051150</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20282,10 +20282,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128399925</v>
+        <v>128399873</v>
       </c>
       <c r="B189" t="n">
-        <v>91490</v>
+        <v>57716</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20293,21 +20293,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20317,10 +20317,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>426047</v>
+        <v>426193</v>
       </c>
       <c r="R189" t="n">
-        <v>7051252</v>
+        <v>7050977</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20353,6 +20353,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20379,10 +20384,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128399939</v>
+        <v>128399862</v>
       </c>
       <c r="B190" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20390,21 +20395,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20414,10 +20419,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>426300</v>
+        <v>426292</v>
       </c>
       <c r="R190" t="n">
-        <v>7051058</v>
+        <v>7050995</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20450,6 +20455,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20476,10 +20486,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128399873</v>
+        <v>128399925</v>
       </c>
       <c r="B191" t="n">
-        <v>57716</v>
+        <v>91490</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20487,21 +20497,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20511,10 +20521,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>426193</v>
+        <v>426047</v>
       </c>
       <c r="R191" t="n">
-        <v>7050977</v>
+        <v>7051252</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20547,11 +20557,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20578,10 +20583,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128399862</v>
+        <v>128399939</v>
       </c>
       <c r="B192" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20589,21 +20594,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20613,10 +20618,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>426292</v>
+        <v>426300</v>
       </c>
       <c r="R192" t="n">
-        <v>7050995</v>
+        <v>7051058</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20649,11 +20654,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 40068-2025 artfynd.xlsx
+++ b/artfynd/A 40068-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128398786</v>
+        <v>128398758</v>
       </c>
       <c r="B2" t="n">
-        <v>75196</v>
+        <v>82975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425776</v>
+        <v>426187</v>
       </c>
       <c r="R2" t="n">
-        <v>7051259</v>
+        <v>7051025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Högstubbe # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128398759</v>
+        <v>128398742</v>
       </c>
       <c r="B3" t="n">
-        <v>88894</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426187</v>
+        <v>426374</v>
       </c>
       <c r="R3" t="n">
-        <v>7051025</v>
+        <v>7050919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128398742</v>
+        <v>128398786</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>75196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426374</v>
+        <v>425776</v>
       </c>
       <c r="R4" t="n">
-        <v>7050919</v>
+        <v>7051259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +990,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Högstubbe # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128398722</v>
+        <v>128398759</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>88894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426695</v>
+        <v>426187</v>
       </c>
       <c r="R5" t="n">
-        <v>7051338</v>
+        <v>7051025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128398798</v>
+        <v>128398722</v>
       </c>
       <c r="B6" t="n">
         <v>79116</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425947</v>
+        <v>426695</v>
       </c>
       <c r="R6" t="n">
-        <v>7051321</v>
+        <v>7051338</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128398758</v>
+        <v>128398798</v>
       </c>
       <c r="B7" t="n">
-        <v>82975</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426187</v>
+        <v>425947</v>
       </c>
       <c r="R7" t="n">
-        <v>7051025</v>
+        <v>7051321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128398768</v>
+        <v>128398746</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,39 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426158</v>
+        <v>426300</v>
       </c>
       <c r="R8" t="n">
-        <v>7051146</v>
+        <v>7050902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1449,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128398774</v>
+        <v>128398768</v>
       </c>
       <c r="B9" t="n">
         <v>57716</v>
@@ -1490,7 +1480,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1499,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>425970</v>
+        <v>426158</v>
       </c>
       <c r="R9" t="n">
-        <v>7051235</v>
+        <v>7051146</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1576,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128398775</v>
+        <v>128398774</v>
       </c>
       <c r="B10" t="n">
         <v>57716</v>
@@ -1616,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>425892</v>
+        <v>425970</v>
       </c>
       <c r="R10" t="n">
-        <v>7051220</v>
+        <v>7051235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1693,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128398746</v>
+        <v>128398775</v>
       </c>
       <c r="B11" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,34 +1694,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426300</v>
+        <v>425892</v>
       </c>
       <c r="R11" t="n">
-        <v>7050902</v>
+        <v>7051220</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1768,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128398790</v>
+        <v>128398762</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>91512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,39 +1811,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>425825</v>
+        <v>426225</v>
       </c>
       <c r="R12" t="n">
-        <v>7051257</v>
+        <v>7051098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,12 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128398762</v>
+        <v>128398790</v>
       </c>
       <c r="B13" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,34 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426225</v>
+        <v>425825</v>
       </c>
       <c r="R13" t="n">
-        <v>7051098</v>
+        <v>7051257</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1992,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128398811</v>
+        <v>128398740</v>
       </c>
       <c r="B14" t="n">
-        <v>91490</v>
+        <v>91512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426091</v>
+        <v>426327</v>
       </c>
       <c r="R14" t="n">
-        <v>7051202</v>
+        <v>7051074</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128398740</v>
+        <v>128398811</v>
       </c>
       <c r="B15" t="n">
-        <v>91512</v>
+        <v>91490</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426327</v>
+        <v>426091</v>
       </c>
       <c r="R15" t="n">
-        <v>7051074</v>
+        <v>7051202</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2676,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128398770</v>
+        <v>128398773</v>
       </c>
       <c r="B20" t="n">
-        <v>91948</v>
+        <v>75202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6486</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426115</v>
+        <v>425978</v>
       </c>
       <c r="R20" t="n">
-        <v>7051178</v>
+        <v>7051231</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128398821</v>
+        <v>128398771</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>91512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,21 +2794,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426200</v>
+        <v>426068</v>
       </c>
       <c r="R21" t="n">
-        <v>7051338</v>
+        <v>7051189</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,32 +2890,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128398729</v>
+        <v>128398770</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>91948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426468</v>
+        <v>426115</v>
       </c>
       <c r="R22" t="n">
-        <v>7051179</v>
+        <v>7051178</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,32 +2997,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128398752</v>
+        <v>128398718</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>92796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3032,10 +3032,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426206</v>
+        <v>426807</v>
       </c>
       <c r="R23" t="n">
-        <v>7050935</v>
+        <v>7051311</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3104,10 +3104,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128398771</v>
+        <v>128398821</v>
       </c>
       <c r="B24" t="n">
-        <v>91512</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426068</v>
+        <v>426200</v>
       </c>
       <c r="R24" t="n">
-        <v>7051189</v>
+        <v>7051338</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3211,32 +3211,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128398718</v>
+        <v>128398753</v>
       </c>
       <c r="B25" t="n">
-        <v>92796</v>
+        <v>80221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426807</v>
+        <v>426191</v>
       </c>
       <c r="R25" t="n">
-        <v>7051311</v>
+        <v>7050957</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,6 +3302,21 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3318,32 +3333,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128398773</v>
+        <v>128398730</v>
       </c>
       <c r="B26" t="n">
-        <v>75202</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3353,10 +3368,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>425978</v>
+        <v>426382</v>
       </c>
       <c r="R26" t="n">
-        <v>7051231</v>
+        <v>7051149</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3388,7 +3403,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3398,7 +3413,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3425,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128398753</v>
+        <v>128398729</v>
       </c>
       <c r="B27" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3436,21 +3451,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3460,10 +3475,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426191</v>
+        <v>426468</v>
       </c>
       <c r="R27" t="n">
-        <v>7050957</v>
+        <v>7051179</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3495,7 +3510,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3505,7 +3520,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3516,21 +3531,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3547,7 +3547,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128398730</v>
+        <v>128398752</v>
       </c>
       <c r="B28" t="n">
         <v>79116</v>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426382</v>
+        <v>426206</v>
       </c>
       <c r="R28" t="n">
-        <v>7051149</v>
+        <v>7050935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128398724</v>
+        <v>128398819</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>91494</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>426447</v>
+        <v>426181</v>
       </c>
       <c r="R30" t="n">
-        <v>7051254</v>
+        <v>7051325</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3877,32 +3877,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128398819</v>
+        <v>128398788</v>
       </c>
       <c r="B31" t="n">
-        <v>91494</v>
+        <v>75195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>426181</v>
+        <v>425804</v>
       </c>
       <c r="R31" t="n">
-        <v>7051325</v>
+        <v>7051255</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3968,6 +3968,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Glasbjörk</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3984,32 +3989,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128398788</v>
+        <v>128398791</v>
       </c>
       <c r="B32" t="n">
-        <v>75195</v>
+        <v>75196</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>492</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4019,10 +4024,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>425804</v>
+        <v>425847</v>
       </c>
       <c r="R32" t="n">
-        <v>7051255</v>
+        <v>7051261</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4054,7 +4059,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4064,7 +4069,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4076,9 +4081,19 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Glasbjörk</t>
+          <t>Betula pubescens</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4096,10 +4111,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398791</v>
+        <v>128398724</v>
       </c>
       <c r="B33" t="n">
-        <v>75196</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4107,21 +4122,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4131,10 +4146,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>425847</v>
+        <v>426447</v>
       </c>
       <c r="R33" t="n">
-        <v>7051261</v>
+        <v>7051254</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4166,7 +4181,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4176,7 +4191,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,21 +4202,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4218,32 +4218,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128398755</v>
+        <v>128398801</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>91948</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426166</v>
+        <v>425985</v>
       </c>
       <c r="R34" t="n">
-        <v>7050989</v>
+        <v>7051282</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,10 +4325,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128398738</v>
+        <v>128398741</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,34 +4336,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426341</v>
+        <v>426298</v>
       </c>
       <c r="R35" t="n">
-        <v>7051103</v>
+        <v>7051029</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4395,7 +4400,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4405,7 +4410,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4432,7 +4442,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128398794</v>
+        <v>128398755</v>
       </c>
       <c r="B36" t="n">
         <v>79116</v>
@@ -4467,10 +4477,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>425876</v>
+        <v>426166</v>
       </c>
       <c r="R36" t="n">
-        <v>7051324</v>
+        <v>7050989</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4502,7 +4512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4512,7 +4522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4539,32 +4549,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128398801</v>
+        <v>128398738</v>
       </c>
       <c r="B37" t="n">
-        <v>91948</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4574,10 +4584,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>425985</v>
+        <v>426341</v>
       </c>
       <c r="R37" t="n">
-        <v>7051282</v>
+        <v>7051103</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4609,7 +4619,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4619,7 +4629,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4646,10 +4656,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128398741</v>
+        <v>128398794</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4657,39 +4667,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>426298</v>
+        <v>425876</v>
       </c>
       <c r="R38" t="n">
-        <v>7051029</v>
+        <v>7051324</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4721,7 +4726,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4731,12 +4736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4763,32 +4763,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128398795</v>
+        <v>128398785</v>
       </c>
       <c r="B39" t="n">
-        <v>91512</v>
+        <v>92191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>425894</v>
+        <v>425708</v>
       </c>
       <c r="R39" t="n">
-        <v>7051343</v>
+        <v>7051228</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4977,32 +4977,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128398785</v>
+        <v>128398795</v>
       </c>
       <c r="B41" t="n">
-        <v>92191</v>
+        <v>91512</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>425708</v>
+        <v>425894</v>
       </c>
       <c r="R41" t="n">
-        <v>7051228</v>
+        <v>7051343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,32 +5084,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128398787</v>
+        <v>128398736</v>
       </c>
       <c r="B42" t="n">
-        <v>75196</v>
+        <v>92191</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>425795</v>
+        <v>426352</v>
       </c>
       <c r="R42" t="n">
-        <v>7051251</v>
+        <v>7051151</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5191,10 +5191,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128398749</v>
+        <v>128398787</v>
       </c>
       <c r="B43" t="n">
-        <v>86805</v>
+        <v>75196</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,21 +5202,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>427</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426252</v>
+        <v>425795</v>
       </c>
       <c r="R43" t="n">
-        <v>7050919</v>
+        <v>7051251</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5271,12 +5271,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5303,32 +5298,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128398736</v>
+        <v>128398800</v>
       </c>
       <c r="B44" t="n">
-        <v>92191</v>
+        <v>91508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5338,10 +5333,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>426352</v>
+        <v>425985</v>
       </c>
       <c r="R44" t="n">
-        <v>7051151</v>
+        <v>7051282</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,7 +5368,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5383,7 +5378,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5410,10 +5405,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128398800</v>
+        <v>128398749</v>
       </c>
       <c r="B45" t="n">
-        <v>91508</v>
+        <v>86805</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,21 +5416,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>427</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5445,10 +5440,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>425985</v>
+        <v>426252</v>
       </c>
       <c r="R45" t="n">
-        <v>7051282</v>
+        <v>7050919</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5480,7 +5475,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5490,7 +5485,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>KOH+ rödaktig på hatt, fot och rosa/violett på basalmycel.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5517,50 +5517,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128398807</v>
+        <v>128398731</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>92191</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>426011</v>
+        <v>426369</v>
       </c>
       <c r="R46" t="n">
-        <v>7051282</v>
+        <v>7051152</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5592,7 +5587,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5602,12 +5597,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5634,10 +5624,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128398721</v>
+        <v>128398797</v>
       </c>
       <c r="B47" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5645,39 +5635,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426773</v>
+        <v>425919</v>
       </c>
       <c r="R47" t="n">
-        <v>7051349</v>
+        <v>7051350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5694,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5719,12 +5704,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,7 +5731,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128398797</v>
+        <v>128398812</v>
       </c>
       <c r="B48" t="n">
         <v>79116</v>
@@ -5786,10 +5766,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>425919</v>
+        <v>426097</v>
       </c>
       <c r="R48" t="n">
-        <v>7051350</v>
+        <v>7051199</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5821,7 +5801,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5831,7 +5811,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5858,7 +5838,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128398812</v>
+        <v>128398725</v>
       </c>
       <c r="B49" t="n">
         <v>79116</v>
@@ -5893,10 +5873,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426097</v>
+        <v>426492</v>
       </c>
       <c r="R49" t="n">
-        <v>7051199</v>
+        <v>7051269</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,7 +5908,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5938,7 +5918,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5965,10 +5945,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128398725</v>
+        <v>128398807</v>
       </c>
       <c r="B50" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5976,34 +5956,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>426492</v>
+        <v>426011</v>
       </c>
       <c r="R50" t="n">
-        <v>7051269</v>
+        <v>7051282</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6035,7 +6020,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6045,7 +6030,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6072,45 +6062,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128398731</v>
+        <v>128398721</v>
       </c>
       <c r="B51" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>426369</v>
+        <v>426773</v>
       </c>
       <c r="R51" t="n">
-        <v>7051152</v>
+        <v>7051349</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6142,7 +6137,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6152,7 +6147,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6179,48 +6179,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398804</v>
+        <v>128398743</v>
       </c>
       <c r="B52" t="n">
-        <v>75202</v>
+        <v>91490</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6486</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>426000</v>
+        <v>426371</v>
       </c>
       <c r="R52" t="n">
-        <v>7051290</v>
+        <v>7050917</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6252,7 +6249,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6262,7 +6259,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6270,11 +6267,6 @@
       </c>
       <c r="AE52" t="b">
         <v>0</v>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -6294,10 +6286,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128398793</v>
+        <v>128398802</v>
       </c>
       <c r="B53" t="n">
-        <v>57716</v>
+        <v>91790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6305,39 +6297,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>425908</v>
+        <v>425985</v>
       </c>
       <c r="R53" t="n">
-        <v>7051281</v>
+        <v>7051282</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6369,7 +6356,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6379,12 +6366,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6411,32 +6393,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128398734</v>
+        <v>128398727</v>
       </c>
       <c r="B54" t="n">
-        <v>92191</v>
+        <v>79116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6446,10 +6428,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>426329</v>
+        <v>426516</v>
       </c>
       <c r="R54" t="n">
-        <v>7051146</v>
+        <v>7051239</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6481,7 +6463,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6491,7 +6473,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6518,45 +6500,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128398743</v>
+        <v>128398804</v>
       </c>
       <c r="B55" t="n">
-        <v>91490</v>
+        <v>75202</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>6486</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426371</v>
+        <v>426000</v>
       </c>
       <c r="R55" t="n">
-        <v>7050917</v>
+        <v>7051290</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6588,7 +6573,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6598,7 +6583,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6606,6 +6591,11 @@
       </c>
       <c r="AE55" t="b">
         <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG55" t="b">
         <v>0</v>
@@ -6625,32 +6615,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128398802</v>
+        <v>128398734</v>
       </c>
       <c r="B56" t="n">
-        <v>91790</v>
+        <v>92191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6660,10 +6650,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>425985</v>
+        <v>426329</v>
       </c>
       <c r="R56" t="n">
-        <v>7051282</v>
+        <v>7051146</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6695,7 +6685,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6705,7 +6695,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6732,7 +6722,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128398814</v>
+        <v>128398793</v>
       </c>
       <c r="B57" t="n">
         <v>57716</v>
@@ -6772,10 +6762,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426097</v>
+        <v>425908</v>
       </c>
       <c r="R57" t="n">
-        <v>7051199</v>
+        <v>7051281</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6807,7 +6797,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6817,7 +6807,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6849,7 +6839,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128398822</v>
+        <v>128398814</v>
       </c>
       <c r="B58" t="n">
         <v>57716</v>
@@ -6889,10 +6879,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426200</v>
+        <v>426097</v>
       </c>
       <c r="R58" t="n">
-        <v>7051338</v>
+        <v>7051199</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6924,7 +6914,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6934,7 +6924,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6966,7 +6956,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128398719</v>
+        <v>128398822</v>
       </c>
       <c r="B59" t="n">
         <v>57716</v>
@@ -7006,10 +6996,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426799</v>
+        <v>426200</v>
       </c>
       <c r="R59" t="n">
-        <v>7051328</v>
+        <v>7051338</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7041,7 +7031,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7051,7 +7041,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7083,10 +7073,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128398727</v>
+        <v>128398719</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7094,34 +7084,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>426516</v>
+        <v>426799</v>
       </c>
       <c r="R60" t="n">
-        <v>7051239</v>
+        <v>7051328</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7153,7 +7148,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7163,7 +7158,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7190,32 +7190,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128398769</v>
+        <v>128398726</v>
       </c>
       <c r="B61" t="n">
-        <v>91494</v>
+        <v>75195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>426135</v>
+        <v>426522</v>
       </c>
       <c r="R61" t="n">
-        <v>7051154</v>
+        <v>7051242</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7281,6 +7281,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Betula pubescens</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Hålighet vid basen, på ved # Betula pubescens</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7297,10 +7312,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128398781</v>
+        <v>128398769</v>
       </c>
       <c r="B62" t="n">
-        <v>57716</v>
+        <v>91494</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7308,39 +7323,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>425754</v>
+        <v>426135</v>
       </c>
       <c r="R62" t="n">
-        <v>7051180</v>
+        <v>7051154</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7372,7 +7382,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7382,12 +7392,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7638,45 +7643,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128398726</v>
+        <v>128398781</v>
       </c>
       <c r="B65" t="n">
-        <v>75195</v>
+        <v>57716</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>426522</v>
+        <v>425754</v>
       </c>
       <c r="R65" t="n">
-        <v>7051242</v>
+        <v>7051180</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7708,7 +7718,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7718,7 +7728,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7729,21 +7744,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Betula pubescens</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Hålighet vid basen, på ved # Betula pubescens</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8509,10 +8509,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128398779</v>
+        <v>128398720</v>
       </c>
       <c r="B73" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8520,39 +8520,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>425818</v>
+        <v>426773</v>
       </c>
       <c r="R73" t="n">
-        <v>7051169</v>
+        <v>7051341</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8584,7 +8579,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8594,12 +8589,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8626,10 +8616,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128398720</v>
+        <v>128398779</v>
       </c>
       <c r="B74" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8637,34 +8627,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426773</v>
+        <v>425818</v>
       </c>
       <c r="R74" t="n">
-        <v>7051341</v>
+        <v>7051169</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8696,7 +8691,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8706,7 +8701,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8733,10 +8733,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128398789</v>
+        <v>128398754</v>
       </c>
       <c r="B75" t="n">
-        <v>57716</v>
+        <v>80222</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8744,39 +8744,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>425804</v>
+        <v>426191</v>
       </c>
       <c r="R75" t="n">
-        <v>7051258</v>
+        <v>7050957</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8808,7 +8803,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8818,12 +8813,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8834,6 +8824,21 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8957,10 +8962,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128398754</v>
+        <v>128398789</v>
       </c>
       <c r="B77" t="n">
-        <v>80222</v>
+        <v>57716</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8968,34 +8973,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426191</v>
+        <v>425804</v>
       </c>
       <c r="R77" t="n">
-        <v>7050957</v>
+        <v>7051258</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9027,7 +9037,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9037,7 +9047,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9048,21 +9063,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9181,10 +9181,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128398813</v>
+        <v>128398780</v>
       </c>
       <c r="B79" t="n">
-        <v>82975</v>
+        <v>57716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9192,34 +9192,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>426097</v>
+        <v>425756</v>
       </c>
       <c r="R79" t="n">
-        <v>7051199</v>
+        <v>7051171</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9251,7 +9256,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9261,7 +9266,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9288,10 +9298,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128398723</v>
+        <v>128398784</v>
       </c>
       <c r="B80" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9299,34 +9309,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>426515</v>
+        <v>425712</v>
       </c>
       <c r="R80" t="n">
-        <v>7051308</v>
+        <v>7051206</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9358,7 +9373,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9368,7 +9383,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9395,10 +9415,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128398751</v>
+        <v>128398813</v>
       </c>
       <c r="B81" t="n">
-        <v>79116</v>
+        <v>82975</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9406,21 +9426,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9430,10 +9450,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>426239</v>
+        <v>426097</v>
       </c>
       <c r="R81" t="n">
-        <v>7050935</v>
+        <v>7051199</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9465,7 +9485,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9475,7 +9495,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9609,10 +9629,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128398780</v>
+        <v>128398723</v>
       </c>
       <c r="B83" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9620,39 +9640,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>425756</v>
+        <v>426515</v>
       </c>
       <c r="R83" t="n">
-        <v>7051171</v>
+        <v>7051308</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9684,7 +9699,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9694,12 +9709,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9726,10 +9736,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128398784</v>
+        <v>128398751</v>
       </c>
       <c r="B84" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9737,39 +9747,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>425712</v>
+        <v>426239</v>
       </c>
       <c r="R84" t="n">
-        <v>7051206</v>
+        <v>7050935</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9801,7 +9806,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9811,12 +9816,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9843,10 +9843,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128398728</v>
+        <v>128398761</v>
       </c>
       <c r="B85" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9854,39 +9854,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>426475</v>
+        <v>426231</v>
       </c>
       <c r="R85" t="n">
-        <v>7051191</v>
+        <v>7051061</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9918,7 +9913,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9928,12 +9923,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9960,10 +9950,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128398761</v>
+        <v>128398728</v>
       </c>
       <c r="B86" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9971,34 +9961,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Stor-Grässjön N, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>426231</v>
+        <v>426475</v>
       </c>
       <c r="R86" t="n">
-        <v>7051061</v>
+        <v>7051191</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10030,7 +10025,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10040,7 +10035,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10067,7 +10067,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128399850</v>
+        <v>128399908</v>
       </c>
       <c r="B87" t="n">
         <v>57716</v>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>426803</v>
+        <v>426080</v>
       </c>
       <c r="R87" t="n">
-        <v>7051361</v>
+        <v>7051237</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10169,7 +10169,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128399908</v>
+        <v>128399850</v>
       </c>
       <c r="B88" t="n">
         <v>57716</v>
@@ -10204,10 +10204,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>426080</v>
+        <v>426803</v>
       </c>
       <c r="R88" t="n">
-        <v>7051237</v>
+        <v>7051361</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128399888</v>
+        <v>128399895</v>
       </c>
       <c r="B89" t="n">
         <v>57716</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>425774</v>
+        <v>425879</v>
       </c>
       <c r="R89" t="n">
-        <v>7051220</v>
+        <v>7051238</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128399916</v>
+        <v>128399888</v>
       </c>
       <c r="B90" t="n">
         <v>57716</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>426279</v>
+        <v>425774</v>
       </c>
       <c r="R90" t="n">
-        <v>7051408</v>
+        <v>7051220</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10475,7 +10475,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128399875</v>
+        <v>128399916</v>
       </c>
       <c r="B91" t="n">
         <v>57716</v>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>426207</v>
+        <v>426279</v>
       </c>
       <c r="R91" t="n">
-        <v>7051009</v>
+        <v>7051408</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10577,7 +10577,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128399895</v>
+        <v>128399875</v>
       </c>
       <c r="B92" t="n">
         <v>57716</v>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>425879</v>
+        <v>426207</v>
       </c>
       <c r="R92" t="n">
-        <v>7051238</v>
+        <v>7051009</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10679,10 +10679,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128399849</v>
+        <v>128399940</v>
       </c>
       <c r="B93" t="n">
-        <v>57716</v>
+        <v>91517</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426803</v>
+        <v>426338</v>
       </c>
       <c r="R93" t="n">
-        <v>7051353</v>
+        <v>7050977</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10750,11 +10750,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10781,10 +10776,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128399949</v>
+        <v>128399849</v>
       </c>
       <c r="B94" t="n">
-        <v>88894</v>
+        <v>57716</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10792,21 +10787,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10816,10 +10811,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426768</v>
+        <v>426803</v>
       </c>
       <c r="R94" t="n">
-        <v>7051367</v>
+        <v>7051353</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10852,6 +10847,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128399940</v>
+        <v>128399949</v>
       </c>
       <c r="B95" t="n">
-        <v>91512</v>
+        <v>88899</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10889,21 +10889,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>426338</v>
+        <v>426768</v>
       </c>
       <c r="R95" t="n">
-        <v>7050977</v>
+        <v>7051367</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128399898</v>
+        <v>128399832</v>
       </c>
       <c r="B96" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>425894</v>
+        <v>426401</v>
       </c>
       <c r="R96" t="n">
-        <v>7051256</v>
+        <v>7051237</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11046,11 +11046,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11077,32 +11072,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128399886</v>
+        <v>128399836</v>
       </c>
       <c r="B97" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11112,10 +11107,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>425743</v>
+        <v>426093</v>
       </c>
       <c r="R97" t="n">
-        <v>7051241</v>
+        <v>7051184</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11148,11 +11143,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11179,32 +11169,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128399832</v>
+        <v>128399898</v>
       </c>
       <c r="B98" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11214,10 +11204,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>426401</v>
+        <v>425894</v>
       </c>
       <c r="R98" t="n">
-        <v>7051237</v>
+        <v>7051256</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11250,6 +11240,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11276,32 +11271,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128399836</v>
+        <v>128399886</v>
       </c>
       <c r="B99" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11311,10 +11306,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>426093</v>
+        <v>425743</v>
       </c>
       <c r="R99" t="n">
-        <v>7051184</v>
+        <v>7051241</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11347,6 +11342,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11376,7 +11376,7 @@
         <v>128399922</v>
       </c>
       <c r="B100" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>128399936</v>
       </c>
       <c r="B101" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>128399829</v>
       </c>
       <c r="B102" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>128399941</v>
       </c>
       <c r="B103" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11965,32 +11965,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128399863</v>
+        <v>128399834</v>
       </c>
       <c r="B106" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12000,10 +12000,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426347</v>
+        <v>426228</v>
       </c>
       <c r="R106" t="n">
-        <v>7050960</v>
+        <v>7050978</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12036,11 +12036,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12067,7 +12062,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128399868</v>
+        <v>128399903</v>
       </c>
       <c r="B107" t="n">
         <v>57716</v>
@@ -12102,10 +12097,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426274</v>
+        <v>425972</v>
       </c>
       <c r="R107" t="n">
-        <v>7050964</v>
+        <v>7051285</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12142,7 +12137,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12169,7 +12164,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128399881</v>
+        <v>128399863</v>
       </c>
       <c r="B108" t="n">
         <v>57716</v>
@@ -12204,10 +12199,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>425942</v>
+        <v>426347</v>
       </c>
       <c r="R108" t="n">
-        <v>7051274</v>
+        <v>7050960</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12244,7 +12239,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12271,32 +12266,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128399834</v>
+        <v>128399868</v>
       </c>
       <c r="B109" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12306,10 +12301,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426228</v>
+        <v>426274</v>
       </c>
       <c r="R109" t="n">
-        <v>7050978</v>
+        <v>7050964</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12342,6 +12337,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12368,7 +12368,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128399903</v>
+        <v>128399881</v>
       </c>
       <c r="B110" t="n">
         <v>57716</v>
@@ -12403,10 +12403,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>425972</v>
+        <v>425942</v>
       </c>
       <c r="R110" t="n">
-        <v>7051285</v>
+        <v>7051274</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12473,7 +12473,7 @@
         <v>128399945</v>
       </c>
       <c r="B111" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12567,10 +12567,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128399935</v>
+        <v>128399904</v>
       </c>
       <c r="B112" t="n">
-        <v>91508</v>
+        <v>57716</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12578,21 +12578,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12602,10 +12602,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>425974</v>
+        <v>426012</v>
       </c>
       <c r="R112" t="n">
-        <v>7051249</v>
+        <v>7051306</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12638,6 +12638,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12664,10 +12669,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128399943</v>
+        <v>128399870</v>
       </c>
       <c r="B113" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12675,21 +12680,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12699,10 +12704,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>425756</v>
+        <v>426156</v>
       </c>
       <c r="R113" t="n">
-        <v>7051245</v>
+        <v>7050998</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12735,6 +12740,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12761,10 +12771,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128399904</v>
+        <v>128399935</v>
       </c>
       <c r="B114" t="n">
-        <v>57716</v>
+        <v>91513</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12772,21 +12782,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12796,10 +12806,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426012</v>
+        <v>425974</v>
       </c>
       <c r="R114" t="n">
-        <v>7051306</v>
+        <v>7051249</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12832,11 +12842,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12863,32 +12868,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128399870</v>
+        <v>128399833</v>
       </c>
       <c r="B115" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12898,10 +12903,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426156</v>
+        <v>426263</v>
       </c>
       <c r="R115" t="n">
-        <v>7050998</v>
+        <v>7051287</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12934,11 +12939,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12965,10 +12965,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128399833</v>
+        <v>128399831</v>
       </c>
       <c r="B116" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13000,10 +13000,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426263</v>
+        <v>426425</v>
       </c>
       <c r="R116" t="n">
-        <v>7051287</v>
+        <v>7051289</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13062,32 +13062,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128399831</v>
+        <v>128399943</v>
       </c>
       <c r="B117" t="n">
-        <v>92191</v>
+        <v>91517</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426425</v>
+        <v>425756</v>
       </c>
       <c r="R117" t="n">
-        <v>7051289</v>
+        <v>7051245</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13162,7 +13162,7 @@
         <v>128399928</v>
       </c>
       <c r="B118" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13256,32 +13256,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128399872</v>
+        <v>128399838</v>
       </c>
       <c r="B119" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426187</v>
+        <v>425752</v>
       </c>
       <c r="R119" t="n">
-        <v>7050975</v>
+        <v>7051219</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13327,11 +13327,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13358,7 +13353,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128399853</v>
+        <v>128399872</v>
       </c>
       <c r="B120" t="n">
         <v>57716</v>
@@ -13387,24 +13382,16 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426736</v>
+        <v>426187</v>
       </c>
       <c r="R120" t="n">
-        <v>7051344</v>
+        <v>7050975</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13441,7 +13428,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>ca 4 m upp i grantickerötad gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13468,7 +13455,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128399914</v>
+        <v>128399853</v>
       </c>
       <c r="B121" t="n">
         <v>57716</v>
@@ -13497,16 +13484,24 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426219</v>
+        <v>426736</v>
       </c>
       <c r="R121" t="n">
-        <v>7051364</v>
+        <v>7051344</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13543,7 +13538,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>ca 4 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13570,7 +13565,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128399852</v>
+        <v>128399914</v>
       </c>
       <c r="B122" t="n">
         <v>57716</v>
@@ -13605,10 +13600,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>426765</v>
+        <v>426219</v>
       </c>
       <c r="R122" t="n">
-        <v>7051373</v>
+        <v>7051364</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13672,7 +13667,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128399897</v>
+        <v>128399852</v>
       </c>
       <c r="B123" t="n">
         <v>57716</v>
@@ -13707,10 +13702,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>425892</v>
+        <v>426765</v>
       </c>
       <c r="R123" t="n">
-        <v>7051251</v>
+        <v>7051373</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13747,7 +13742,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13774,7 +13769,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128399902</v>
+        <v>128399897</v>
       </c>
       <c r="B124" t="n">
         <v>57716</v>
@@ -13809,10 +13804,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>425902</v>
+        <v>425892</v>
       </c>
       <c r="R124" t="n">
-        <v>7051312</v>
+        <v>7051251</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13876,7 +13871,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128399871</v>
+        <v>128399902</v>
       </c>
       <c r="B125" t="n">
         <v>57716</v>
@@ -13911,10 +13906,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>426154</v>
+        <v>425902</v>
       </c>
       <c r="R125" t="n">
-        <v>7050994</v>
+        <v>7051312</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13978,32 +13973,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128399838</v>
+        <v>128399871</v>
       </c>
       <c r="B126" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14013,10 +14008,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>425752</v>
+        <v>426154</v>
       </c>
       <c r="R126" t="n">
-        <v>7051219</v>
+        <v>7050994</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14049,6 +14044,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14075,10 +14075,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128399901</v>
+        <v>128399920</v>
       </c>
       <c r="B127" t="n">
-        <v>57716</v>
+        <v>91495</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14086,21 +14086,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14110,10 +14110,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>425880</v>
+        <v>426277</v>
       </c>
       <c r="R127" t="n">
-        <v>7051304</v>
+        <v>7051183</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14146,11 +14146,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14177,10 +14172,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128399878</v>
+        <v>128399948</v>
       </c>
       <c r="B128" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14188,21 +14183,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14212,10 +14207,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>426047</v>
+        <v>426395</v>
       </c>
       <c r="R128" t="n">
-        <v>7051186</v>
+        <v>7051398</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14252,7 +14247,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14279,10 +14274,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128399876</v>
+        <v>128399942</v>
       </c>
       <c r="B129" t="n">
-        <v>57716</v>
+        <v>91517</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14290,21 +14285,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14314,10 +14309,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>426244</v>
+        <v>425904</v>
       </c>
       <c r="R129" t="n">
-        <v>7051052</v>
+        <v>7051248</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14350,11 +14345,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14381,7 +14371,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128399905</v>
+        <v>128399901</v>
       </c>
       <c r="B130" t="n">
         <v>57716</v>
@@ -14416,10 +14406,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426029</v>
+        <v>425880</v>
       </c>
       <c r="R130" t="n">
-        <v>7051287</v>
+        <v>7051304</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14456,7 +14446,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14483,10 +14473,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128399920</v>
+        <v>128399878</v>
       </c>
       <c r="B131" t="n">
-        <v>91490</v>
+        <v>57716</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14494,21 +14484,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14518,10 +14508,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426277</v>
+        <v>426047</v>
       </c>
       <c r="R131" t="n">
-        <v>7051183</v>
+        <v>7051186</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14554,6 +14544,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14580,10 +14575,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128399942</v>
+        <v>128399876</v>
       </c>
       <c r="B132" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14591,21 +14586,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14615,10 +14610,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>425904</v>
+        <v>426244</v>
       </c>
       <c r="R132" t="n">
-        <v>7051248</v>
+        <v>7051052</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14651,6 +14646,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14677,10 +14677,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128399948</v>
+        <v>128399905</v>
       </c>
       <c r="B133" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14688,21 +14688,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14712,10 +14712,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426395</v>
+        <v>426029</v>
       </c>
       <c r="R133" t="n">
-        <v>7051398</v>
+        <v>7051287</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14782,7 +14782,7 @@
         <v>128399930</v>
       </c>
       <c r="B134" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>128399931</v>
       </c>
       <c r="B135" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14973,10 +14973,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128399929</v>
+        <v>128399918</v>
       </c>
       <c r="B136" t="n">
-        <v>91508</v>
+        <v>91449</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14984,21 +14984,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>426276</v>
+        <v>426224</v>
       </c>
       <c r="R136" t="n">
-        <v>7050944</v>
+        <v>7050981</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15070,10 +15070,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128399918</v>
+        <v>128399929</v>
       </c>
       <c r="B137" t="n">
-        <v>91444</v>
+        <v>91513</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15081,21 +15081,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>112</v>
+        <v>1204</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15105,10 +15105,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>426224</v>
+        <v>426276</v>
       </c>
       <c r="R137" t="n">
-        <v>7050981</v>
+        <v>7050944</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15881,10 +15881,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128399880</v>
+        <v>128399933</v>
       </c>
       <c r="B145" t="n">
-        <v>57716</v>
+        <v>91513</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15892,21 +15892,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15916,10 +15916,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>425981</v>
+        <v>426218</v>
       </c>
       <c r="R145" t="n">
-        <v>7051240</v>
+        <v>7051146</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15952,11 +15952,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15983,10 +15978,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128399933</v>
+        <v>128399880</v>
       </c>
       <c r="B146" t="n">
-        <v>91508</v>
+        <v>57716</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15994,21 +15989,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16018,10 +16013,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>426218</v>
+        <v>425981</v>
       </c>
       <c r="R146" t="n">
-        <v>7051146</v>
+        <v>7051240</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16054,6 +16049,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16182,10 +16182,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128399828</v>
+        <v>128399892</v>
       </c>
       <c r="B148" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16193,21 +16193,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16217,10 +16217,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>426225</v>
+        <v>425853</v>
       </c>
       <c r="R148" t="n">
-        <v>7050963</v>
+        <v>7051216</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16253,6 +16253,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16279,10 +16284,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128399937</v>
+        <v>128399883</v>
       </c>
       <c r="B149" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16290,21 +16295,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16314,10 +16319,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>426734</v>
+        <v>425851</v>
       </c>
       <c r="R149" t="n">
-        <v>7051350</v>
+        <v>7051202</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16350,6 +16355,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16376,10 +16386,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128399946</v>
+        <v>128399861</v>
       </c>
       <c r="B150" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16387,21 +16397,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16411,10 +16421,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>426083</v>
+        <v>426285</v>
       </c>
       <c r="R150" t="n">
-        <v>7051231</v>
+        <v>7051199</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16447,6 +16457,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16473,7 +16488,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128399892</v>
+        <v>128399855</v>
       </c>
       <c r="B151" t="n">
         <v>57716</v>
@@ -16508,10 +16523,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>425853</v>
+        <v>426639</v>
       </c>
       <c r="R151" t="n">
-        <v>7051216</v>
+        <v>7051351</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16548,7 +16563,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16575,10 +16590,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128399883</v>
+        <v>128399828</v>
       </c>
       <c r="B152" t="n">
-        <v>57716</v>
+        <v>91499</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16586,21 +16601,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16610,10 +16625,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>425851</v>
+        <v>426225</v>
       </c>
       <c r="R152" t="n">
-        <v>7051202</v>
+        <v>7050963</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16646,11 +16661,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16677,10 +16687,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128399861</v>
+        <v>128399946</v>
       </c>
       <c r="B153" t="n">
-        <v>57716</v>
+        <v>91517</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16688,21 +16698,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16712,10 +16722,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>426285</v>
+        <v>426083</v>
       </c>
       <c r="R153" t="n">
-        <v>7051199</v>
+        <v>7051231</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16748,11 +16758,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16779,10 +16784,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128399855</v>
+        <v>128399937</v>
       </c>
       <c r="B154" t="n">
-        <v>57716</v>
+        <v>91517</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16790,21 +16795,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16814,10 +16819,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>426639</v>
+        <v>426734</v>
       </c>
       <c r="R154" t="n">
-        <v>7051351</v>
+        <v>7051350</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16850,11 +16855,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16881,7 +16881,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128399885</v>
+        <v>128399911</v>
       </c>
       <c r="B155" t="n">
         <v>57716</v>
@@ -16916,10 +16916,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>425748</v>
+        <v>426174</v>
       </c>
       <c r="R155" t="n">
-        <v>7051212</v>
+        <v>7051335</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16983,7 +16983,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128399911</v>
+        <v>128399913</v>
       </c>
       <c r="B156" t="n">
         <v>57716</v>
@@ -17018,10 +17018,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>426174</v>
+        <v>426203</v>
       </c>
       <c r="R156" t="n">
-        <v>7051335</v>
+        <v>7051368</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17085,7 +17085,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128399913</v>
+        <v>128399885</v>
       </c>
       <c r="B157" t="n">
         <v>57716</v>
@@ -17120,10 +17120,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>426203</v>
+        <v>425748</v>
       </c>
       <c r="R157" t="n">
-        <v>7051368</v>
+        <v>7051212</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17187,32 +17187,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128399856</v>
+        <v>128399839</v>
       </c>
       <c r="B158" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17222,10 +17222,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>426646</v>
+        <v>425971</v>
       </c>
       <c r="R158" t="n">
-        <v>7051365</v>
+        <v>7051280</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17258,11 +17258,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17289,10 +17284,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128399909</v>
+        <v>128399827</v>
       </c>
       <c r="B159" t="n">
-        <v>57716</v>
+        <v>91499</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17300,34 +17295,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Stor-grässlåttsjön, Jmt</t>
+          <t>Stor-grässjön, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>426175</v>
+        <v>426813</v>
       </c>
       <c r="R159" t="n">
-        <v>7051323</v>
+        <v>7051371</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17360,11 +17355,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17391,32 +17381,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128399839</v>
+        <v>128399856</v>
       </c>
       <c r="B160" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17426,10 +17416,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>425971</v>
+        <v>426646</v>
       </c>
       <c r="R160" t="n">
-        <v>7051280</v>
+        <v>7051365</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17462,6 +17452,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17488,10 +17483,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128399827</v>
+        <v>128399909</v>
       </c>
       <c r="B161" t="n">
-        <v>91494</v>
+        <v>57716</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17499,34 +17494,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Stor-grässjön, Jmt</t>
+          <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>426813</v>
+        <v>426175</v>
       </c>
       <c r="R161" t="n">
-        <v>7051371</v>
+        <v>7051323</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17559,6 +17554,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17588,7 +17588,7 @@
         <v>128399837</v>
       </c>
       <c r="B162" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>128399840</v>
       </c>
       <c r="B163" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>128399926</v>
       </c>
       <c r="B164" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18080,10 +18080,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128399869</v>
+        <v>128399934</v>
       </c>
       <c r="B167" t="n">
-        <v>57716</v>
+        <v>91513</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18091,21 +18091,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18115,10 +18115,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>426163</v>
+        <v>426135</v>
       </c>
       <c r="R167" t="n">
-        <v>7050993</v>
+        <v>7051163</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18151,11 +18151,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18182,32 +18177,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128399899</v>
+        <v>128399843</v>
       </c>
       <c r="B168" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18217,10 +18212,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>425928</v>
+        <v>426425</v>
       </c>
       <c r="R168" t="n">
-        <v>7051283</v>
+        <v>7051273</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18253,11 +18248,6 @@
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18284,32 +18274,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128399843</v>
+        <v>128399869</v>
       </c>
       <c r="B169" t="n">
-        <v>92191</v>
+        <v>57716</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18319,10 +18309,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>426425</v>
+        <v>426163</v>
       </c>
       <c r="R169" t="n">
-        <v>7051273</v>
+        <v>7050993</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18355,6 +18345,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18381,10 +18376,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128399934</v>
+        <v>128399899</v>
       </c>
       <c r="B170" t="n">
-        <v>91508</v>
+        <v>57716</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18392,21 +18387,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18416,10 +18411,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>426135</v>
+        <v>425928</v>
       </c>
       <c r="R170" t="n">
-        <v>7051163</v>
+        <v>7051283</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18452,6 +18447,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18478,10 +18478,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128399938</v>
+        <v>128399884</v>
       </c>
       <c r="B171" t="n">
-        <v>91512</v>
+        <v>57716</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18489,21 +18489,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18513,10 +18513,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>426205</v>
+        <v>425770</v>
       </c>
       <c r="R171" t="n">
-        <v>7051276</v>
+        <v>7051183</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18549,6 +18549,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18575,7 +18580,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128399884</v>
+        <v>128399893</v>
       </c>
       <c r="B172" t="n">
         <v>57716</v>
@@ -18610,10 +18615,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>425770</v>
+        <v>425861</v>
       </c>
       <c r="R172" t="n">
-        <v>7051183</v>
+        <v>7051227</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18650,7 +18655,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18677,7 +18682,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128399893</v>
+        <v>128399887</v>
       </c>
       <c r="B173" t="n">
         <v>57716</v>
@@ -18712,10 +18717,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>425861</v>
+        <v>425756</v>
       </c>
       <c r="R173" t="n">
-        <v>7051227</v>
+        <v>7051229</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18752,7 +18757,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18779,7 +18784,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128399887</v>
+        <v>128399882</v>
       </c>
       <c r="B174" t="n">
         <v>57716</v>
@@ -18814,10 +18819,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>425756</v>
+        <v>425864</v>
       </c>
       <c r="R174" t="n">
-        <v>7051229</v>
+        <v>7051211</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18854,7 +18859,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18881,7 +18886,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128399882</v>
+        <v>128399854</v>
       </c>
       <c r="B175" t="n">
         <v>57716</v>
@@ -18910,16 +18915,24 @@
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>425864</v>
+        <v>426733</v>
       </c>
       <c r="R175" t="n">
-        <v>7051211</v>
+        <v>7051347</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18956,7 +18969,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18983,53 +18996,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128399854</v>
+        <v>128399835</v>
       </c>
       <c r="B176" t="n">
-        <v>57716</v>
+        <v>92196</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
           <t>Stor-grässlåttsjön, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>426733</v>
+        <v>426132</v>
       </c>
       <c r="R176" t="n">
-        <v>7051347</v>
+        <v>7051150</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19062,11 +19067,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Färskt påbörjat bohål ca 2,7 upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19093,32 +19093,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128399835</v>
+        <v>128399921</v>
       </c>
       <c r="B177" t="n">
-        <v>92191</v>
+        <v>91495</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-     